--- a/GearSage-client/pkgGear/data_raw/daiwa_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_rod_import.xlsx
@@ -436,8 +436,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>DR1000</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -471,8 +471,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>DR1001</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -506,8 +506,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>DR1002</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -541,8 +541,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>DR1003</v>
       </c>
       <c r="B5" t="str">
         <v/>
@@ -576,8 +576,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>DR1004</v>
       </c>
       <c r="B6" t="str">
         <v/>
@@ -611,8 +611,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>DR1005</v>
       </c>
       <c r="B7" t="str">
         <v/>
@@ -646,8 +646,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>DR1006</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -681,8 +681,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>DR1007</v>
       </c>
       <c r="B9" t="str">
         <v/>
@@ -716,8 +716,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>DR1008</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -751,8 +751,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>DR1009</v>
       </c>
       <c r="B11" t="str">
         <v/>
@@ -786,8 +786,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>DR1010</v>
       </c>
       <c r="B12" t="str">
         <v/>
@@ -821,8 +821,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>DR1011</v>
       </c>
       <c r="B13" t="str">
         <v/>
@@ -856,8 +856,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>DR1012</v>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -891,8 +891,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>DR1013</v>
       </c>
       <c r="B15" t="str">
         <v/>
@@ -926,8 +926,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>DR1014</v>
       </c>
       <c r="B16" t="str">
         <v/>
@@ -961,8 +961,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>DR1015</v>
       </c>
       <c r="B17" t="str">
         <v/>
@@ -996,8 +996,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>DR1016</v>
       </c>
       <c r="B18" t="str">
         <v/>
@@ -1031,8 +1031,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>DR1017</v>
       </c>
       <c r="B19" t="str">
         <v/>
@@ -1066,8 +1066,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>DR1018</v>
       </c>
       <c r="B20" t="str">
         <v/>
@@ -1101,8 +1101,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>DR1019</v>
       </c>
       <c r="B21" t="str">
         <v/>
@@ -1136,8 +1136,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>DR1020</v>
       </c>
       <c r="B22" t="str">
         <v/>
@@ -1171,8 +1171,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>DR1021</v>
       </c>
       <c r="B23" t="str">
         <v/>
@@ -1206,8 +1206,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>DR1022</v>
       </c>
       <c r="B24" t="str">
         <v/>
@@ -1241,8 +1241,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>DR1023</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -1276,8 +1276,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>DR1024</v>
       </c>
       <c r="B26" t="str">
         <v/>
@@ -1311,8 +1311,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>DR1025</v>
       </c>
       <c r="B27" t="str">
         <v/>
@@ -1346,8 +1346,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>DR1026</v>
       </c>
       <c r="B28" t="str">
         <v/>
@@ -1381,8 +1381,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>DR1027</v>
       </c>
       <c r="B29" t="str">
         <v/>
@@ -1416,8 +1416,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>DR1028</v>
       </c>
       <c r="B30" t="str">
         <v/>
@@ -1451,8 +1451,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>DR1029</v>
       </c>
       <c r="B31" t="str">
         <v/>
@@ -1486,8 +1486,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>DR1030</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -1521,8 +1521,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>DR1031</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -1556,8 +1556,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>DR1032</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -1591,8 +1591,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>DR1033</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -1626,8 +1626,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>DR1034</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -1661,8 +1661,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>DR1035</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -1696,8 +1696,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>DR1036</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -1731,8 +1731,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>DR1037</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -1766,8 +1766,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>DR1038</v>
       </c>
       <c r="B40" t="str">
         <v/>
@@ -1801,8 +1801,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>DR1039</v>
       </c>
       <c r="B41" t="str">
         <v/>
@@ -1836,8 +1836,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>DR1040</v>
       </c>
       <c r="B42" t="str">
         <v/>
@@ -1871,8 +1871,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>DR1041</v>
       </c>
       <c r="B43" t="str">
         <v/>
@@ -1906,8 +1906,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>DR1042</v>
       </c>
       <c r="B44" t="str">
         <v/>
@@ -1941,8 +1941,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>DR1043</v>
       </c>
       <c r="B45" t="str">
         <v/>
@@ -1976,8 +1976,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>DR1044</v>
       </c>
       <c r="B46" t="str">
         <v/>
@@ -2011,8 +2011,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>DR1045</v>
       </c>
       <c r="B47" t="str">
         <v/>
@@ -2046,8 +2046,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>DR1046</v>
       </c>
       <c r="B48" t="str">
         <v/>
@@ -2081,8 +2081,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>DR1047</v>
       </c>
       <c r="B49" t="str">
         <v/>
@@ -2116,8 +2116,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>DR1048</v>
       </c>
       <c r="B50" t="str">
         <v/>
@@ -2151,8 +2151,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>DR1049</v>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -2186,8 +2186,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>DR1050</v>
       </c>
       <c r="B52" t="str">
         <v/>
@@ -2221,8 +2221,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>DR1051</v>
       </c>
       <c r="B53" t="str">
         <v/>
@@ -2256,8 +2256,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>53</v>
+      <c r="A54" t="str">
+        <v>DR1052</v>
       </c>
       <c r="B54" t="str">
         <v/>
@@ -2291,8 +2291,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55">
-        <v>54</v>
+      <c r="A55" t="str">
+        <v>DR1053</v>
       </c>
       <c r="B55" t="str">
         <v/>
@@ -2326,8 +2326,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56">
-        <v>55</v>
+      <c r="A56" t="str">
+        <v>DR1054</v>
       </c>
       <c r="B56" t="str">
         <v/>
@@ -2361,8 +2361,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57">
-        <v>56</v>
+      <c r="A57" t="str">
+        <v>DR1055</v>
       </c>
       <c r="B57" t="str">
         <v/>
@@ -2396,8 +2396,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58">
-        <v>57</v>
+      <c r="A58" t="str">
+        <v>DR1056</v>
       </c>
       <c r="B58" t="str">
         <v/>
@@ -2431,8 +2431,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59">
-        <v>58</v>
+      <c r="A59" t="str">
+        <v>DR1057</v>
       </c>
       <c r="B59" t="str">
         <v/>
@@ -2578,11 +2578,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>DRD10000</v>
+      </c>
+      <c r="B2" t="str">
+        <v>DR1000</v>
       </c>
       <c r="C2" t="str">
         <v>S</v>
@@ -2679,11 +2679,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="A3" t="str">
+        <v>DRD10001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>DR1000</v>
       </c>
       <c r="C3" t="str">
         <v>S</v>
@@ -2780,11 +2780,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="A4" t="str">
+        <v>DRD10002</v>
+      </c>
+      <c r="B4" t="str">
+        <v>DR1000</v>
       </c>
       <c r="C4" t="str">
         <v>S</v>
@@ -2881,11 +2881,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
+      <c r="A5" t="str">
+        <v>DRD10003</v>
+      </c>
+      <c r="B5" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C5" t="str">
         <v>S</v>
@@ -2982,11 +2982,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
+      <c r="A6" t="str">
+        <v>DRD10004</v>
+      </c>
+      <c r="B6" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C6" t="str">
         <v>S</v>
@@ -3083,11 +3083,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
+      <c r="A7" t="str">
+        <v>DRD10005</v>
+      </c>
+      <c r="B7" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C7" t="str">
         <v>S</v>
@@ -3184,11 +3184,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
+      <c r="A8" t="str">
+        <v>DRD10006</v>
+      </c>
+      <c r="B8" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C8" t="str">
         <v>S</v>
@@ -3285,11 +3285,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
+      <c r="A9" t="str">
+        <v>DRD10007</v>
+      </c>
+      <c r="B9" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C9" t="str">
         <v>S</v>
@@ -3386,11 +3386,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
+      <c r="A10" t="str">
+        <v>DRD10008</v>
+      </c>
+      <c r="B10" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C10" t="str">
         <v>S</v>
@@ -3487,11 +3487,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
+      <c r="A11" t="str">
+        <v>DRD10009</v>
+      </c>
+      <c r="B11" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C11" t="str">
         <v>S</v>
@@ -3588,11 +3588,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
+      <c r="A12" t="str">
+        <v>DRD10010</v>
+      </c>
+      <c r="B12" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C12" t="str">
         <v>S</v>
@@ -3689,11 +3689,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
+      <c r="A13" t="str">
+        <v>DRD10011</v>
+      </c>
+      <c r="B13" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C13" t="str">
         <v>S</v>
@@ -3790,11 +3790,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
+      <c r="A14" t="str">
+        <v>DRD10012</v>
+      </c>
+      <c r="B14" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C14" t="str">
         <v>S</v>
@@ -3891,11 +3891,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
+      <c r="A15" t="str">
+        <v>DRD10013</v>
+      </c>
+      <c r="B15" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C15" t="str">
         <v>S</v>
@@ -3992,11 +3992,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
+      <c r="A16" t="str">
+        <v>DRD10014</v>
+      </c>
+      <c r="B16" t="str">
+        <v>DR1001</v>
       </c>
       <c r="C16" t="str">
         <v>S</v>
@@ -4093,11 +4093,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>3</v>
+      <c r="A17" t="str">
+        <v>DRD10015</v>
+      </c>
+      <c r="B17" t="str">
+        <v>DR1002</v>
       </c>
       <c r="C17" t="str">
         <v>S</v>
@@ -4194,11 +4194,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>3</v>
+      <c r="A18" t="str">
+        <v>DRD10016</v>
+      </c>
+      <c r="B18" t="str">
+        <v>DR1002</v>
       </c>
       <c r="C18" t="str">
         <v>S</v>
@@ -4295,11 +4295,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>3</v>
+      <c r="A19" t="str">
+        <v>DRD10017</v>
+      </c>
+      <c r="B19" t="str">
+        <v>DR1002</v>
       </c>
       <c r="C19" t="str">
         <v>S</v>
@@ -4396,11 +4396,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>3</v>
+      <c r="A20" t="str">
+        <v>DRD10018</v>
+      </c>
+      <c r="B20" t="str">
+        <v>DR1002</v>
       </c>
       <c r="C20" t="str">
         <v>S</v>
@@ -4497,11 +4497,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>3</v>
+      <c r="A21" t="str">
+        <v>DRD10019</v>
+      </c>
+      <c r="B21" t="str">
+        <v>DR1002</v>
       </c>
       <c r="C21" t="str">
         <v>C</v>
@@ -4598,11 +4598,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
+      <c r="A22" t="str">
+        <v>DRD10020</v>
+      </c>
+      <c r="B22" t="str">
+        <v>DR1002</v>
       </c>
       <c r="C22" t="str">
         <v>C</v>
@@ -4699,11 +4699,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>3</v>
+      <c r="A23" t="str">
+        <v>DRD10021</v>
+      </c>
+      <c r="B23" t="str">
+        <v>DR1002</v>
       </c>
       <c r="C23" t="str">
         <v>C</v>
@@ -4800,11 +4800,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
+      <c r="A24" t="str">
+        <v>DRD10022</v>
+      </c>
+      <c r="B24" t="str">
+        <v>DR1003</v>
       </c>
       <c r="C24" t="str">
         <v>C</v>
@@ -4901,11 +4901,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>4</v>
+      <c r="A25" t="str">
+        <v>DRD10023</v>
+      </c>
+      <c r="B25" t="str">
+        <v>DR1003</v>
       </c>
       <c r="C25" t="str">
         <v>C</v>
@@ -5002,11 +5002,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>4</v>
+      <c r="A26" t="str">
+        <v>DRD10024</v>
+      </c>
+      <c r="B26" t="str">
+        <v>DR1003</v>
       </c>
       <c r="C26" t="str">
         <v>C</v>
@@ -5103,11 +5103,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>5</v>
+      <c r="A27" t="str">
+        <v>DRD10025</v>
+      </c>
+      <c r="B27" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C27" t="str">
         <v>S</v>
@@ -5204,11 +5204,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>5</v>
+      <c r="A28" t="str">
+        <v>DRD10026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C28" t="str">
         <v>S</v>
@@ -5305,11 +5305,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>5</v>
+      <c r="A29" t="str">
+        <v>DRD10027</v>
+      </c>
+      <c r="B29" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C29" t="str">
         <v>S</v>
@@ -5406,11 +5406,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>5</v>
+      <c r="A30" t="str">
+        <v>DRD10028</v>
+      </c>
+      <c r="B30" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C30" t="str">
         <v>S</v>
@@ -5507,11 +5507,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>5</v>
+      <c r="A31" t="str">
+        <v>DRD10029</v>
+      </c>
+      <c r="B31" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C31" t="str">
         <v>S</v>
@@ -5608,11 +5608,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32">
-        <v>5</v>
+      <c r="A32" t="str">
+        <v>DRD10030</v>
+      </c>
+      <c r="B32" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C32" t="str">
         <v>S</v>
@@ -5709,11 +5709,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33">
-        <v>5</v>
+      <c r="A33" t="str">
+        <v>DRD10031</v>
+      </c>
+      <c r="B33" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C33" t="str">
         <v>S</v>
@@ -5810,11 +5810,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34">
-        <v>5</v>
+      <c r="A34" t="str">
+        <v>DRD10032</v>
+      </c>
+      <c r="B34" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C34" t="str">
         <v>S</v>
@@ -5911,11 +5911,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35">
-        <v>5</v>
+      <c r="A35" t="str">
+        <v>DRD10033</v>
+      </c>
+      <c r="B35" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C35" t="str">
         <v>S</v>
@@ -6012,11 +6012,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36">
-        <v>5</v>
+      <c r="A36" t="str">
+        <v>DRD10034</v>
+      </c>
+      <c r="B36" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C36" t="str">
         <v>S</v>
@@ -6113,11 +6113,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37">
-        <v>5</v>
+      <c r="A37" t="str">
+        <v>DRD10035</v>
+      </c>
+      <c r="B37" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C37" t="str">
         <v>S</v>
@@ -6214,11 +6214,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38">
-        <v>5</v>
+      <c r="A38" t="str">
+        <v>DRD10036</v>
+      </c>
+      <c r="B38" t="str">
+        <v>DR1004</v>
       </c>
       <c r="C38" t="str">
         <v>S</v>
@@ -6315,11 +6315,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39">
-        <v>6</v>
+      <c r="A39" t="str">
+        <v>DRD10037</v>
+      </c>
+      <c r="B39" t="str">
+        <v>DR1005</v>
       </c>
       <c r="C39" t="str">
         <v>S</v>
@@ -6416,11 +6416,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40">
-        <v>6</v>
+      <c r="A40" t="str">
+        <v>DRD10038</v>
+      </c>
+      <c r="B40" t="str">
+        <v>DR1005</v>
       </c>
       <c r="C40" t="str">
         <v>S</v>
@@ -6517,11 +6517,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41">
-        <v>6</v>
+      <c r="A41" t="str">
+        <v>DRD10039</v>
+      </c>
+      <c r="B41" t="str">
+        <v>DR1005</v>
       </c>
       <c r="C41" t="str">
         <v>S</v>
@@ -6618,11 +6618,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42">
-        <v>6</v>
+      <c r="A42" t="str">
+        <v>DRD10040</v>
+      </c>
+      <c r="B42" t="str">
+        <v>DR1005</v>
       </c>
       <c r="C42" t="str">
         <v>S</v>
@@ -6719,11 +6719,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43">
-        <v>6</v>
+      <c r="A43" t="str">
+        <v>DRD10041</v>
+      </c>
+      <c r="B43" t="str">
+        <v>DR1005</v>
       </c>
       <c r="C43" t="str">
         <v>C</v>
@@ -6820,11 +6820,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44">
-        <v>7</v>
+      <c r="A44" t="str">
+        <v>DRD10042</v>
+      </c>
+      <c r="B44" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C44" t="str">
         <v>S</v>
@@ -6921,11 +6921,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45">
-        <v>7</v>
+      <c r="A45" t="str">
+        <v>DRD10043</v>
+      </c>
+      <c r="B45" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C45" t="str">
         <v>S</v>
@@ -7022,11 +7022,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46">
-        <v>7</v>
+      <c r="A46" t="str">
+        <v>DRD10044</v>
+      </c>
+      <c r="B46" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C46" t="str">
         <v>S</v>
@@ -7123,11 +7123,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47">
-        <v>7</v>
+      <c r="A47" t="str">
+        <v>DRD10045</v>
+      </c>
+      <c r="B47" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C47" t="str">
         <v>S</v>
@@ -7224,11 +7224,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48">
-        <v>7</v>
+      <c r="A48" t="str">
+        <v>DRD10046</v>
+      </c>
+      <c r="B48" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C48" t="str">
         <v>S</v>
@@ -7325,11 +7325,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49">
-        <v>7</v>
+      <c r="A49" t="str">
+        <v>DRD10047</v>
+      </c>
+      <c r="B49" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C49" t="str">
         <v>S</v>
@@ -7426,11 +7426,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50">
-        <v>7</v>
+      <c r="A50" t="str">
+        <v>DRD10048</v>
+      </c>
+      <c r="B50" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C50" t="str">
         <v>S</v>
@@ -7527,11 +7527,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51">
-        <v>7</v>
+      <c r="A51" t="str">
+        <v>DRD10049</v>
+      </c>
+      <c r="B51" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C51" t="str">
         <v>S</v>
@@ -7628,11 +7628,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52">
-        <v>7</v>
+      <c r="A52" t="str">
+        <v>DRD10050</v>
+      </c>
+      <c r="B52" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C52" t="str">
         <v>S</v>
@@ -7729,11 +7729,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53">
-        <v>7</v>
+      <c r="A53" t="str">
+        <v>DRD10051</v>
+      </c>
+      <c r="B53" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C53" t="str">
         <v>S</v>
@@ -7830,11 +7830,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54">
-        <v>7</v>
+      <c r="A54" t="str">
+        <v>DRD10052</v>
+      </c>
+      <c r="B54" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C54" t="str">
         <v>S</v>
@@ -7931,11 +7931,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55">
-        <v>7</v>
+      <c r="A55" t="str">
+        <v>DRD10053</v>
+      </c>
+      <c r="B55" t="str">
+        <v>DR1006</v>
       </c>
       <c r="C55" t="str">
         <v>S</v>
@@ -8032,11 +8032,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56">
-        <v>8</v>
+      <c r="A56" t="str">
+        <v>DRD10054</v>
+      </c>
+      <c r="B56" t="str">
+        <v>DR1007</v>
       </c>
       <c r="C56" t="str">
         <v>S</v>
@@ -8133,11 +8133,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57">
-        <v>8</v>
+      <c r="A57" t="str">
+        <v>DRD10055</v>
+      </c>
+      <c r="B57" t="str">
+        <v>DR1007</v>
       </c>
       <c r="C57" t="str">
         <v>S</v>
@@ -8234,11 +8234,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58">
-        <v>8</v>
+      <c r="A58" t="str">
+        <v>DRD10056</v>
+      </c>
+      <c r="B58" t="str">
+        <v>DR1007</v>
       </c>
       <c r="C58" t="str">
         <v>S</v>
@@ -8335,11 +8335,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59">
-        <v>8</v>
+      <c r="A59" t="str">
+        <v>DRD10057</v>
+      </c>
+      <c r="B59" t="str">
+        <v>DR1007</v>
       </c>
       <c r="C59" t="str">
         <v>S</v>
@@ -8436,11 +8436,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60">
-        <v>8</v>
+      <c r="A60" t="str">
+        <v>DRD10058</v>
+      </c>
+      <c r="B60" t="str">
+        <v>DR1007</v>
       </c>
       <c r="C60" t="str">
         <v>S</v>
@@ -8537,11 +8537,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61">
-        <v>8</v>
+      <c r="A61" t="str">
+        <v>DRD10059</v>
+      </c>
+      <c r="B61" t="str">
+        <v>DR1007</v>
       </c>
       <c r="C61" t="str">
         <v>S</v>
@@ -8638,11 +8638,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62">
-        <v>8</v>
+      <c r="A62" t="str">
+        <v>DRD10060</v>
+      </c>
+      <c r="B62" t="str">
+        <v>DR1007</v>
       </c>
       <c r="C62" t="str">
         <v>S</v>
@@ -8739,11 +8739,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63">
-        <v>8</v>
+      <c r="A63" t="str">
+        <v>DRD10061</v>
+      </c>
+      <c r="B63" t="str">
+        <v>DR1007</v>
       </c>
       <c r="C63" t="str">
         <v>S</v>
@@ -8840,11 +8840,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64">
-        <v>8</v>
+      <c r="A64" t="str">
+        <v>DRD10062</v>
+      </c>
+      <c r="B64" t="str">
+        <v>DR1007</v>
       </c>
       <c r="C64" t="str">
         <v>S</v>
@@ -8941,11 +8941,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65">
-        <v>9</v>
+      <c r="A65" t="str">
+        <v>DRD10063</v>
+      </c>
+      <c r="B65" t="str">
+        <v>DR1008</v>
       </c>
       <c r="C65" t="str">
         <v>S</v>
@@ -9042,11 +9042,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66">
-        <v>9</v>
+      <c r="A66" t="str">
+        <v>DRD10064</v>
+      </c>
+      <c r="B66" t="str">
+        <v>DR1008</v>
       </c>
       <c r="C66" t="str">
         <v>S</v>
@@ -9143,11 +9143,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67">
-        <v>9</v>
+      <c r="A67" t="str">
+        <v>DRD10065</v>
+      </c>
+      <c r="B67" t="str">
+        <v>DR1008</v>
       </c>
       <c r="C67" t="str">
         <v>S</v>
@@ -9244,11 +9244,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68">
-        <v>9</v>
+      <c r="A68" t="str">
+        <v>DRD10066</v>
+      </c>
+      <c r="B68" t="str">
+        <v>DR1008</v>
       </c>
       <c r="C68" t="str">
         <v>S</v>
@@ -9345,11 +9345,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69">
-        <v>9</v>
+      <c r="A69" t="str">
+        <v>DRD10067</v>
+      </c>
+      <c r="B69" t="str">
+        <v>DR1008</v>
       </c>
       <c r="C69" t="str">
         <v>S</v>
@@ -9446,11 +9446,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70">
-        <v>10</v>
+      <c r="A70" t="str">
+        <v>DRD10068</v>
+      </c>
+      <c r="B70" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C70" t="str">
         <v>S</v>
@@ -9547,11 +9547,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71">
-        <v>10</v>
+      <c r="A71" t="str">
+        <v>DRD10069</v>
+      </c>
+      <c r="B71" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C71" t="str">
         <v>S</v>
@@ -9648,11 +9648,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72">
-        <v>10</v>
+      <c r="A72" t="str">
+        <v>DRD10070</v>
+      </c>
+      <c r="B72" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C72" t="str">
         <v>S</v>
@@ -9749,11 +9749,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73">
-        <v>10</v>
+      <c r="A73" t="str">
+        <v>DRD10071</v>
+      </c>
+      <c r="B73" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C73" t="str">
         <v>S</v>
@@ -9850,11 +9850,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74">
-        <v>10</v>
+      <c r="A74" t="str">
+        <v>DRD10072</v>
+      </c>
+      <c r="B74" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C74" t="str">
         <v>S</v>
@@ -9951,11 +9951,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75">
-        <v>10</v>
+      <c r="A75" t="str">
+        <v>DRD10073</v>
+      </c>
+      <c r="B75" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C75" t="str">
         <v>S</v>
@@ -10052,11 +10052,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76">
-        <v>10</v>
+      <c r="A76" t="str">
+        <v>DRD10074</v>
+      </c>
+      <c r="B76" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C76" t="str">
         <v>S</v>
@@ -10153,11 +10153,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77">
-        <v>10</v>
+      <c r="A77" t="str">
+        <v>DRD10075</v>
+      </c>
+      <c r="B77" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C77" t="str">
         <v>S</v>
@@ -10254,11 +10254,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78">
-        <v>10</v>
+      <c r="A78" t="str">
+        <v>DRD10076</v>
+      </c>
+      <c r="B78" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C78" t="str">
         <v>S</v>
@@ -10355,11 +10355,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79">
-        <v>10</v>
+      <c r="A79" t="str">
+        <v>DRD10077</v>
+      </c>
+      <c r="B79" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C79" t="str">
         <v>S</v>
@@ -10456,11 +10456,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80">
-        <v>10</v>
+      <c r="A80" t="str">
+        <v>DRD10078</v>
+      </c>
+      <c r="B80" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C80" t="str">
         <v>S</v>
@@ -10557,11 +10557,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81">
-        <v>10</v>
+      <c r="A81" t="str">
+        <v>DRD10079</v>
+      </c>
+      <c r="B81" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C81" t="str">
         <v>S</v>
@@ -10658,11 +10658,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82">
-        <v>10</v>
+      <c r="A82" t="str">
+        <v>DRD10080</v>
+      </c>
+      <c r="B82" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C82" t="str">
         <v>S</v>
@@ -10759,11 +10759,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83">
-        <v>10</v>
+      <c r="A83" t="str">
+        <v>DRD10081</v>
+      </c>
+      <c r="B83" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C83" t="str">
         <v>S</v>
@@ -10860,11 +10860,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84">
-        <v>10</v>
+      <c r="A84" t="str">
+        <v>DRD10082</v>
+      </c>
+      <c r="B84" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C84" t="str">
         <v>S</v>
@@ -10961,11 +10961,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85">
-        <v>10</v>
+      <c r="A85" t="str">
+        <v>DRD10083</v>
+      </c>
+      <c r="B85" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C85" t="str">
         <v>S</v>
@@ -11062,11 +11062,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86">
-        <v>10</v>
+      <c r="A86" t="str">
+        <v>DRD10084</v>
+      </c>
+      <c r="B86" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C86" t="str">
         <v>C</v>
@@ -11163,11 +11163,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87">
-        <v>10</v>
+      <c r="A87" t="str">
+        <v>DRD10085</v>
+      </c>
+      <c r="B87" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C87" t="str">
         <v>C</v>
@@ -11264,11 +11264,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88">
-        <v>10</v>
+      <c r="A88" t="str">
+        <v>DRD10086</v>
+      </c>
+      <c r="B88" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C88" t="str">
         <v>C</v>
@@ -11365,11 +11365,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89">
-        <v>10</v>
+      <c r="A89" t="str">
+        <v>DRD10087</v>
+      </c>
+      <c r="B89" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C89" t="str">
         <v>C</v>
@@ -11466,11 +11466,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90">
-        <v>10</v>
+      <c r="A90" t="str">
+        <v>DRD10088</v>
+      </c>
+      <c r="B90" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C90" t="str">
         <v>C</v>
@@ -11567,11 +11567,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91">
-        <v>10</v>
+      <c r="A91" t="str">
+        <v>DRD10089</v>
+      </c>
+      <c r="B91" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C91" t="str">
         <v>S</v>
@@ -11668,11 +11668,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92">
-        <v>10</v>
+      <c r="A92" t="str">
+        <v>DRD10090</v>
+      </c>
+      <c r="B92" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C92" t="str">
         <v>S</v>
@@ -11769,11 +11769,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93">
-        <v>10</v>
+      <c r="A93" t="str">
+        <v>DRD10091</v>
+      </c>
+      <c r="B93" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C93" t="str">
         <v>S</v>
@@ -11870,11 +11870,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94">
-        <v>10</v>
+      <c r="A94" t="str">
+        <v>DRD10092</v>
+      </c>
+      <c r="B94" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C94" t="str">
         <v>S</v>
@@ -11971,11 +11971,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95">
-        <v>10</v>
+      <c r="A95" t="str">
+        <v>DRD10093</v>
+      </c>
+      <c r="B95" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C95" t="str">
         <v>C</v>
@@ -12072,11 +12072,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96">
-        <v>10</v>
+      <c r="A96" t="str">
+        <v>DRD10094</v>
+      </c>
+      <c r="B96" t="str">
+        <v>DR1009</v>
       </c>
       <c r="C96" t="str">
         <v>C</v>
@@ -12173,11 +12173,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97">
-        <v>11</v>
+      <c r="A97" t="str">
+        <v>DRD10095</v>
+      </c>
+      <c r="B97" t="str">
+        <v>DR1010</v>
       </c>
       <c r="C97" t="str">
         <v>S</v>
@@ -12274,11 +12274,11 @@
       </c>
     </row>
     <row r="98" xml:space="preserve">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98">
-        <v>11</v>
+      <c r="A98" t="str">
+        <v>DRD10096</v>
+      </c>
+      <c r="B98" t="str">
+        <v>DR1010</v>
       </c>
       <c r="C98" t="str">
         <v>S</v>
@@ -12376,11 +12376,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99">
-        <v>11</v>
+      <c r="A99" t="str">
+        <v>DRD10097</v>
+      </c>
+      <c r="B99" t="str">
+        <v>DR1010</v>
       </c>
       <c r="C99" t="str">
         <v>S</v>
@@ -12477,11 +12477,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100">
-        <v>11</v>
+      <c r="A100" t="str">
+        <v>DRD10098</v>
+      </c>
+      <c r="B100" t="str">
+        <v>DR1010</v>
       </c>
       <c r="C100" t="str">
         <v>S</v>
@@ -12578,11 +12578,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101">
-        <v>11</v>
+      <c r="A101" t="str">
+        <v>DRD10099</v>
+      </c>
+      <c r="B101" t="str">
+        <v>DR1010</v>
       </c>
       <c r="C101" t="str">
         <v>C</v>
@@ -12679,11 +12679,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102">
-        <v>101</v>
-      </c>
-      <c r="B102">
-        <v>11</v>
+      <c r="A102" t="str">
+        <v>DRD10100</v>
+      </c>
+      <c r="B102" t="str">
+        <v>DR1010</v>
       </c>
       <c r="C102" t="str">
         <v>C</v>
@@ -12780,11 +12780,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103">
-        <v>102</v>
-      </c>
-      <c r="B103">
-        <v>11</v>
+      <c r="A103" t="str">
+        <v>DRD10101</v>
+      </c>
+      <c r="B103" t="str">
+        <v>DR1010</v>
       </c>
       <c r="C103" t="str">
         <v>C</v>
@@ -12881,11 +12881,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104">
-        <v>103</v>
-      </c>
-      <c r="B104">
-        <v>11</v>
+      <c r="A104" t="str">
+        <v>DRD10102</v>
+      </c>
+      <c r="B104" t="str">
+        <v>DR1010</v>
       </c>
       <c r="C104" t="str">
         <v>S</v>
@@ -12982,11 +12982,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105">
-        <v>104</v>
-      </c>
-      <c r="B105">
-        <v>11</v>
+      <c r="A105" t="str">
+        <v>DRD10103</v>
+      </c>
+      <c r="B105" t="str">
+        <v>DR1010</v>
       </c>
       <c r="C105" t="str">
         <v>S</v>
@@ -13083,11 +13083,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106">
-        <v>105</v>
-      </c>
-      <c r="B106">
-        <v>12</v>
+      <c r="A106" t="str">
+        <v>DRD10104</v>
+      </c>
+      <c r="B106" t="str">
+        <v>DR1011</v>
       </c>
       <c r="C106" t="str">
         <v>S</v>
@@ -13184,11 +13184,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107">
-        <v>106</v>
-      </c>
-      <c r="B107">
-        <v>12</v>
+      <c r="A107" t="str">
+        <v>DRD10105</v>
+      </c>
+      <c r="B107" t="str">
+        <v>DR1011</v>
       </c>
       <c r="C107" t="str">
         <v>S</v>
@@ -13285,11 +13285,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108">
-        <v>107</v>
-      </c>
-      <c r="B108">
-        <v>12</v>
+      <c r="A108" t="str">
+        <v>DRD10106</v>
+      </c>
+      <c r="B108" t="str">
+        <v>DR1011</v>
       </c>
       <c r="C108" t="str">
         <v>S</v>
@@ -13386,11 +13386,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109">
-        <v>108</v>
-      </c>
-      <c r="B109">
-        <v>12</v>
+      <c r="A109" t="str">
+        <v>DRD10107</v>
+      </c>
+      <c r="B109" t="str">
+        <v>DR1011</v>
       </c>
       <c r="C109" t="str">
         <v>C</v>
@@ -13487,11 +13487,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110">
-        <v>109</v>
-      </c>
-      <c r="B110">
-        <v>12</v>
+      <c r="A110" t="str">
+        <v>DRD10108</v>
+      </c>
+      <c r="B110" t="str">
+        <v>DR1011</v>
       </c>
       <c r="C110" t="str">
         <v>C</v>
@@ -13588,11 +13588,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111">
-        <v>110</v>
-      </c>
-      <c r="B111">
-        <v>13</v>
+      <c r="A111" t="str">
+        <v>DRD10109</v>
+      </c>
+      <c r="B111" t="str">
+        <v>DR1012</v>
       </c>
       <c r="C111" t="str">
         <v>C</v>
@@ -13689,11 +13689,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112">
-        <v>111</v>
-      </c>
-      <c r="B112">
-        <v>13</v>
+      <c r="A112" t="str">
+        <v>DRD10110</v>
+      </c>
+      <c r="B112" t="str">
+        <v>DR1012</v>
       </c>
       <c r="C112" t="str">
         <v>C</v>
@@ -13790,11 +13790,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113">
-        <v>112</v>
-      </c>
-      <c r="B113">
-        <v>13</v>
+      <c r="A113" t="str">
+        <v>DRD10111</v>
+      </c>
+      <c r="B113" t="str">
+        <v>DR1012</v>
       </c>
       <c r="C113" t="str">
         <v>C</v>
@@ -13891,11 +13891,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114">
-        <v>113</v>
-      </c>
-      <c r="B114">
-        <v>13</v>
+      <c r="A114" t="str">
+        <v>DRD10112</v>
+      </c>
+      <c r="B114" t="str">
+        <v>DR1012</v>
       </c>
       <c r="C114" t="str">
         <v>C</v>
@@ -13992,11 +13992,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115">
-        <v>114</v>
-      </c>
-      <c r="B115">
-        <v>14</v>
+      <c r="A115" t="str">
+        <v>DRD10113</v>
+      </c>
+      <c r="B115" t="str">
+        <v>DR1013</v>
       </c>
       <c r="C115" t="str">
         <v>S</v>
@@ -14093,11 +14093,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116">
-        <v>115</v>
-      </c>
-      <c r="B116">
-        <v>14</v>
+      <c r="A116" t="str">
+        <v>DRD10114</v>
+      </c>
+      <c r="B116" t="str">
+        <v>DR1013</v>
       </c>
       <c r="C116" t="str">
         <v>S</v>
@@ -14194,11 +14194,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117">
-        <v>116</v>
-      </c>
-      <c r="B117">
-        <v>14</v>
+      <c r="A117" t="str">
+        <v>DRD10115</v>
+      </c>
+      <c r="B117" t="str">
+        <v>DR1013</v>
       </c>
       <c r="C117" t="str">
         <v>S</v>
@@ -14295,11 +14295,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118">
-        <v>117</v>
-      </c>
-      <c r="B118">
-        <v>14</v>
+      <c r="A118" t="str">
+        <v>DRD10116</v>
+      </c>
+      <c r="B118" t="str">
+        <v>DR1013</v>
       </c>
       <c r="C118" t="str">
         <v>S</v>
@@ -14396,11 +14396,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119">
-        <v>118</v>
-      </c>
-      <c r="B119">
-        <v>14</v>
+      <c r="A119" t="str">
+        <v>DRD10117</v>
+      </c>
+      <c r="B119" t="str">
+        <v>DR1013</v>
       </c>
       <c r="C119" t="str">
         <v>S</v>
@@ -14497,11 +14497,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120">
-        <v>119</v>
-      </c>
-      <c r="B120">
-        <v>14</v>
+      <c r="A120" t="str">
+        <v>DRD10118</v>
+      </c>
+      <c r="B120" t="str">
+        <v>DR1013</v>
       </c>
       <c r="C120" t="str">
         <v>S</v>
@@ -14598,11 +14598,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121">
-        <v>120</v>
-      </c>
-      <c r="B121">
-        <v>14</v>
+      <c r="A121" t="str">
+        <v>DRD10119</v>
+      </c>
+      <c r="B121" t="str">
+        <v>DR1013</v>
       </c>
       <c r="C121" t="str">
         <v>S</v>
@@ -14699,11 +14699,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122">
-        <v>121</v>
-      </c>
-      <c r="B122">
-        <v>15</v>
+      <c r="A122" t="str">
+        <v>DRD10120</v>
+      </c>
+      <c r="B122" t="str">
+        <v>DR1014</v>
       </c>
       <c r="C122" t="str">
         <v>C</v>
@@ -14800,11 +14800,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123">
-        <v>122</v>
-      </c>
-      <c r="B123">
-        <v>15</v>
+      <c r="A123" t="str">
+        <v>DRD10121</v>
+      </c>
+      <c r="B123" t="str">
+        <v>DR1014</v>
       </c>
       <c r="C123" t="str">
         <v>C</v>
@@ -14901,11 +14901,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124">
-        <v>123</v>
-      </c>
-      <c r="B124">
-        <v>15</v>
+      <c r="A124" t="str">
+        <v>DRD10122</v>
+      </c>
+      <c r="B124" t="str">
+        <v>DR1014</v>
       </c>
       <c r="C124" t="str">
         <v>C</v>
@@ -15002,11 +15002,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125">
-        <v>124</v>
-      </c>
-      <c r="B125">
-        <v>15</v>
+      <c r="A125" t="str">
+        <v>DRD10123</v>
+      </c>
+      <c r="B125" t="str">
+        <v>DR1014</v>
       </c>
       <c r="C125" t="str">
         <v>C</v>
@@ -15103,11 +15103,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126">
-        <v>125</v>
-      </c>
-      <c r="B126">
-        <v>15</v>
+      <c r="A126" t="str">
+        <v>DRD10124</v>
+      </c>
+      <c r="B126" t="str">
+        <v>DR1014</v>
       </c>
       <c r="C126" t="str">
         <v>C</v>
@@ -15204,11 +15204,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127">
-        <v>126</v>
-      </c>
-      <c r="B127">
-        <v>15</v>
+      <c r="A127" t="str">
+        <v>DRD10125</v>
+      </c>
+      <c r="B127" t="str">
+        <v>DR1014</v>
       </c>
       <c r="C127" t="str">
         <v>C</v>
@@ -15305,11 +15305,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128">
-        <v>127</v>
-      </c>
-      <c r="B128">
-        <v>15</v>
+      <c r="A128" t="str">
+        <v>DRD10126</v>
+      </c>
+      <c r="B128" t="str">
+        <v>DR1014</v>
       </c>
       <c r="C128" t="str">
         <v>C</v>
@@ -15406,11 +15406,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129">
-        <v>128</v>
-      </c>
-      <c r="B129">
-        <v>15</v>
+      <c r="A129" t="str">
+        <v>DRD10127</v>
+      </c>
+      <c r="B129" t="str">
+        <v>DR1014</v>
       </c>
       <c r="C129" t="str">
         <v>C</v>
@@ -15507,11 +15507,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130">
-        <v>129</v>
-      </c>
-      <c r="B130">
-        <v>15</v>
+      <c r="A130" t="str">
+        <v>DRD10128</v>
+      </c>
+      <c r="B130" t="str">
+        <v>DR1014</v>
       </c>
       <c r="C130" t="str">
         <v>C</v>
@@ -15608,11 +15608,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131">
-        <v>130</v>
-      </c>
-      <c r="B131">
-        <v>15</v>
+      <c r="A131" t="str">
+        <v>DRD10129</v>
+      </c>
+      <c r="B131" t="str">
+        <v>DR1014</v>
       </c>
       <c r="C131" t="str">
         <v>C</v>
@@ -15709,11 +15709,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132">
-        <v>131</v>
-      </c>
-      <c r="B132">
-        <v>16</v>
+      <c r="A132" t="str">
+        <v>DRD10130</v>
+      </c>
+      <c r="B132" t="str">
+        <v>DR1015</v>
       </c>
       <c r="C132" t="str">
         <v>S</v>
@@ -15810,11 +15810,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133">
-        <v>132</v>
-      </c>
-      <c r="B133">
-        <v>16</v>
+      <c r="A133" t="str">
+        <v>DRD10131</v>
+      </c>
+      <c r="B133" t="str">
+        <v>DR1015</v>
       </c>
       <c r="C133" t="str">
         <v>S</v>
@@ -15911,11 +15911,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134">
-        <v>133</v>
-      </c>
-      <c r="B134">
-        <v>16</v>
+      <c r="A134" t="str">
+        <v>DRD10132</v>
+      </c>
+      <c r="B134" t="str">
+        <v>DR1015</v>
       </c>
       <c r="C134" t="str">
         <v>S</v>
@@ -16012,11 +16012,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135">
-        <v>134</v>
-      </c>
-      <c r="B135">
-        <v>17</v>
+      <c r="A135" t="str">
+        <v>DRD10133</v>
+      </c>
+      <c r="B135" t="str">
+        <v>DR1016</v>
       </c>
       <c r="C135" t="str">
         <v>C</v>
@@ -16113,11 +16113,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136">
-        <v>135</v>
-      </c>
-      <c r="B136">
-        <v>17</v>
+      <c r="A136" t="str">
+        <v>DRD10134</v>
+      </c>
+      <c r="B136" t="str">
+        <v>DR1016</v>
       </c>
       <c r="C136" t="str">
         <v>C</v>
@@ -16214,11 +16214,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137">
-        <v>136</v>
-      </c>
-      <c r="B137">
-        <v>17</v>
+      <c r="A137" t="str">
+        <v>DRD10135</v>
+      </c>
+      <c r="B137" t="str">
+        <v>DR1016</v>
       </c>
       <c r="C137" t="str">
         <v>C</v>
@@ -16315,11 +16315,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138">
-        <v>137</v>
-      </c>
-      <c r="B138">
-        <v>17</v>
+      <c r="A138" t="str">
+        <v>DRD10136</v>
+      </c>
+      <c r="B138" t="str">
+        <v>DR1016</v>
       </c>
       <c r="C138" t="str">
         <v>C</v>
@@ -16416,11 +16416,11 @@
       </c>
     </row>
     <row r="139" xml:space="preserve">
-      <c r="A139">
-        <v>138</v>
-      </c>
-      <c r="B139">
-        <v>17</v>
+      <c r="A139" t="str">
+        <v>DRD10137</v>
+      </c>
+      <c r="B139" t="str">
+        <v>DR1016</v>
       </c>
       <c r="C139" t="str">
         <v>C</v>
@@ -16521,11 +16521,11 @@
       </c>
     </row>
     <row r="140" xml:space="preserve">
-      <c r="A140">
-        <v>139</v>
-      </c>
-      <c r="B140">
-        <v>17</v>
+      <c r="A140" t="str">
+        <v>DRD10138</v>
+      </c>
+      <c r="B140" t="str">
+        <v>DR1016</v>
       </c>
       <c r="C140" t="str">
         <v>C</v>
@@ -16626,11 +16626,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141">
-        <v>140</v>
-      </c>
-      <c r="B141">
-        <v>17</v>
+      <c r="A141" t="str">
+        <v>DRD10139</v>
+      </c>
+      <c r="B141" t="str">
+        <v>DR1016</v>
       </c>
       <c r="C141" t="str">
         <v>C</v>
@@ -16727,11 +16727,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142">
-        <v>141</v>
-      </c>
-      <c r="B142">
-        <v>18</v>
+      <c r="A142" t="str">
+        <v>DRD10140</v>
+      </c>
+      <c r="B142" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C142" t="str">
         <v>C</v>
@@ -16828,11 +16828,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143">
-        <v>142</v>
-      </c>
-      <c r="B143">
-        <v>18</v>
+      <c r="A143" t="str">
+        <v>DRD10141</v>
+      </c>
+      <c r="B143" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C143" t="str">
         <v>S</v>
@@ -16929,11 +16929,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144">
-        <v>143</v>
-      </c>
-      <c r="B144">
-        <v>18</v>
+      <c r="A144" t="str">
+        <v>DRD10142</v>
+      </c>
+      <c r="B144" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C144" t="str">
         <v>S</v>
@@ -17030,11 +17030,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145">
-        <v>144</v>
-      </c>
-      <c r="B145">
-        <v>18</v>
+      <c r="A145" t="str">
+        <v>DRD10143</v>
+      </c>
+      <c r="B145" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C145" t="str">
         <v>S</v>
@@ -17131,11 +17131,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146">
-        <v>145</v>
-      </c>
-      <c r="B146">
-        <v>18</v>
+      <c r="A146" t="str">
+        <v>DRD10144</v>
+      </c>
+      <c r="B146" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C146" t="str">
         <v>C</v>
@@ -17232,11 +17232,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147">
-        <v>146</v>
-      </c>
-      <c r="B147">
-        <v>18</v>
+      <c r="A147" t="str">
+        <v>DRD10145</v>
+      </c>
+      <c r="B147" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C147" t="str">
         <v>C</v>
@@ -17333,11 +17333,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148">
-        <v>147</v>
-      </c>
-      <c r="B148">
-        <v>18</v>
+      <c r="A148" t="str">
+        <v>DRD10146</v>
+      </c>
+      <c r="B148" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C148" t="str">
         <v>S</v>
@@ -17434,11 +17434,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149">
-        <v>148</v>
-      </c>
-      <c r="B149">
-        <v>18</v>
+      <c r="A149" t="str">
+        <v>DRD10147</v>
+      </c>
+      <c r="B149" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C149" t="str">
         <v>S</v>
@@ -17535,11 +17535,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150">
-        <v>149</v>
-      </c>
-      <c r="B150">
-        <v>18</v>
+      <c r="A150" t="str">
+        <v>DRD10148</v>
+      </c>
+      <c r="B150" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C150" t="str">
         <v>C</v>
@@ -17636,11 +17636,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151">
-        <v>150</v>
-      </c>
-      <c r="B151">
-        <v>18</v>
+      <c r="A151" t="str">
+        <v>DRD10149</v>
+      </c>
+      <c r="B151" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C151" t="str">
         <v>S</v>
@@ -17737,11 +17737,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152">
-        <v>151</v>
-      </c>
-      <c r="B152">
-        <v>18</v>
+      <c r="A152" t="str">
+        <v>DRD10150</v>
+      </c>
+      <c r="B152" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C152" t="str">
         <v>C</v>
@@ -17838,11 +17838,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153">
-        <v>152</v>
-      </c>
-      <c r="B153">
-        <v>18</v>
+      <c r="A153" t="str">
+        <v>DRD10151</v>
+      </c>
+      <c r="B153" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C153" t="str">
         <v>C</v>
@@ -17939,11 +17939,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154">
-        <v>153</v>
-      </c>
-      <c r="B154">
-        <v>18</v>
+      <c r="A154" t="str">
+        <v>DRD10152</v>
+      </c>
+      <c r="B154" t="str">
+        <v>DR1017</v>
       </c>
       <c r="C154" t="str">
         <v>C</v>
@@ -18040,11 +18040,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155">
-        <v>154</v>
-      </c>
-      <c r="B155">
-        <v>19</v>
+      <c r="A155" t="str">
+        <v>DRD10153</v>
+      </c>
+      <c r="B155" t="str">
+        <v>DR1018</v>
       </c>
       <c r="C155" t="str">
         <v>S</v>
@@ -18141,11 +18141,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156">
-        <v>155</v>
-      </c>
-      <c r="B156">
-        <v>19</v>
+      <c r="A156" t="str">
+        <v>DRD10154</v>
+      </c>
+      <c r="B156" t="str">
+        <v>DR1018</v>
       </c>
       <c r="C156" t="str">
         <v>S</v>
@@ -18242,11 +18242,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157">
-        <v>156</v>
-      </c>
-      <c r="B157">
-        <v>19</v>
+      <c r="A157" t="str">
+        <v>DRD10155</v>
+      </c>
+      <c r="B157" t="str">
+        <v>DR1018</v>
       </c>
       <c r="C157" t="str">
         <v>S</v>
@@ -18343,11 +18343,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158">
-        <v>157</v>
-      </c>
-      <c r="B158">
-        <v>19</v>
+      <c r="A158" t="str">
+        <v>DRD10156</v>
+      </c>
+      <c r="B158" t="str">
+        <v>DR1018</v>
       </c>
       <c r="C158" t="str">
         <v>S</v>
@@ -18444,11 +18444,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159">
-        <v>158</v>
-      </c>
-      <c r="B159">
-        <v>19</v>
+      <c r="A159" t="str">
+        <v>DRD10157</v>
+      </c>
+      <c r="B159" t="str">
+        <v>DR1018</v>
       </c>
       <c r="C159" t="str">
         <v>S</v>
@@ -18545,11 +18545,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160">
-        <v>159</v>
-      </c>
-      <c r="B160">
-        <v>20</v>
+      <c r="A160" t="str">
+        <v>DRD10158</v>
+      </c>
+      <c r="B160" t="str">
+        <v>DR1019</v>
       </c>
       <c r="C160" t="str">
         <v>C</v>
@@ -18646,11 +18646,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161">
-        <v>160</v>
-      </c>
-      <c r="B161">
-        <v>20</v>
+      <c r="A161" t="str">
+        <v>DRD10159</v>
+      </c>
+      <c r="B161" t="str">
+        <v>DR1019</v>
       </c>
       <c r="C161" t="str">
         <v>C</v>
@@ -18747,11 +18747,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162">
-        <v>161</v>
-      </c>
-      <c r="B162">
-        <v>20</v>
+      <c r="A162" t="str">
+        <v>DRD10160</v>
+      </c>
+      <c r="B162" t="str">
+        <v>DR1019</v>
       </c>
       <c r="C162" t="str">
         <v>C</v>
@@ -18848,11 +18848,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163">
-        <v>162</v>
-      </c>
-      <c r="B163">
-        <v>20</v>
+      <c r="A163" t="str">
+        <v>DRD10161</v>
+      </c>
+      <c r="B163" t="str">
+        <v>DR1019</v>
       </c>
       <c r="C163" t="str">
         <v>C</v>
@@ -18949,11 +18949,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164">
-        <v>163</v>
-      </c>
-      <c r="B164">
-        <v>20</v>
+      <c r="A164" t="str">
+        <v>DRD10162</v>
+      </c>
+      <c r="B164" t="str">
+        <v>DR1019</v>
       </c>
       <c r="C164" t="str">
         <v>C</v>
@@ -19050,11 +19050,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165">
-        <v>164</v>
-      </c>
-      <c r="B165">
-        <v>20</v>
+      <c r="A165" t="str">
+        <v>DRD10163</v>
+      </c>
+      <c r="B165" t="str">
+        <v>DR1019</v>
       </c>
       <c r="C165" t="str">
         <v>C</v>
@@ -19151,11 +19151,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166">
-        <v>165</v>
-      </c>
-      <c r="B166">
-        <v>20</v>
+      <c r="A166" t="str">
+        <v>DRD10164</v>
+      </c>
+      <c r="B166" t="str">
+        <v>DR1019</v>
       </c>
       <c r="C166" t="str">
         <v>C</v>
@@ -19252,11 +19252,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167">
-        <v>166</v>
-      </c>
-      <c r="B167">
-        <v>21</v>
+      <c r="A167" t="str">
+        <v>DRD10165</v>
+      </c>
+      <c r="B167" t="str">
+        <v>DR1020</v>
       </c>
       <c r="C167" t="str">
         <v>C</v>
@@ -19353,11 +19353,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168">
-        <v>167</v>
-      </c>
-      <c r="B168">
-        <v>21</v>
+      <c r="A168" t="str">
+        <v>DRD10166</v>
+      </c>
+      <c r="B168" t="str">
+        <v>DR1020</v>
       </c>
       <c r="C168" t="str">
         <v>C</v>
@@ -19454,11 +19454,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169">
-        <v>168</v>
-      </c>
-      <c r="B169">
-        <v>21</v>
+      <c r="A169" t="str">
+        <v>DRD10167</v>
+      </c>
+      <c r="B169" t="str">
+        <v>DR1020</v>
       </c>
       <c r="C169" t="str">
         <v>C</v>
@@ -19555,11 +19555,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170">
-        <v>169</v>
-      </c>
-      <c r="B170">
-        <v>21</v>
+      <c r="A170" t="str">
+        <v>DRD10168</v>
+      </c>
+      <c r="B170" t="str">
+        <v>DR1020</v>
       </c>
       <c r="C170" t="str">
         <v>C</v>
@@ -19656,11 +19656,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171">
-        <v>170</v>
-      </c>
-      <c r="B171">
-        <v>21</v>
+      <c r="A171" t="str">
+        <v>DRD10169</v>
+      </c>
+      <c r="B171" t="str">
+        <v>DR1020</v>
       </c>
       <c r="C171" t="str">
         <v>C</v>
@@ -19757,11 +19757,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172">
-        <v>171</v>
-      </c>
-      <c r="B172">
-        <v>21</v>
+      <c r="A172" t="str">
+        <v>DRD10170</v>
+      </c>
+      <c r="B172" t="str">
+        <v>DR1020</v>
       </c>
       <c r="C172" t="str">
         <v>C</v>
@@ -19858,11 +19858,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173">
-        <v>172</v>
-      </c>
-      <c r="B173">
-        <v>21</v>
+      <c r="A173" t="str">
+        <v>DRD10171</v>
+      </c>
+      <c r="B173" t="str">
+        <v>DR1020</v>
       </c>
       <c r="C173" t="str">
         <v>S</v>
@@ -19959,11 +19959,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174">
-        <v>173</v>
-      </c>
-      <c r="B174">
-        <v>21</v>
+      <c r="A174" t="str">
+        <v>DRD10172</v>
+      </c>
+      <c r="B174" t="str">
+        <v>DR1020</v>
       </c>
       <c r="C174" t="str">
         <v>C</v>
@@ -20060,11 +20060,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175">
-        <v>174</v>
-      </c>
-      <c r="B175">
-        <v>21</v>
+      <c r="A175" t="str">
+        <v>DRD10173</v>
+      </c>
+      <c r="B175" t="str">
+        <v>DR1020</v>
       </c>
       <c r="C175" t="str">
         <v>C</v>
@@ -20161,11 +20161,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176">
-        <v>175</v>
-      </c>
-      <c r="B176">
-        <v>21</v>
+      <c r="A176" t="str">
+        <v>DRD10174</v>
+      </c>
+      <c r="B176" t="str">
+        <v>DR1020</v>
       </c>
       <c r="C176" t="str">
         <v>S</v>
@@ -20262,11 +20262,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177">
-        <v>176</v>
-      </c>
-      <c r="B177">
-        <v>22</v>
+      <c r="A177" t="str">
+        <v>DRD10175</v>
+      </c>
+      <c r="B177" t="str">
+        <v>DR1021</v>
       </c>
       <c r="C177" t="str">
         <v>S</v>
@@ -20363,11 +20363,11 @@
       </c>
     </row>
     <row r="178" xml:space="preserve">
-      <c r="A178">
-        <v>177</v>
-      </c>
-      <c r="B178">
-        <v>22</v>
+      <c r="A178" t="str">
+        <v>DRD10176</v>
+      </c>
+      <c r="B178" t="str">
+        <v>DR1021</v>
       </c>
       <c r="C178" t="str">
         <v>S</v>
@@ -20470,11 +20470,11 @@
       </c>
     </row>
     <row r="179" xml:space="preserve">
-      <c r="A179">
-        <v>178</v>
-      </c>
-      <c r="B179">
-        <v>22</v>
+      <c r="A179" t="str">
+        <v>DRD10177</v>
+      </c>
+      <c r="B179" t="str">
+        <v>DR1021</v>
       </c>
       <c r="C179" t="str">
         <v>S</v>
@@ -20577,11 +20577,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180">
-        <v>179</v>
-      </c>
-      <c r="B180">
-        <v>22</v>
+      <c r="A180" t="str">
+        <v>DRD10178</v>
+      </c>
+      <c r="B180" t="str">
+        <v>DR1021</v>
       </c>
       <c r="C180" t="str">
         <v>S</v>
@@ -20678,11 +20678,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181">
-        <v>180</v>
-      </c>
-      <c r="B181">
-        <v>23</v>
+      <c r="A181" t="str">
+        <v>DRD10179</v>
+      </c>
+      <c r="B181" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C181" t="str">
         <v>C</v>
@@ -20779,11 +20779,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182">
-        <v>181</v>
-      </c>
-      <c r="B182">
-        <v>23</v>
+      <c r="A182" t="str">
+        <v>DRD10180</v>
+      </c>
+      <c r="B182" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C182" t="str">
         <v>C</v>
@@ -20880,11 +20880,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183">
-        <v>182</v>
-      </c>
-      <c r="B183">
-        <v>23</v>
+      <c r="A183" t="str">
+        <v>DRD10181</v>
+      </c>
+      <c r="B183" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C183" t="str">
         <v>C</v>
@@ -20981,11 +20981,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184">
-        <v>183</v>
-      </c>
-      <c r="B184">
-        <v>23</v>
+      <c r="A184" t="str">
+        <v>DRD10182</v>
+      </c>
+      <c r="B184" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C184" t="str">
         <v>C</v>
@@ -21082,11 +21082,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185">
-        <v>184</v>
-      </c>
-      <c r="B185">
-        <v>23</v>
+      <c r="A185" t="str">
+        <v>DRD10183</v>
+      </c>
+      <c r="B185" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C185" t="str">
         <v>C</v>
@@ -21183,11 +21183,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186">
-        <v>185</v>
-      </c>
-      <c r="B186">
-        <v>23</v>
+      <c r="A186" t="str">
+        <v>DRD10184</v>
+      </c>
+      <c r="B186" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C186" t="str">
         <v>C</v>
@@ -21284,11 +21284,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187">
-        <v>186</v>
-      </c>
-      <c r="B187">
-        <v>23</v>
+      <c r="A187" t="str">
+        <v>DRD10185</v>
+      </c>
+      <c r="B187" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C187" t="str">
         <v>C</v>
@@ -21385,11 +21385,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188">
-        <v>187</v>
-      </c>
-      <c r="B188">
-        <v>23</v>
+      <c r="A188" t="str">
+        <v>DRD10186</v>
+      </c>
+      <c r="B188" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C188" t="str">
         <v>C</v>
@@ -21486,11 +21486,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189">
-        <v>188</v>
-      </c>
-      <c r="B189">
-        <v>23</v>
+      <c r="A189" t="str">
+        <v>DRD10187</v>
+      </c>
+      <c r="B189" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C189" t="str">
         <v>C</v>
@@ -21587,11 +21587,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190">
-        <v>189</v>
-      </c>
-      <c r="B190">
-        <v>23</v>
+      <c r="A190" t="str">
+        <v>DRD10188</v>
+      </c>
+      <c r="B190" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C190" t="str">
         <v>C</v>
@@ -21688,11 +21688,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191">
-        <v>190</v>
-      </c>
-      <c r="B191">
-        <v>23</v>
+      <c r="A191" t="str">
+        <v>DRD10189</v>
+      </c>
+      <c r="B191" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C191" t="str">
         <v>C</v>
@@ -21789,11 +21789,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192">
-        <v>191</v>
-      </c>
-      <c r="B192">
-        <v>23</v>
+      <c r="A192" t="str">
+        <v>DRD10190</v>
+      </c>
+      <c r="B192" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C192" t="str">
         <v>S</v>
@@ -21890,11 +21890,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193">
-        <v>192</v>
-      </c>
-      <c r="B193">
-        <v>23</v>
+      <c r="A193" t="str">
+        <v>DRD10191</v>
+      </c>
+      <c r="B193" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C193" t="str">
         <v>S</v>
@@ -21991,11 +21991,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194">
-        <v>193</v>
-      </c>
-      <c r="B194">
-        <v>23</v>
+      <c r="A194" t="str">
+        <v>DRD10192</v>
+      </c>
+      <c r="B194" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C194" t="str">
         <v>S</v>
@@ -22092,11 +22092,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195">
-        <v>194</v>
-      </c>
-      <c r="B195">
-        <v>23</v>
+      <c r="A195" t="str">
+        <v>DRD10193</v>
+      </c>
+      <c r="B195" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C195" t="str">
         <v>S</v>
@@ -22193,11 +22193,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196">
-        <v>195</v>
-      </c>
-      <c r="B196">
-        <v>23</v>
+      <c r="A196" t="str">
+        <v>DRD10194</v>
+      </c>
+      <c r="B196" t="str">
+        <v>DR1022</v>
       </c>
       <c r="C196" t="str">
         <v>S</v>
@@ -22294,11 +22294,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197">
-        <v>196</v>
-      </c>
-      <c r="B197">
-        <v>24</v>
+      <c r="A197" t="str">
+        <v>DRD10195</v>
+      </c>
+      <c r="B197" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C197" t="str">
         <v>C</v>
@@ -22395,11 +22395,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198">
-        <v>197</v>
-      </c>
-      <c r="B198">
-        <v>24</v>
+      <c r="A198" t="str">
+        <v>DRD10196</v>
+      </c>
+      <c r="B198" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C198" t="str">
         <v>C</v>
@@ -22496,11 +22496,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199">
-        <v>198</v>
-      </c>
-      <c r="B199">
-        <v>24</v>
+      <c r="A199" t="str">
+        <v>DRD10197</v>
+      </c>
+      <c r="B199" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C199" t="str">
         <v>C</v>
@@ -22597,11 +22597,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200">
-        <v>199</v>
-      </c>
-      <c r="B200">
-        <v>24</v>
+      <c r="A200" t="str">
+        <v>DRD10198</v>
+      </c>
+      <c r="B200" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C200" t="str">
         <v>C</v>
@@ -22698,11 +22698,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201">
-        <v>200</v>
-      </c>
-      <c r="B201">
-        <v>24</v>
+      <c r="A201" t="str">
+        <v>DRD10199</v>
+      </c>
+      <c r="B201" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C201" t="str">
         <v>C</v>
@@ -22799,11 +22799,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202">
-        <v>201</v>
-      </c>
-      <c r="B202">
-        <v>24</v>
+      <c r="A202" t="str">
+        <v>DRD10200</v>
+      </c>
+      <c r="B202" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C202" t="str">
         <v>C</v>
@@ -22900,11 +22900,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203">
-        <v>202</v>
-      </c>
-      <c r="B203">
-        <v>24</v>
+      <c r="A203" t="str">
+        <v>DRD10201</v>
+      </c>
+      <c r="B203" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C203" t="str">
         <v>C</v>
@@ -23001,11 +23001,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204">
-        <v>203</v>
-      </c>
-      <c r="B204">
-        <v>24</v>
+      <c r="A204" t="str">
+        <v>DRD10202</v>
+      </c>
+      <c r="B204" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C204" t="str">
         <v>C</v>
@@ -23102,11 +23102,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205">
-        <v>204</v>
-      </c>
-      <c r="B205">
-        <v>24</v>
+      <c r="A205" t="str">
+        <v>DRD10203</v>
+      </c>
+      <c r="B205" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C205" t="str">
         <v>C</v>
@@ -23203,11 +23203,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206">
-        <v>205</v>
-      </c>
-      <c r="B206">
-        <v>24</v>
+      <c r="A206" t="str">
+        <v>DRD10204</v>
+      </c>
+      <c r="B206" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C206" t="str">
         <v>C</v>
@@ -23304,11 +23304,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207">
-        <v>206</v>
-      </c>
-      <c r="B207">
-        <v>24</v>
+      <c r="A207" t="str">
+        <v>DRD10205</v>
+      </c>
+      <c r="B207" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C207" t="str">
         <v>C</v>
@@ -23405,11 +23405,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208">
-        <v>207</v>
-      </c>
-      <c r="B208">
-        <v>24</v>
+      <c r="A208" t="str">
+        <v>DRD10206</v>
+      </c>
+      <c r="B208" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C208" t="str">
         <v>C</v>
@@ -23506,11 +23506,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209">
-        <v>208</v>
-      </c>
-      <c r="B209">
-        <v>24</v>
+      <c r="A209" t="str">
+        <v>DRD10207</v>
+      </c>
+      <c r="B209" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C209" t="str">
         <v>C</v>
@@ -23607,11 +23607,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210">
-        <v>209</v>
-      </c>
-      <c r="B210">
-        <v>24</v>
+      <c r="A210" t="str">
+        <v>DRD10208</v>
+      </c>
+      <c r="B210" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C210" t="str">
         <v>C</v>
@@ -23708,11 +23708,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211">
-        <v>210</v>
-      </c>
-      <c r="B211">
-        <v>24</v>
+      <c r="A211" t="str">
+        <v>DRD10209</v>
+      </c>
+      <c r="B211" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C211" t="str">
         <v>C</v>
@@ -23809,11 +23809,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212">
-        <v>211</v>
-      </c>
-      <c r="B212">
-        <v>24</v>
+      <c r="A212" t="str">
+        <v>DRD10210</v>
+      </c>
+      <c r="B212" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C212" t="str">
         <v>C</v>
@@ -23910,11 +23910,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213">
-        <v>212</v>
-      </c>
-      <c r="B213">
-        <v>24</v>
+      <c r="A213" t="str">
+        <v>DRD10211</v>
+      </c>
+      <c r="B213" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C213" t="str">
         <v>C</v>
@@ -24011,11 +24011,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214">
-        <v>213</v>
-      </c>
-      <c r="B214">
-        <v>24</v>
+      <c r="A214" t="str">
+        <v>DRD10212</v>
+      </c>
+      <c r="B214" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C214" t="str">
         <v>C</v>
@@ -24112,11 +24112,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215">
-        <v>214</v>
-      </c>
-      <c r="B215">
-        <v>24</v>
+      <c r="A215" t="str">
+        <v>DRD10213</v>
+      </c>
+      <c r="B215" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C215" t="str">
         <v>C</v>
@@ -24213,11 +24213,11 @@
       </c>
     </row>
     <row r="216" xml:space="preserve">
-      <c r="A216">
-        <v>215</v>
-      </c>
-      <c r="B216">
-        <v>24</v>
+      <c r="A216" t="str">
+        <v>DRD10214</v>
+      </c>
+      <c r="B216" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C216" t="str">
         <v>C</v>
@@ -24315,11 +24315,11 @@
       </c>
     </row>
     <row r="217" xml:space="preserve">
-      <c r="A217">
-        <v>216</v>
-      </c>
-      <c r="B217">
-        <v>24</v>
+      <c r="A217" t="str">
+        <v>DRD10215</v>
+      </c>
+      <c r="B217" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C217" t="str">
         <v>C</v>
@@ -24417,11 +24417,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218">
-        <v>217</v>
-      </c>
-      <c r="B218">
-        <v>24</v>
+      <c r="A218" t="str">
+        <v>DRD10216</v>
+      </c>
+      <c r="B218" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C218" t="str">
         <v>C</v>
@@ -24518,11 +24518,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219">
-        <v>218</v>
-      </c>
-      <c r="B219">
-        <v>24</v>
+      <c r="A219" t="str">
+        <v>DRD10217</v>
+      </c>
+      <c r="B219" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C219" t="str">
         <v>C</v>
@@ -24619,11 +24619,11 @@
       </c>
     </row>
     <row r="220" xml:space="preserve">
-      <c r="A220">
-        <v>219</v>
-      </c>
-      <c r="B220">
-        <v>24</v>
+      <c r="A220" t="str">
+        <v>DRD10218</v>
+      </c>
+      <c r="B220" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C220" t="str">
         <v>C</v>
@@ -24721,11 +24721,11 @@
       </c>
     </row>
     <row r="221" xml:space="preserve">
-      <c r="A221">
-        <v>220</v>
-      </c>
-      <c r="B221">
-        <v>24</v>
+      <c r="A221" t="str">
+        <v>DRD10219</v>
+      </c>
+      <c r="B221" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C221" t="str">
         <v>C</v>
@@ -24823,11 +24823,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222">
-        <v>221</v>
-      </c>
-      <c r="B222">
-        <v>24</v>
+      <c r="A222" t="str">
+        <v>DRD10220</v>
+      </c>
+      <c r="B222" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C222" t="str">
         <v>S</v>
@@ -24924,11 +24924,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223">
-        <v>222</v>
-      </c>
-      <c r="B223">
-        <v>24</v>
+      <c r="A223" t="str">
+        <v>DRD10221</v>
+      </c>
+      <c r="B223" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C223" t="str">
         <v>S</v>
@@ -25025,11 +25025,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224">
-        <v>223</v>
-      </c>
-      <c r="B224">
-        <v>24</v>
+      <c r="A224" t="str">
+        <v>DRD10222</v>
+      </c>
+      <c r="B224" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C224" t="str">
         <v>S</v>
@@ -25126,11 +25126,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225">
-        <v>224</v>
-      </c>
-      <c r="B225">
-        <v>24</v>
+      <c r="A225" t="str">
+        <v>DRD10223</v>
+      </c>
+      <c r="B225" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C225" t="str">
         <v>S</v>
@@ -25227,11 +25227,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226">
-        <v>225</v>
-      </c>
-      <c r="B226">
-        <v>24</v>
+      <c r="A226" t="str">
+        <v>DRD10224</v>
+      </c>
+      <c r="B226" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C226" t="str">
         <v>S</v>
@@ -25328,11 +25328,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227">
-        <v>226</v>
-      </c>
-      <c r="B227">
-        <v>24</v>
+      <c r="A227" t="str">
+        <v>DRD10225</v>
+      </c>
+      <c r="B227" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C227" t="str">
         <v>S</v>
@@ -25429,11 +25429,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228">
-        <v>227</v>
-      </c>
-      <c r="B228">
-        <v>24</v>
+      <c r="A228" t="str">
+        <v>DRD10226</v>
+      </c>
+      <c r="B228" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C228" t="str">
         <v>S</v>
@@ -25530,11 +25530,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229">
-        <v>228</v>
-      </c>
-      <c r="B229">
-        <v>24</v>
+      <c r="A229" t="str">
+        <v>DRD10227</v>
+      </c>
+      <c r="B229" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C229" t="str">
         <v>S</v>
@@ -25631,11 +25631,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230">
-        <v>229</v>
-      </c>
-      <c r="B230">
-        <v>24</v>
+      <c r="A230" t="str">
+        <v>DRD10228</v>
+      </c>
+      <c r="B230" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C230" t="str">
         <v>S</v>
@@ -25732,11 +25732,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231">
-        <v>230</v>
-      </c>
-      <c r="B231">
-        <v>24</v>
+      <c r="A231" t="str">
+        <v>DRD10229</v>
+      </c>
+      <c r="B231" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C231" t="str">
         <v>S</v>
@@ -25833,11 +25833,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232">
-        <v>231</v>
-      </c>
-      <c r="B232">
-        <v>24</v>
+      <c r="A232" t="str">
+        <v>DRD10230</v>
+      </c>
+      <c r="B232" t="str">
+        <v>DR1023</v>
       </c>
       <c r="C232" t="str">
         <v>S</v>
@@ -25934,11 +25934,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233">
-        <v>232</v>
-      </c>
-      <c r="B233">
-        <v>25</v>
+      <c r="A233" t="str">
+        <v>DRD10231</v>
+      </c>
+      <c r="B233" t="str">
+        <v>DR1024</v>
       </c>
       <c r="C233" t="str">
         <v>C</v>
@@ -26035,11 +26035,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234">
-        <v>233</v>
-      </c>
-      <c r="B234">
-        <v>25</v>
+      <c r="A234" t="str">
+        <v>DRD10232</v>
+      </c>
+      <c r="B234" t="str">
+        <v>DR1024</v>
       </c>
       <c r="C234" t="str">
         <v>C</v>
@@ -26136,11 +26136,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235">
-        <v>234</v>
-      </c>
-      <c r="B235">
-        <v>25</v>
+      <c r="A235" t="str">
+        <v>DRD10233</v>
+      </c>
+      <c r="B235" t="str">
+        <v>DR1024</v>
       </c>
       <c r="C235" t="str">
         <v>C</v>
@@ -26237,11 +26237,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236">
-        <v>235</v>
-      </c>
-      <c r="B236">
-        <v>25</v>
+      <c r="A236" t="str">
+        <v>DRD10234</v>
+      </c>
+      <c r="B236" t="str">
+        <v>DR1024</v>
       </c>
       <c r="C236" t="str">
         <v>C</v>
@@ -26338,11 +26338,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237">
-        <v>236</v>
-      </c>
-      <c r="B237">
-        <v>25</v>
+      <c r="A237" t="str">
+        <v>DRD10235</v>
+      </c>
+      <c r="B237" t="str">
+        <v>DR1024</v>
       </c>
       <c r="C237" t="str">
         <v>S</v>
@@ -26439,11 +26439,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238">
-        <v>237</v>
-      </c>
-      <c r="B238">
-        <v>26</v>
+      <c r="A238" t="str">
+        <v>DRD10236</v>
+      </c>
+      <c r="B238" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C238" t="str">
         <v>C</v>
@@ -26540,11 +26540,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239">
-        <v>238</v>
-      </c>
-      <c r="B239">
-        <v>26</v>
+      <c r="A239" t="str">
+        <v>DRD10237</v>
+      </c>
+      <c r="B239" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C239" t="str">
         <v>C</v>
@@ -26641,11 +26641,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240">
-        <v>239</v>
-      </c>
-      <c r="B240">
-        <v>26</v>
+      <c r="A240" t="str">
+        <v>DRD10238</v>
+      </c>
+      <c r="B240" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C240" t="str">
         <v>C</v>
@@ -26742,11 +26742,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241">
-        <v>240</v>
-      </c>
-      <c r="B241">
-        <v>26</v>
+      <c r="A241" t="str">
+        <v>DRD10239</v>
+      </c>
+      <c r="B241" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C241" t="str">
         <v>C</v>
@@ -26843,11 +26843,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242">
-        <v>241</v>
-      </c>
-      <c r="B242">
-        <v>26</v>
+      <c r="A242" t="str">
+        <v>DRD10240</v>
+      </c>
+      <c r="B242" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C242" t="str">
         <v>C</v>
@@ -26944,11 +26944,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243">
-        <v>242</v>
-      </c>
-      <c r="B243">
-        <v>26</v>
+      <c r="A243" t="str">
+        <v>DRD10241</v>
+      </c>
+      <c r="B243" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C243" t="str">
         <v>C</v>
@@ -27045,11 +27045,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244">
-        <v>243</v>
-      </c>
-      <c r="B244">
-        <v>26</v>
+      <c r="A244" t="str">
+        <v>DRD10242</v>
+      </c>
+      <c r="B244" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C244" t="str">
         <v>C</v>
@@ -27146,11 +27146,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245">
-        <v>244</v>
-      </c>
-      <c r="B245">
-        <v>26</v>
+      <c r="A245" t="str">
+        <v>DRD10243</v>
+      </c>
+      <c r="B245" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C245" t="str">
         <v>C</v>
@@ -27247,11 +27247,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246">
-        <v>245</v>
-      </c>
-      <c r="B246">
-        <v>26</v>
+      <c r="A246" t="str">
+        <v>DRD10244</v>
+      </c>
+      <c r="B246" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C246" t="str">
         <v>C</v>
@@ -27348,11 +27348,11 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247">
-        <v>246</v>
-      </c>
-      <c r="B247">
-        <v>26</v>
+      <c r="A247" t="str">
+        <v>DRD10245</v>
+      </c>
+      <c r="B247" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C247" t="str">
         <v>C</v>
@@ -27449,11 +27449,11 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248">
-        <v>247</v>
-      </c>
-      <c r="B248">
-        <v>26</v>
+      <c r="A248" t="str">
+        <v>DRD10246</v>
+      </c>
+      <c r="B248" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C248" t="str">
         <v>S</v>
@@ -27550,11 +27550,11 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249">
-        <v>248</v>
-      </c>
-      <c r="B249">
-        <v>26</v>
+      <c r="A249" t="str">
+        <v>DRD10247</v>
+      </c>
+      <c r="B249" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C249" t="str">
         <v>S</v>
@@ -27651,11 +27651,11 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250">
-        <v>249</v>
-      </c>
-      <c r="B250">
-        <v>26</v>
+      <c r="A250" t="str">
+        <v>DRD10248</v>
+      </c>
+      <c r="B250" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C250" t="str">
         <v>S</v>
@@ -27752,11 +27752,11 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251">
-        <v>250</v>
-      </c>
-      <c r="B251">
-        <v>26</v>
+      <c r="A251" t="str">
+        <v>DRD10249</v>
+      </c>
+      <c r="B251" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C251" t="str">
         <v>S</v>
@@ -27853,11 +27853,11 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252">
-        <v>251</v>
-      </c>
-      <c r="B252">
-        <v>26</v>
+      <c r="A252" t="str">
+        <v>DRD10250</v>
+      </c>
+      <c r="B252" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C252" t="str">
         <v>S</v>
@@ -27954,11 +27954,11 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253">
-        <v>252</v>
-      </c>
-      <c r="B253">
-        <v>26</v>
+      <c r="A253" t="str">
+        <v>DRD10251</v>
+      </c>
+      <c r="B253" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C253" t="str">
         <v>C</v>
@@ -28055,11 +28055,11 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254">
-        <v>253</v>
-      </c>
-      <c r="B254">
-        <v>26</v>
+      <c r="A254" t="str">
+        <v>DRD10252</v>
+      </c>
+      <c r="B254" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C254" t="str">
         <v>C</v>
@@ -28156,11 +28156,11 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255">
-        <v>254</v>
-      </c>
-      <c r="B255">
-        <v>26</v>
+      <c r="A255" t="str">
+        <v>DRD10253</v>
+      </c>
+      <c r="B255" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C255" t="str">
         <v>C</v>
@@ -28257,11 +28257,11 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256">
-        <v>255</v>
-      </c>
-      <c r="B256">
-        <v>26</v>
+      <c r="A256" t="str">
+        <v>DRD10254</v>
+      </c>
+      <c r="B256" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C256" t="str">
         <v>C</v>
@@ -28358,11 +28358,11 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257">
-        <v>256</v>
-      </c>
-      <c r="B257">
-        <v>26</v>
+      <c r="A257" t="str">
+        <v>DRD10255</v>
+      </c>
+      <c r="B257" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C257" t="str">
         <v>C</v>
@@ -28459,11 +28459,11 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258">
-        <v>257</v>
-      </c>
-      <c r="B258">
-        <v>26</v>
+      <c r="A258" t="str">
+        <v>DRD10256</v>
+      </c>
+      <c r="B258" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C258" t="str">
         <v>C</v>
@@ -28560,11 +28560,11 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259">
-        <v>258</v>
-      </c>
-      <c r="B259">
-        <v>26</v>
+      <c r="A259" t="str">
+        <v>DRD10257</v>
+      </c>
+      <c r="B259" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C259" t="str">
         <v>S</v>
@@ -28661,11 +28661,11 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260">
-        <v>259</v>
-      </c>
-      <c r="B260">
-        <v>26</v>
+      <c r="A260" t="str">
+        <v>DRD10258</v>
+      </c>
+      <c r="B260" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C260" t="str">
         <v>S</v>
@@ -28762,11 +28762,11 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261">
-        <v>260</v>
-      </c>
-      <c r="B261">
-        <v>26</v>
+      <c r="A261" t="str">
+        <v>DRD10259</v>
+      </c>
+      <c r="B261" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C261" t="str">
         <v>S</v>
@@ -28863,11 +28863,11 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262">
-        <v>261</v>
-      </c>
-      <c r="B262">
-        <v>26</v>
+      <c r="A262" t="str">
+        <v>DRD10260</v>
+      </c>
+      <c r="B262" t="str">
+        <v>DR1025</v>
       </c>
       <c r="C262" t="str">
         <v>S</v>
@@ -28964,11 +28964,11 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263">
-        <v>262</v>
-      </c>
-      <c r="B263">
-        <v>27</v>
+      <c r="A263" t="str">
+        <v>DRD10261</v>
+      </c>
+      <c r="B263" t="str">
+        <v>DR1026</v>
       </c>
       <c r="C263" t="str">
         <v>C</v>
@@ -29065,11 +29065,11 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264">
-        <v>263</v>
-      </c>
-      <c r="B264">
-        <v>27</v>
+      <c r="A264" t="str">
+        <v>DRD10262</v>
+      </c>
+      <c r="B264" t="str">
+        <v>DR1026</v>
       </c>
       <c r="C264" t="str">
         <v>C</v>
@@ -29166,11 +29166,11 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265">
-        <v>264</v>
-      </c>
-      <c r="B265">
-        <v>27</v>
+      <c r="A265" t="str">
+        <v>DRD10263</v>
+      </c>
+      <c r="B265" t="str">
+        <v>DR1026</v>
       </c>
       <c r="C265" t="str">
         <v>C</v>
@@ -29267,11 +29267,11 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266">
-        <v>265</v>
-      </c>
-      <c r="B266">
-        <v>27</v>
+      <c r="A266" t="str">
+        <v>DRD10264</v>
+      </c>
+      <c r="B266" t="str">
+        <v>DR1026</v>
       </c>
       <c r="C266" t="str">
         <v>S</v>
@@ -29368,11 +29368,11 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267">
-        <v>266</v>
-      </c>
-      <c r="B267">
-        <v>27</v>
+      <c r="A267" t="str">
+        <v>DRD10265</v>
+      </c>
+      <c r="B267" t="str">
+        <v>DR1026</v>
       </c>
       <c r="C267" t="str">
         <v>S</v>
@@ -29469,11 +29469,11 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268">
-        <v>267</v>
-      </c>
-      <c r="B268">
-        <v>28</v>
+      <c r="A268" t="str">
+        <v>DRD10266</v>
+      </c>
+      <c r="B268" t="str">
+        <v>DR1027</v>
       </c>
       <c r="C268" t="str">
         <v>C</v>
@@ -29570,11 +29570,11 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269">
-        <v>268</v>
-      </c>
-      <c r="B269">
-        <v>28</v>
+      <c r="A269" t="str">
+        <v>DRD10267</v>
+      </c>
+      <c r="B269" t="str">
+        <v>DR1027</v>
       </c>
       <c r="C269" t="str">
         <v>S</v>
@@ -29671,11 +29671,11 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270">
-        <v>269</v>
-      </c>
-      <c r="B270">
-        <v>28</v>
+      <c r="A270" t="str">
+        <v>DRD10268</v>
+      </c>
+      <c r="B270" t="str">
+        <v>DR1027</v>
       </c>
       <c r="C270" t="str">
         <v>C</v>
@@ -29772,11 +29772,11 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271">
-        <v>270</v>
-      </c>
-      <c r="B271">
-        <v>28</v>
+      <c r="A271" t="str">
+        <v>DRD10269</v>
+      </c>
+      <c r="B271" t="str">
+        <v>DR1027</v>
       </c>
       <c r="C271" t="str">
         <v>S</v>
@@ -29873,11 +29873,11 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272">
-        <v>271</v>
-      </c>
-      <c r="B272">
-        <v>28</v>
+      <c r="A272" t="str">
+        <v>DRD10270</v>
+      </c>
+      <c r="B272" t="str">
+        <v>DR1027</v>
       </c>
       <c r="C272" t="str">
         <v>C</v>
@@ -29974,11 +29974,11 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273">
-        <v>272</v>
-      </c>
-      <c r="B273">
-        <v>28</v>
+      <c r="A273" t="str">
+        <v>DRD10271</v>
+      </c>
+      <c r="B273" t="str">
+        <v>DR1027</v>
       </c>
       <c r="C273" t="str">
         <v>S</v>
@@ -30075,11 +30075,11 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274">
-        <v>273</v>
-      </c>
-      <c r="B274">
-        <v>28</v>
+      <c r="A274" t="str">
+        <v>DRD10272</v>
+      </c>
+      <c r="B274" t="str">
+        <v>DR1027</v>
       </c>
       <c r="C274" t="str">
         <v>S</v>
@@ -30176,11 +30176,11 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275">
-        <v>274</v>
-      </c>
-      <c r="B275">
-        <v>28</v>
+      <c r="A275" t="str">
+        <v>DRD10273</v>
+      </c>
+      <c r="B275" t="str">
+        <v>DR1027</v>
       </c>
       <c r="C275" t="str">
         <v>C</v>
@@ -30277,11 +30277,11 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276">
-        <v>275</v>
-      </c>
-      <c r="B276">
-        <v>29</v>
+      <c r="A276" t="str">
+        <v>DRD10274</v>
+      </c>
+      <c r="B276" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C276" t="str">
         <v>C</v>
@@ -30378,11 +30378,11 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277">
-        <v>276</v>
-      </c>
-      <c r="B277">
-        <v>29</v>
+      <c r="A277" t="str">
+        <v>DRD10275</v>
+      </c>
+      <c r="B277" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C277" t="str">
         <v>C</v>
@@ -30479,11 +30479,11 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278">
-        <v>277</v>
-      </c>
-      <c r="B278">
-        <v>29</v>
+      <c r="A278" t="str">
+        <v>DRD10276</v>
+      </c>
+      <c r="B278" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C278" t="str">
         <v>C</v>
@@ -30580,11 +30580,11 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279">
-        <v>278</v>
-      </c>
-      <c r="B279">
-        <v>29</v>
+      <c r="A279" t="str">
+        <v>DRD10277</v>
+      </c>
+      <c r="B279" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C279" t="str">
         <v>C</v>
@@ -30681,11 +30681,11 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280">
-        <v>279</v>
-      </c>
-      <c r="B280">
-        <v>29</v>
+      <c r="A280" t="str">
+        <v>DRD10278</v>
+      </c>
+      <c r="B280" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C280" t="str">
         <v>C</v>
@@ -30782,11 +30782,11 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281">
-        <v>280</v>
-      </c>
-      <c r="B281">
-        <v>29</v>
+      <c r="A281" t="str">
+        <v>DRD10279</v>
+      </c>
+      <c r="B281" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C281" t="str">
         <v>C</v>
@@ -30883,11 +30883,11 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282">
-        <v>281</v>
-      </c>
-      <c r="B282">
-        <v>29</v>
+      <c r="A282" t="str">
+        <v>DRD10280</v>
+      </c>
+      <c r="B282" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C282" t="str">
         <v>C</v>
@@ -30984,11 +30984,11 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283">
-        <v>282</v>
-      </c>
-      <c r="B283">
-        <v>29</v>
+      <c r="A283" t="str">
+        <v>DRD10281</v>
+      </c>
+      <c r="B283" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C283" t="str">
         <v>C</v>
@@ -31085,11 +31085,11 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284">
-        <v>283</v>
-      </c>
-      <c r="B284">
-        <v>29</v>
+      <c r="A284" t="str">
+        <v>DRD10282</v>
+      </c>
+      <c r="B284" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C284" t="str">
         <v>C</v>
@@ -31186,11 +31186,11 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285">
-        <v>284</v>
-      </c>
-      <c r="B285">
-        <v>29</v>
+      <c r="A285" t="str">
+        <v>DRD10283</v>
+      </c>
+      <c r="B285" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C285" t="str">
         <v>C</v>
@@ -31287,11 +31287,11 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286">
-        <v>285</v>
-      </c>
-      <c r="B286">
-        <v>29</v>
+      <c r="A286" t="str">
+        <v>DRD10284</v>
+      </c>
+      <c r="B286" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C286" t="str">
         <v>C</v>
@@ -31388,11 +31388,11 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287">
-        <v>286</v>
-      </c>
-      <c r="B287">
-        <v>29</v>
+      <c r="A287" t="str">
+        <v>DRD10285</v>
+      </c>
+      <c r="B287" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C287" t="str">
         <v>C</v>
@@ -31489,11 +31489,11 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288">
-        <v>287</v>
-      </c>
-      <c r="B288">
-        <v>29</v>
+      <c r="A288" t="str">
+        <v>DRD10286</v>
+      </c>
+      <c r="B288" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C288" t="str">
         <v>C</v>
@@ -31590,11 +31590,11 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289">
-        <v>288</v>
-      </c>
-      <c r="B289">
-        <v>29</v>
+      <c r="A289" t="str">
+        <v>DRD10287</v>
+      </c>
+      <c r="B289" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C289" t="str">
         <v>C</v>
@@ -31691,11 +31691,11 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290">
-        <v>289</v>
-      </c>
-      <c r="B290">
-        <v>29</v>
+      <c r="A290" t="str">
+        <v>DRD10288</v>
+      </c>
+      <c r="B290" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C290" t="str">
         <v>C</v>
@@ -31792,11 +31792,11 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291">
-        <v>290</v>
-      </c>
-      <c r="B291">
-        <v>29</v>
+      <c r="A291" t="str">
+        <v>DRD10289</v>
+      </c>
+      <c r="B291" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C291" t="str">
         <v>S</v>
@@ -31893,11 +31893,11 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292">
-        <v>291</v>
-      </c>
-      <c r="B292">
-        <v>29</v>
+      <c r="A292" t="str">
+        <v>DRD10290</v>
+      </c>
+      <c r="B292" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C292" t="str">
         <v>S</v>
@@ -31994,11 +31994,11 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293">
-        <v>292</v>
-      </c>
-      <c r="B293">
-        <v>29</v>
+      <c r="A293" t="str">
+        <v>DRD10291</v>
+      </c>
+      <c r="B293" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C293" t="str">
         <v>S</v>
@@ -32095,11 +32095,11 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294">
-        <v>293</v>
-      </c>
-      <c r="B294">
-        <v>29</v>
+      <c r="A294" t="str">
+        <v>DRD10292</v>
+      </c>
+      <c r="B294" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C294" t="str">
         <v>S</v>
@@ -32196,11 +32196,11 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295">
-        <v>294</v>
-      </c>
-      <c r="B295">
-        <v>29</v>
+      <c r="A295" t="str">
+        <v>DRD10293</v>
+      </c>
+      <c r="B295" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C295" t="str">
         <v>S</v>
@@ -32297,11 +32297,11 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296">
-        <v>295</v>
-      </c>
-      <c r="B296">
-        <v>29</v>
+      <c r="A296" t="str">
+        <v>DRD10294</v>
+      </c>
+      <c r="B296" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C296" t="str">
         <v>S</v>
@@ -32398,11 +32398,11 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297">
-        <v>296</v>
-      </c>
-      <c r="B297">
-        <v>29</v>
+      <c r="A297" t="str">
+        <v>DRD10295</v>
+      </c>
+      <c r="B297" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C297" t="str">
         <v>S</v>
@@ -32499,11 +32499,11 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298">
-        <v>297</v>
-      </c>
-      <c r="B298">
-        <v>29</v>
+      <c r="A298" t="str">
+        <v>DRD10296</v>
+      </c>
+      <c r="B298" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C298" t="str">
         <v>S</v>
@@ -32600,11 +32600,11 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299">
-        <v>298</v>
-      </c>
-      <c r="B299">
-        <v>29</v>
+      <c r="A299" t="str">
+        <v>DRD10297</v>
+      </c>
+      <c r="B299" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C299" t="str">
         <v>C</v>
@@ -32701,11 +32701,11 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300">
-        <v>299</v>
-      </c>
-      <c r="B300">
-        <v>29</v>
+      <c r="A300" t="str">
+        <v>DRD10298</v>
+      </c>
+      <c r="B300" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C300" t="str">
         <v>C</v>
@@ -32802,11 +32802,11 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301">
-        <v>300</v>
-      </c>
-      <c r="B301">
-        <v>29</v>
+      <c r="A301" t="str">
+        <v>DRD10299</v>
+      </c>
+      <c r="B301" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C301" t="str">
         <v>C</v>
@@ -32903,11 +32903,11 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302">
-        <v>301</v>
-      </c>
-      <c r="B302">
-        <v>29</v>
+      <c r="A302" t="str">
+        <v>DRD10300</v>
+      </c>
+      <c r="B302" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C302" t="str">
         <v>C</v>
@@ -33004,11 +33004,11 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303">
-        <v>302</v>
-      </c>
-      <c r="B303">
-        <v>29</v>
+      <c r="A303" t="str">
+        <v>DRD10301</v>
+      </c>
+      <c r="B303" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C303" t="str">
         <v>C</v>
@@ -33105,11 +33105,11 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304">
-        <v>303</v>
-      </c>
-      <c r="B304">
-        <v>29</v>
+      <c r="A304" t="str">
+        <v>DRD10302</v>
+      </c>
+      <c r="B304" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C304" t="str">
         <v>C</v>
@@ -33206,11 +33206,11 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305">
-        <v>304</v>
-      </c>
-      <c r="B305">
-        <v>29</v>
+      <c r="A305" t="str">
+        <v>DRD10303</v>
+      </c>
+      <c r="B305" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C305" t="str">
         <v>C</v>
@@ -33307,11 +33307,11 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306">
-        <v>305</v>
-      </c>
-      <c r="B306">
-        <v>29</v>
+      <c r="A306" t="str">
+        <v>DRD10304</v>
+      </c>
+      <c r="B306" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C306" t="str">
         <v>C</v>
@@ -33408,11 +33408,11 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307">
-        <v>306</v>
-      </c>
-      <c r="B307">
-        <v>29</v>
+      <c r="A307" t="str">
+        <v>DRD10305</v>
+      </c>
+      <c r="B307" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C307" t="str">
         <v>C</v>
@@ -33509,11 +33509,11 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308">
-        <v>307</v>
-      </c>
-      <c r="B308">
-        <v>29</v>
+      <c r="A308" t="str">
+        <v>DRD10306</v>
+      </c>
+      <c r="B308" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C308" t="str">
         <v>C</v>
@@ -33610,11 +33610,11 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309">
-        <v>308</v>
-      </c>
-      <c r="B309">
-        <v>29</v>
+      <c r="A309" t="str">
+        <v>DRD10307</v>
+      </c>
+      <c r="B309" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C309" t="str">
         <v>C</v>
@@ -33711,11 +33711,11 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310">
-        <v>309</v>
-      </c>
-      <c r="B310">
-        <v>29</v>
+      <c r="A310" t="str">
+        <v>DRD10308</v>
+      </c>
+      <c r="B310" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C310" t="str">
         <v>C</v>
@@ -33812,11 +33812,11 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311">
-        <v>310</v>
-      </c>
-      <c r="B311">
-        <v>29</v>
+      <c r="A311" t="str">
+        <v>DRD10309</v>
+      </c>
+      <c r="B311" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C311" t="str">
         <v>C</v>
@@ -33913,11 +33913,11 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312">
-        <v>311</v>
-      </c>
-      <c r="B312">
-        <v>29</v>
+      <c r="A312" t="str">
+        <v>DRD10310</v>
+      </c>
+      <c r="B312" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C312" t="str">
         <v>C</v>
@@ -34014,11 +34014,11 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313">
-        <v>312</v>
-      </c>
-      <c r="B313">
-        <v>29</v>
+      <c r="A313" t="str">
+        <v>DRD10311</v>
+      </c>
+      <c r="B313" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C313" t="str">
         <v>C</v>
@@ -34115,11 +34115,11 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314">
-        <v>313</v>
-      </c>
-      <c r="B314">
-        <v>29</v>
+      <c r="A314" t="str">
+        <v>DRD10312</v>
+      </c>
+      <c r="B314" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C314" t="str">
         <v>S</v>
@@ -34216,11 +34216,11 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315">
-        <v>314</v>
-      </c>
-      <c r="B315">
-        <v>29</v>
+      <c r="A315" t="str">
+        <v>DRD10313</v>
+      </c>
+      <c r="B315" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C315" t="str">
         <v>S</v>
@@ -34317,11 +34317,11 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316">
-        <v>315</v>
-      </c>
-      <c r="B316">
-        <v>29</v>
+      <c r="A316" t="str">
+        <v>DRD10314</v>
+      </c>
+      <c r="B316" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C316" t="str">
         <v>S</v>
@@ -34418,11 +34418,11 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317">
-        <v>316</v>
-      </c>
-      <c r="B317">
-        <v>29</v>
+      <c r="A317" t="str">
+        <v>DRD10315</v>
+      </c>
+      <c r="B317" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C317" t="str">
         <v>S</v>
@@ -34519,11 +34519,11 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318">
-        <v>317</v>
-      </c>
-      <c r="B318">
-        <v>29</v>
+      <c r="A318" t="str">
+        <v>DRD10316</v>
+      </c>
+      <c r="B318" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C318" t="str">
         <v>S</v>
@@ -34620,11 +34620,11 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319">
-        <v>318</v>
-      </c>
-      <c r="B319">
-        <v>29</v>
+      <c r="A319" t="str">
+        <v>DRD10317</v>
+      </c>
+      <c r="B319" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C319" t="str">
         <v>S</v>
@@ -34721,11 +34721,11 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320">
-        <v>319</v>
-      </c>
-      <c r="B320">
-        <v>29</v>
+      <c r="A320" t="str">
+        <v>DRD10318</v>
+      </c>
+      <c r="B320" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C320" t="str">
         <v>S</v>
@@ -34822,11 +34822,11 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321">
-        <v>320</v>
-      </c>
-      <c r="B321">
-        <v>29</v>
+      <c r="A321" t="str">
+        <v>DRD10319</v>
+      </c>
+      <c r="B321" t="str">
+        <v>DR1028</v>
       </c>
       <c r="C321" t="str">
         <v>S</v>
@@ -34923,11 +34923,11 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322">
-        <v>321</v>
-      </c>
-      <c r="B322">
-        <v>30</v>
+      <c r="A322" t="str">
+        <v>DRD10320</v>
+      </c>
+      <c r="B322" t="str">
+        <v>DR1029</v>
       </c>
       <c r="C322" t="str">
         <v>S</v>
@@ -35024,11 +35024,11 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323">
-        <v>322</v>
-      </c>
-      <c r="B323">
-        <v>30</v>
+      <c r="A323" t="str">
+        <v>DRD10321</v>
+      </c>
+      <c r="B323" t="str">
+        <v>DR1029</v>
       </c>
       <c r="C323" t="str">
         <v>S</v>
@@ -35125,11 +35125,11 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324">
-        <v>323</v>
-      </c>
-      <c r="B324">
-        <v>30</v>
+      <c r="A324" t="str">
+        <v>DRD10322</v>
+      </c>
+      <c r="B324" t="str">
+        <v>DR1029</v>
       </c>
       <c r="C324" t="str">
         <v>S</v>
@@ -35226,11 +35226,11 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325">
-        <v>324</v>
-      </c>
-      <c r="B325">
-        <v>31</v>
+      <c r="A325" t="str">
+        <v>DRD10323</v>
+      </c>
+      <c r="B325" t="str">
+        <v>DR1030</v>
       </c>
       <c r="C325" t="str">
         <v>S</v>
@@ -35327,11 +35327,11 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326">
-        <v>325</v>
-      </c>
-      <c r="B326">
-        <v>31</v>
+      <c r="A326" t="str">
+        <v>DRD10324</v>
+      </c>
+      <c r="B326" t="str">
+        <v>DR1030</v>
       </c>
       <c r="C326" t="str">
         <v>S</v>
@@ -35428,11 +35428,11 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327">
-        <v>326</v>
-      </c>
-      <c r="B327">
-        <v>31</v>
+      <c r="A327" t="str">
+        <v>DRD10325</v>
+      </c>
+      <c r="B327" t="str">
+        <v>DR1030</v>
       </c>
       <c r="C327" t="str">
         <v>S</v>
@@ -35529,11 +35529,11 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328">
-        <v>327</v>
-      </c>
-      <c r="B328">
-        <v>31</v>
+      <c r="A328" t="str">
+        <v>DRD10326</v>
+      </c>
+      <c r="B328" t="str">
+        <v>DR1030</v>
       </c>
       <c r="C328" t="str">
         <v>S</v>
@@ -35630,11 +35630,11 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329">
-        <v>328</v>
-      </c>
-      <c r="B329">
-        <v>31</v>
+      <c r="A329" t="str">
+        <v>DRD10327</v>
+      </c>
+      <c r="B329" t="str">
+        <v>DR1030</v>
       </c>
       <c r="C329" t="str">
         <v>S</v>
@@ -35731,11 +35731,11 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330">
-        <v>329</v>
-      </c>
-      <c r="B330">
-        <v>31</v>
+      <c r="A330" t="str">
+        <v>DRD10328</v>
+      </c>
+      <c r="B330" t="str">
+        <v>DR1030</v>
       </c>
       <c r="C330" t="str">
         <v>S</v>
@@ -35832,11 +35832,11 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331">
-        <v>330</v>
-      </c>
-      <c r="B331">
-        <v>31</v>
+      <c r="A331" t="str">
+        <v>DRD10329</v>
+      </c>
+      <c r="B331" t="str">
+        <v>DR1030</v>
       </c>
       <c r="C331" t="str">
         <v>S</v>
@@ -35933,11 +35933,11 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332">
-        <v>331</v>
-      </c>
-      <c r="B332">
-        <v>31</v>
+      <c r="A332" t="str">
+        <v>DRD10330</v>
+      </c>
+      <c r="B332" t="str">
+        <v>DR1030</v>
       </c>
       <c r="C332" t="str">
         <v>C</v>
@@ -36034,11 +36034,11 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333">
-        <v>332</v>
-      </c>
-      <c r="B333">
-        <v>31</v>
+      <c r="A333" t="str">
+        <v>DRD10331</v>
+      </c>
+      <c r="B333" t="str">
+        <v>DR1030</v>
       </c>
       <c r="C333" t="str">
         <v>C</v>
@@ -36135,11 +36135,11 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334">
-        <v>333</v>
-      </c>
-      <c r="B334">
-        <v>32</v>
+      <c r="A334" t="str">
+        <v>DRD10332</v>
+      </c>
+      <c r="B334" t="str">
+        <v>DR1031</v>
       </c>
       <c r="C334" t="str">
         <v>C</v>
@@ -36236,11 +36236,11 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335">
-        <v>334</v>
-      </c>
-      <c r="B335">
-        <v>32</v>
+      <c r="A335" t="str">
+        <v>DRD10333</v>
+      </c>
+      <c r="B335" t="str">
+        <v>DR1031</v>
       </c>
       <c r="C335" t="str">
         <v>C</v>
@@ -36337,11 +36337,11 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336">
-        <v>335</v>
-      </c>
-      <c r="B336">
-        <v>32</v>
+      <c r="A336" t="str">
+        <v>DRD10334</v>
+      </c>
+      <c r="B336" t="str">
+        <v>DR1031</v>
       </c>
       <c r="C336" t="str">
         <v>C</v>
@@ -36438,11 +36438,11 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337">
-        <v>336</v>
-      </c>
-      <c r="B337">
-        <v>32</v>
+      <c r="A337" t="str">
+        <v>DRD10335</v>
+      </c>
+      <c r="B337" t="str">
+        <v>DR1031</v>
       </c>
       <c r="C337" t="str">
         <v>S</v>
@@ -36539,11 +36539,11 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338">
-        <v>337</v>
-      </c>
-      <c r="B338">
-        <v>32</v>
+      <c r="A338" t="str">
+        <v>DRD10336</v>
+      </c>
+      <c r="B338" t="str">
+        <v>DR1031</v>
       </c>
       <c r="C338" t="str">
         <v>S</v>
@@ -36640,11 +36640,11 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339">
-        <v>338</v>
-      </c>
-      <c r="B339">
-        <v>33</v>
+      <c r="A339" t="str">
+        <v>DRD10337</v>
+      </c>
+      <c r="B339" t="str">
+        <v>DR1032</v>
       </c>
       <c r="C339" t="str">
         <v>S</v>
@@ -36741,11 +36741,11 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340">
-        <v>339</v>
-      </c>
-      <c r="B340">
-        <v>33</v>
+      <c r="A340" t="str">
+        <v>DRD10338</v>
+      </c>
+      <c r="B340" t="str">
+        <v>DR1032</v>
       </c>
       <c r="C340" t="str">
         <v>S</v>
@@ -36842,11 +36842,11 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341">
-        <v>340</v>
-      </c>
-      <c r="B341">
-        <v>33</v>
+      <c r="A341" t="str">
+        <v>DRD10339</v>
+      </c>
+      <c r="B341" t="str">
+        <v>DR1032</v>
       </c>
       <c r="C341" t="str">
         <v>S</v>
@@ -36943,11 +36943,11 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342">
-        <v>341</v>
-      </c>
-      <c r="B342">
-        <v>34</v>
+      <c r="A342" t="str">
+        <v>DRD10340</v>
+      </c>
+      <c r="B342" t="str">
+        <v>DR1033</v>
       </c>
       <c r="C342" t="str">
         <v>S</v>
@@ -37044,11 +37044,11 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343">
-        <v>342</v>
-      </c>
-      <c r="B343">
-        <v>34</v>
+      <c r="A343" t="str">
+        <v>DRD10341</v>
+      </c>
+      <c r="B343" t="str">
+        <v>DR1033</v>
       </c>
       <c r="C343" t="str">
         <v>S</v>
@@ -37145,11 +37145,11 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344">
-        <v>343</v>
-      </c>
-      <c r="B344">
-        <v>34</v>
+      <c r="A344" t="str">
+        <v>DRD10342</v>
+      </c>
+      <c r="B344" t="str">
+        <v>DR1033</v>
       </c>
       <c r="C344" t="str">
         <v>S</v>
@@ -37246,11 +37246,11 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345">
-        <v>344</v>
-      </c>
-      <c r="B345">
-        <v>34</v>
+      <c r="A345" t="str">
+        <v>DRD10343</v>
+      </c>
+      <c r="B345" t="str">
+        <v>DR1033</v>
       </c>
       <c r="C345" t="str">
         <v>S</v>
@@ -37347,11 +37347,11 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346">
-        <v>345</v>
-      </c>
-      <c r="B346">
-        <v>34</v>
+      <c r="A346" t="str">
+        <v>DRD10344</v>
+      </c>
+      <c r="B346" t="str">
+        <v>DR1033</v>
       </c>
       <c r="C346" t="str">
         <v>C</v>
@@ -37448,11 +37448,11 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347">
-        <v>346</v>
-      </c>
-      <c r="B347">
-        <v>34</v>
+      <c r="A347" t="str">
+        <v>DRD10345</v>
+      </c>
+      <c r="B347" t="str">
+        <v>DR1033</v>
       </c>
       <c r="C347" t="str">
         <v>C</v>
@@ -37549,11 +37549,11 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348">
-        <v>347</v>
-      </c>
-      <c r="B348">
-        <v>34</v>
+      <c r="A348" t="str">
+        <v>DRD10346</v>
+      </c>
+      <c r="B348" t="str">
+        <v>DR1033</v>
       </c>
       <c r="C348" t="str">
         <v>C</v>
@@ -37650,11 +37650,11 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349">
-        <v>348</v>
-      </c>
-      <c r="B349">
-        <v>34</v>
+      <c r="A349" t="str">
+        <v>DRD10347</v>
+      </c>
+      <c r="B349" t="str">
+        <v>DR1033</v>
       </c>
       <c r="C349" t="str">
         <v>S</v>
@@ -37751,11 +37751,11 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350">
-        <v>349</v>
-      </c>
-      <c r="B350">
-        <v>34</v>
+      <c r="A350" t="str">
+        <v>DRD10348</v>
+      </c>
+      <c r="B350" t="str">
+        <v>DR1033</v>
       </c>
       <c r="C350" t="str">
         <v>C</v>
@@ -37852,11 +37852,11 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351">
-        <v>350</v>
-      </c>
-      <c r="B351">
-        <v>35</v>
+      <c r="A351" t="str">
+        <v>DRD10349</v>
+      </c>
+      <c r="B351" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C351" t="str">
         <v>C</v>
@@ -37953,11 +37953,11 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352">
-        <v>351</v>
-      </c>
-      <c r="B352">
-        <v>35</v>
+      <c r="A352" t="str">
+        <v>DRD10350</v>
+      </c>
+      <c r="B352" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C352" t="str">
         <v>C</v>
@@ -38054,11 +38054,11 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353">
-        <v>352</v>
-      </c>
-      <c r="B353">
-        <v>35</v>
+      <c r="A353" t="str">
+        <v>DRD10351</v>
+      </c>
+      <c r="B353" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C353" t="str">
         <v>C</v>
@@ -38155,11 +38155,11 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354">
-        <v>353</v>
-      </c>
-      <c r="B354">
-        <v>35</v>
+      <c r="A354" t="str">
+        <v>DRD10352</v>
+      </c>
+      <c r="B354" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C354" t="str">
         <v>C</v>
@@ -38256,11 +38256,11 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355">
-        <v>354</v>
-      </c>
-      <c r="B355">
-        <v>35</v>
+      <c r="A355" t="str">
+        <v>DRD10353</v>
+      </c>
+      <c r="B355" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C355" t="str">
         <v>C</v>
@@ -38357,11 +38357,11 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356">
-        <v>355</v>
-      </c>
-      <c r="B356">
-        <v>35</v>
+      <c r="A356" t="str">
+        <v>DRD10354</v>
+      </c>
+      <c r="B356" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C356" t="str">
         <v>S</v>
@@ -38458,11 +38458,11 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357">
-        <v>356</v>
-      </c>
-      <c r="B357">
-        <v>35</v>
+      <c r="A357" t="str">
+        <v>DRD10355</v>
+      </c>
+      <c r="B357" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C357" t="str">
         <v>S</v>
@@ -38559,11 +38559,11 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358">
-        <v>357</v>
-      </c>
-      <c r="B358">
-        <v>35</v>
+      <c r="A358" t="str">
+        <v>DRD10356</v>
+      </c>
+      <c r="B358" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C358" t="str">
         <v>S</v>
@@ -38660,11 +38660,11 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359">
-        <v>358</v>
-      </c>
-      <c r="B359">
-        <v>35</v>
+      <c r="A359" t="str">
+        <v>DRD10357</v>
+      </c>
+      <c r="B359" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C359" t="str">
         <v>C</v>
@@ -38761,11 +38761,11 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360">
-        <v>359</v>
-      </c>
-      <c r="B360">
-        <v>35</v>
+      <c r="A360" t="str">
+        <v>DRD10358</v>
+      </c>
+      <c r="B360" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C360" t="str">
         <v>C</v>
@@ -38862,11 +38862,11 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361">
-        <v>360</v>
-      </c>
-      <c r="B361">
-        <v>35</v>
+      <c r="A361" t="str">
+        <v>DRD10359</v>
+      </c>
+      <c r="B361" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C361" t="str">
         <v>C</v>
@@ -38963,11 +38963,11 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362">
-        <v>361</v>
-      </c>
-      <c r="B362">
-        <v>35</v>
+      <c r="A362" t="str">
+        <v>DRD10360</v>
+      </c>
+      <c r="B362" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C362" t="str">
         <v>C</v>
@@ -39064,11 +39064,11 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363">
-        <v>362</v>
-      </c>
-      <c r="B363">
-        <v>35</v>
+      <c r="A363" t="str">
+        <v>DRD10361</v>
+      </c>
+      <c r="B363" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C363" t="str">
         <v>C</v>
@@ -39165,11 +39165,11 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364">
-        <v>363</v>
-      </c>
-      <c r="B364">
-        <v>35</v>
+      <c r="A364" t="str">
+        <v>DRD10362</v>
+      </c>
+      <c r="B364" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C364" t="str">
         <v>C</v>
@@ -39266,11 +39266,11 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365">
-        <v>364</v>
-      </c>
-      <c r="B365">
-        <v>35</v>
+      <c r="A365" t="str">
+        <v>DRD10363</v>
+      </c>
+      <c r="B365" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C365" t="str">
         <v>C</v>
@@ -39367,11 +39367,11 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366">
-        <v>365</v>
-      </c>
-      <c r="B366">
-        <v>35</v>
+      <c r="A366" t="str">
+        <v>DRD10364</v>
+      </c>
+      <c r="B366" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C366" t="str">
         <v>C</v>
@@ -39468,11 +39468,11 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367">
-        <v>366</v>
-      </c>
-      <c r="B367">
-        <v>35</v>
+      <c r="A367" t="str">
+        <v>DRD10365</v>
+      </c>
+      <c r="B367" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C367" t="str">
         <v>C</v>
@@ -39569,11 +39569,11 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368">
-        <v>367</v>
-      </c>
-      <c r="B368">
-        <v>35</v>
+      <c r="A368" t="str">
+        <v>DRD10366</v>
+      </c>
+      <c r="B368" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C368" t="str">
         <v>C</v>
@@ -39670,11 +39670,11 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369">
-        <v>368</v>
-      </c>
-      <c r="B369">
-        <v>35</v>
+      <c r="A369" t="str">
+        <v>DRD10367</v>
+      </c>
+      <c r="B369" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C369" t="str">
         <v>C</v>
@@ -39771,11 +39771,11 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370">
-        <v>369</v>
-      </c>
-      <c r="B370">
-        <v>35</v>
+      <c r="A370" t="str">
+        <v>DRD10368</v>
+      </c>
+      <c r="B370" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C370" t="str">
         <v>S</v>
@@ -39872,11 +39872,11 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371">
-        <v>370</v>
-      </c>
-      <c r="B371">
-        <v>35</v>
+      <c r="A371" t="str">
+        <v>DRD10369</v>
+      </c>
+      <c r="B371" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C371" t="str">
         <v>S</v>
@@ -39973,11 +39973,11 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372">
-        <v>371</v>
-      </c>
-      <c r="B372">
-        <v>35</v>
+      <c r="A372" t="str">
+        <v>DRD10370</v>
+      </c>
+      <c r="B372" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C372" t="str">
         <v>S</v>
@@ -40074,11 +40074,11 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373">
-        <v>372</v>
-      </c>
-      <c r="B373">
-        <v>35</v>
+      <c r="A373" t="str">
+        <v>DRD10371</v>
+      </c>
+      <c r="B373" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C373" t="str">
         <v>S</v>
@@ -40175,11 +40175,11 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374">
-        <v>373</v>
-      </c>
-      <c r="B374">
-        <v>35</v>
+      <c r="A374" t="str">
+        <v>DRD10372</v>
+      </c>
+      <c r="B374" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C374" t="str">
         <v>S</v>
@@ -40276,11 +40276,11 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375">
-        <v>374</v>
-      </c>
-      <c r="B375">
-        <v>35</v>
+      <c r="A375" t="str">
+        <v>DRD10373</v>
+      </c>
+      <c r="B375" t="str">
+        <v>DR1034</v>
       </c>
       <c r="C375" t="str">
         <v>S</v>
@@ -40377,11 +40377,11 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376">
-        <v>375</v>
-      </c>
-      <c r="B376">
-        <v>36</v>
+      <c r="A376" t="str">
+        <v>DRD10374</v>
+      </c>
+      <c r="B376" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C376" t="str">
         <v>S</v>
@@ -40478,11 +40478,11 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377">
-        <v>376</v>
-      </c>
-      <c r="B377">
-        <v>36</v>
+      <c r="A377" t="str">
+        <v>DRD10375</v>
+      </c>
+      <c r="B377" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C377" t="str">
         <v>S</v>
@@ -40579,11 +40579,11 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378">
-        <v>377</v>
-      </c>
-      <c r="B378">
-        <v>36</v>
+      <c r="A378" t="str">
+        <v>DRD10376</v>
+      </c>
+      <c r="B378" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C378" t="str">
         <v>S</v>
@@ -40680,11 +40680,11 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379">
-        <v>378</v>
-      </c>
-      <c r="B379">
-        <v>36</v>
+      <c r="A379" t="str">
+        <v>DRD10377</v>
+      </c>
+      <c r="B379" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C379" t="str">
         <v>S</v>
@@ -40781,11 +40781,11 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380">
-        <v>379</v>
-      </c>
-      <c r="B380">
-        <v>36</v>
+      <c r="A380" t="str">
+        <v>DRD10378</v>
+      </c>
+      <c r="B380" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C380" t="str">
         <v>S</v>
@@ -40882,11 +40882,11 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381">
-        <v>380</v>
-      </c>
-      <c r="B381">
-        <v>36</v>
+      <c r="A381" t="str">
+        <v>DRD10379</v>
+      </c>
+      <c r="B381" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C381" t="str">
         <v>S</v>
@@ -40983,11 +40983,11 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382">
-        <v>381</v>
-      </c>
-      <c r="B382">
-        <v>36</v>
+      <c r="A382" t="str">
+        <v>DRD10380</v>
+      </c>
+      <c r="B382" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C382" t="str">
         <v>S</v>
@@ -41084,11 +41084,11 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383">
-        <v>382</v>
-      </c>
-      <c r="B383">
-        <v>36</v>
+      <c r="A383" t="str">
+        <v>DRD10381</v>
+      </c>
+      <c r="B383" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C383" t="str">
         <v>S</v>
@@ -41185,11 +41185,11 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384">
-        <v>383</v>
-      </c>
-      <c r="B384">
-        <v>36</v>
+      <c r="A384" t="str">
+        <v>DRD10382</v>
+      </c>
+      <c r="B384" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C384" t="str">
         <v>S</v>
@@ -41286,11 +41286,11 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385">
-        <v>384</v>
-      </c>
-      <c r="B385">
-        <v>36</v>
+      <c r="A385" t="str">
+        <v>DRD10383</v>
+      </c>
+      <c r="B385" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C385" t="str">
         <v>S</v>
@@ -41387,11 +41387,11 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386">
-        <v>385</v>
-      </c>
-      <c r="B386">
-        <v>36</v>
+      <c r="A386" t="str">
+        <v>DRD10384</v>
+      </c>
+      <c r="B386" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C386" t="str">
         <v>S</v>
@@ -41488,11 +41488,11 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387">
-        <v>386</v>
-      </c>
-      <c r="B387">
-        <v>36</v>
+      <c r="A387" t="str">
+        <v>DRD10385</v>
+      </c>
+      <c r="B387" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C387" t="str">
         <v>S</v>
@@ -41589,11 +41589,11 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388">
-        <v>387</v>
-      </c>
-      <c r="B388">
-        <v>36</v>
+      <c r="A388" t="str">
+        <v>DRD10386</v>
+      </c>
+      <c r="B388" t="str">
+        <v>DR1035</v>
       </c>
       <c r="C388" t="str">
         <v>S</v>
@@ -41690,11 +41690,11 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389">
-        <v>388</v>
-      </c>
-      <c r="B389">
-        <v>37</v>
+      <c r="A389" t="str">
+        <v>DRD10387</v>
+      </c>
+      <c r="B389" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C389" t="str">
         <v>S</v>
@@ -41791,11 +41791,11 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390">
-        <v>389</v>
-      </c>
-      <c r="B390">
-        <v>37</v>
+      <c r="A390" t="str">
+        <v>DRD10388</v>
+      </c>
+      <c r="B390" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C390" t="str">
         <v>S</v>
@@ -41892,11 +41892,11 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391">
-        <v>390</v>
-      </c>
-      <c r="B391">
-        <v>37</v>
+      <c r="A391" t="str">
+        <v>DRD10389</v>
+      </c>
+      <c r="B391" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C391" t="str">
         <v>S</v>
@@ -41993,11 +41993,11 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392">
-        <v>391</v>
-      </c>
-      <c r="B392">
-        <v>37</v>
+      <c r="A392" t="str">
+        <v>DRD10390</v>
+      </c>
+      <c r="B392" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C392" t="str">
         <v>S</v>
@@ -42094,11 +42094,11 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393">
-        <v>392</v>
-      </c>
-      <c r="B393">
-        <v>37</v>
+      <c r="A393" t="str">
+        <v>DRD10391</v>
+      </c>
+      <c r="B393" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C393" t="str">
         <v>S</v>
@@ -42195,11 +42195,11 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394">
-        <v>393</v>
-      </c>
-      <c r="B394">
-        <v>37</v>
+      <c r="A394" t="str">
+        <v>DRD10392</v>
+      </c>
+      <c r="B394" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C394" t="str">
         <v>S</v>
@@ -42296,11 +42296,11 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395">
-        <v>394</v>
-      </c>
-      <c r="B395">
-        <v>37</v>
+      <c r="A395" t="str">
+        <v>DRD10393</v>
+      </c>
+      <c r="B395" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C395" t="str">
         <v>S</v>
@@ -42397,11 +42397,11 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396">
-        <v>395</v>
-      </c>
-      <c r="B396">
-        <v>37</v>
+      <c r="A396" t="str">
+        <v>DRD10394</v>
+      </c>
+      <c r="B396" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C396" t="str">
         <v>C</v>
@@ -42498,11 +42498,11 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397">
-        <v>396</v>
-      </c>
-      <c r="B397">
-        <v>37</v>
+      <c r="A397" t="str">
+        <v>DRD10395</v>
+      </c>
+      <c r="B397" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C397" t="str">
         <v>C</v>
@@ -42599,11 +42599,11 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398">
-        <v>397</v>
-      </c>
-      <c r="B398">
-        <v>37</v>
+      <c r="A398" t="str">
+        <v>DRD10396</v>
+      </c>
+      <c r="B398" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C398" t="str">
         <v>C</v>
@@ -42700,11 +42700,11 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399">
-        <v>398</v>
-      </c>
-      <c r="B399">
-        <v>37</v>
+      <c r="A399" t="str">
+        <v>DRD10397</v>
+      </c>
+      <c r="B399" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C399" t="str">
         <v>S</v>
@@ -42801,11 +42801,11 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400">
-        <v>399</v>
-      </c>
-      <c r="B400">
-        <v>37</v>
+      <c r="A400" t="str">
+        <v>DRD10398</v>
+      </c>
+      <c r="B400" t="str">
+        <v>DR1036</v>
       </c>
       <c r="C400" t="str">
         <v>C</v>
@@ -42902,11 +42902,11 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401">
-        <v>400</v>
-      </c>
-      <c r="B401">
-        <v>38</v>
+      <c r="A401" t="str">
+        <v>DRD10399</v>
+      </c>
+      <c r="B401" t="str">
+        <v>DR1037</v>
       </c>
       <c r="C401" t="str">
         <v>S</v>
@@ -43003,11 +43003,11 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402">
-        <v>401</v>
-      </c>
-      <c r="B402">
-        <v>38</v>
+      <c r="A402" t="str">
+        <v>DRD10400</v>
+      </c>
+      <c r="B402" t="str">
+        <v>DR1037</v>
       </c>
       <c r="C402" t="str">
         <v>S</v>
@@ -43104,11 +43104,11 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403">
-        <v>402</v>
-      </c>
-      <c r="B403">
-        <v>38</v>
+      <c r="A403" t="str">
+        <v>DRD10401</v>
+      </c>
+      <c r="B403" t="str">
+        <v>DR1037</v>
       </c>
       <c r="C403" t="str">
         <v>S</v>
@@ -43205,11 +43205,11 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404">
-        <v>403</v>
-      </c>
-      <c r="B404">
-        <v>38</v>
+      <c r="A404" t="str">
+        <v>DRD10402</v>
+      </c>
+      <c r="B404" t="str">
+        <v>DR1037</v>
       </c>
       <c r="C404" t="str">
         <v>C</v>
@@ -43306,11 +43306,11 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405">
-        <v>404</v>
-      </c>
-      <c r="B405">
-        <v>39</v>
+      <c r="A405" t="str">
+        <v>DRD10403</v>
+      </c>
+      <c r="B405" t="str">
+        <v>DR1038</v>
       </c>
       <c r="C405" t="str">
         <v>S</v>
@@ -43407,11 +43407,11 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406">
-        <v>405</v>
-      </c>
-      <c r="B406">
-        <v>39</v>
+      <c r="A406" t="str">
+        <v>DRD10404</v>
+      </c>
+      <c r="B406" t="str">
+        <v>DR1038</v>
       </c>
       <c r="C406" t="str">
         <v>S</v>
@@ -43508,11 +43508,11 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407">
-        <v>406</v>
-      </c>
-      <c r="B407">
-        <v>39</v>
+      <c r="A407" t="str">
+        <v>DRD10405</v>
+      </c>
+      <c r="B407" t="str">
+        <v>DR1038</v>
       </c>
       <c r="C407" t="str">
         <v>S</v>
@@ -43609,11 +43609,11 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408">
-        <v>407</v>
-      </c>
-      <c r="B408">
-        <v>39</v>
+      <c r="A408" t="str">
+        <v>DRD10406</v>
+      </c>
+      <c r="B408" t="str">
+        <v>DR1038</v>
       </c>
       <c r="C408" t="str">
         <v>S</v>
@@ -43710,11 +43710,11 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409">
-        <v>408</v>
-      </c>
-      <c r="B409">
-        <v>39</v>
+      <c r="A409" t="str">
+        <v>DRD10407</v>
+      </c>
+      <c r="B409" t="str">
+        <v>DR1038</v>
       </c>
       <c r="C409" t="str">
         <v>C</v>
@@ -43811,11 +43811,11 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410">
-        <v>409</v>
-      </c>
-      <c r="B410">
-        <v>39</v>
+      <c r="A410" t="str">
+        <v>DRD10408</v>
+      </c>
+      <c r="B410" t="str">
+        <v>DR1038</v>
       </c>
       <c r="C410" t="str">
         <v>S</v>
@@ -43912,11 +43912,11 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411">
-        <v>410</v>
-      </c>
-      <c r="B411">
-        <v>39</v>
+      <c r="A411" t="str">
+        <v>DRD10409</v>
+      </c>
+      <c r="B411" t="str">
+        <v>DR1038</v>
       </c>
       <c r="C411" t="str">
         <v>S</v>
@@ -44013,11 +44013,11 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412">
-        <v>411</v>
-      </c>
-      <c r="B412">
-        <v>39</v>
+      <c r="A412" t="str">
+        <v>DRD10410</v>
+      </c>
+      <c r="B412" t="str">
+        <v>DR1038</v>
       </c>
       <c r="C412" t="str">
         <v>S</v>
@@ -44114,11 +44114,11 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413">
-        <v>412</v>
-      </c>
-      <c r="B413">
-        <v>39</v>
+      <c r="A413" t="str">
+        <v>DRD10411</v>
+      </c>
+      <c r="B413" t="str">
+        <v>DR1038</v>
       </c>
       <c r="C413" t="str">
         <v>S</v>
@@ -44215,11 +44215,11 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414">
-        <v>413</v>
-      </c>
-      <c r="B414">
-        <v>39</v>
+      <c r="A414" t="str">
+        <v>DRD10412</v>
+      </c>
+      <c r="B414" t="str">
+        <v>DR1038</v>
       </c>
       <c r="C414" t="str">
         <v>S</v>
@@ -44316,11 +44316,11 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415">
-        <v>414</v>
-      </c>
-      <c r="B415">
-        <v>40</v>
+      <c r="A415" t="str">
+        <v>DRD10413</v>
+      </c>
+      <c r="B415" t="str">
+        <v>DR1039</v>
       </c>
       <c r="C415" t="str">
         <v>C</v>
@@ -44417,11 +44417,11 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416">
-        <v>415</v>
-      </c>
-      <c r="B416">
-        <v>40</v>
+      <c r="A416" t="str">
+        <v>DRD10414</v>
+      </c>
+      <c r="B416" t="str">
+        <v>DR1039</v>
       </c>
       <c r="C416" t="str">
         <v>C</v>
@@ -44518,11 +44518,11 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417">
-        <v>416</v>
-      </c>
-      <c r="B417">
-        <v>41</v>
+      <c r="A417" t="str">
+        <v>DRD10415</v>
+      </c>
+      <c r="B417" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C417" t="str">
         <v>S</v>
@@ -44619,11 +44619,11 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418">
-        <v>417</v>
-      </c>
-      <c r="B418">
-        <v>41</v>
+      <c r="A418" t="str">
+        <v>DRD10416</v>
+      </c>
+      <c r="B418" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C418" t="str">
         <v>S</v>
@@ -44720,11 +44720,11 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419">
-        <v>418</v>
-      </c>
-      <c r="B419">
-        <v>41</v>
+      <c r="A419" t="str">
+        <v>DRD10417</v>
+      </c>
+      <c r="B419" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C419" t="str">
         <v>S</v>
@@ -44821,11 +44821,11 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420">
-        <v>419</v>
-      </c>
-      <c r="B420">
-        <v>41</v>
+      <c r="A420" t="str">
+        <v>DRD10418</v>
+      </c>
+      <c r="B420" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C420" t="str">
         <v>S</v>
@@ -44922,11 +44922,11 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421">
-        <v>420</v>
-      </c>
-      <c r="B421">
-        <v>41</v>
+      <c r="A421" t="str">
+        <v>DRD10419</v>
+      </c>
+      <c r="B421" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C421" t="str">
         <v>S</v>
@@ -45023,11 +45023,11 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422">
-        <v>421</v>
-      </c>
-      <c r="B422">
-        <v>41</v>
+      <c r="A422" t="str">
+        <v>DRD10420</v>
+      </c>
+      <c r="B422" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C422" t="str">
         <v>S</v>
@@ -45124,11 +45124,11 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423">
-        <v>422</v>
-      </c>
-      <c r="B423">
-        <v>41</v>
+      <c r="A423" t="str">
+        <v>DRD10421</v>
+      </c>
+      <c r="B423" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C423" t="str">
         <v>S</v>
@@ -45225,11 +45225,11 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424">
-        <v>423</v>
-      </c>
-      <c r="B424">
-        <v>41</v>
+      <c r="A424" t="str">
+        <v>DRD10422</v>
+      </c>
+      <c r="B424" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C424" t="str">
         <v>C</v>
@@ -45326,11 +45326,11 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425">
-        <v>424</v>
-      </c>
-      <c r="B425">
-        <v>41</v>
+      <c r="A425" t="str">
+        <v>DRD10423</v>
+      </c>
+      <c r="B425" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C425" t="str">
         <v>C</v>
@@ -45427,11 +45427,11 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426">
-        <v>425</v>
-      </c>
-      <c r="B426">
-        <v>41</v>
+      <c r="A426" t="str">
+        <v>DRD10424</v>
+      </c>
+      <c r="B426" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C426" t="str">
         <v>C</v>
@@ -45528,11 +45528,11 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427">
-        <v>426</v>
-      </c>
-      <c r="B427">
-        <v>41</v>
+      <c r="A427" t="str">
+        <v>DRD10425</v>
+      </c>
+      <c r="B427" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C427" t="str">
         <v>S</v>
@@ -45629,11 +45629,11 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428">
-        <v>427</v>
-      </c>
-      <c r="B428">
-        <v>41</v>
+      <c r="A428" t="str">
+        <v>DRD10426</v>
+      </c>
+      <c r="B428" t="str">
+        <v>DR1040</v>
       </c>
       <c r="C428" t="str">
         <v>C</v>
@@ -45730,11 +45730,11 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429">
-        <v>428</v>
-      </c>
-      <c r="B429">
-        <v>42</v>
+      <c r="A429" t="str">
+        <v>DRD10427</v>
+      </c>
+      <c r="B429" t="str">
+        <v>DR1041</v>
       </c>
       <c r="C429" t="str">
         <v>S</v>
@@ -45831,11 +45831,11 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430">
-        <v>429</v>
-      </c>
-      <c r="B430">
-        <v>42</v>
+      <c r="A430" t="str">
+        <v>DRD10428</v>
+      </c>
+      <c r="B430" t="str">
+        <v>DR1041</v>
       </c>
       <c r="C430" t="str">
         <v>S</v>
@@ -45932,11 +45932,11 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431">
-        <v>430</v>
-      </c>
-      <c r="B431">
-        <v>42</v>
+      <c r="A431" t="str">
+        <v>DRD10429</v>
+      </c>
+      <c r="B431" t="str">
+        <v>DR1041</v>
       </c>
       <c r="C431" t="str">
         <v>S</v>
@@ -46033,11 +46033,11 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432">
-        <v>431</v>
-      </c>
-      <c r="B432">
-        <v>42</v>
+      <c r="A432" t="str">
+        <v>DRD10430</v>
+      </c>
+      <c r="B432" t="str">
+        <v>DR1041</v>
       </c>
       <c r="C432" t="str">
         <v>S</v>
@@ -46134,11 +46134,11 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433">
-        <v>432</v>
-      </c>
-      <c r="B433">
-        <v>42</v>
+      <c r="A433" t="str">
+        <v>DRD10431</v>
+      </c>
+      <c r="B433" t="str">
+        <v>DR1041</v>
       </c>
       <c r="C433" t="str">
         <v>S</v>
@@ -46235,11 +46235,11 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434">
-        <v>433</v>
-      </c>
-      <c r="B434">
-        <v>42</v>
+      <c r="A434" t="str">
+        <v>DRD10432</v>
+      </c>
+      <c r="B434" t="str">
+        <v>DR1041</v>
       </c>
       <c r="C434" t="str">
         <v>S</v>
@@ -46336,11 +46336,11 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435">
-        <v>434</v>
-      </c>
-      <c r="B435">
-        <v>43</v>
+      <c r="A435" t="str">
+        <v>DRD10433</v>
+      </c>
+      <c r="B435" t="str">
+        <v>DR1042</v>
       </c>
       <c r="C435" t="str">
         <v>S</v>
@@ -46437,11 +46437,11 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436">
-        <v>435</v>
-      </c>
-      <c r="B436">
-        <v>43</v>
+      <c r="A436" t="str">
+        <v>DRD10434</v>
+      </c>
+      <c r="B436" t="str">
+        <v>DR1042</v>
       </c>
       <c r="C436" t="str">
         <v>S</v>
@@ -46538,11 +46538,11 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437">
-        <v>436</v>
-      </c>
-      <c r="B437">
-        <v>43</v>
+      <c r="A437" t="str">
+        <v>DRD10435</v>
+      </c>
+      <c r="B437" t="str">
+        <v>DR1042</v>
       </c>
       <c r="C437" t="str">
         <v>S</v>
@@ -46639,11 +46639,11 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438">
-        <v>437</v>
-      </c>
-      <c r="B438">
-        <v>43</v>
+      <c r="A438" t="str">
+        <v>DRD10436</v>
+      </c>
+      <c r="B438" t="str">
+        <v>DR1042</v>
       </c>
       <c r="C438" t="str">
         <v>S</v>
@@ -46740,11 +46740,11 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439">
-        <v>438</v>
-      </c>
-      <c r="B439">
-        <v>43</v>
+      <c r="A439" t="str">
+        <v>DRD10437</v>
+      </c>
+      <c r="B439" t="str">
+        <v>DR1042</v>
       </c>
       <c r="C439" t="str">
         <v>S</v>
@@ -46841,11 +46841,11 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440">
-        <v>439</v>
-      </c>
-      <c r="B440">
-        <v>43</v>
+      <c r="A440" t="str">
+        <v>DRD10438</v>
+      </c>
+      <c r="B440" t="str">
+        <v>DR1042</v>
       </c>
       <c r="C440" t="str">
         <v>S</v>
@@ -46942,11 +46942,11 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441">
-        <v>440</v>
-      </c>
-      <c r="B441">
-        <v>43</v>
+      <c r="A441" t="str">
+        <v>DRD10439</v>
+      </c>
+      <c r="B441" t="str">
+        <v>DR1042</v>
       </c>
       <c r="C441" t="str">
         <v>S</v>
@@ -47043,11 +47043,11 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442">
-        <v>441</v>
-      </c>
-      <c r="B442">
-        <v>43</v>
+      <c r="A442" t="str">
+        <v>DRD10440</v>
+      </c>
+      <c r="B442" t="str">
+        <v>DR1042</v>
       </c>
       <c r="C442" t="str">
         <v>S</v>
@@ -47144,11 +47144,11 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443">
-        <v>442</v>
-      </c>
-      <c r="B443">
-        <v>43</v>
+      <c r="A443" t="str">
+        <v>DRD10441</v>
+      </c>
+      <c r="B443" t="str">
+        <v>DR1042</v>
       </c>
       <c r="C443" t="str">
         <v>S</v>
@@ -47245,11 +47245,11 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444">
-        <v>443</v>
-      </c>
-      <c r="B444">
-        <v>43</v>
+      <c r="A444" t="str">
+        <v>DRD10442</v>
+      </c>
+      <c r="B444" t="str">
+        <v>DR1042</v>
       </c>
       <c r="C444" t="str">
         <v>S</v>
@@ -47346,11 +47346,11 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445">
-        <v>444</v>
-      </c>
-      <c r="B445">
-        <v>44</v>
+      <c r="A445" t="str">
+        <v>DRD10443</v>
+      </c>
+      <c r="B445" t="str">
+        <v>DR1043</v>
       </c>
       <c r="C445" t="str">
         <v>S</v>
@@ -47447,11 +47447,11 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446">
-        <v>445</v>
-      </c>
-      <c r="B446">
-        <v>44</v>
+      <c r="A446" t="str">
+        <v>DRD10444</v>
+      </c>
+      <c r="B446" t="str">
+        <v>DR1043</v>
       </c>
       <c r="C446" t="str">
         <v>S</v>
@@ -47548,11 +47548,11 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447">
-        <v>446</v>
-      </c>
-      <c r="B447">
-        <v>44</v>
+      <c r="A447" t="str">
+        <v>DRD10445</v>
+      </c>
+      <c r="B447" t="str">
+        <v>DR1043</v>
       </c>
       <c r="C447" t="str">
         <v>S</v>
@@ -47649,11 +47649,11 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448">
-        <v>447</v>
-      </c>
-      <c r="B448">
-        <v>44</v>
+      <c r="A448" t="str">
+        <v>DRD10446</v>
+      </c>
+      <c r="B448" t="str">
+        <v>DR1043</v>
       </c>
       <c r="C448" t="str">
         <v>S</v>
@@ -47750,11 +47750,11 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449">
-        <v>448</v>
-      </c>
-      <c r="B449">
-        <v>44</v>
+      <c r="A449" t="str">
+        <v>DRD10447</v>
+      </c>
+      <c r="B449" t="str">
+        <v>DR1043</v>
       </c>
       <c r="C449" t="str">
         <v>S</v>
@@ -47851,11 +47851,11 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450">
-        <v>449</v>
-      </c>
-      <c r="B450">
-        <v>44</v>
+      <c r="A450" t="str">
+        <v>DRD10448</v>
+      </c>
+      <c r="B450" t="str">
+        <v>DR1043</v>
       </c>
       <c r="C450" t="str">
         <v>C</v>
@@ -47952,11 +47952,11 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451">
-        <v>450</v>
-      </c>
-      <c r="B451">
-        <v>44</v>
+      <c r="A451" t="str">
+        <v>DRD10449</v>
+      </c>
+      <c r="B451" t="str">
+        <v>DR1043</v>
       </c>
       <c r="C451" t="str">
         <v>C</v>
@@ -48053,11 +48053,11 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452">
-        <v>451</v>
-      </c>
-      <c r="B452">
-        <v>45</v>
+      <c r="A452" t="str">
+        <v>DRD10450</v>
+      </c>
+      <c r="B452" t="str">
+        <v>DR1044</v>
       </c>
       <c r="C452" t="str">
         <v>S</v>
@@ -48154,11 +48154,11 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453">
-        <v>452</v>
-      </c>
-      <c r="B453">
-        <v>45</v>
+      <c r="A453" t="str">
+        <v>DRD10451</v>
+      </c>
+      <c r="B453" t="str">
+        <v>DR1044</v>
       </c>
       <c r="C453" t="str">
         <v>S</v>
@@ -48255,11 +48255,11 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454">
-        <v>453</v>
-      </c>
-      <c r="B454">
-        <v>45</v>
+      <c r="A454" t="str">
+        <v>DRD10452</v>
+      </c>
+      <c r="B454" t="str">
+        <v>DR1044</v>
       </c>
       <c r="C454" t="str">
         <v>S</v>
@@ -48356,11 +48356,11 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455">
-        <v>454</v>
-      </c>
-      <c r="B455">
-        <v>46</v>
+      <c r="A455" t="str">
+        <v>DRD10453</v>
+      </c>
+      <c r="B455" t="str">
+        <v>DR1045</v>
       </c>
       <c r="C455" t="str">
         <v>S</v>
@@ -48457,11 +48457,11 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456">
-        <v>455</v>
-      </c>
-      <c r="B456">
-        <v>46</v>
+      <c r="A456" t="str">
+        <v>DRD10454</v>
+      </c>
+      <c r="B456" t="str">
+        <v>DR1045</v>
       </c>
       <c r="C456" t="str">
         <v>S</v>
@@ -48558,11 +48558,11 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457">
-        <v>456</v>
-      </c>
-      <c r="B457">
-        <v>46</v>
+      <c r="A457" t="str">
+        <v>DRD10455</v>
+      </c>
+      <c r="B457" t="str">
+        <v>DR1045</v>
       </c>
       <c r="C457" t="str">
         <v>S</v>
@@ -48659,11 +48659,11 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458">
-        <v>457</v>
-      </c>
-      <c r="B458">
-        <v>47</v>
+      <c r="A458" t="str">
+        <v>DRD10456</v>
+      </c>
+      <c r="B458" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C458" t="str">
         <v>S</v>
@@ -48760,11 +48760,11 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459">
-        <v>458</v>
-      </c>
-      <c r="B459">
-        <v>47</v>
+      <c r="A459" t="str">
+        <v>DRD10457</v>
+      </c>
+      <c r="B459" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C459" t="str">
         <v>S</v>
@@ -48861,11 +48861,11 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460">
-        <v>459</v>
-      </c>
-      <c r="B460">
-        <v>47</v>
+      <c r="A460" t="str">
+        <v>DRD10458</v>
+      </c>
+      <c r="B460" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C460" t="str">
         <v>S</v>
@@ -48962,11 +48962,11 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461">
-        <v>460</v>
-      </c>
-      <c r="B461">
-        <v>47</v>
+      <c r="A461" t="str">
+        <v>DRD10459</v>
+      </c>
+      <c r="B461" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C461" t="str">
         <v>S</v>
@@ -49063,11 +49063,11 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462">
-        <v>461</v>
-      </c>
-      <c r="B462">
-        <v>47</v>
+      <c r="A462" t="str">
+        <v>DRD10460</v>
+      </c>
+      <c r="B462" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C462" t="str">
         <v>S</v>
@@ -49164,11 +49164,11 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463">
-        <v>462</v>
-      </c>
-      <c r="B463">
-        <v>47</v>
+      <c r="A463" t="str">
+        <v>DRD10461</v>
+      </c>
+      <c r="B463" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C463" t="str">
         <v>S</v>
@@ -49265,11 +49265,11 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464">
-        <v>463</v>
-      </c>
-      <c r="B464">
-        <v>47</v>
+      <c r="A464" t="str">
+        <v>DRD10462</v>
+      </c>
+      <c r="B464" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C464" t="str">
         <v>S</v>
@@ -49366,11 +49366,11 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465">
-        <v>464</v>
-      </c>
-      <c r="B465">
-        <v>47</v>
+      <c r="A465" t="str">
+        <v>DRD10463</v>
+      </c>
+      <c r="B465" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C465" t="str">
         <v>S</v>
@@ -49467,11 +49467,11 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466">
-        <v>465</v>
-      </c>
-      <c r="B466">
-        <v>47</v>
+      <c r="A466" t="str">
+        <v>DRD10464</v>
+      </c>
+      <c r="B466" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C466" t="str">
         <v>S</v>
@@ -49568,11 +49568,11 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467">
-        <v>466</v>
-      </c>
-      <c r="B467">
-        <v>47</v>
+      <c r="A467" t="str">
+        <v>DRD10465</v>
+      </c>
+      <c r="B467" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C467" t="str">
         <v>S</v>
@@ -49669,11 +49669,11 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468">
-        <v>467</v>
-      </c>
-      <c r="B468">
-        <v>47</v>
+      <c r="A468" t="str">
+        <v>DRD10466</v>
+      </c>
+      <c r="B468" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C468" t="str">
         <v>C</v>
@@ -49770,11 +49770,11 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469">
-        <v>468</v>
-      </c>
-      <c r="B469">
-        <v>47</v>
+      <c r="A469" t="str">
+        <v>DRD10467</v>
+      </c>
+      <c r="B469" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C469" t="str">
         <v>C</v>
@@ -49871,11 +49871,11 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470">
-        <v>469</v>
-      </c>
-      <c r="B470">
-        <v>47</v>
+      <c r="A470" t="str">
+        <v>DRD10468</v>
+      </c>
+      <c r="B470" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C470" t="str">
         <v>C</v>
@@ -49972,11 +49972,11 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471">
-        <v>470</v>
-      </c>
-      <c r="B471">
-        <v>47</v>
+      <c r="A471" t="str">
+        <v>DRD10469</v>
+      </c>
+      <c r="B471" t="str">
+        <v>DR1046</v>
       </c>
       <c r="C471" t="str">
         <v>C</v>
@@ -50073,11 +50073,11 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472">
-        <v>471</v>
-      </c>
-      <c r="B472">
-        <v>48</v>
+      <c r="A472" t="str">
+        <v>DRD10470</v>
+      </c>
+      <c r="B472" t="str">
+        <v>DR1047</v>
       </c>
       <c r="C472" t="str">
         <v>S</v>
@@ -50174,11 +50174,11 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473">
-        <v>472</v>
-      </c>
-      <c r="B473">
-        <v>48</v>
+      <c r="A473" t="str">
+        <v>DRD10471</v>
+      </c>
+      <c r="B473" t="str">
+        <v>DR1047</v>
       </c>
       <c r="C473" t="str">
         <v>S</v>
@@ -50275,11 +50275,11 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474">
-        <v>473</v>
-      </c>
-      <c r="B474">
-        <v>48</v>
+      <c r="A474" t="str">
+        <v>DRD10472</v>
+      </c>
+      <c r="B474" t="str">
+        <v>DR1047</v>
       </c>
       <c r="C474" t="str">
         <v>S</v>
@@ -50376,11 +50376,11 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475">
-        <v>474</v>
-      </c>
-      <c r="B475">
-        <v>48</v>
+      <c r="A475" t="str">
+        <v>DRD10473</v>
+      </c>
+      <c r="B475" t="str">
+        <v>DR1047</v>
       </c>
       <c r="C475" t="str">
         <v>S</v>
@@ -50477,11 +50477,11 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476">
-        <v>475</v>
-      </c>
-      <c r="B476">
-        <v>48</v>
+      <c r="A476" t="str">
+        <v>DRD10474</v>
+      </c>
+      <c r="B476" t="str">
+        <v>DR1047</v>
       </c>
       <c r="C476" t="str">
         <v>S</v>
@@ -50578,11 +50578,11 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477">
-        <v>476</v>
-      </c>
-      <c r="B477">
-        <v>48</v>
+      <c r="A477" t="str">
+        <v>DRD10475</v>
+      </c>
+      <c r="B477" t="str">
+        <v>DR1047</v>
       </c>
       <c r="C477" t="str">
         <v>S</v>
@@ -50679,11 +50679,11 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478">
-        <v>477</v>
-      </c>
-      <c r="B478">
-        <v>48</v>
+      <c r="A478" t="str">
+        <v>DRD10476</v>
+      </c>
+      <c r="B478" t="str">
+        <v>DR1047</v>
       </c>
       <c r="C478" t="str">
         <v>S</v>
@@ -50780,11 +50780,11 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479">
-        <v>478</v>
-      </c>
-      <c r="B479">
-        <v>48</v>
+      <c r="A479" t="str">
+        <v>DRD10477</v>
+      </c>
+      <c r="B479" t="str">
+        <v>DR1047</v>
       </c>
       <c r="C479" t="str">
         <v>S</v>
@@ -50881,11 +50881,11 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480">
-        <v>479</v>
-      </c>
-      <c r="B480">
-        <v>48</v>
+      <c r="A480" t="str">
+        <v>DRD10478</v>
+      </c>
+      <c r="B480" t="str">
+        <v>DR1047</v>
       </c>
       <c r="C480" t="str">
         <v>S</v>
@@ -50982,11 +50982,11 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481">
-        <v>480</v>
-      </c>
-      <c r="B481">
-        <v>48</v>
+      <c r="A481" t="str">
+        <v>DRD10479</v>
+      </c>
+      <c r="B481" t="str">
+        <v>DR1047</v>
       </c>
       <c r="C481" t="str">
         <v>S</v>
@@ -51083,11 +51083,11 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482">
-        <v>481</v>
-      </c>
-      <c r="B482">
-        <v>49</v>
+      <c r="A482" t="str">
+        <v>DRD10480</v>
+      </c>
+      <c r="B482" t="str">
+        <v>DR1048</v>
       </c>
       <c r="C482" t="str">
         <v>S</v>
@@ -51184,11 +51184,11 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483">
-        <v>482</v>
-      </c>
-      <c r="B483">
-        <v>49</v>
+      <c r="A483" t="str">
+        <v>DRD10481</v>
+      </c>
+      <c r="B483" t="str">
+        <v>DR1048</v>
       </c>
       <c r="C483" t="str">
         <v>S</v>
@@ -51285,11 +51285,11 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484">
-        <v>483</v>
-      </c>
-      <c r="B484">
-        <v>49</v>
+      <c r="A484" t="str">
+        <v>DRD10482</v>
+      </c>
+      <c r="B484" t="str">
+        <v>DR1048</v>
       </c>
       <c r="C484" t="str">
         <v>S</v>
@@ -51386,11 +51386,11 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485">
-        <v>484</v>
-      </c>
-      <c r="B485">
-        <v>49</v>
+      <c r="A485" t="str">
+        <v>DRD10483</v>
+      </c>
+      <c r="B485" t="str">
+        <v>DR1048</v>
       </c>
       <c r="C485" t="str">
         <v>S</v>
@@ -51487,11 +51487,11 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486">
-        <v>485</v>
-      </c>
-      <c r="B486">
-        <v>49</v>
+      <c r="A486" t="str">
+        <v>DRD10484</v>
+      </c>
+      <c r="B486" t="str">
+        <v>DR1048</v>
       </c>
       <c r="C486" t="str">
         <v>S</v>
@@ -51588,11 +51588,11 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487">
-        <v>486</v>
-      </c>
-      <c r="B487">
-        <v>49</v>
+      <c r="A487" t="str">
+        <v>DRD10485</v>
+      </c>
+      <c r="B487" t="str">
+        <v>DR1048</v>
       </c>
       <c r="C487" t="str">
         <v>S</v>
@@ -51689,11 +51689,11 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488">
-        <v>487</v>
-      </c>
-      <c r="B488">
-        <v>49</v>
+      <c r="A488" t="str">
+        <v>DRD10486</v>
+      </c>
+      <c r="B488" t="str">
+        <v>DR1048</v>
       </c>
       <c r="C488" t="str">
         <v>S</v>
@@ -51790,11 +51790,11 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489">
-        <v>488</v>
-      </c>
-      <c r="B489">
-        <v>50</v>
+      <c r="A489" t="str">
+        <v>DRD10487</v>
+      </c>
+      <c r="B489" t="str">
+        <v>DR1049</v>
       </c>
       <c r="C489" t="str">
         <v>S</v>
@@ -51891,11 +51891,11 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490">
-        <v>489</v>
-      </c>
-      <c r="B490">
-        <v>50</v>
+      <c r="A490" t="str">
+        <v>DRD10488</v>
+      </c>
+      <c r="B490" t="str">
+        <v>DR1049</v>
       </c>
       <c r="C490" t="str">
         <v>S</v>
@@ -51992,11 +51992,11 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491">
-        <v>490</v>
-      </c>
-      <c r="B491">
-        <v>50</v>
+      <c r="A491" t="str">
+        <v>DRD10489</v>
+      </c>
+      <c r="B491" t="str">
+        <v>DR1049</v>
       </c>
       <c r="C491" t="str">
         <v>S</v>
@@ -52093,11 +52093,11 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492">
-        <v>491</v>
-      </c>
-      <c r="B492">
-        <v>50</v>
+      <c r="A492" t="str">
+        <v>DRD10490</v>
+      </c>
+      <c r="B492" t="str">
+        <v>DR1049</v>
       </c>
       <c r="C492" t="str">
         <v>S</v>
@@ -52194,11 +52194,11 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493">
-        <v>492</v>
-      </c>
-      <c r="B493">
-        <v>50</v>
+      <c r="A493" t="str">
+        <v>DRD10491</v>
+      </c>
+      <c r="B493" t="str">
+        <v>DR1049</v>
       </c>
       <c r="C493" t="str">
         <v>S</v>
@@ -52295,11 +52295,11 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494">
-        <v>493</v>
-      </c>
-      <c r="B494">
-        <v>50</v>
+      <c r="A494" t="str">
+        <v>DRD10492</v>
+      </c>
+      <c r="B494" t="str">
+        <v>DR1049</v>
       </c>
       <c r="C494" t="str">
         <v>S</v>
@@ -52396,11 +52396,11 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495">
-        <v>494</v>
-      </c>
-      <c r="B495">
-        <v>50</v>
+      <c r="A495" t="str">
+        <v>DRD10493</v>
+      </c>
+      <c r="B495" t="str">
+        <v>DR1049</v>
       </c>
       <c r="C495" t="str">
         <v>S</v>
@@ -52497,11 +52497,11 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496">
-        <v>495</v>
-      </c>
-      <c r="B496">
-        <v>50</v>
+      <c r="A496" t="str">
+        <v>DRD10494</v>
+      </c>
+      <c r="B496" t="str">
+        <v>DR1049</v>
       </c>
       <c r="C496" t="str">
         <v>S</v>
@@ -52598,11 +52598,11 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497">
-        <v>496</v>
-      </c>
-      <c r="B497">
-        <v>50</v>
+      <c r="A497" t="str">
+        <v>DRD10495</v>
+      </c>
+      <c r="B497" t="str">
+        <v>DR1049</v>
       </c>
       <c r="C497" t="str">
         <v>C</v>
@@ -52699,11 +52699,11 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498">
-        <v>497</v>
-      </c>
-      <c r="B498">
-        <v>50</v>
+      <c r="A498" t="str">
+        <v>DRD10496</v>
+      </c>
+      <c r="B498" t="str">
+        <v>DR1049</v>
       </c>
       <c r="C498" t="str">
         <v>C</v>
@@ -52800,11 +52800,11 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499">
-        <v>498</v>
-      </c>
-      <c r="B499">
-        <v>51</v>
+      <c r="A499" t="str">
+        <v>DRD10497</v>
+      </c>
+      <c r="B499" t="str">
+        <v>DR1050</v>
       </c>
       <c r="C499" t="str">
         <v>S</v>
@@ -52901,11 +52901,11 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500">
-        <v>499</v>
-      </c>
-      <c r="B500">
-        <v>51</v>
+      <c r="A500" t="str">
+        <v>DRD10498</v>
+      </c>
+      <c r="B500" t="str">
+        <v>DR1050</v>
       </c>
       <c r="C500" t="str">
         <v>S</v>
@@ -53002,11 +53002,11 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501">
-        <v>500</v>
-      </c>
-      <c r="B501">
-        <v>51</v>
+      <c r="A501" t="str">
+        <v>DRD10499</v>
+      </c>
+      <c r="B501" t="str">
+        <v>DR1050</v>
       </c>
       <c r="C501" t="str">
         <v>C</v>
@@ -53103,11 +53103,11 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502">
-        <v>501</v>
-      </c>
-      <c r="B502">
-        <v>52</v>
+      <c r="A502" t="str">
+        <v>DRD10500</v>
+      </c>
+      <c r="B502" t="str">
+        <v>DR1051</v>
       </c>
       <c r="C502" t="str">
         <v>S</v>
@@ -53204,11 +53204,11 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503">
-        <v>502</v>
-      </c>
-      <c r="B503">
-        <v>52</v>
+      <c r="A503" t="str">
+        <v>DRD10501</v>
+      </c>
+      <c r="B503" t="str">
+        <v>DR1051</v>
       </c>
       <c r="C503" t="str">
         <v>S</v>
@@ -53305,11 +53305,11 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504">
-        <v>503</v>
-      </c>
-      <c r="B504">
-        <v>52</v>
+      <c r="A504" t="str">
+        <v>DRD10502</v>
+      </c>
+      <c r="B504" t="str">
+        <v>DR1051</v>
       </c>
       <c r="C504" t="str">
         <v>S</v>
@@ -53406,11 +53406,11 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505">
-        <v>504</v>
-      </c>
-      <c r="B505">
-        <v>52</v>
+      <c r="A505" t="str">
+        <v>DRD10503</v>
+      </c>
+      <c r="B505" t="str">
+        <v>DR1051</v>
       </c>
       <c r="C505" t="str">
         <v>S</v>
@@ -53507,11 +53507,11 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506">
-        <v>505</v>
-      </c>
-      <c r="B506">
-        <v>52</v>
+      <c r="A506" t="str">
+        <v>DRD10504</v>
+      </c>
+      <c r="B506" t="str">
+        <v>DR1051</v>
       </c>
       <c r="C506" t="str">
         <v>S</v>
@@ -53608,11 +53608,11 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507">
-        <v>506</v>
-      </c>
-      <c r="B507">
-        <v>52</v>
+      <c r="A507" t="str">
+        <v>DRD10505</v>
+      </c>
+      <c r="B507" t="str">
+        <v>DR1051</v>
       </c>
       <c r="C507" t="str">
         <v>S</v>
@@ -53709,11 +53709,11 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508">
-        <v>507</v>
-      </c>
-      <c r="B508">
-        <v>53</v>
+      <c r="A508" t="str">
+        <v>DRD10506</v>
+      </c>
+      <c r="B508" t="str">
+        <v>DR1052</v>
       </c>
       <c r="C508" t="str">
         <v>S</v>
@@ -53810,11 +53810,11 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509">
-        <v>508</v>
-      </c>
-      <c r="B509">
-        <v>53</v>
+      <c r="A509" t="str">
+        <v>DRD10507</v>
+      </c>
+      <c r="B509" t="str">
+        <v>DR1052</v>
       </c>
       <c r="C509" t="str">
         <v>S</v>
@@ -53911,11 +53911,11 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510">
-        <v>509</v>
-      </c>
-      <c r="B510">
-        <v>53</v>
+      <c r="A510" t="str">
+        <v>DRD10508</v>
+      </c>
+      <c r="B510" t="str">
+        <v>DR1052</v>
       </c>
       <c r="C510" t="str">
         <v>S</v>
@@ -54012,11 +54012,11 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511">
-        <v>510</v>
-      </c>
-      <c r="B511">
-        <v>53</v>
+      <c r="A511" t="str">
+        <v>DRD10509</v>
+      </c>
+      <c r="B511" t="str">
+        <v>DR1052</v>
       </c>
       <c r="C511" t="str">
         <v>S</v>
@@ -54113,11 +54113,11 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512">
-        <v>511</v>
-      </c>
-      <c r="B512">
-        <v>53</v>
+      <c r="A512" t="str">
+        <v>DRD10510</v>
+      </c>
+      <c r="B512" t="str">
+        <v>DR1052</v>
       </c>
       <c r="C512" t="str">
         <v>S</v>
@@ -54214,11 +54214,11 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513">
-        <v>512</v>
-      </c>
-      <c r="B513">
-        <v>53</v>
+      <c r="A513" t="str">
+        <v>DRD10511</v>
+      </c>
+      <c r="B513" t="str">
+        <v>DR1052</v>
       </c>
       <c r="C513" t="str">
         <v>S</v>
@@ -54315,11 +54315,11 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514">
-        <v>513</v>
-      </c>
-      <c r="B514">
-        <v>53</v>
+      <c r="A514" t="str">
+        <v>DRD10512</v>
+      </c>
+      <c r="B514" t="str">
+        <v>DR1052</v>
       </c>
       <c r="C514" t="str">
         <v>C</v>
@@ -54416,11 +54416,11 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515">
-        <v>514</v>
-      </c>
-      <c r="B515">
-        <v>53</v>
+      <c r="A515" t="str">
+        <v>DRD10513</v>
+      </c>
+      <c r="B515" t="str">
+        <v>DR1052</v>
       </c>
       <c r="C515" t="str">
         <v>C</v>
@@ -54517,11 +54517,11 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516">
-        <v>515</v>
-      </c>
-      <c r="B516">
-        <v>54</v>
+      <c r="A516" t="str">
+        <v>DRD10514</v>
+      </c>
+      <c r="B516" t="str">
+        <v>DR1053</v>
       </c>
       <c r="C516" t="str">
         <v>S</v>
@@ -54618,11 +54618,11 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517">
-        <v>516</v>
-      </c>
-      <c r="B517">
-        <v>54</v>
+      <c r="A517" t="str">
+        <v>DRD10515</v>
+      </c>
+      <c r="B517" t="str">
+        <v>DR1053</v>
       </c>
       <c r="C517" t="str">
         <v>S</v>
@@ -54719,11 +54719,11 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518">
-        <v>517</v>
-      </c>
-      <c r="B518">
-        <v>54</v>
+      <c r="A518" t="str">
+        <v>DRD10516</v>
+      </c>
+      <c r="B518" t="str">
+        <v>DR1053</v>
       </c>
       <c r="C518" t="str">
         <v>S</v>
@@ -54820,11 +54820,11 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519">
-        <v>518</v>
-      </c>
-      <c r="B519">
-        <v>55</v>
+      <c r="A519" t="str">
+        <v>DRD10517</v>
+      </c>
+      <c r="B519" t="str">
+        <v>DR1054</v>
       </c>
       <c r="C519" t="str">
         <v>S</v>
@@ -54921,11 +54921,11 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520">
-        <v>519</v>
-      </c>
-      <c r="B520">
-        <v>55</v>
+      <c r="A520" t="str">
+        <v>DRD10518</v>
+      </c>
+      <c r="B520" t="str">
+        <v>DR1054</v>
       </c>
       <c r="C520" t="str">
         <v>S</v>
@@ -55022,11 +55022,11 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521">
-        <v>520</v>
-      </c>
-      <c r="B521">
-        <v>55</v>
+      <c r="A521" t="str">
+        <v>DRD10519</v>
+      </c>
+      <c r="B521" t="str">
+        <v>DR1054</v>
       </c>
       <c r="C521" t="str">
         <v>S</v>
@@ -55123,11 +55123,11 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522">
-        <v>521</v>
-      </c>
-      <c r="B522">
-        <v>55</v>
+      <c r="A522" t="str">
+        <v>DRD10520</v>
+      </c>
+      <c r="B522" t="str">
+        <v>DR1054</v>
       </c>
       <c r="C522" t="str">
         <v>S</v>
@@ -55224,11 +55224,11 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523">
-        <v>522</v>
-      </c>
-      <c r="B523">
-        <v>55</v>
+      <c r="A523" t="str">
+        <v>DRD10521</v>
+      </c>
+      <c r="B523" t="str">
+        <v>DR1054</v>
       </c>
       <c r="C523" t="str">
         <v>S</v>
@@ -55325,11 +55325,11 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524">
-        <v>523</v>
-      </c>
-      <c r="B524">
-        <v>56</v>
+      <c r="A524" t="str">
+        <v>DRD10522</v>
+      </c>
+      <c r="B524" t="str">
+        <v>DR1055</v>
       </c>
       <c r="C524" t="str">
         <v>S</v>
@@ -55426,11 +55426,11 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525">
-        <v>524</v>
-      </c>
-      <c r="B525">
-        <v>56</v>
+      <c r="A525" t="str">
+        <v>DRD10523</v>
+      </c>
+      <c r="B525" t="str">
+        <v>DR1055</v>
       </c>
       <c r="C525" t="str">
         <v>S</v>
@@ -55527,11 +55527,11 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526">
-        <v>525</v>
-      </c>
-      <c r="B526">
-        <v>56</v>
+      <c r="A526" t="str">
+        <v>DRD10524</v>
+      </c>
+      <c r="B526" t="str">
+        <v>DR1055</v>
       </c>
       <c r="C526" t="str">
         <v>S</v>
@@ -55628,11 +55628,11 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527">
-        <v>526</v>
-      </c>
-      <c r="B527">
-        <v>56</v>
+      <c r="A527" t="str">
+        <v>DRD10525</v>
+      </c>
+      <c r="B527" t="str">
+        <v>DR1055</v>
       </c>
       <c r="C527" t="str">
         <v>S</v>
@@ -55729,11 +55729,11 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528">
-        <v>527</v>
-      </c>
-      <c r="B528">
-        <v>57</v>
+      <c r="A528" t="str">
+        <v>DRD10526</v>
+      </c>
+      <c r="B528" t="str">
+        <v>DR1056</v>
       </c>
       <c r="C528" t="str">
         <v>S</v>
@@ -55830,11 +55830,11 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529">
-        <v>528</v>
-      </c>
-      <c r="B529">
-        <v>57</v>
+      <c r="A529" t="str">
+        <v>DRD10527</v>
+      </c>
+      <c r="B529" t="str">
+        <v>DR1056</v>
       </c>
       <c r="C529" t="str">
         <v>S</v>
@@ -55931,11 +55931,11 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530">
-        <v>529</v>
-      </c>
-      <c r="B530">
-        <v>57</v>
+      <c r="A530" t="str">
+        <v>DRD10528</v>
+      </c>
+      <c r="B530" t="str">
+        <v>DR1056</v>
       </c>
       <c r="C530" t="str">
         <v>S</v>
@@ -56032,11 +56032,11 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531">
-        <v>530</v>
-      </c>
-      <c r="B531">
-        <v>57</v>
+      <c r="A531" t="str">
+        <v>DRD10529</v>
+      </c>
+      <c r="B531" t="str">
+        <v>DR1056</v>
       </c>
       <c r="C531" t="str">
         <v>S</v>
@@ -56133,11 +56133,11 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532">
-        <v>531</v>
-      </c>
-      <c r="B532">
-        <v>57</v>
+      <c r="A532" t="str">
+        <v>DRD10530</v>
+      </c>
+      <c r="B532" t="str">
+        <v>DR1056</v>
       </c>
       <c r="C532" t="str">
         <v>S</v>
@@ -56234,11 +56234,11 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533">
-        <v>532</v>
-      </c>
-      <c r="B533">
-        <v>58</v>
+      <c r="A533" t="str">
+        <v>DRD10531</v>
+      </c>
+      <c r="B533" t="str">
+        <v>DR1057</v>
       </c>
       <c r="C533" t="str">
         <v>S</v>
@@ -56335,11 +56335,11 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534">
-        <v>533</v>
-      </c>
-      <c r="B534">
-        <v>58</v>
+      <c r="A534" t="str">
+        <v>DRD10532</v>
+      </c>
+      <c r="B534" t="str">
+        <v>DR1057</v>
       </c>
       <c r="C534" t="str">
         <v>S</v>
@@ -56436,11 +56436,11 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535">
-        <v>534</v>
-      </c>
-      <c r="B535">
-        <v>58</v>
+      <c r="A535" t="str">
+        <v>DRD10533</v>
+      </c>
+      <c r="B535" t="str">
+        <v>DR1057</v>
       </c>
       <c r="C535" t="str">
         <v>S</v>

--- a/GearSage-client/pkgGear/data_raw/daiwa_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_rod_import.xlsx
@@ -439,8 +439,8 @@
       <c r="A2" t="str">
         <v>DR1000</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>2</v>
       </c>
       <c r="C2" t="str">
         <v>モアザン ブランジーノ CGSmorethan BRANZINO CGS</v>
@@ -474,8 +474,8 @@
       <c r="A3" t="str">
         <v>DR1001</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="str">
         <v>モアザンMORETHAN</v>
@@ -509,8 +509,8 @@
       <c r="A4" t="str">
         <v>DR1002</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>2</v>
       </c>
       <c r="C4" t="str">
         <v>ラブラックス AGS BS（ボートシーバス）LABRAX AGS BS（BOAT SEABASS）</v>
@@ -544,8 +544,8 @@
       <c r="A5" t="str">
         <v>DR1003</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>2</v>
       </c>
       <c r="C5" t="str">
         <v>モアザン ブランジーノ EX AGS ベイトモデルMORETHAN BRANZINO EX AGS</v>
@@ -579,8 +579,8 @@
       <c r="A6" t="str">
         <v>DR1004</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>ラブラックス AGSLABRAX AGS</v>
@@ -614,8 +614,8 @@
       <c r="A7" t="str">
         <v>DR1005</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="str">
         <v>モアザン ワイズメンMORETHAN WISEMEN</v>
@@ -649,8 +649,8 @@
       <c r="A8" t="str">
         <v>DR1006</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>2</v>
       </c>
       <c r="C8" t="str">
         <v>スカイハイSKYHIGH</v>
@@ -684,8 +684,8 @@
       <c r="A9" t="str">
         <v>DR1007</v>
       </c>
-      <c r="B9" t="str">
-        <v/>
+      <c r="B9">
+        <v>2</v>
       </c>
       <c r="C9" t="str">
         <v>モアザン ブランジーノ EX AGSMORETHAN BRANZINO EX AGS</v>
@@ -719,8 +719,8 @@
       <c r="A10" t="str">
         <v>DR1008</v>
       </c>
-      <c r="B10" t="str">
-        <v/>
+      <c r="B10">
+        <v>2</v>
       </c>
       <c r="C10" t="str">
         <v>シーバスフラットXSEABASS FLAT X</v>
@@ -754,8 +754,8 @@
       <c r="A11" t="str">
         <v>DR1009</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
+      <c r="B11">
+        <v>2</v>
       </c>
       <c r="C11" t="str">
         <v>ラテオLATEO</v>
@@ -789,8 +789,8 @@
       <c r="A12" t="str">
         <v>DR1010</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="B12">
+        <v>2</v>
       </c>
       <c r="C12" t="str">
         <v>ラテオ BSLATEO BS</v>
@@ -824,8 +824,8 @@
       <c r="A13" t="str">
         <v>DR1011</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="str">
         <v>スカイハイ ボートゲームSKYHIGH BOATGAME</v>
@@ -859,8 +859,8 @@
       <c r="A14" t="str">
         <v>DR1012</v>
       </c>
-      <c r="B14" t="str">
-        <v/>
+      <c r="B14">
+        <v>2</v>
       </c>
       <c r="C14" t="str">
         <v>ハートランド AGS（ベイトキャスティングモデル）HEARTLAND AGS（BAITCASTING MODELS）</v>
@@ -894,8 +894,8 @@
       <c r="A15" t="str">
         <v>DR1013</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
+      <c r="B15">
+        <v>2</v>
       </c>
       <c r="C15" t="str">
         <v>ハートランド AGS（スピニングモデル）HEARTLAND AGS（SPINNING MODELS）</v>
@@ -929,8 +929,8 @@
       <c r="A16" t="str">
         <v>DR1014</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="str">
         <v>スティーズ（ベイトキャスティングモデル）STEEZ（BAITCASTING MODEL）</v>
@@ -964,8 +964,8 @@
       <c r="A17" t="str">
         <v>DR1015</v>
       </c>
-      <c r="B17" t="str">
-        <v/>
+      <c r="B17">
+        <v>2</v>
       </c>
       <c r="C17" t="str">
         <v>スティーズ （スピニングモデル）STEEZ（SPINNING MODEL）</v>
@@ -999,8 +999,8 @@
       <c r="A18" t="str">
         <v>DR1016</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
+      <c r="B18">
+        <v>2</v>
       </c>
       <c r="C18" t="str">
         <v>スティーズ ショアコンペティション（ベイトキャスティングモデル）STEEZ SHORE COMPETITION（BAITCASTING MODEL）</v>
@@ -1034,8 +1034,8 @@
       <c r="A19" t="str">
         <v>DR1017</v>
       </c>
-      <c r="B19" t="str">
-        <v/>
+      <c r="B19">
+        <v>2</v>
       </c>
       <c r="C19" t="str">
         <v>スティーズ リアルコントロールSTEEZ REAL CONTROL</v>
@@ -1069,8 +1069,8 @@
       <c r="A20" t="str">
         <v>DR1018</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
+      <c r="B20">
+        <v>2</v>
       </c>
       <c r="C20" t="str">
         <v>ハートランド（スピニングモデル）HEARTLAND（SPINNING MODELS）</v>
@@ -1104,8 +1104,8 @@
       <c r="A21" t="str">
         <v>DR1019</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>2</v>
       </c>
       <c r="C21" t="str">
         <v>ハートランド（ベイトキャスティングモデル）HEARTLAND（BAITCASTING MODELS）</v>
@@ -1139,8 +1139,8 @@
       <c r="A22" t="str">
         <v>DR1020</v>
       </c>
-      <c r="B22" t="str">
-        <v/>
+      <c r="B22">
+        <v>2</v>
       </c>
       <c r="C22" t="str">
         <v>ブラックレーベル トラベルBLACK LABEL TRAVEL</v>
@@ -1174,8 +1174,8 @@
       <c r="A23" t="str">
         <v>DR1021</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
+      <c r="B23">
+        <v>2</v>
       </c>
       <c r="C23" t="str">
         <v>スティーズ ショアコンペティション（スピニングモデル）STEEZ SHORE COMPETITION（SPINNING MODEL）</v>
@@ -1209,8 +1209,8 @@
       <c r="A24" t="str">
         <v>DR1022</v>
       </c>
-      <c r="B24" t="str">
-        <v/>
+      <c r="B24">
+        <v>2</v>
       </c>
       <c r="C24" t="str">
         <v>SWAGGERSWAGGER</v>
@@ -1244,8 +1244,8 @@
       <c r="A25" t="str">
         <v>DR1023</v>
       </c>
-      <c r="B25" t="str">
-        <v/>
+      <c r="B25">
+        <v>2</v>
       </c>
       <c r="C25" t="str">
         <v>ブラックレーベルBLACK LABEL</v>
@@ -1279,8 +1279,8 @@
       <c r="A26" t="str">
         <v>DR1024</v>
       </c>
-      <c r="B26" t="str">
-        <v/>
+      <c r="B26">
+        <v>2</v>
       </c>
       <c r="C26" t="str">
         <v>タトゥーラ エリートTATULA ELITE</v>
@@ -1314,8 +1314,8 @@
       <c r="A27" t="str">
         <v>DR1025</v>
       </c>
-      <c r="B27" t="str">
-        <v/>
+      <c r="B27">
+        <v>2</v>
       </c>
       <c r="C27" t="str">
         <v>タトゥーラTATULA</v>
@@ -1349,8 +1349,8 @@
       <c r="A28" t="str">
         <v>DR1026</v>
       </c>
-      <c r="B28" t="str">
-        <v/>
+      <c r="B28">
+        <v>2</v>
       </c>
       <c r="C28" t="str">
         <v>タトゥーラ トラベルTATULA TRAVEL</v>
@@ -1384,8 +1384,8 @@
       <c r="A29" t="str">
         <v>DR1027</v>
       </c>
-      <c r="B29" t="str">
-        <v/>
+      <c r="B29">
+        <v>2</v>
       </c>
       <c r="C29" t="str">
         <v>B.B.B（トリプルビー）B.B.B</v>
@@ -1419,8 +1419,8 @@
       <c r="A30" t="str">
         <v>DR1028</v>
       </c>
-      <c r="B30" t="str">
-        <v/>
+      <c r="B30">
+        <v>2</v>
       </c>
       <c r="C30" t="str">
         <v>ブレイゾンBLAZON</v>
@@ -1454,8 +1454,8 @@
       <c r="A31" t="str">
         <v>DR1029</v>
       </c>
-      <c r="B31" t="str">
-        <v/>
+      <c r="B31">
+        <v>2</v>
       </c>
       <c r="C31" t="str">
         <v>カムイランケタムKAMUY RANKE TAM</v>
@@ -1489,8 +1489,8 @@
       <c r="A32" t="str">
         <v>DR1030</v>
       </c>
-      <c r="B32" t="str">
-        <v/>
+      <c r="B32">
+        <v>2</v>
       </c>
       <c r="C32" t="str">
         <v>モバイルパックMOBILE PACK</v>
@@ -1524,8 +1524,8 @@
       <c r="A33" t="str">
         <v>DR1031</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
+      <c r="B33">
+        <v>2</v>
       </c>
       <c r="C33" t="str">
         <v>ブレイゾン モバイルBLAZON MOBILE</v>
@@ -1559,8 +1559,8 @@
       <c r="A34" t="str">
         <v>DR1032</v>
       </c>
-      <c r="B34" t="str">
-        <v/>
+      <c r="B34">
+        <v>2</v>
       </c>
       <c r="C34" t="str">
         <v>シルバークリーク AK（アキアジ）SILVER CREEK AK（AKIAJI）</v>
@@ -1594,8 +1594,8 @@
       <c r="A35" t="str">
         <v>DR1033</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
+      <c r="B35">
+        <v>2</v>
       </c>
       <c r="C35" t="str">
         <v>シルバークリーク グラスプログレッシブSILVER CREEK GLASS PROGRESSIVE</v>
@@ -1629,8 +1629,8 @@
       <c r="A36" t="str">
         <v>DR1034</v>
       </c>
-      <c r="B36" t="str">
-        <v/>
+      <c r="B36">
+        <v>2</v>
       </c>
       <c r="C36" t="str">
         <v>タトゥーラ XTTATULA XT</v>
@@ -1664,8 +1664,8 @@
       <c r="A37" t="str">
         <v>DR1035</v>
       </c>
-      <c r="B37" t="str">
-        <v/>
+      <c r="B37">
+        <v>2</v>
       </c>
       <c r="C37" t="str">
         <v>プレッソ-LTD AGSPRESSO-LTD AGS</v>
@@ -1699,8 +1699,8 @@
       <c r="A38" t="str">
         <v>DR1036</v>
       </c>
-      <c r="B38" t="str">
-        <v/>
+      <c r="B38">
+        <v>2</v>
       </c>
       <c r="C38" t="str">
         <v>シルバークリーク トラッドSilver Creek Trad</v>
@@ -1734,8 +1734,8 @@
       <c r="A39" t="str">
         <v>DR1037</v>
       </c>
-      <c r="B39" t="str">
-        <v/>
+      <c r="B39">
+        <v>2</v>
       </c>
       <c r="C39" t="str">
         <v>シルバークリーク AurumSILVER CREEK AURUM</v>
@@ -1769,8 +1769,8 @@
       <c r="A40" t="str">
         <v>DR1038</v>
       </c>
-      <c r="B40" t="str">
-        <v/>
+      <c r="B40">
+        <v>2</v>
       </c>
       <c r="C40" t="str">
         <v>プレッソ AIR AGSPRESSO AIR AGS</v>
@@ -1804,8 +1804,8 @@
       <c r="A41" t="str">
         <v>DR1039</v>
       </c>
-      <c r="B41" t="str">
-        <v/>
+      <c r="B41">
+        <v>2</v>
       </c>
       <c r="C41" t="str">
         <v>シルバークリーク レイクジギングSILVER CREEK LAKE JIGGING</v>
@@ -1839,8 +1839,8 @@
       <c r="A42" t="str">
         <v>DR1040</v>
       </c>
-      <c r="B42" t="str">
-        <v/>
+      <c r="B42">
+        <v>2</v>
       </c>
       <c r="C42" t="str">
         <v>ピュアリストPURELIST</v>
@@ -1874,8 +1874,8 @@
       <c r="A43" t="str">
         <v>DR1041</v>
       </c>
-      <c r="B43" t="str">
-        <v/>
+      <c r="B43">
+        <v>2</v>
       </c>
       <c r="C43" t="str">
         <v>プレッソ MXPRESSO MX</v>
@@ -1909,8 +1909,8 @@
       <c r="A44" t="str">
         <v>DR1042</v>
       </c>
-      <c r="B44" t="str">
-        <v/>
+      <c r="B44">
+        <v>2</v>
       </c>
       <c r="C44" t="str">
         <v>イプリミIPRIMI</v>
@@ -1944,8 +1944,8 @@
       <c r="A45" t="str">
         <v>DR1043</v>
       </c>
-      <c r="B45" t="str">
-        <v/>
+      <c r="B45">
+        <v>2</v>
       </c>
       <c r="C45" t="str">
         <v>トラウト X NTTROUT X NT</v>
@@ -1979,8 +1979,8 @@
       <c r="A46" t="str">
         <v>DR1044</v>
       </c>
-      <c r="B46" t="str">
-        <v/>
+      <c r="B46">
+        <v>2</v>
       </c>
       <c r="C46" t="str">
         <v>ロッホモア フライコンボLOCHMOR FLY COMBO</v>
@@ -2014,8 +2014,8 @@
       <c r="A47" t="str">
         <v>DR1045</v>
       </c>
-      <c r="B47" t="str">
-        <v/>
+      <c r="B47">
+        <v>2</v>
       </c>
       <c r="C47" t="str">
         <v>ピュアリスト AKPURELIST AK</v>
@@ -2049,8 +2049,8 @@
       <c r="A48" t="str">
         <v>DR1046</v>
       </c>
-      <c r="B48" t="str">
-        <v/>
+      <c r="B48">
+        <v>2</v>
       </c>
       <c r="C48" t="str">
         <v>ワイズストリームWISE STREAM</v>
@@ -2084,8 +2084,8 @@
       <c r="A49" t="str">
         <v>DR1047</v>
       </c>
-      <c r="B49" t="str">
-        <v/>
+      <c r="B49">
+        <v>2</v>
       </c>
       <c r="C49" t="str">
         <v>トラウト X ATTROUT X AT</v>
@@ -2119,8 +2119,8 @@
       <c r="A50" t="str">
         <v>DR1048</v>
       </c>
-      <c r="B50" t="str">
-        <v/>
+      <c r="B50">
+        <v>2</v>
       </c>
       <c r="C50" t="str">
         <v>月下美人 MX アジングGEKKABIJIN MX AJING</v>
@@ -2154,8 +2154,8 @@
       <c r="A51" t="str">
         <v>DR1049</v>
       </c>
-      <c r="B51" t="str">
-        <v/>
+      <c r="B51">
+        <v>2</v>
       </c>
       <c r="C51" t="str">
         <v>月下美人 AIRGEKKABIJIN AIR</v>
@@ -2189,8 +2189,8 @@
       <c r="A52" t="str">
         <v>DR1050</v>
       </c>
-      <c r="B52" t="str">
-        <v/>
+      <c r="B52">
+        <v>2</v>
       </c>
       <c r="C52" t="str">
         <v>月下美人 AIR AJINGBOATGEKKABIJIN AIR AJINGBOAT</v>
@@ -2224,8 +2224,8 @@
       <c r="A53" t="str">
         <v>DR1051</v>
       </c>
-      <c r="B53" t="str">
-        <v/>
+      <c r="B53">
+        <v>2</v>
       </c>
       <c r="C53" t="str">
         <v>月下美人 EXGEKKABIJIN EX</v>
@@ -2259,8 +2259,8 @@
       <c r="A54" t="str">
         <v>DR1052</v>
       </c>
-      <c r="B54" t="str">
-        <v/>
+      <c r="B54">
+        <v>2</v>
       </c>
       <c r="C54" t="str">
         <v>月下美人 MXGEKKABIJIN MX</v>
@@ -2294,8 +2294,8 @@
       <c r="A55" t="str">
         <v>DR1053</v>
       </c>
-      <c r="B55" t="str">
-        <v/>
+      <c r="B55">
+        <v>2</v>
       </c>
       <c r="C55" t="str">
         <v>月下美人 MX モバイルGEKKABIJIN MX MOBILE</v>
@@ -2329,8 +2329,8 @@
       <c r="A56" t="str">
         <v>DR1054</v>
       </c>
-      <c r="B56" t="str">
-        <v/>
+      <c r="B56">
+        <v>2</v>
       </c>
       <c r="C56" t="str">
         <v>アジメバル ＸAJIMEBARU X</v>
@@ -2364,8 +2364,8 @@
       <c r="A57" t="str">
         <v>DR1055</v>
       </c>
-      <c r="B57" t="str">
-        <v/>
+      <c r="B57">
+        <v>2</v>
       </c>
       <c r="C57" t="str">
         <v>月下美人（メバルモデル）GEKKABIJIN MEBARUMODEL</v>
@@ -2399,8 +2399,8 @@
       <c r="A58" t="str">
         <v>DR1056</v>
       </c>
-      <c r="B58" t="str">
-        <v/>
+      <c r="B58">
+        <v>2</v>
       </c>
       <c r="C58" t="str">
         <v>月下美人 AJINGGEKKABIJIN AJING</v>
@@ -2434,8 +2434,8 @@
       <c r="A59" t="str">
         <v>DR1057</v>
       </c>
-      <c r="B59" t="str">
-        <v/>
+      <c r="B59">
+        <v>2</v>
       </c>
       <c r="C59" t="str">
         <v>月下美人 MX AJING BOATGEKKABIJIN MX AJING BOAT</v>
@@ -2474,7 +2474,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG535"/>
+  <dimension ref="A1:AI535"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2576,6 +2576,12 @@
       <c r="AG1" t="str">
         <v>Description</v>
       </c>
+      <c r="AH1" t="str">
+        <v>Extra Spec 1</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>Extra Spec 2</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -2677,6 +2683,12 @@
       <c r="AG2" t="str">
         <v>「URBAN SIDE CUSTOM」——港湾ロッドの頂点に君臨し続ける名機。バチ抜けやマイクロベイトパターン、ストラクチャー撃ちなど、繊細な釣りにおいて、CGSと新開発ブランクが生み出す超高感度と優れた操作性が際立つ。M46Xを纏ったフィネスブランクは、繊細かつしなやかでありながら、圧倒的なシャープさを兼ね備え、中型ルアーの操作にも対応。港湾ロッドの究極形、ここに誕生。</v>
       </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -2778,6 +2790,12 @@
       <c r="AG3" t="str">
         <v>「MATCH THE BITE CUSTOM」——さまざまなフィールドに対応する超攻撃型ロッド。M46Xを全身に纏い、細身化されたブランクは、94というレングスを感じさせない圧倒的な先軽感を実現。CGSを採用したショートグリップとの相乗効果で、究極の操作性も実現。ハリのあるティップは、多彩なアクション入力を可能にし、細身ながら粘り強いバットは、大型シーバスとのファイトでも安心感をもたらす。このロッドでしか獲れないシーバスが存在する。</v>
       </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -2879,6 +2897,12 @@
       <c r="AG4" t="str">
         <v>「STREAM LUNKER CUSTOM」——DAIWA伝統のオールラウンドロッド。繊細なバイトも逃さず捉える柔軟なティップは、ドリフトの自由度を高め、流れの中でもナチュラルな誘いを実現。圧倒的な飛距離性能と、ランカー相手にも主導権を渡さないパワフルなバットを兼ね備える。操作感をさらに高めるCGSとの相乗効果により、小型ルアーから大型ルアーまで思いのままにコントロールが可能。全セクションにM46Xを採用した超高弾性・細身ブランクが、圧倒的シャープさと驚異的な粘り強さを両立。相反する全ての要素を満たす、至高のオールラウンダー。</v>
       </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -2980,6 +3004,12 @@
       <c r="AG5" t="str">
         <v>鬼掛けティップを搭載する港湾部のテクニカルロッドL/MLとは、Lパワーの繊細な穂先と、MLパワーのバットを組み合わせの意味。シーバスのショートバイトを絡めとるデーモン調子のティップを持ちながら、シャープなキャスト性能を両立させる港湾部のテクニカルロッド。バチ抜けやハクパターンなどの繊細なゲームはもちろん、ミノーやバイブレーションのピンポイント撃ちにも高次元で対応。春だけではなく通年活躍するロッドに仕上がっている。</v>
       </c>
+      <c r="AH5" t="str">
+        <v/>
+      </c>
+      <c r="AI5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -3081,6 +3111,12 @@
       <c r="AG6" t="str">
         <v>キャストとロッドワークが冴える港湾部のスタンダードロッド自分の腕の延長のように動く、芯の通ったような張りのあるブランクを搭載。港湾部で求められるアキュラシーの高いキャストと、トゥイッチやジャークといったルアー操作性を磨き込んだ。港湾部は護岸やフェンスなどの構造物によって、キャストを制限されるシチュエーションも多い。オーバーヘッドはもちろん、サイドキャストやアンダーハンドなどもしやすい軽快性も持ち味だ。</v>
       </c>
+      <c r="AH6" t="str">
+        <v/>
+      </c>
+      <c r="AI6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -3182,6 +3218,12 @@
       <c r="AG7" t="str">
         <v>重量級ルアー操作に長けた攻撃的なパワーロッド大型ルアーの操作性に優れる張りのあるMパワーの穂先と、体積の大きいルアーの遠投性に優れたMHのハイパワーなバットを組み合わせた攻撃的なロッド。大型ルアーのシーバス誘因性を最大限まで発揮させるテクニカルロッドで、運河から河川、干潟などに対応する。ストラクチャー回りや流れの変化などのピンポイントにルアーを送り届け、正確なアクションでシーバスを誘い出す。ショートレングスならではダイレクト感はランカーを獲ったという価値観をいっそう高めてくれるだろう。ルアーの下限は12㎝級のミノーにも対応する幅広さをもたせている。</v>
       </c>
+      <c r="AH7" t="str">
+        <v/>
+      </c>
+      <c r="AI7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -3283,6 +3325,12 @@
       <c r="AG8" t="str">
         <v>絶妙なパワーと高いルアー操作性が魅力の強粘ロッドMLMとはMLとMの間の絶妙なパワーバランスの意味。絶妙なパワーバランスと癖のないレギュラーテーパーによって、8～12㎝級のミノーやシンキングペンシルを自在に操るウェーディングロッド。持った瞬間にあらゆるルアーをシューティングキャストし、軽快にシャーキング、ドックウォークさせて食わせるイメージが浮かぶ。優れた操作性と、ショートグリップ設計により、港湾部のピンポイント撃ちも得意とする。</v>
       </c>
+      <c r="AH8" t="str">
+        <v/>
+      </c>
+      <c r="AI8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -3384,6 +3432,12 @@
       <c r="AG9" t="str">
         <v>幅広いルアーに対応し、操作性に優れるウェーディング特化型ロッドウェーディングゲーム用ロッドに求められる性能を徹底追及。流れの変化やルアーのアクションの変化を鮮明に感じ取れることを最優先し、MLパワーのしなやかなティップを、遠投性に長けるMパワーの強いバットを組み合わせた。ゲームベストを着た状況でも扱いやすいセッティングを追求し、ややショートグリップとしたが、軽量設計の穂先と取り回しの良い9フィート3インチのレングスと相まって先重りを感じさせない軽快さが持ち味。結果、優れた操作性はおかっぱりでも本領を発揮する。</v>
       </c>
+      <c r="AH9" t="str">
+        <v/>
+      </c>
+      <c r="AI9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -3485,6 +3539,12 @@
       <c r="AG10" t="str">
         <v>大型ルアーでランカーを仕留めるビッグプラグスペシャルロッド大型のトップウォータールアーやジョイントルアーを用いた豪快なシーバスゲームに魅了されたアングラーに向けた開発した超攻撃型ロッド。優れた重量バランスで大型ルアーを軽快に操り、強い粘りで掛かったシーバスの動きを封じ込める。シリーズの中で圧倒的なパワーを誇るモンスターロッドで、これで獲れないシーバスはいない。</v>
       </c>
+      <c r="AH10" t="str">
+        <v/>
+      </c>
+      <c r="AI10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -3586,6 +3646,12 @@
       <c r="AG11" t="str">
         <v>あらゆるシチュエーションに対応するザ・スタンダードロッドBRANZINOの王道アイテムの97ML/Mをスタンダードモデルとなるmorethanとしてアレンジ。剛性バランスを見直すことで、あらゆるウエイトのルアーをキャストしやすくしている。MLパワーのティップとMパワーのバットによりフィネスゲームからパワーゲームまで対応。9'6''の王道レングスと相まって使う場所や時期を選ばないスタンダード。</v>
       </c>
+      <c r="AH11" t="str">
+        <v/>
+      </c>
+      <c r="AI11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -3687,6 +3753,12 @@
       <c r="AG12" t="str">
         <v>キレのあるキャストとルアー操作性が持ち味のパワーロッド説明不要とはこのロッドのこと。手にすればわかる素直さが持ち味。おかっぱり、ウェーディング、港湾、サーフに小磯と、どこでも使いたくなる一本だ。8～12㎝前後のルアーを中心に、水押しの強いウェイク系ルアーや体高のあるシンキングペンシルも得意とする。ミノーやシンキングペンシルのリトリーブはもちろんのことながら、張りのあるティップを搭載するので中型のルアーを積極的に動かす釣りも面白い。</v>
       </c>
+      <c r="AH12" t="str">
+        <v/>
+      </c>
+      <c r="AI12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -3788,6 +3860,12 @@
       <c r="AG13" t="str">
         <v>コノシロなどの大型ベイトパターンを攻略するランカーロッド大型のトップウォータープラグやウェイク系、ジョイント系ルアーで攻撃的なゲームを展開するためのハイパワーロッド。コノシロやイナッコ、落ちアユパターンで本領を発揮する。高剛性のバットにより、太い流れの中で掛けたランカーも瞬時に水面まで浮かせる。また、ただのハイパワーロッドではない、絶妙な張りの穂先によって12㎝級のミノーやシンキングペンシルにもマッチ。周年使えるパワーゲームロッドに仕上がった。</v>
       </c>
+      <c r="AH13" t="str">
+        <v/>
+      </c>
+      <c r="AI13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -3889,6 +3967,12 @@
       <c r="AG14" t="str">
         <v>大河川の河口やサーフで本領を発揮する遠投ロッド遠投が武器となる大河川の河口やサーフで真価を発揮する遠投モデル。パワーランクはML/M。近年のタフコンディション化する釣り場の状況に合わせて、MLパワーの繊細な穂先と、Mパワーの強いバットを組み合わせた。優れた流速感度と、ルアーのアクションを最大限まで引き出すしなやかなティップが魅力。8～12㎝クラスのミノーやシンキングペンシルや25g前後のバイブレーションはもちろん、使用頻度の増えている6㎝クラスのシンキングペンシルや10g台のメタルバイブなどにも対応。この対応力は展開の読めない釣りにおいて非常に心強い武器になる。</v>
       </c>
+      <c r="AH14" t="str">
+        <v/>
+      </c>
+      <c r="AI14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -3990,6 +4074,12 @@
       <c r="AG15" t="str">
         <v>遠投性に長けた大場所のスタンダードロッド港湾部やサーフ、磯などの開けたエリアのスタンダードロッド。12～14㎝前後のミノーや10～12㎝のシンキングペンシルのキャスト性能は秀逸。癖のない調子により、バットの荷重がスムーズに穂先に移り、ルアーを最後まで力強く押し出すので、ピンポイントに正確に遠投することが可能。また、高反発の細身ブランクによって、向かい風にも動じない。あらゆるアングラーに体感してほしい爽快さだ。また、ロングロッドながら重量バランスに優れ、長時間のキャストはもちろん、ルアーの操作も軽快に行える。あらゆるルアーを正確に遠投でき、繊細なティップでルアーアクションを的確に感じとることができる。</v>
       </c>
+      <c r="AH15" t="str">
+        <v/>
+      </c>
+      <c r="AI15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -4091,6 +4181,12 @@
       <c r="AG16" t="str">
         <v>大型ルアーの遠投で新たなゲームを開拓する長距離砲サーフや磯をはじめ、大河川の遠投ゲームを制するハイパワーロッド。特出すべきはその対応幅。50g前後の大型のトップウォータープラグはもちろん、スタンダードサイズの12㎝、14㎝といったミノーから、30～60gの幅広いメタル系ルアー（メタルバイブやメタルジグ）に至るまで、あらゆるルアーを失速させずに沖の潮目まで鋭く飛ばす。ジグにおいては100mは当たり前。さらには、絶妙な張りのブランクと優れた重量バランスにより、大遠投した先の大型ルアーのアクションも自在。沖を回遊するシーバスを意のままのアクションで翻弄する新たなゲームを切り開く。</v>
       </c>
+      <c r="AH16" t="str">
+        <v/>
+      </c>
+      <c r="AI16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -4192,6 +4288,12 @@
       <c r="AG17" t="str">
         <v>【ワーム&amp;ミノー】しなやかで張りのある設計のブランクスは、ジグヘッドリグや8cm前後の軽量ミノーでもしっかりと曲がり、ルアーをストラクチャーの奥に撃ち込みやすい。ブレが少ないのでキャストの正確性やロッドワークのレスポンスも大幅に向上。細軸フックとの相性もよいタフコンディション時のマストアイテム。</v>
       </c>
+      <c r="AH17" t="str">
+        <v/>
+      </c>
+      <c r="AI17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -4293,6 +4395,12 @@
       <c r="AG18" t="str">
         <v>【トゥイッチ&amp;ジャーキング】細かなロッド操作を得意とするショートロッド。トップウォータールアーのドッグウォークや、ミノーのジャーキング、ワームのワインドまでルアーを積極的に動かす釣りを得意とする。</v>
       </c>
+      <c r="AH18" t="str">
+        <v/>
+      </c>
+      <c r="AI18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -4394,6 +4502,12 @@
       <c r="AG19" t="str">
         <v>【スピニング・オールラウンド】あらゆるタイプのルアーに素直に対応する癖の無いブランクスを搭載し、ピンスポットシューティングからオープンウォーターの遠投まで幅広く対応するオールラウンドロッド。</v>
       </c>
+      <c r="AH19" t="str">
+        <v/>
+      </c>
+      <c r="AI19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -4495,6 +4609,12 @@
       <c r="AG20" t="str">
         <v>【遠投&amp;ランカーシーバス】シャローフラットに点在するシモリを中・大型ミノーやバイブレーションの遠投で探る釣りに最適な遠投ロッド。冬のランカー便のマストアイテム。強いバットにより、小型青物のキャスティングゲームにも対応する。</v>
       </c>
+      <c r="AH20" t="str">
+        <v/>
+      </c>
+      <c r="AI20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -4596,6 +4716,12 @@
       <c r="AG21" t="str">
         <v>【ベイト・オールラウンド】穴撃ちから遠投まで幅広く対応するベイトのオールラウンドロッド。基本となるミノーやバイブレーションのただ巻きはもちろん、トップウォーターなどの連続トゥイッチなども軽快にこなす。</v>
       </c>
+      <c r="AH21" t="str">
+        <v/>
+      </c>
+      <c r="AI21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -4697,6 +4823,12 @@
       <c r="AG22" t="str">
         <v>【パワーカスタム】12cmクラスのミノーから、大型のウェイク系ルアー、ヘビーウエイトの鉄板バイブなどに対応するハイパワーベイトロッド。コノシロやマイワシといった大型のベイトを捕食しているシーンや、秋のパワフルなシーバス相手のベストアイテム。</v>
       </c>
+      <c r="AH22" t="str">
+        <v/>
+      </c>
+      <c r="AI22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -4798,6 +4930,12 @@
       <c r="AG23" t="str">
         <v>【ビッグベイト】100gを超える大型のルアーに対応するハイパワーのビッグベイト用ロッド。超重量級のルアーを扱うためのパワーと操作性と、魚をフックアップさせ、口切れを防ぐ柔軟性を絶妙なバランスで搭載する。</v>
       </c>
+      <c r="AH23" t="str">
+        <v/>
+      </c>
+      <c r="AI23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -4899,6 +5037,12 @@
       <c r="AG24" t="str">
         <v>– POWER BITE CUSTOM–超大型のトップウォータープラグや17㎝を超えるスイムベイトを自在に操り、ランカーシーバスのバイトを引き出すパワーロッド。ダウンクロスで掛けたランカーシーバスも持ち前のパワーでねじ伏せる。青物やアカメ狙いも視野に入れる最強のパワーロッド。</v>
       </c>
+      <c r="AH24" t="str">
+        <v/>
+      </c>
+      <c r="AI24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -5000,6 +5144,12 @@
       <c r="AG25" t="str">
         <v>–TECHNICAL VERSATILE CUSTOM–港湾部や中規模河川などに最適なテクニカルモデル。低弾道のショートキャストからフルキャストまで抜群のアキュラシーでピンスポットを攻略。ロッドアクションを多用する14ｃｍ超のミノーによるジャーキングやトップウォータープラグを軸としたゲームで抜群。7㎝前後の小型ルアーも使いやすく、取り回しのいいレングスはウェーディングでの使用にも最適。</v>
       </c>
+      <c r="AH25" t="str">
+        <v/>
+      </c>
+      <c r="AI25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -5101,6 +5251,12 @@
       <c r="AG26" t="str">
         <v>–POWER DISTANCE CUSTOM–12～14㎝クラスのミノーやシンペン、重量級大型ウェイクベイトから、アンダー10gの小型ルアーまで幅広いルアーに対応し、100ｍ超の圧倒的な飛距離を叩き出す遠投モデル。中・大型河川をはじめ、干潟などのオープンエリアの攻略に最適で。ショアゲーム、ウェーディングを問わずマルチに対応する。</v>
       </c>
+      <c r="AH26" t="str">
+        <v/>
+      </c>
+      <c r="AI26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -5202,6 +5358,12 @@
       <c r="AG27" t="str">
         <v>運河から都市型河川といったフィールドにマッチする港湾モデル。小型のミノーやシンキングペンシル、バイブレーションをピンスポットへ撃ち込める。また、トゥィッチやジャークも軽快にこなす。</v>
       </c>
+      <c r="AH27" t="str">
+        <v/>
+      </c>
+      <c r="AI27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -5303,6 +5465,12 @@
       <c r="AG28" t="str">
         <v>小型のミノーやシンキングペンシルに最適なフィネスモデル。バチ抜けゲームや小型のイカパターンなどで強みを発揮する。高感度、ハイレスポンスなブランクは、シビアな状況下で強い武器となる。</v>
       </c>
+      <c r="AH28" t="str">
+        <v/>
+      </c>
+      <c r="AI28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -5404,6 +5572,12 @@
       <c r="AG29" t="str">
         <v>都市型河川や干潟のウェーディングの釣りに最適なバーサタイルモデル。中型のシンキングペンシルやミノー、ワームなどを軽快に操ることができる。明暗の釣りやボトム変化、潮流変化の攻略に最適。</v>
       </c>
+      <c r="AH29" t="str">
+        <v/>
+      </c>
+      <c r="AI29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -5505,6 +5679,12 @@
       <c r="AG30" t="str">
         <v>都市型河川や干潟のウェーディングの釣りで飛距離が必要なときに活躍する遠投モデル。12cmクラスまでのミノーや中型のシンキングペンシル、バイブレーションなどに最適で、潮の変化を探し出してシーバスを包囲する。</v>
       </c>
+      <c r="AH30" t="str">
+        <v/>
+      </c>
+      <c r="AI30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -5606,6 +5786,12 @@
       <c r="AG31" t="str">
         <v>タイダルリバーや汽水湖などで出番の多い、大型のシンキングペンシルやスラローム系ルアーをはじめ、中大型のミノー、バイブレーションに対応するパワーモデル。高い遠投性能とパワーを有する強いバットを持つ。</v>
       </c>
+      <c r="AH31" t="str">
+        <v/>
+      </c>
+      <c r="AI31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -5707,6 +5893,12 @@
       <c r="AG32" t="str">
         <v>天然河川の中下流部から河口域で活躍するシーバスのセンターアイテム。中～大型のミノーやシンキングペンシルを遠投して流れを攻略するスタイルや、デイゲームの高比重のバイブレーションやブレードの釣りにマッチする。</v>
       </c>
+      <c r="AH32" t="str">
+        <v/>
+      </c>
+      <c r="AI32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -5808,6 +6000,12 @@
       <c r="AG33" t="str">
         <v>天然河川の中下流部から河口域で活躍するパワーモデル。高比重のルアーを遠投してのランカーゲームに最適。コノシロや秋のイナッコ、アユなどの大型のベイトが豊富なエリアでは欠かせない。</v>
       </c>
+      <c r="AH33" t="str">
+        <v/>
+      </c>
+      <c r="AI33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -5909,6 +6107,12 @@
       <c r="AG34" t="str">
         <v>流れの強い河川の下流部や河口域、サーフで活躍するハイパワーモデル。ヘビーバイブレーションやシンキングペンシル、ジョイント系ルアーに対応。強い流れで暴れるランカーの引きにも屈しない強靭なバットを有する。</v>
       </c>
+      <c r="AH34" t="str">
+        <v/>
+      </c>
+      <c r="AI34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -6010,6 +6214,12 @@
       <c r="AG35" t="str">
         <v>河口やサーフに対応する遠投モデル。通常の12cmクラスのルアーはもちろん、軽量のルアーの遠投も得意なので、シャローランナーや小型のシンペンなどを沖へ届け、食い渋るシーバスをナチュラルに誘惑できる。</v>
       </c>
+      <c r="AH35" t="str">
+        <v/>
+      </c>
+      <c r="AI35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -6111,6 +6321,12 @@
       <c r="AG36" t="str">
         <v>河口やサーフに対応する遠投モデル。12cmクラスのルアーを中心に、高比重のバイブレーションまでしっかりとカバー。絶えず変化する河口の潮を読み解き、シーバスに的確にアプローチする。</v>
       </c>
+      <c r="AH36" t="str">
+        <v/>
+      </c>
+      <c r="AI36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -6212,6 +6428,12 @@
       <c r="AG37" t="str">
         <v>磯のヒラスズキやマルスズキに対応するロングモデル。ネジレに強いブランクが、遠投性はもちろん、シモリ際にタイトに撃ち込むアキュラシーやシャープさにも貢献。サーフでも扱える軽快さを兼ね備える。軽さと携帯性を両立する3ピース設計。</v>
       </c>
+      <c r="AH37" t="str">
+        <v/>
+      </c>
+      <c r="AI37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -6313,6 +6535,12 @@
       <c r="AG38" t="str">
         <v>磯やサーフで活躍するハイパワーモデル。メタルジグやヘビーシンキングペンシルを大遠投し、沖の潮目やシモリの狙い撃ちが可能。ハイパワーのブランクが、大型のヒラスズキはもちろん、不意の青物にもしっかりと対応する。軽さと携帯性を両立する3ピース設計。</v>
       </c>
+      <c r="AH38" t="str">
+        <v/>
+      </c>
+      <c r="AI38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -6414,6 +6642,12 @@
       <c r="AG39" t="str">
         <v>村越正海監修のロングヒラスズキロッド。15フィートという長さからは想像できないほどシャープなブランクで、根際につくヒラスズキの元へミノーを飛ばし、その長さでミノーを自在なコースでトレース。ターゲットを確実に誘い出す。</v>
       </c>
+      <c r="AH39" t="str">
+        <v/>
+      </c>
+      <c r="AI39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -6515,6 +6749,12 @@
       <c r="AG40" t="str">
         <v>13フィートの細身ブランクが風の影響を最小限に抑え、根際につくヒラスズキへより正確なアプローチを可能にする。極細ブランク＋AGSの組み合わせにより1フィート短いロッドであるかのような軽快な操作性を持つ。磯では2ピース感覚、磯までのアプローチでは小継の4ピースで扱え、高い機動力を備える。</v>
       </c>
+      <c r="AH40" t="str">
+        <v/>
+      </c>
+      <c r="AI40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -6616,6 +6856,12 @@
       <c r="AG41" t="str">
         <v>荷重移動のスムーズな細身粘強のX45フルシールドのブランク。的確にピンポイントシューティングできるテクニカルロッド。フィネスな釣りにも対応する反面、バットはランカーにも動じない粘り強さを持つ。</v>
       </c>
+      <c r="AH41" t="str">
+        <v/>
+      </c>
+      <c r="AI41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -6717,6 +6963,12 @@
       <c r="AG42" t="str">
         <v>3DXで武装した高反発の細身ブランクが強烈な向かい風を切り裂いてミノーを弾丸のようにピンポイントへ送り届ける。狙いはランカーサイズのヒラスズキ、強靭なバットが大物を瞬時に浮かせる。</v>
       </c>
+      <c r="AH42" t="str">
+        <v/>
+      </c>
+      <c r="AI42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -6818,6 +7070,12 @@
       <c r="AG43" t="str">
         <v>ベイトリールと相性の良い荷重移動がスムーズなブランクに設計。風をもろともせずに低弾道でピンポイントを撃ち抜くライナーキャストはもちろん、ピンポイントにそっとルアーを置いてくるようなキャストも自在にこなす頼もしいキャスト性能を持つ。ファイトは粘り強くパワフル。ランカーヒラスズキや青物を強いトルクとベイトならではの巻きパワーで浮かせ、ランディングに導く。</v>
       </c>
+      <c r="AH43" t="str">
+        <v/>
+      </c>
+      <c r="AI43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -6919,6 +7177,12 @@
       <c r="AG44" t="str">
         <v>運河や都市型河川といった小場所に最適なショートモデル取り回しが良いのでルアーをピンスポットへ撃ち込みやすく、トゥイッチやジャークなどのロッドワークが軽快。シーバスをはじめ、チヌのトップゲームなどにも対応する。</v>
       </c>
+      <c r="AH44" t="str">
+        <v/>
+      </c>
+      <c r="AI44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -7020,6 +7284,12 @@
       <c r="AG45" t="str">
         <v>小場所に潜む大物を狙うパワフルなショートモデル重量のあるトップウォータープラグやミノーをピンスポットに撃ち込んだり、ロッド操作でドッグウォークやジャークなどを駆使して魚を誘い出す釣法に最適。港湾部のおかっぱりはもちろん、最盛期のウェーディングゲームも活躍の場となる。</v>
       </c>
+      <c r="AH45" t="str">
+        <v/>
+      </c>
+      <c r="AI45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -7121,6 +7391,12 @@
       <c r="AG46" t="str">
         <v>軽量ルアーにマッチするフィネスモデル小・中型のミノーやシンキングペンシル、ワームを使ったフィネスな釣法に最適。港湾部や運河のバチ抜けやマイクロベイトパターンのシーバスゲームだけでなく、大型メバルゲームやチニングにも対応する。</v>
       </c>
+      <c r="AH46" t="str">
+        <v/>
+      </c>
+      <c r="AI46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -7222,6 +7498,12 @@
       <c r="AG47" t="str">
         <v>おかっぱりやウェーディングを問わないバーサタイルモデル中・大型ミノーやシンキングペンシルなどに最適。ラインテンションの調整が重要なドリフト釣法からルアーを積極的に動かす釣法までマルチに対応する。</v>
       </c>
+      <c r="AH47" t="str">
+        <v/>
+      </c>
+      <c r="AI47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -7323,6 +7605,12 @@
       <c r="AG48" t="str">
         <v>キャストしやすいバーサタイルモデル河川の中下流域からサーフまで幅広く活躍するアイテムで、中・大型のミノーやシンキングペンシルを遠投して流れを攻略するスタイルや、デイゲームのバイブレーションやブレードの釣りにマッチする。</v>
       </c>
+      <c r="AH48" t="str">
+        <v/>
+      </c>
+      <c r="AI48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -7424,6 +7712,12 @@
       <c r="AG49" t="str">
         <v>使い所を選ばないバーサタイルモデル河川の中下流域からサーフ、堤防まで幅広く活躍するバーサタイルモデル。中・大型のプラグから、メタルジグの遠投まで幅広くこなせるので、河川のシーバスをはじめ、サーフや堤防でのライトショアジギングにも最適。</v>
       </c>
+      <c r="AH49" t="str">
+        <v/>
+      </c>
+      <c r="AI49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -7525,6 +7819,12 @@
       <c r="AG50" t="str">
         <v>大物にも安心なバーサタイルモデル河川の中下流域からサーフ、堤防まで幅広く活躍するハイパワーモデル。大型プラグの遠投や、ジグのシャクりやすさにこだわって設計。ランカーシーバスや青物の引きにも屈しないパワーが魅力。</v>
       </c>
+      <c r="AH50" t="str">
+        <v/>
+      </c>
+      <c r="AI50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -7626,6 +7926,12 @@
       <c r="AG51" t="str">
         <v>軽量ルアーの遠投を得意とするロングモデル河口域やサーフに対応する遠投モデル。12cmクラスまでのミノーはもちろん、小型のバイブレーションやワームなどの軽量ルアーの遠投も得意とする。食い渋るシーバスやフラットフィッシュをナチュラルに誘惑できる。</v>
       </c>
+      <c r="AH51" t="str">
+        <v/>
+      </c>
+      <c r="AI51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -7727,6 +8033,12 @@
       <c r="AG52" t="str">
         <v>オープンエリアを得意とするロングモデル河口域やサーフ、堤防に対応する遠投モデル。12cmクラスのミノーやシンキングペンシルを中心に、高比重のバイブレーションまでしっかりとカバー。シーバスから青物、フラットフィッシュまで幅広く対応する。</v>
       </c>
+      <c r="AH52" t="str">
+        <v/>
+      </c>
+      <c r="AI52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -7828,6 +8140,12 @@
       <c r="AG53" t="str">
         <v>オープンエリアを得意とするハイパワーロングモデル流れの強い河川の下流部や河口域を大型のシンキングペンシルやジョイント系ルアーで攻略したり、沖堤防などでヘビーバイブレーションやブレードを遠投する釣りにも最適。ランカーシーバスや青物の引きにも屈しないパワーが魅力。</v>
       </c>
+      <c r="AH53" t="str">
+        <v/>
+      </c>
+      <c r="AI53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -7929,6 +8247,12 @@
       <c r="AG54" t="str">
         <v>サーフや磯に対応するロングモデルサーフのシーバスやフラットフィッシュ、磯のマルスズキ狙いに最適なロングモデル。しなやかなブランクにより、ミノーはもちろん、ヘビーシンキングペンシルからワームまで幅広いルアーに対応する。</v>
       </c>
+      <c r="AH54" t="str">
+        <v/>
+      </c>
+      <c r="AI54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -8030,6 +8354,12 @@
       <c r="AG55" t="str">
         <v>サーフや磯に対応するハイパワーロングモデルサーフのシーバスやフラットフィッシュ、磯のマル・ヒラスズキ、青物狙いに最適なハイパワーなロングモデル。大型のミノーやヘビーシンキングペンシル、引き抵抗の強い大型メタルバイブなどにも対応する。</v>
       </c>
+      <c r="AH55" t="str">
+        <v/>
+      </c>
+      <c r="AI55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -8131,6 +8461,12 @@
       <c r="AG56" t="str">
         <v>スモールプラグからミノーまで幅広く対応。 最高のパフォーマンスを実現した超軽量ロッド。 アーバンサイドカスタム史上最軽量。高次元の感度と操作性を武器にスモールプラグから12cm級ミノーまでを自在に操ってシーバスを誘い出す。バチ抜けから初夏のピン撃ち、ウェーディングまでこなす大野ゆうき監修モデル。 ■特徴 大野ゆうきの右腕ともいえるアーバンサイドカスタムが97gという圧倒的な軽さとシャープさを得て大幅にブラッシュアップ。しなやかながら張りがある絶妙なブランクスによって、スモールプラグから10cm級ミノーまでを自在に操ってシーバスを誘い出す。操作性が大幅に向上したことで、スタイルの守備範囲も大幅に拡大。バチ抜けから初夏のピン撃ち、ウェーディングまでこなす。軽さがもたらす圧倒的な感度によって、スモールプラグのアクションも鮮明。1匹目のシーバスのヒットは特に注意していただきたい。まるで素肌感覚のような感度に驚いてロッドを落とすかもしれない。 左にスクロール</v>
       </c>
+      <c r="AH56" t="str">
+        <v/>
+      </c>
+      <c r="AI56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -8232,6 +8568,12 @@
       <c r="AG57" t="str">
         <v>キャスト精度、操作性に優れるテクニカルロッド 大野ゆうき監修スペシャルモデル あらゆるキャストモーションや、ジャークやダートなどのルアー操作が軽快な大野ゆうき監修のスペシャルモデル。おかっぱりを中心とする港湾や河川のゲームに幅広く対応する。 ■特徴 オーバーヘッド、サイドハンド、アンダーハンドといったあらゆるキャストモーションや、ジャークやダートなどのルアー操作が軽快な大野ゆうき監修のスペシャルモデル。従来のモデルはキャスト精度を確保するためにMLとMの中間に設定。やりとりにおいてはオーバーパワーになっていた。今回のモデルはブランクのポテンシャルが大きく向上したことでMLパワーとしてリニューアル。シャープなブランクが、正確なキャストとロッドワークをもたらすと同時に、粘りのあるバラシの少ないファイトを両立。このシリーズのブランク特性の進化を象徴する一本に仕上がっている。 左にスクロール</v>
       </c>
+      <c r="AH57" t="str">
+        <v/>
+      </c>
+      <c r="AI57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -8333,6 +8675,12 @@
       <c r="AG58" t="str">
         <v>キャストの先に広がるのは鮮明な世界。 遠距離フィネスゲームを征するピンポイントシューター アーバンサイドカスタムの操作性を極限まで保ったままレングスアップ。高い感度とさらなる遠投力で、スモールプラグから12cm級ミノーまでを自在に操作。マイクロベイトパターンの攻略や、バチやサヨリのような微波動ベイトの攻略に欠かせない。 ■特徴 アーバンサイドカスタムの操作性を極限まで保ったまま9フィート4インチまでレングスアップ。それによって、対応するフィールドが大幅に拡大。港湾モデルと思われがちだが、繊細な水流変化を見逃さない高い感度と、遠投性によって干 潟はもちろん、ナミノハナやハクといったマイクロベイトを偏食することの多い小磯攻略などでも無類の強さを発揮。サヨリのような微波動ベイトの攻略に欠かせない。高い感度とさらなる遠投力で、スモールプラグをはじめ、80mmクラスのシンペンや12cm級ミノーまでを自在に操作。大野ゆうき監修モデル。 左にスクロール</v>
       </c>
+      <c r="AH58" t="str">
+        <v/>
+      </c>
+      <c r="AI58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -8434,6 +8782,12 @@
       <c r="AG59" t="str">
         <v>都市型河川にマッチするテクニカルロッド大野ゆうき監修スペシャルモデル 87MLをロングレングス化し、遠投性を強化した大野ゆうきの監修のスペシャルモデル。操作性を極限まで保ってロングレングス化したこだわりのブランクは、キャストの正確性にも優れる。 ■特徴 MT BRANZINO EX AGS 87MLをロングレングス化し、遠投性を強化した大野ゆうきの監修のスペシャルモデル。大野ゆうきがサンプルを手にした際、従来品の87MLM並みに軽くて操作が高いと絶賛。軽量化に磨きをかけたブランクが、ロッドの汎用性が拡大。特に小型のルアーのキャスト性能や、感度において大きな優位性をもたらした。先がる感と操作性にこだわり抜いたブランクは鞭のようにしなやかな半面、MLとは思えないほどのパワーと粘りを兼ね備える。 左にスクロール</v>
       </c>
+      <c r="AH59" t="str">
+        <v/>
+      </c>
+      <c r="AI59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -8535,6 +8889,12 @@
       <c r="AG60" t="str">
         <v>小～大型ルアーまで万能に対応するオールラウンダー Mパワーの強いバットとしなやかなMLパワーのティップを組み合わせたリバーゲームモデル。この組み合わせにより、使えるルアーやフィールドの幅が拡大。河川にとどまらず、汽水湖などでも幅広く活躍する。 ■特徴 ルアーを弾き飛ばし、ランカーの動きを封じ込めるMパワーの強いバットセクションと、ルアーの動きを引き出すと同時に、ルアーが弾かれるのを防ぐしなやかなMLパワーのティップを組み合わせたリバーゲームモデル。この組み合わせにより、使えるルアーやフィールドの幅が拡大。河川にとどまらず、汽水湖などでも幅広く活躍する核となる一本。 左にスクロール</v>
       </c>
+      <c r="AH60" t="str">
+        <v/>
+      </c>
+      <c r="AI60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -8636,6 +8996,12 @@
       <c r="AG61" t="str">
         <v>大型プラグを使ったパワーゲームロッド 河川の中下流部から河口域で活躍するパワーモデル。ボラやコノシロ、落ちアユなどの大型ベイトを捕食するランカーを大型ルアーで獲る攻撃的なモデル。 ■特徴 河川の中下流部から河口域で活躍するパワーモデル。ボラやコノシロ、落ちアユなどの大型ベイトを捕食するランカーを大型ルアーで獲る攻撃的なモデル。張りのあるMパワーのティップで重いルアーを的確に操作し、強靭なMHパワーのバットでシーバスを一気に引き寄せる。パワーゲームに合わせてセレクトした握り込みやすい小判型のエアセンサーリールシートによってさらに正確な振り抜きと力強いホールド性を実現。 左にスクロール</v>
       </c>
+      <c r="AH61" t="str">
+        <v/>
+      </c>
+      <c r="AI61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -8737,6 +9103,12 @@
       <c r="AG62" t="str">
         <v>オープンウォーターでの遠投ゲーム 強靭なMパワーのバットで遠投したルアーの着底や水流の変化といった情報を、高感度でショートバイトを弾きにくいしなやかなMLパワーのティップが逃さずキャッチする。 ■特徴 サーフや河口の釣りで重要な遠投性と感度に、さらなる軽快性をプラス。強靭なMパワーのバットで遠投したルアーの着底や、水流の変化といった情報を、高感度でショートバイトを弾きにくいしなやかなMLパワーのティップが逃さずキャッチする。遠投ゲームに合わせてセレクトした握り込みやすい小判型のエアセンサーリールシートによって、さらに正確な振り抜きと操作性を実現。 左にスクロール</v>
       </c>
+      <c r="AH62" t="str">
+        <v/>
+      </c>
+      <c r="AI62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -8838,6 +9210,12 @@
       <c r="AG63" t="str">
         <v>強いミィディアムパワーのバットと、鋭敏なソリッド穂先を組み合わせたことで、遠投性、魚を浮かすパワー、ルアーの水押し感度と、鬼掛け性能を高次元で組み合わせている。8cm～12cm前後のプラグや、20g前後バイブレーションが扱いやすい。水押の弱いシャローランナーやシンキングペンシルを多用する干潟や河川下流部の攻略で特に強い威力を発揮する。 ※通年使えるアイテムです。ソリッド＝バチ抜け専用ではありません。 ■特徴 パワーと究極の水押し感度を合わせ持つ、新BRANZINOならではの至極の1本。シャローマスターの異名を持つ山内勝己監修の新バーサタイルロッド。絶妙なしなやかにチューニングしたメガトップがわずかな流速変化をも感知するとともに、ルアーにバイトしたシーバスをフックに絡めとる。一方、強いバットによって、細身のシンキングペンシルからブレードベイトに至るまで、あらゆるリトリーブ系ルアーに対応する。 左にスクロール</v>
       </c>
+      <c r="AH63" t="str">
+        <v/>
+      </c>
+      <c r="AI63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -8939,6 +9317,12 @@
       <c r="AG64" t="str">
         <v>コノシロや成長したイナッコなどを捕食するランカーシーバスにアジャストしたハイパワーモデルで、12cmクラスのミノーから、ガルバストロングなどの大型プラグまでに対応。MとMHの間に調整された絶妙なパワー感と、レギュラーテーパーによって長時間のキャストでも疲れにくく、ロッドを曲げこんでのパワーファイトも行いやすくなっている。 ■特徴 パワーと操作性を融合させた、新BRANZINOならではの至極の1本。ルアーを精度よくキャストしやすいレギューラーテーパーに設計された軽量ブランクを搭載。中・大型のルアーをピンポイントに撃ち込み、その軽さで自在にトレースするのはもちろん、大型ルアーにアクションを付ける新しい戦略を実現。河川や汽水湖など幅広く活躍するハイパワー&amp;アクティブロッド。大野ゆうき監修モデル。 左にスクロール</v>
       </c>
+      <c r="AH64" t="str">
+        <v/>
+      </c>
+      <c r="AI64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -9040,6 +9424,12 @@
       <c r="AG65" t="str">
         <v>港湾部や運河などのピンポイントにミノーやバイブレーションを精度よく投げてシーバスをヒットに導くショートモデル。</v>
       </c>
+      <c r="AH65" t="str">
+        <v/>
+      </c>
+      <c r="AI65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -9141,6 +9531,12 @@
       <c r="AG66" t="str">
         <v>港湾部やから河川まで幅広く対応するシーバスのオールラウンドモデル。</v>
       </c>
+      <c r="AH66" t="str">
+        <v/>
+      </c>
+      <c r="AI66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -9242,6 +9638,12 @@
       <c r="AG67" t="str">
         <v>河川やサーフでミノーやシンキングペンシル、ワームを駆使してシーバスやフラットフィッシュを狙うロングモデル。</v>
       </c>
+      <c r="AH67" t="str">
+        <v/>
+      </c>
+      <c r="AI67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -9343,6 +9745,12 @@
       <c r="AG68" t="str">
         <v>河川の下流域や堤防、サーフで重たい鉄板バイブレーションや、大型ミノーなどを飛ばしてシーバス&amp;フラットフィッシュを狙うパワーモデル。</v>
       </c>
+      <c r="AH68" t="str">
+        <v/>
+      </c>
+      <c r="AI68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -9444,6 +9852,12 @@
       <c r="AG69" t="str">
         <v>大型河川からサーフまで対応する遠投モデル。フラットフィッシュをメインに、シーバスはもちろん、ライトショアジギングにも対応する。</v>
       </c>
+      <c r="AH69" t="str">
+        <v/>
+      </c>
+      <c r="AI69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -9545,6 +9959,12 @@
       <c r="AG70" t="str">
         <v>運河や都市型河川といった小場所に最適なショートモデル。取り回しが良いので小型のミノーやシンキングペンシル、バイブレーションをピンスポットへ撃ち込みやすく、トゥィッチやジャークなどのロッドワークが軽快。</v>
       </c>
+      <c r="AH70" t="str">
+        <v/>
+      </c>
+      <c r="AI70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -9646,6 +10066,12 @@
       <c r="AG71" t="str">
         <v>小・中型のミノーやシンキングペンシル、ワームを使ったフィネスな釣法に最適なライトモデル。港湾部や運河のバチ抜けだけでなく、ライトゲームやマイクロベイトパターン攻略にも対応。</v>
       </c>
+      <c r="AH71" t="str">
+        <v/>
+      </c>
+      <c r="AI71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -9747,6 +10173,12 @@
       <c r="AG72" t="str">
         <v>おかっぱりやウェーディングを問わないバーサタイルモデル。中・大型ミノーやシンキングペンシルなどに最適。ラインテンションの調整が重要なドリフト釣法からルアーを積極的に動かす釣法までマルチに対応する。</v>
       </c>
+      <c r="AH72" t="str">
+        <v/>
+      </c>
+      <c r="AI72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -9848,6 +10280,12 @@
       <c r="AG73" t="str">
         <v>都市型河川や干潟のウェーディングの釣りで飛距離が必要なときに活躍する遠投モデル。12cmクラスまでのミノーやシンキングペンシル、バイブレーションなどに最適。シーバスが潜む潮流変化を狙い撃てる。</v>
       </c>
+      <c r="AH73" t="str">
+        <v/>
+      </c>
+      <c r="AI73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -9949,6 +10387,12 @@
       <c r="AG74" t="str">
         <v>河川下流部や汽水湖などで出番の多い、大型のシンキングペンシルやスラローム系ルアーをはじめ、中・大型のミノー、バイブレーションまで幅広く対応。高い遠投性能とランカーに負けないバットパワーが魅力。</v>
       </c>
+      <c r="AH74" t="str">
+        <v/>
+      </c>
+      <c r="AI74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -10050,6 +10494,12 @@
       <c r="AG75" t="str">
         <v>水流感度や食い込み性能に優れたしなやかなMパワーのティップと、遠投性、ファイト性能に優れた強いMHパワーのバットを合わせ持つアイテム。10～12㎝前後のルアーを軸としたランカーシーバス狙いに最適。</v>
       </c>
+      <c r="AH75" t="str">
+        <v/>
+      </c>
+      <c r="AI75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -10151,6 +10601,12 @@
       <c r="AG76" t="str">
         <v>高比重のルアーを遠投しての大物狙いに最適なパワーモデル。シーバスをはじめ、フラットフィッシュ、ライトショアジギングまで幅広く対応するバーサタイルモデル。</v>
       </c>
+      <c r="AH76" t="str">
+        <v/>
+      </c>
+      <c r="AI76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -10252,6 +10708,12 @@
       <c r="AG77" t="str">
         <v>水流感度や食い込み性能に優れたしなやかなMLパワーのティップと、遠投性、ファイト性能に優れた強いMパワーのバットを合わせ持つアイテム。幅広いルアーとエリアに対応するバーサタイルな調子。</v>
       </c>
+      <c r="AH77" t="str">
+        <v/>
+      </c>
+      <c r="AI77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -10353,6 +10815,12 @@
       <c r="AG78" t="str">
         <v>高比重のルアーを遠投しての大物狙いに最適なパワーモデル。シーバスをはじめ、フラットフィッシュ、ライトショアジギングまで幅広く対応するバーサタイルモデル。</v>
       </c>
+      <c r="AH78" t="str">
+        <v/>
+      </c>
+      <c r="AI78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -10454,6 +10922,12 @@
       <c r="AG79" t="str">
         <v>高比重のルアーを遠投しての大物狙いに最適なパワーモデル。シーバスをはじめ、フラットフィッシュ、ライトショアジギングまで幅広く対応するバーサタイルモデル。</v>
       </c>
+      <c r="AH79" t="str">
+        <v/>
+      </c>
+      <c r="AI79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -10555,6 +11029,12 @@
       <c r="AG80" t="str">
         <v>河口域やサーフに対応する遠投モデル。12cmクラスのルアーはもちろん、軽量ルアーの遠投も得意とし、シャローランナーや小型のバイブレーションなどを沖へ届け、食い渋るシーバスをナチュラルに誘惑できる。</v>
       </c>
+      <c r="AH80" t="str">
+        <v/>
+      </c>
+      <c r="AI80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -10656,6 +11136,12 @@
       <c r="AG81" t="str">
         <v>河口域やサーフに対応する遠投モデル。12cmクラスのルアーを中心に、高比重のバイブレーションまでしっかりとカバー。絶えず変化する河口の潮を読み解き、シーバスに的確にアプローチする。</v>
       </c>
+      <c r="AH81" t="str">
+        <v/>
+      </c>
+      <c r="AI81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -10757,6 +11243,12 @@
       <c r="AG82" t="str">
         <v>流れの強い河川の下流部や河口域、サーフで活躍するハイパワーモデル。ヘビーバイブレーションやシンキングペンシル、ジョイント系ルアーに対応。ランカーの引きにも屈しない</v>
       </c>
+      <c r="AH82" t="str">
+        <v/>
+      </c>
+      <c r="AI82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -10858,6 +11350,12 @@
       <c r="AG83" t="str">
         <v>サーフでのシーバスやフラットフィッシュ、青物狙いに最適な遠投モデル。しなやかさとパワーのバランスがよく、遠投を続けても疲れにくい。巻き物のミノーはもちろん、ロッド操作の必要なジグも気兼ねなく扱える。</v>
       </c>
+      <c r="AH83" t="str">
+        <v/>
+      </c>
+      <c r="AI83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -10959,6 +11457,12 @@
       <c r="AG84" t="str">
         <v>磯のヒラスズキやマルスズキにも対応するロングモデル。ネジレに強いブランクが、遠投はもちろん、シモリ際にタイトに撃ち込むアキュラシーやシャープさにも貢献。サーフでも扱える軽快さを兼ね備える。</v>
       </c>
+      <c r="AH84" t="str">
+        <v/>
+      </c>
+      <c r="AI84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -11060,6 +11564,12 @@
       <c r="AG85" t="str">
         <v>磯やサーフで活躍するハイパワーモデル。ジグやヘビーシンキングペンシルを大遠投し、沖の潮目やシモリの狙い撃ちが可能。ハイパワーなブランクなので、シーバスはもちろん、小・中型青物狙いにも最適。</v>
       </c>
+      <c r="AH85" t="str">
+        <v/>
+      </c>
+      <c r="AI85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -11161,6 +11671,12 @@
       <c r="AG86" t="str">
         <v>ビッグベイトや大型のトップウォータープラグに特化したハイパワーモデル。強靭なパワーを持ちながらも粘りのあるブランクは、キャスト時の体の負荷を最小限に抑える一方、シーバスの身切れを防ぐ。MAX130g表記だが、下は12cmミノー25gあたりも扱え、上は200gもフルキャストできる。加減すれば、300gまで対応可能。</v>
       </c>
+      <c r="AH86" t="str">
+        <v/>
+      </c>
+      <c r="AI86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -11262,6 +11778,12 @@
       <c r="AG87" t="str">
         <v>運河や都市型河川のおかっぱりを中心に活躍するショートモデル。小・中型のプラグや、20g前後のバイブレーション、ワームにも対応。シーバスやクロダイ、ライトロックフィッシュなどに最適。</v>
       </c>
+      <c r="AH87" t="str">
+        <v/>
+      </c>
+      <c r="AI87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -11363,6 +11885,12 @@
       <c r="AG88" t="str">
         <v>河川の下流域から河口、汽水湖、干潟などの大場所の攻略に最適なロングモデル。中・大型ミノーやウェイク系のプラグ、30gを超えるバイブレーションなどを遠投し、リトリーブして探るスタイルに最適。</v>
       </c>
+      <c r="AH88" t="str">
+        <v/>
+      </c>
+      <c r="AI88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -11464,6 +11992,12 @@
       <c r="AG89" t="str">
         <v>高比重のルアーを遠投しての大物狙いに最適なパワーモデル。シーバスをはじめ、フラットフィッシュ、ライトショアジギングまで幅広く対応するバーサタイルモデル。</v>
       </c>
+      <c r="AH89" t="str">
+        <v/>
+      </c>
+      <c r="AI89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -11565,6 +12099,12 @@
       <c r="AG90" t="str">
         <v>河口やサーフ、堤防などの遠投性能が物を言うポイントに最適なロングモデル。強いバットがバイブレーションやミノーを沖まで飛ばし、大物にも対応する。一方、しなやかなティップがルアー本来のアクションを引き出す。</v>
       </c>
+      <c r="AH90" t="str">
+        <v/>
+      </c>
+      <c r="AI90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -11666,6 +12206,12 @@
       <c r="AG91" t="str">
         <v>小・中型のプラグやワームなどを軽快なロッドワークで操ることができるショートモデル。河川や港でのシーバスやクロダイ、軽いジグやワーム、小型のエギを使ったミドルゲーム、テンヤタチウオまでマルチに対応。</v>
       </c>
+      <c r="AH91" t="str">
+        <v/>
+      </c>
+      <c r="AI91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -11767,6 +12313,12 @@
       <c r="AG92" t="str">
         <v>高比重のルアーを遠投しての大物狙いに最適なパワーモデル。シーバスをはじめ、フラットフィッシュ、ライトショアジギングまで幅広く対応するバーサタイルモデル。</v>
       </c>
+      <c r="AH92" t="str">
+        <v/>
+      </c>
+      <c r="AI92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -11868,6 +12420,12 @@
       <c r="AG93" t="str">
         <v>サーフでのシーバスやフラットフィッシュ、青物狙いに最適な遠投モデル。しなやかさとパワーのバランスがよく、遠投を続けても疲れにくい。巻き物のミノーはもちろん、ロッド操作の必要なジグも気兼ねなく扱える。</v>
       </c>
+      <c r="AH93" t="str">
+        <v/>
+      </c>
+      <c r="AI93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -11969,6 +12527,12 @@
       <c r="AG94" t="str">
         <v>磯やサーフで活躍するハイパワーモデル。ジグやヘビーシンキングペンシルを大遠投し、沖の潮目やシモリの狙い撃ちが可能。ハイパワーなブランクなので、シーバスはもちろん、小・中型青物狙いにも最適。</v>
       </c>
+      <c r="AH94" t="str">
+        <v/>
+      </c>
+      <c r="AI94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -12070,6 +12634,12 @@
       <c r="AG95" t="str">
         <v>運河や都市型河川のおかっぱりを中心に活躍するショートモデル。小・中型のプラグや、20g前後のバイブレーション、ワームにも対応。シーバスやクロダイ、ライトロックフィッシュなどに最適。</v>
       </c>
+      <c r="AH95" t="str">
+        <v/>
+      </c>
+      <c r="AI95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -12171,6 +12741,12 @@
       <c r="AG96" t="str">
         <v>河川の下流域から河口、汽水湖、干潟などの大場所の攻略に最適なロングモデル。中・大型ミノーやウェイク系のプラグ、30gを超えるバイブレーションなどを遠投し、リトリーブして探るスタイルに最適。</v>
       </c>
+      <c r="AH96" t="str">
+        <v/>
+      </c>
+      <c r="AI96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -12272,6 +12848,12 @@
       <c r="AG97" t="str">
         <v>8～10㎝前後のミノーやジグヘッドリグをストラクチャーの奥に撃ち込むための穴撃ちモデル。穂先のブレが少ないのでキャストの正確性やルアー操作性が向上。タフコンディション攻略にも欠かせない。</v>
       </c>
+      <c r="AH97" t="str">
+        <v/>
+      </c>
+      <c r="AI97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98" xml:space="preserve">
       <c r="A98" t="str">
@@ -12374,6 +12956,12 @@
         <v xml:space="preserve">細かなロッド操作を得意とするショートロッド。
 トップウォータールアーのドッグウォークや、ミノーのジャーキング、ワームのワインドまでルアーを積極的に動かす釣りを得意とする。誘って食わす醍醐味を味わえる。魚の口切れ、ハリの伸びを考量してMパワーに設定しているが、69MSよりもややパワーを強く設定。サワラやイナダにも対応できるアイテム。</v>
       </c>
+      <c r="AH98" t="str">
+        <v/>
+      </c>
+      <c r="AI98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -12475,6 +13063,12 @@
       <c r="AG99" t="str">
         <v>あらゆるタイプのルアーに対応するオールラウンドモデル。癖のない調子なので、ピンスポットシューティングからオープンウォーターの遠投まで幅広く対応。一本は持ち込みたいマストアイテム。</v>
       </c>
+      <c r="AH99" t="str">
+        <v/>
+      </c>
+      <c r="AI99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -12576,6 +13170,12 @@
       <c r="AG100" t="str">
         <v>シャローフラットに点在するシモリや、ベイトフィッシュの群れを中・大型ミノーやバイブレーションの遠投で探る釣りに最適な遠投ロッド。強いバットにより、小型青物のキャスティングゲームにも対応。</v>
       </c>
+      <c r="AH100" t="str">
+        <v/>
+      </c>
+      <c r="AI100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -12677,6 +13277,12 @@
       <c r="AG101" t="str">
         <v>8～10㎝前後のミノーやジグヘッドリグをストラクチャーの奥に撃ち込むための穴撃ちモデル。曲がりこむが張りがあり、ブレが少ないブランクスによってキャストの正確性や手返しが向上。投げ込む楽しさが味わえる。</v>
       </c>
+      <c r="AH101" t="str">
+        <v/>
+      </c>
+      <c r="AI101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -12778,6 +13384,12 @@
       <c r="AG102" t="str">
         <v>穴撃ちから遠投まで幅広く対応するベイトのオールラウンドロッド。基本となるミノーやバイブレーションのリトリーブはもちろん、トップウォーターなどの連続トゥイッチなども軽快にこなす。</v>
       </c>
+      <c r="AH102" t="str">
+        <v/>
+      </c>
+      <c r="AI102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -12879,6 +13491,12 @@
       <c r="AG103" t="str">
         <v>100ℊを超える大型のルアーに対応するハイパワーのビッグベイト用ロッド。超重量級のルアーを扱うためのパワーと操作性と、魚をフックアップさせ、口切れを防ぐ柔軟性をベストなバランスに調整。</v>
       </c>
+      <c r="AH103" t="str">
+        <v/>
+      </c>
+      <c r="AI103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -12980,6 +13598,12 @@
       <c r="AG104" t="str">
         <v>サワラをはじめ、イナダ、シーバス、根魚など、あらゆるターゲットを誘惑するブレードジギングモデル。荷重移動が滑らかな強粘ブランク設計により、ルアーの巻きが軽く、バラシにくいのが特長。SLJにも対応する万能性を備え合わせる。</v>
       </c>
+      <c r="AH104" t="str">
+        <v/>
+      </c>
+      <c r="AI104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -13081,6 +13705,12 @@
       <c r="AG105" t="str">
         <v>ナブラに向かってメタルジグやミノー、トップウォータープラグを撃ち込んで青物を誘い出すパワフルなキャスティングモデル。シーバスロッドの派生ならではの遠投性と正確性に優れたキャストが持ち味。</v>
       </c>
+      <c r="AH105" t="str">
+        <v/>
+      </c>
+      <c r="AI105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -13182,6 +13812,12 @@
       <c r="AG106" t="str">
         <v>スピニングモデル運河のストラクチャーゲームや護岸の穴撃ちをはじめとするショアラインに近いエリアで強みを発揮するシューティングモデル。80mm前後のミノーやトップウォータープラグを中心に、ジグヘッドリグなどあらゆるタイプのルアーに対応。癖のない調子のため、オーバーヘッドキャストはもちろん、アンダーハンドやサイドハンドなどのテクニカルなキャストもスムーズにこなすことができる。シーバスゲームをとことん楽しめる一本。</v>
       </c>
+      <c r="AH106" t="str">
+        <v/>
+      </c>
+      <c r="AI106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -13283,6 +13919,12 @@
       <c r="AG107" t="str">
         <v>スピニングモデルオープンウォーターの釣りにウエイトを置いて開発した遠投モデル。中・大型ミノーやトップウォータープラグ、バイブレーションなどを遠投して、シーバスや青物を探るスタイルに最適。ベリーに張りがあるのでワームの操作性も秀逸。フラットフィッシュやロックフィッシュのワームゲームにも対応する。ボートに乗る際に必ず備えておきたいマストアイテム。</v>
       </c>
+      <c r="AH107" t="str">
+        <v/>
+      </c>
+      <c r="AI107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -13384,6 +14026,12 @@
       <c r="AG108" t="str">
         <v>スピニングモデルブリやサワラを意識したハイパワーモデル。ナブラに向かってメタルジグやブレード、ジャークベイト、トップウォータープラグを撃ち込んで青物を誘い出すパワフルなゲームに対応する。大きめのルアーを使うシーバスゲームもカバーする。</v>
       </c>
+      <c r="AH108" t="str">
+        <v/>
+      </c>
+      <c r="AI108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -13485,6 +14133,12 @@
       <c r="AG109" t="str">
         <v>ベイトモデル穴撃ちから遠投まで幅広く対応するベイトのオールラウンドモデル。ボートゲームで広く使われる10cm前後のミノーや20g前後のバイブレーションのリトリーブはもちろん、トップウォータープラグなどの連続トゥイッチも軽快。ショートレングスながら、柔軟に曲がりこんでバラシを防ぐ。</v>
       </c>
+      <c r="AH109" t="str">
+        <v/>
+      </c>
+      <c r="AI109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -13586,6 +14240,12 @@
       <c r="AG110" t="str">
         <v>ベイトモデル大型のトップウォータープラグやメタルジグなどでシーバスや青物にアプローチするハイパワーモデル。ハイパワーながら曲がりこんでキャストしやすい調子と、やや長めのレングスにより、より遠くのナブラにもアプローチできる反面、ミヨシに立った際は足元まできっちりとルアーを操作できる。</v>
       </c>
+      <c r="AH110" t="str">
+        <v/>
+      </c>
+      <c r="AI110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -13687,6 +14347,12 @@
       <c r="AG111" t="str">
         <v>ハートランドのベイトロッドの中で核を成すロッド「疾風」。疾風の名を持ち、軽量～中量級ルアーを意のままに操るモデル、それが疾風七弐Ｍ。 SVF COMPILE-Xの高弾性素材を細身、肉厚のチューブラーパワースリム構造にて仕上げたブランクは、柔軟さとピンとした張りを感じることが出来る、ハートランドならではの感覚を有する。 パワーバンド内では長め、且つ細身に仕上げたグリップは、軽量ルアーの繊細なアプローチ、操作を可能にしながら、遠投性能も確保。スモラバや高比重ノーシンカー、シャッドなどのスモールプラグからミノー、バイブレーションと、Mクラスの食わせのアプローチを完遂することが可能。柔よく剛を制す、柔軟さの中に芯を持つ新たなる疾風が誕生した。</v>
       </c>
+      <c r="AH111" t="str">
+        <v/>
+      </c>
+      <c r="AI111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -13788,6 +14454,12 @@
       <c r="AG112" t="str">
         <v>バスフィッシングの世界に常に独自の発想で新しい釣法を提案し続けるハートランドの20周年記念モデル。「究極の岸釣りバーサタイル」との呼び声の高い「04白疾風」、「07白疾風」に継ぐ次世代の「究極の岸釣りバーサタイル」を村上晴彦とハートランドがダイワテクノロジーで形にした。その名が示す通り、ブランクはSVFコンパイルXを細身肉厚に巻くハートランドのフラッグシップのみに許された唯一無二の製法で作り上げられたもの。またハートランドでは初となるSVFコンパイルXにX45と3DXでアシストされた細身肉厚のブランクは、遊びやパワーロスといったものを一切排除した仕様となっている。さらにガイドには軽量・高剛性・トラブルレスのRタイプフレームと、薄肉・軽量のCリングとNリングを搭載したAGSを採用することでブランクの性能をさらに引き出す。疾風七弐よりも2インチ長くなったことで、遠投性能は疾風七弐以上のものがあるのは言うまでもない。SVFコンパイルXとチューブラーパワースリムによる硬くて曲がるという独特の性能と、ティップの先端から元まで淀みなベンディングカーブを描く村上調子により、テキサスリグやラバージグの掛けモノはもとよりバイブレーション、クランクベイト、ミノーまで扱える、「白疾風」を「疾風」感覚で操作できる珠玉のロッドに仕上がった。</v>
       </c>
+      <c r="AH112" t="str">
+        <v/>
+      </c>
+      <c r="AI112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -13889,6 +14561,12 @@
       <c r="AG113" t="str">
         <v>名作「…（ドットスリー）」をベースにSVFコンパイルXの素性を最大限生かし、さらに細く厚く巻き上げたロングバージョン。二代目ドットスリーのコンセプトを継承した究極の村上的ベイトフィネスロッドを表現するために、超感覚をもたらすSVFコンパイルXの素性を最大限生かすために、敢えてX45フルシールドや3DXという補強構造を取っ払い、チューブラーパワースリム構造をさらに昇華すべく、芯金を細径化し、二代目ドットスリーより細く厚く巻かれたブランクはハートランドのフラッグシップモデルだけに許された特別なコンストラクション。二代目ドットスリーよりも17”伸ばし、細く厚く巻かれたブランクは細く、柔らかいという表現にしてはシャンとしている。シャープでありながらパラボリックにベントする究極に気持ちいい「細・軽・ピン」ロッド。思わず絶句する仕上がりとなっている。</v>
       </c>
+      <c r="AH113" t="str">
+        <v/>
+      </c>
+      <c r="AI113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -13990,6 +14668,12 @@
       <c r="AG114" t="str">
         <v>ハートランド歴代の作品の中で最も支持される不朽の名作「疾風」そして「疾風七弐TYPE-E / TYPE-W」のロングバージョン、それが疾風七伍 AGS。疾風七弐よりも3"伸ばし、レジン量を究極まで減らし繊維量を密入させたSVF COMPILE-Xの弾性率をさらに高弾性化させることで細くそしてシャープに仕上げたのはもとより、竿がベントしたときの反発スピードがさらに高速化され、疾風七弐では届かなかった範囲までを射程範囲にする遠投性能と更なる高感度を手に入れた。SVF COMPILE-XにX45と3DXでアシストされたブランクは細径ロッドの弱点であったロッドのネジレとパワーロスを抑制し、ロッド本来のパワーを引き出す玄人好みのセッティング。SVF COMPILE-Xとチューブラーパワースリムによる強靭な筋肉量がもたらす遠投性能と感度を次世代『AGS』を採用することで昇華。キャスト時にはガイドがたわむことなくロッドに伝達しパワーロスなくロッドを絞り込むことで遠投を実現。村上晴彦とハートランドによりデザインされたテーパーはティップの先端から元まで淀みなくベンディングカーブを描く村上調子となっており、その細さからは想像できないパワーを秘めている。</v>
       </c>
+      <c r="AH114" t="str">
+        <v/>
+      </c>
+      <c r="AI114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -14091,6 +14775,12 @@
       <c r="AG115" t="str">
         <v>「より軽いウェイトのルアーを気持ちよく使いたい」を実現するべくHLロッド史上初となるSMT（スーパーメタルトップ）モデル。ティップ部にAGSよりも更に小口径なトルザイトリングガイドを採用することでチューブラーよりも重量のあるSMT穂先を軽量化することで目感度と手感度に優れたSMTのレスポンスを更に向上させことに成功し、感度はもとより1gジグヘッドリグをキャストしたときに竿先の反発力が失われずリニアに生かせる為、竿先のスウィングスピードが速くなり気持ちの良いキャストフィールを実現しより繊細な操作も可能にした。</v>
       </c>
+      <c r="AH115" t="str">
+        <v/>
+      </c>
+      <c r="AI115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -14192,6 +14882,12 @@
       <c r="AG116" t="str">
         <v>村上晴彦がAGS(エア・ガイド・システム)のアドバンテージを最大限に生かそうと研究を重ねた結果生み出された意欲作。ひとことで言えば0.8号のPEライン＋1.5号のフロロリーダーで50アップを釣るための竿である。「軟らか強い」と、本人はいつものように独自の表現方法でこの竿を語ってくれたが、要するにパワーが変幻自在に移り変わり、釣り人の意図を忠実に反映してくれるということ。だから、軟らかい竿として使いたい時、強い竿として使いたい時、それぞれに言うことを聞いてくれる。「そやからリールを無茶苦茶巻け、魚の顔をこちら側に向けさせることができる」能力を持っている。 ベースは今なお名竿として語り継がれるHL-Z 682LFS-ti 冴掛 Midge direction。これにAGSをコラボさせることにより、PE PERFORMANCEコンセプトのさらなる進化を見た。PEラインにありがちなライントラブルを極限まで低減させ、超軽量リグを気持ちよく扱うため、2000番サイズ以下のスピニングリールと細糸PEの使用を前提に、ダイワ独自のAGSと村上晴彦の理論が融合したこだわりのオリジナルガイドセッティングを施した。AGSの軽さがブランクのポテンシャルを最大限に引き出し、キャスト時の空を切るようなシャープな振り抜けを実現させた。村上が「シュッとまっすぐに飛んでいくで」と評したように、そのフィールは異次元の気持ち良さ。そしてティップ部のブレの少ないライン放出はアキュラシーキャストを生み出し、一般のチタンやSUSフレームガイドよりも高剛性ゆえ、感度も向上。 さらに穂先にはしなやか且つ鋭敏なメガトップを搭載し、チューブラーにはブランクのネジレを極限まで抑えるX45を纏っている。感覚はオールソリッドに近いが、ベリー～バットはチューブラーなので驚くほど軽い。魚を掛けてからも、ガイドがたわまない分、竿がキチンと仕事をしてくれ、穂先から徐々に曲がって美しいカーブを描く。このよどみない曲りはダイワの技術の結晶であるV-JOINTとヘラ合わせの賜物。冴掛 Midge directionを6’10”という絶妙なレングスに延長することで、より幅広いフィールドに対応できるようになった。驚くのはシャッド等のプラグのトゥイッチやジャークにも穂先が負けないこと。したがって、使用ルアーの幅は意外に広い。結果として、これ以上ないと思われるライトリグ万能の「遊び竿」が完成。「今日はこの竿で気持ちよく遊んでみたい…」そんな趣味の世界を最高に満喫させてくれる一竿である。</v>
       </c>
+      <c r="AH116" t="str">
+        <v/>
+      </c>
+      <c r="AI116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -14293,6 +14989,12 @@
       <c r="AG117" t="str">
         <v>バスフィッシングの世界で常に独自の世界を展開し、新たな息吹を吹き込み続けるハートランドの24モデル。 ハートランドらしさを持ちながら、軽さを突き詰めたセッティングは、ルアーやラインの挙動をすべて掌握が可能となり、アングラｰの意のままにリグを操り、ルアーに生命を吹き込む。 2000番台のスピニングリールを組み合わせ、3g前後までのルアーを使用した際には、今までに無い気持ちえぇ体感を約束。 冴掛の名のもとに付けられた「Feather Touch Technical」が表すように、手にした瞬間、まるで羽を持っているかのような錯覚に陥ることだろう。</v>
       </c>
+      <c r="AH117" t="str">
+        <v/>
+      </c>
+      <c r="AI117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -14394,6 +15096,12 @@
       <c r="AG118" t="str">
         <v>バスフィッシングの世界に常に独自の発想で新しい釣法を提案し続けるハートランドの20モデル。ハートランド歴代の作品の中で最も支持される不朽の名作「冴掛」を最先端テクノロジーを搭載しブラッシュアップさせたロングバージョン、それが冴掛 七弐AGS。冴掛より4”伸ばし、SVFコンパイルXの弾性率をさらに高弾性化させることで細くそしてシャープに仕上げたのはもとより、竿がベントしたときの反発スピードがさらに高速化され冴掛では届かなかった範囲までを射程範囲にする遠投性能と冴掛特有の冴え渡る掛け調子をさらに昇華させた。</v>
       </c>
+      <c r="AH118" t="str">
+        <v/>
+      </c>
+      <c r="AI118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -14495,6 +15203,12 @@
       <c r="AG119" t="str">
         <v>ハートランド20周年記念モデル。軽量･高剛性･トラブルレスのRタイプフレームと薄肉･軽量のCリングとNリングを搭載の『AGS』により高感度化を実現。「SVF COMPILE-X」を細身肉厚に巻くフラッグシップのみに許された唯一無二の製法と高弾性化により06震斬では届かなかった範囲までを射程範囲にする遠投性能はもとより、更なる高感度を手に入れた。またハートランドでは初となる「SVF COMPILE-X」に「X45」と「3DX」でアシストされたブランクは遊びやパワーロスといったものを一切排除している。クランク、ミノー、シャッドなどのサーチベイトからテキサスリグ、キャロ、スイムベイトさらにはスモラバ、ネイルリグ、ノーシンカーまでリーダーの太さを使い分けることでルアーの使用範囲を広げて汎用性を高めたロッドになっている。</v>
       </c>
+      <c r="AH119" t="str">
+        <v/>
+      </c>
+      <c r="AI119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -14596,6 +15310,12 @@
       <c r="AG120" t="str">
         <v>不朽の銘竿「冴掛」の冴え渡る掛け心地を継承し、「もっと飛ばしたい、もっと遠投先の感度をあげたい」という誰もが思う「もっと」をPE PERFORMANCEコンセプトと共にダイワテクノロジーで形にした。遠投性能と低伸度の特性を持った細糸PEラインがもたらす感度を次世代『AGS』を採用することで昇華。ハートランドのフラッグシップのみに許された唯一無二の製法であるレジン量を究極まで減らし繊維量を密入させたSVFコンパイルXを細身肉厚に巻き弾性率を高弾性化させることで竿がベントしたときの反発スピードがさらに高速化され、別誂 冴掛では届かなかった範囲までを射程範囲にする遠投性能はもとより、更なる高感度を手に入れた。村上晴彦とハートランドによりデザインされたテーパーはティップの先端から元まで淀みなくベンディングカーブを描く村上調子となっており、まるで柔と剛という相反する要素を両立した仕上がりになっている。</v>
       </c>
+      <c r="AH120" t="str">
+        <v/>
+      </c>
+      <c r="AI120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -14697,6 +15417,12 @@
       <c r="AG121" t="str">
         <v>ハートランドの歴代の作品の中で、独自の外観、スペックを有した08白震斬をベースにSVF COMPILE-Xを最大限に生かすセッティングを施し、より細く、厚く巻き上げたバーサタイルロングスピン、それが「白震斬85AGS」。素材、製法共に進化した22白震斬は、SVF COMPILE-Xの素材感を堪能するべく…83AGS同様に敢えてX45フルシールドや3DXという補強構造を取り払い、チューブラーパワースリム構造により、細く厚く且つシャープに仕上げられた。08白震斬よりも11”伸ばされたブランクは、SVF COMPILE-X、AGSを採用することで、初代と同等以上の操作感をもたらし、幅広いルアーに対応する懐の深いロッドに仕上がった。魚を掛けてからは延べざおの如く弧を描き、持つ者を恍惚な表情へと導く。白い妖刀ここに再臨。</v>
       </c>
+      <c r="AH121" t="str">
+        <v/>
+      </c>
+      <c r="AI121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -14798,6 +15524,12 @@
       <c r="AG122" t="str">
         <v>テーパーを一から見直し、緩急のはっきりしたテーパーに強靭なベリー～バットを持ち合わせ、ボトムのタッチ感やボトムでの繊細な操作にこだわった王道ベイトフィネスロッド、ハーミットパワーチューンに対し、ネコリグのミドストアクションが秀逸な歴代ハーミットの中層ミドストアクションをさらに昇華させたロッド、それが26ハーミット。歴代ハーミットのテーパーを踏襲し、ティップに「“へ”の字テーパー」を施したメガトップRを採用。フルチューブラーではなく、ソリッドティップにすることで、その重みをいかした振り調子を出しやすく、ベイトでのミドストアクションを引き出す。『AGS』と「CWS」を採用し、DAIWAカーボン成形技術とSVFの『トレカ®M46X』、3DXが融合することで、胴ブレせず、ロールをさせずテールだけを震わせるホバストからロールをさせるミドストまでシェイクピッチを自在にコントロールしやすく、スラックラインシェイクのラインの緩急やルアーの操作感度も感じ取れ、水深10ｍ以深のルアーの状態でさえ手に取るように分かる高感度なベイトミドストロッド。Application ：Hover Strolling /Mid Strolling /Bottom Strolling /Neko Rig /Down Shot Rig /No Sinker Rig /Small Rubber Jig /Jighead Rig /Wacky Jighead Rig /Small PlugTECHNOLOGY：SVF NANOPLUS/AGS/CWS/X45フルシールド/3DX/MEGATOP R/ZERO_SEAT</v>
       </c>
+      <c r="AH122" t="str">
+        <v/>
+      </c>
+      <c r="AI122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -14899,6 +15631,12 @@
       <c r="AG123" t="str">
         <v>ネコリグのミドストアクションが秀逸な歴代ハーミットに対し、テーパーを一から見直し、緩急のはっきりしたテーパーに強靭なベリー～バットを持ち合わせ、ボトムのタッチ感やボトムでの繊細な操作にこだわった全国区ベイトフィネスロッド、それが、ハーミットパワーチューン。ティップに「”へ”の字テーパー」を施した高弾性のメガトップを採用することで、ボトムのタッチ感度と軽量リグを手前に引っ張り過ぎず、カバーやストラクチャーにもたれさせたまま揺する操作を両立。高低差のあるストラクチャーでもベリーが仕事をすることでスタックを躱し、繊細な操作が可能。『AGS』と「CWS」を採用し、SVFコンパイルXと『トレカ®M46X』が融合することで、感度と瞬発力が飛躍的に向上。リグの操作感とフッキング性能も昇華することで、今までにないシャープな振り抜きと遠投性能がアップした異次元のベイトフィネスロッドに仕上がった。Application ：Neko Rig /Down Shot Rig /No Sinker Rig /Small Rubber Jig /Free RigTECHNOLOGY：SVF COMPILE-Xナノプラス/AGS/CWS/X45フルシールド/MEGATOP/ZERO_SEAT</v>
       </c>
+      <c r="AH123" t="str">
+        <v/>
+      </c>
+      <c r="AI123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -15000,6 +15738,12 @@
       <c r="AG124" t="str">
         <v>今までの既成概念を覆すジャークベイトなどルアーをアクションさせた時の水中の挙動を把握できるロッド、それが26スペクター。 08ウェアウルフをベースに、『AGS』と「CWS」を採用し、SVFコンパイルXと『トレカ®M46X』が融合することで、シャープな振り抜きと遠投性能、 感度、フッキング性能が飛躍的に向上。 DAIWA伝統のマルチテーパーデザインが投げやすさと遠投性能という相反する要素を高次元で両立。 キャスト時に先端が曲がらない「”へ”の字テーパー」を施したティップがルアーの飛行姿勢を安定させ、ＳＶＦコンパイルＸの『トレカ®Ｍ46Ｘ』を搭載した深く曲がりつつも超高弾性チューブラーの反発力により、今まで体感したことのない軽い力での遠投を可能に。 ティップに「”へ”の字テーパー」にすることで操作系ハードベイトで重要なルアーをアングラーのロッド捌きに対しスポイルすることなくルアーに伝え、 狙い通りのアクションをさせることが出来る。ティップをチューブラーではなく「”へ”の字テーパー」を施した高弾性メガトップソリッドティップと組み合わせることにより、 今まで感じ取れなかった水中のジャークベイトがダートするときに伴うローリングアクションをも引き抵抗(重さ)ではなく振動で感じ取れ、 水中のルアーの状態が手に取るように把握できる未曽有の手感度を有する。 このジャークベイトで感じ取れる操作感度は、ワームフィッシングでも威力を発揮。 操作したときのリグの状態を把握できる操作感度が昇華することで、現在のバスフィッシングシーンに必要なフィネスワーミングにも完全対応する、懐の深いアイテム。 Application ：Jerkbait /Spinnerbait /Topwater Plug /Snagless Neko Rig /Small Rubber Jig / No Sinker Rig /Down Shot Rig/ TECHNOLOGY：SVF COMPILE-Xナノプラス/AGS/CWS/X45フルシールド/MEGATOP/ZERO_SEAT</v>
       </c>
+      <c r="AH124" t="str">
+        <v/>
+      </c>
+      <c r="AI124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -15101,6 +15845,12 @@
       <c r="AG125" t="str">
         <v>ソフトなティップでクランクベイトの弛ませ引きが秀逸な21マシンガンキャストタイプⅠに「“へ”の字テーパー」を組み込むことで、ワイヤーベイトにも抜群の対応力をもたせ、ポッパーやジャークベイトなどの操作系ハードベイトまでハードベイトをバーサタイルに扱えるロッド。それが、26マシンガンキャストタイプ1.5。ソフトなティップではなしえなかったワイヤーベイトの弛ませ引きを可能にし、操作系ハードベイトで繊細且つキレのあるアクションが出せるようになっただけでなく、『AGS』と「CWS」を採用し、DAIWAカーボン成型技術とSVFの『トレカ®M46X』が融合することで、シャープな振り抜きと投げやすさに加え、遠投性能と感度を飛躍的に向上させた。Application ：Jerkbait /Topwater Plug /Spinnerbait /Buzzbait /Vibration /Crankbait /Neko Rig /Small Rubber Jig /No Sinker Rig /Down Shot RigTECHNOLOGY：SVF NANOPLUS/AGS/CWS/X45フルシールド/3DX/ZERO_SEAT</v>
       </c>
+      <c r="AH125" t="str">
+        <v/>
+      </c>
+      <c r="AI125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -15202,6 +15952,12 @@
       <c r="AG126" t="str">
         <v>柔軟なソリッドとは一線を画した硬いソリッドティップに、強靭なチューブラーを接合することで、水中のリグを感じ取り繊細な操作を可能にしたロッド、それが26ハリケーン。『AGS』と「CWS」を採用し、SVFコンパイルXと『トレカ®M46X』が融合することで、ティップで感じた変化を減衰することなく手元へ伝え、前作よりシャープな振り抜きと感度、操作性を飛躍的に向上させた。ティップは、21ハリケーンとは異なり、先端に「”へ”の字テーパー」を施した中弾性ソリッドを搭載することで、高弾性ソリッドやチューブラーティップでは躱してしまい、感じ取れないボトムの変化や小さな凹凸、ラインの重みをも感じ取れることはもとより、タッチ感度と操作感度が飛躍的に向上。ハードボトムでは手元に響く反響感度が秀逸で、リグを操作しているときのラインの遊びやラインに掛かるテンションの緩急を伝えてくれる負荷感度もより感じやすくなっている。チューブラーティップでは成し得ないリグをカバーやストラクチャーにもたれさせたまま誘う操作も「”へ”の字テーパー」のソリッドティップが仕事をすることで、張らず緩めずの適度なモタレ感を演出。「”へ”の字テーパー」の中弾性ソリッドティップとＳＶＦコンパイルＸの『トレカ®Ｍ46Ｘ』の組み合わせが、タッチ感度、操作感度、モタレ感、チューブラーで感じ取れない細かな凹凸を感じ取る感度を両立した異次元のロッドに仕上がっている。Application ：Free Rig/ Texas Rig / Leaderless Down Shot Rig /Rubber Jig /Heavy Down Shot Rig /No Sinker RigTECHNOLOGY：SVF COMPILE-Xナノプラス/AGS/CWS/X45フルシールド/3DX/MEGATOP/ZERO_SEAT</v>
       </c>
+      <c r="AH126" t="str">
+        <v/>
+      </c>
+      <c r="AI126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -15303,6 +16059,12 @@
       <c r="AG127" t="str">
         <v>今までの既成概念を覆すジャークベイトなどルアーをアクションさせた時の水中の挙動を把握できるロッド、それが26スペクター。 08ウェアウルフをベースに、『AGS』と「CWS」を採用し、SVFコンパイルXと『トレカ®M46X』が融合することで、シャープな振り抜きと遠投性能、 感度、フッキング性能が飛躍的に向上。 DAIWA伝統のマルチテーパーデザインが投げやすさと遠投性能という相反する要素を高次元で両立。 キャスト時に先端が曲がらない「”へ”の字テーパー」を施したティップがルアーの飛行姿勢を安定させ、ＳＶＦコンパイルＸの『トレカ®Ｍ46Ｘ』を搭載した深く曲がりつつも超高弾性チューブラーの反発力により、今まで体感したことのない軽い力での遠投を可能に。 ティップに「”へ”の字テーパー」にすることで操作系ハードベイトで重要なルアーをアングラーのロッド捌きに対しスポイルすることなくルアーに伝え、 狙い通りのアクションをさせることが出来る。ティップをチューブラーではなく「”へ”の字テーパー」を施した高弾性メガトップソリッドティップと組み合わせることにより、 今まで感じ取れなかった水中のジャークベイトがダートするときに伴うローリングアクションをも引き抵抗(重さ)ではなく振動で感じ取れ、 水中のルアーの状態が手に取るように把握できる未曽有の手感度を有する。 このジャークベイトで感じ取れる操作感度は、ワームフィッシングでも威力を発揮。 操作したときのリグの状態を把握できる操作感度が昇華することで、現在のバスフィッシングシーンに必要なフィネスワーミングにも完全対応する、懐の深いアイテム。 Application ：Jerkbait /Spinnerbait /Topwater Plug /Snagless Neko Rig /Small Rubber Jig / No Sinker Rig /Down Shot Rig/ TECHNOLOGY：SVF COMPILE-Xナノプラス/AGS/CWS/X45フルシールド/MEGATOP/ZERO_SEAT</v>
       </c>
+      <c r="AH127" t="str">
+        <v/>
+      </c>
+      <c r="AI127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -15404,6 +16166,12 @@
       <c r="AG128" t="str">
         <v>DAIWA伝統のマルチテーパーデザインを採用したウェアウルフ、21ブラックジャックとは異なる血統を汲み、繊細さ、感度、操作性、フッキング性能を最大限引き出し、生まれ変わった高感度ワーミングロッド、それが26ブラックジャック。SVFコンパイルX特有の高反発材料での投げやすさとあらゆるリグへの対応力を両立した21ブラックジャックに対し、15ブラックジャック同様のファストテーパーデザインに設計。26ブラックジャックはティップに、「”へ”の字テーパー」を施すことで、カバーやストラクチャーのスタックは躱しながらも繊細な操作が出来、ボトムやカバーへのタッチ感度とリグの操作感度が飛躍的に昇華。『AGS』と「CWS」を採用し、SVFコンパイルXと『トレカ®M46X』が融合することで、繊細さとショートバイトをも敏速に掛けていくフッキング性能に加え、21ブラックジャックよりバットパワーを上げながらも細径化を実現し、シャープな振り抜きと感度、操作性、遠投性能を向上させた。Application ：Free Rig/ Light Texas Rig / Leaderless Down Shot Rig /Heavy Down Shot Rig /Rubber Jig /No sinker RigTECHNOLOGY：SVF COMPILE-Xナノプラス/AGS/CWS/X45フルシールド/ZERO_SEAT</v>
       </c>
+      <c r="AH128" t="str">
+        <v/>
+      </c>
+      <c r="AI128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -15505,6 +16273,12 @@
       <c r="AG129" t="str">
         <v>ボトムやカバーを感じ取り、チューブラーティップでありながらシェイクをしてもリグを手前に引っ張り過ぎず、カバーやストラクチャーにもたれさせたまま揺する操作が秀逸な08ハスラーをベースに、微かなバイトをとって積極的に掛けていくことを可能にしたワーミングロッド、それがグランディー　フィール　”ハスラー69”。『AGS』と「CWS」を採用し、SVFコンパイルXと『トレカ®M46X』が融合することで、シャープさと感度が飛躍的に向上。ハスラー調子と言われる歴代STEEZシリーズの中でもハスラーのみが可能としたリグの操作感と瞬発的なフッキング性能は残しつつ、ティップに、「”へ”の字テーパー」を施すことで、カバーやボトムのタッチ感度とリグの操作感度がさらに昇華。タフなフィールドでも繊細且つアグレッシブなワーミングを完遂する。Application ：Texas Rig /Free Rig /Leaderless Down Shot Rig /No Sinker Rig /Rubber Jig /Swim Jig /Swimbait /SpinnerbaitTECHNOLOGY：SVF COMPILE-Xナノプラス/AGS/CWS/X45フルシールド/ZERO_SEAT</v>
       </c>
+      <c r="AH129" t="str">
+        <v/>
+      </c>
+      <c r="AI129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -15606,6 +16380,12 @@
       <c r="AG130" t="str">
         <v>コンパクトスウィングによるハイスピードキャストで、ピンスポットを射抜くアキュラシー性能が秀逸なマシンガンキャストタイプⅡと、重量級ルアーに負けないパワーと感度を併せ持ち、狙い澄ましたカバーやピンスポットを打ち抜き、遠投も可能にしたマシンガンキャストⅢの中核をなすロッド、それが、マシンガンキャストタイプ2.5。初代から続くワイヤーベイトに特化させたマシンガンキャストタイプⅡの血統を汲みつつ、2oｚクラスのスイムベイトまで対応するバーサタイル性を持ちあわせ、『AGS』と「CWS」を採用し、DAIWAカーボン成型技術とSVFの『トレカ®M46X』が融合することで、6’10”とは思えないシャープな振り抜きと投げやすさに加え、遠投性能と感度を飛躍的に向上させた。Application ：Spinnerbait /Buzzbait /Bladed Jig /Swim Jig /Vibration /Swimbait /Big Bait /Rubber Jig /Texas Rig /Leaderless Down Shot Rig /No Sinker Rig /Topwater Plug /FrogTECHNOLOGY：SVF NANOPLUS/AGS/CWS/X45フルシールド/3DX/ZERO_SEAT</v>
       </c>
+      <c r="AH130" t="str">
+        <v/>
+      </c>
+      <c r="AI130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -15707,6 +16487,12 @@
       <c r="AG131" t="str">
         <v>"バックスライドノーシンカーからジグ・テキサスのライトフリップまで幅広く使え、フルパワーフッキングでしっかり掛けつつもアワセ切れさせないDAIWA伝統のマルチテーパーデザインを踏襲し、新材料の搭載で生まれ変わったロッド、それが26ハリアー。ティップはHパワー、バットがMHパワーの初代バトラーハリアーから続く伝統のテーパーバランスを踏襲しながらもティップに「”へ”の字テーパー」を搭載することで、手感度が飛躍的に向上。スタックを躱し、ラインスラックを作りやすく、繊細な操作を実現。『AGS』と「CWS」を採用し、SVFコンパイルXと『トレカ®M46X』、マルチテーパーデザインが融合することで、感度が飛躍的に向上するだけでなく、パラボリックに曲がるバットがルアーを鋭く弾き出し、シャープなフッキングを決める。Application : Rubber Jig /Texas Rig /Leaderless Down Shot Rig /Free Rig /Heavy Carolina Rig / Swim Jig / No Sinker / Swimbait / Spinnerbait / FrogTECHNOLOGY：SVF COMPILE-Xナノプラス/AGS/CWS/X45フルシールド/3DX/ZERO_SEAT</v>
       </c>
+      <c r="AH131" t="str">
+        <v/>
+      </c>
+      <c r="AI131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -15808,6 +16594,12 @@
       <c r="AG132" t="str">
         <v>より繊細にリグを扱い、より繊細なバイトをとっていくフィネスの究極、それを実現したのがグランディー　フィール　”フィネスゼロ”。『AGS』と「CWS」を採用し、SVFコンパイルXと『トレカ®M46X』が融合することで、従来のロッドでは感知できない超軽量リグでのディープフラットや10ｍ以深のディープの微小な変化やリグの重みを感知しながらリグを操り、居食いをするスモールマウスや低活性時の微弱なバイトを感じ取る、繊細な超先調子且つ張りを抑えたソリッドティップを搭載。視覚で捉えるだけでなく、振動伝達に優れるSVFコンパイルXのチューブラーにより手元でも捉え操作し、ショートバイトも離されるまえにシャープにフッキングすることができる。Application ：Down Shot Rig /Neko Rig /No Sinker Rig /Small Rubber Jig /Jighead Rig /Wacky Jighead RigTECHNOLOGY：SVF COMPILE-Xナノプラス/AGS/CWS/X45フルシールド/MEGA TOP/ZERO_SEAT</v>
       </c>
+      <c r="AH132" t="str">
+        <v/>
+      </c>
+      <c r="AI132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -15909,6 +16701,12 @@
       <c r="AG133" t="str">
         <v>初代STEEZから続くミドストロッドの代名詞、グレイゴーストの名を継承し、大幅に進化したホバスト、ミドスト、ボトストロッド、それがグレイゴースト64。前作からテーパーを大きく見直し、BLX　S64ULのテーパーを踏襲。『AGS』と「CWS」を採用し、DAIWAカーボン成形技術とSVFの『トレカ®M46X』が融合することで、ロールをさせずテールだけを震わせるホバストからロールをさせるミドストまでシェイクピッチを自在にコントロールしやすく、今までのULのミドストロッドでは不可能とされていたマイクロホバストから5”クラスのパワーミドスト、逃がしのアクションまで幅広いルアー・アクションに対応。ティップに「”へ”の字テーパー」を施すことで、スラックラインシェイクのラインの緩急やルアーの操作感度も感じ取れ、水深10ｍ以深のルアーの状態でさえ手に取るように分かる高感度なミドストロッド。Application ：Hover Strolling /Mid Strolling /Bottom Strolling /Down Shot Rig /Neko Rig /No Sinker Rig /Small Rubber Jig /Jighead Rig /Wacky Jighead Rig /Small PlugTECHNOLOGY：SVF NANOPLUS/AGS/CWS/X45フルシールド/3DX/ZERO_SEAT</v>
       </c>
+      <c r="AH133" t="str">
+        <v/>
+      </c>
+      <c r="AI133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -16010,6 +16808,12 @@
       <c r="AG134" t="str">
         <v>TDバトラー時代から続く往年のバーサタイルスピニングの代名詞、ヘルファイヤーの名を継承するアルティメットバーサタイルスピン、それがヘルファイヤー66。ライトリグ寄りのバーサタイルスピンは数ある中で、シャッドのただ巻きからミノーのトゥイッチ、PEのメタルバイブまで一本で完璧にこなす真のバーサタイル性を魅せる。『AGS』と「CWS」を採用し、DAIWAカーボン成形技術とSVFの『トレカ®M46X』が融合することで、バットパワーを落とすことなく細径化と高反発化を実現し、投げやすさと遠投性能、操作性、感度を飛躍的に向上させた。Application ：Small Rubber Jig /Neko Rig /Jighead Rig /Wacky Jighead Rig /No Sinker Rig /Down Shot Rig /Shad /Minnow /Propbait /Bug lure /Jerkbait /Topwater Plug /Crankbait /Metal VibrationTECHNOLOGY：SVF NANOPLUS/AGS/CWS/X45フルシールド/3DX/ZERO_SEAT</v>
       </c>
+      <c r="AH134" t="str">
+        <v/>
+      </c>
+      <c r="AI134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -16111,6 +16915,12 @@
       <c r="AG135" t="str">
         <v>Shore Competition　SC BAIT FINESSE　MULTI-TAPER タフ化が進む現代のフィールドで釣り勝つべく、前作の優位性を維持しつつ随所にブラッシュアップを施し完成した、ショアコンペティション（SC）のベイトフィネスロッド、それが24ウェアウルフ。 前作19ウェアウルフは08ウェアウルフから踏襲されたMパワーのティップにMLパワーのバットを持ち合せたDAIWA伝統のマルチテーパーデザインに超感覚素材であるSVFコンパイルXを纏った唯一無二のロッド。 バットまでパラボリックに曲がり、SVFコンパイルX特有の強いの反発力で軽量ルアーを鋭く弾き出す最大の特徴は堅持しながらも、「より繊細に、より強く」進化した。 嘗ては疑いなく食ってきたスモラバの吊るしやカバーネコリグも昨今は疑い食いによる吸い込みの弱いバイトが多発。それらを喰い込ませ確実にフッキングさせる為にウェアウルフの特長でもある強いティップに繊細さと追従性を加えながらも手感度は損なわない「メガトップR」をバスロッドで初めて搭載。さらにメガトップRのソリッドティップ化により、ボトムの感知能力とボトム（起伏）のモタレ感を付加することで操作性が飛躍的に向上。 加えて08ウェアウルフから19ウェアウルフでの過度な軽量化からの脱却。パラボリックにベンドするスローテーパーのバットと肉薄化により、フッキングの瞬間にグネる感触があったバットを、パワーアップでの解決ではなく、テーパーはそのままに肉厚化と3DXを纏うことで解決。さらにガイドバランスを見直すことで、ブランクのパワーを最大限引き出すことに成功しフッキングパワーとリフティングパワーが向上。 SVFコンパイルXとマルチテーパーデザインによるキャスタビリティー、高感度、高反発力を維持しつつ、操作性、食い込みの良さ、瞬時のフッキングレスポンス、リフティングパワー、それら全てが向上したことによるトータル性能は未踏の領域へ。ウェアウルフは他の追随を許さないまま、さらなる独走に入る。 ■LURE APPLICATION Snagless Neko Rig / Small Rubber Jig / No Sinker Rig / Down Shot Rig ■TECHNOLOGY SVF COMPILE-Xナノプラス／メガトップR／X45フルシールド（＝X45コブラシールド）／3DX／エアセンサーシート</v>
       </c>
+      <c r="AH135" t="str">
+        <v/>
+      </c>
+      <c r="AI135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -16212,6 +17022,12 @@
       <c r="AG136" t="str">
         <v xml:space="preserve">ショアで閃光を放つファストムービング決定打 「最多でも6本で、陸の、自分のゲームを完成したい」 ショアを舞台に、今なお王者の称号を欲しいままにする熱き魂、川村光大郎。2016年にSTEEZ SC（＝Shore Competition）シリーズを立ち上げ、これまでにFIRE WOLF、KING VIPER、SC WEREWOLFと3本の名竿を仕上げてきたが、次に目線を向けたのはクランキングロッドだ。複数本を常備することが難しいショアゲームという特性上、バーサタイル性を第一義に定めたことはもはや言うまでもない。 「求めたのは、陸で出番が多いシャッドクランクからフルサイズ、そしてクローラーベイトまで幅広く使えること」 かつて巻きに多用したグラスモデルのBL+661MLFB-Gはクランク全般に好相性を見せるが抵抗の弱いルアーでは可も不可もない。一方、06&amp;16BLITZを始めとする低弾性カーボンLow Modulus採用モデルでは、大型ルアーまでの汎用性に期待できない。開発は難航を極め、幾度ものテストが繰り返された。 「許容範囲が広く、シャープに振り抜け、小さな振動も拾うために、2年の歳月を費やした。細かな修正を繰り返し、ようやく辿り着いたのは“SVFグラス”であり、繊細なティップという答えだった」 カーボンより弾性率の低いグラス素材を採用した繊細なティップは、如何なるルアーの動きもスポイルせず、バイト時には優れた追従性で「反転すれば勝手に乗る」特性を発揮。グラスマテリアルの中でも樹脂量を極限まで削減したSVFグラスによるグラテック構造は、巻き感度を格段に引き上げることにも成功している。 またしなやかなティップから急激にファストテーパーで立ち上がるベリー～バットにはLow Modulusをコンポジット。X45フルシールドが全身を締め上げ、レギュラークラスクランクでシャープなキャストが決まることは無論、20g前後のクローラーベイトも余裕で振り込め、カバー周りから素早く魚を引き剥がすことも可能に。 ハンドル部はシングルでもダブルでも投げやすいマルチなミドルレングス。グリップ部は使い込むほどに、歴戦の思いが刻まれていくハイグレードコルク。バットエンドは干渉を防ぎ、当たり負けしないラウンド形状をセレクト。 さらにSTEEZ史上、異例となるカラードブランク“川村ブラウン”を採用。ファストムービング機の伝統色を意識しつつ輝きを増し、次なる巻きの世界へと挑む川村の想いがそこに見える。 ■LURE APPLICATION Shad Crankbait / Small Crankbait / Mid Crankbait / Flatside Crankbait / Shad Plug / Minnow /Popper /Pencilbait / Clawler bait ■TECHNOLOGY SVF GLASS／X45フルシールド（＝X45コブラシールド）／エアセンサーシート  </v>
       </c>
+      <c r="AH136" t="str">
+        <v/>
+      </c>
+      <c r="AI136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -16313,6 +17129,12 @@
       <c r="AG137" t="str">
         <v>Shore Competition　SC BAIT FINESSE　MULTI-TAPER タフ化が進む現代のフィールドで釣り勝つべく、前作の優位性を維持しつつ随所にブラッシュアップを施し完成した、ショアコンペティション（SC）のベイトフィネスロッド、それが24ウェアウルフ。 前作19ウェアウルフは08ウェアウルフから踏襲されたMパワーのティップにMLパワーのバットを持ち合せたDAIWA伝統のマルチテーパーデザインに超感覚素材であるSVFコンパイルXを纏った唯一無二のロッド。 バットまでパラボリックに曲がり、SVFコンパイルX特有の強いの反発力で軽量ルアーを鋭く弾き出す最大の特徴は堅持しながらも、「より繊細に、より強く」進化した。 嘗ては疑いなく食ってきたスモラバの吊るしやカバーネコリグも昨今は疑い食いによる吸い込みの弱いバイトが多発。それらを喰い込ませ確実にフッキングさせる為にウェアウルフの特長でもある強いティップに繊細さと追従性を加えながらも手感度は損なわない「メガトップR」をバスロッドで初めて搭載。さらにメガトップRのソリッドティップ化により、ボトムの感知能力とボトム（起伏）のモタレ感を付加することで操作性が飛躍的に向上。 加えて08ウェアウルフから19ウェアウルフでの過度な軽量化からの脱却。パラボリックにベンドするスローテーパーのバットと肉薄化により、フッキングの瞬間にグネる感触があったバットを、パワーアップでの解決ではなく、テーパーはそのままに肉厚化と3DXを纏うことで解決。さらにガイドバランスを見直すことで、ブランクのパワーを最大限引き出すことに成功しフッキングパワーとリフティングパワーが向上。 SVFコンパイルXとマルチテーパーデザインによるキャスタビリティー、高感度、高反発力を維持しつつ、操作性、食い込みの良さ、瞬時のフッキングレスポンス、リフティングパワー、それら全てが向上したことによるトータル性能は未踏の領域へ。ウェアウルフは他の追随を許さないまま、さらなる独走に入る。 ■LURE APPLICATION Snagless Neko Rig / Small Rubber Jig / No Sinker Rig / Down Shot Rig ■TECHNOLOGY SVF COMPILE-Xナノプラス／メガトップR／X45フルシールド（＝X45コブラシールド）／3DX／エアセンサーシート</v>
       </c>
+      <c r="AH137" t="str">
+        <v/>
+      </c>
+      <c r="AI137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -16413,6 +17235,12 @@
       </c>
       <c r="AG138" t="str">
         <v>Shore Competition　SC SWIMBAIT/BIGBAIT 現代のタフ化が進むフィールドで釣り勝つべく、ビッグベイト・スイムベイトの実釣性能を最大限引き出し、STEEZシリーズ最強レベルのバットパワーを持つショアコンペティション（SC）のSB（スイムベイト・ビッグベイト）ロッド、 それがストラトフォートレス68。 ビッグベイト・スイムベイトの遠投性能、近距離を高精度に撃ち込むピッチング性能、バイトに持ち込むために水中のルアーを水に絡ませた艶めかしいアクションを繊細かつ正確に演出させる操作性、そして水中のルアーの状態をアングラー側に伝える感度、突発的なバイトも弾かずしっかり絡めながらも太軸フックを貫通させるバットパワー、強さの中に安心して魚とファイト出来る適度なしなやかさ。 これら相反する要素を絶妙なバランスで一本に纏め上げ完成させたのが、ストラトフォートレス68。 それらを実現したのが、ティップをスティッフにすることで近距離のピッチング性能を向上。ティップを硬くする一方でソリッドティップにすることによりビッグベイトのノリの良さを大幅に向上。 さらに高弾性ソリッドを採用することで、手感度とリニアな操作性を手に入れた。 チューブラーは中弾性カーボンを採用することで硬さの中にもしなやかさを持たせつつ、バットを3DXでアシストする事で、遠投性能を引き出した。 オカッパリのスイムベイト・ビッグベイトで釣り勝つ為に相反する必要な要素を具備し、いまを釣り勝つSBロッドに仕上がった。 ■LURE APPLICATION Swim Bait / Big Bait / Crawlerbait / Alabama Rig / Rubber Jig / Texas Rig / Leaderless Down Shot Rig / No Sinker Rig / Spinnerbait ■TECHNOLOGY SVFナノプラス／X45フルシールド（＝X45コブラシールド）／3DX／メガトップ／エアセンサーシート</v>
+      </c>
+      <c r="AH138" t="str">
+        <v/>
+      </c>
+      <c r="AI138" t="str">
+        <v/>
       </c>
     </row>
     <row r="139" xml:space="preserve">
@@ -16519,6 +17347,12 @@
 この22ファイヤーウルフの性能を維持したまま、センターカット2PCS化することで、携行性を高めつつVジョイントαを搭載することで、通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上。
 釣り勝てるセンターカット2PCSに仕上がった。 ■LURE APPLICATION Snagless Neko Rig /No Sinker Rig /Down Shot Rig /Texas Rig /Leaderless Down Shot Rig /Free Rig /Rubber Jig /Spinnerbait /Vibration /Crankbait /Crawlerbait ■TECHNOLOGY SVFナノプラス／X45フルシールド／Vジョイントα／メガトップ</v>
       </c>
+      <c r="AH139" t="str">
+        <v/>
+      </c>
+      <c r="AI139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140" xml:space="preserve">
       <c r="A140" t="str">
@@ -16624,6 +17458,12 @@
 この22ファイヤーウルフの性能を維持したまま、センターカット2PCS化することで、携行性を高めつつVジョイントαを搭載することで、通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上。
 釣り勝てるセンターカット2PCSに仕上がった。 ■LURE APPLICATION Snagless Neko Rig /No Sinker Rig /Down Shot Rig /Texas Rig /Leaderless Down Shot Rig /Free Rig /Rubber Jig /Spinnerbait /Vibration /Crankbait /Crawlerbait ■TECHNOLOGY SVFナノプラス／X45フルシールド／Vジョイントα／メガトップ</v>
       </c>
+      <c r="AH140" t="str">
+        <v/>
+      </c>
+      <c r="AI140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -16725,6 +17565,12 @@
       <c r="AG141" t="str">
         <v>Shore Competition　SC HEAVY VERSATILE　MULTI-TAPER タフ化が進む現代のフィールドで釣り勝つべく、前作の優位性を維持しつつ、各所にブラッシュアップを施し完成度を高めた、ショアコンペティション（SC）のヘビーバーサタイルモデル、それが24キングヴァイパー。 前作18キングヴァイパーが上限3.5oz.のビッグベイトまで対応したのに対し、24キングヴァイパーは現在のタフなフィールドに対応するべく、適合ルアータイプはそのままに、前作に対して適合ルアーウェイトを引き下げ、上限を3oz.にまで引き下げた。その狙いは使用頻度の高い3/8oz.までのジグ&amp;ワームや、2oz.クラスのビッグベイトに焦点を合わせたパワーランクにすることで、大半の実釣性能を高めることにある。さらにヘビーウェイトのスピナーベイト、そしてマグナムクランクといったファストムービングルアーへの対応力が向上したことも特筆すべき点。また、「硬く、均一なテーパーで曲がるロッド」と評された18キングヴァイパーは強いティップで、バットまでパラボリックに曲がるスローテーパーであったが、24キングヴァイパーにはさらにそれらのリグを繊細に扱えるティップが求められた。 ティップは繊細な操作性と感度を生み出す、22ファイヤーウルフでも採用された先端への字のレギュラーテーパーに、バットはあらゆるウェイトのキャストでも打点がブレない18キングヴァイパーのスローテーパーを踏襲。これら相反するテーパーをマルチテーパーデザインにより1本に纏め上げた。 キャスタビリティー、フルベンドならではの粘り感を残しつつ、感度、操作性、瞬時のフッキングレスポンスを兼備することで、いまを釣り勝つヘビーバーサタイルロッドに生まれ変わった。 ■LURE APPLICATION Rubber Jig / Texas Rig / Leaderless Down Shot Rig / No Sinker Rig / Spinnerbait / Crawler bait / Swim bait / Big Bait / Magnum Crankbait / Frog ■TECHNOLOGY SVFナノプラス／X45フルシールド（＝X45コブラシールド）／3DX／エアセンサーシート</v>
       </c>
+      <c r="AH141" t="str">
+        <v/>
+      </c>
+      <c r="AI141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -16826,6 +17672,12 @@
       <c r="AG142" t="str">
         <v>その軽さから、まるでショートロッドを扱うがごとく軽快にロッドワークが可能な、ヘビーロッドの概念を覆すロッド。ソリッドティップを搭載することで、ジグのスイミングをはじめ、テキサスリグや高比重ノーシンカーなど打ちモノまでこなす懐の広さを持つ。ひとたび魚を掛ければ溢れるバットパワーでバスに主導権を渡すことなくランディングに持ち込む。パワーと操作性を併せ持つ新たなヘビーロッドが完成した。 「7ft3inのヘビーパワーで、しかもソリッドティップ……、『自分には関係ないロッドだな』って、番手だけを見て敬遠されちゃったらイヤですね……。一回でイイから触ってみてほしいですね」 藤田のこの言葉を聞いたDAIWAワークスエンジニアは心の中でツッコんだという。C73H-SV・STの開発が立ち上がった当初、藤田は次のように言っていたからだ。 「撃ちモノ（ジグや重めのリーダーレスダウンショットなど）をよくやるので、そういう釣りを極めたいという思いがあって。リグは重いけれど、感覚的には繊細に扱える、そういうマニアックな釣りに適した、マニアックなロッドが欲しいです」 マニアックなロッドなのだから「自分には関係ない」と思われても本望ではないかと、エンジニアはツッコんだわけだ。それに対する藤田の弁解を聞こう。 「もともとはカバー撃ちとジグスト用に作り始めたんです。とくにジグストでロッドワーク時の糸鳴りを抑えたかった。パンパン鳴るのがすごくイヤで、ジグのアクションもカドがある感じになるし。ラインがジグや水とうまく馴染んでほしいとか、ジグの軌道に合わせてティップがちょっとだけ入ってほしいとか、設計の方に細かく要望を伝えながら作り込みました」 このロッドの特性が最も発揮されるのはフロロ20lb.を組んだときだ。「C73H-SV・STは撃ちモノ用のパワー系ですから、フロロ20lb.の重さとたるみを利用したときにベストな使用感が得られるようにしました」と藤田。「フッキング性能もとても高くて、強いけれど硬すぎないからミス（バラシ）も起きにくい」という。ただし、イイ出来だから多くの人に手に取ってほしくなったわけではないという。 ―― マニアックとの乖離 「シャープだけれどよく曲がって反発するSTEEZ RCブランクのおかげで、専用性だけでなく汎用性も上がっちゃったんです。ジグや各種リグから操作系のビッグプラグやスイムベイトまで“とりあえず使える”レベルじゃなくて、“充分扱いやすい”中・重量級バーサタイルです。本当に、結果的にこうなっちゃった。番手から受ける印象をイイ意味で覆すロッドなので、たくさんの方に触ってほしくなったんです」 ソリッドティップでありながら、 スティッフなティップ～ベリーを持ち、 バットまでベントするテーパーがバーサタイル性を司る</v>
       </c>
+      <c r="AH142" t="str">
+        <v/>
+      </c>
+      <c r="AI142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -16927,6 +17779,12 @@
       <c r="AG143" t="str">
         <v>持ったものを新たな領域にいざなう、フィネスを極めるロッド。圧倒的な軽量感と、繊細なソリッドティップと突き詰められたブランクは、ルアーの挙動はもとより、ラインテンションの変化もアングラーに伝達。あらゆる情報をアングラーに伝えることで、バスの微細なバイトにも即座に反応し掛けることが可能に。軽量ダウンショットやネコリグでのディープの攻略がこのロッドの真骨頂。今までのフィネスロッドの概念を覆すロッドが完成した。 藤田京弥が監修するSTEEZ Real Controlは“結果的に”数多くのDAIWAテクノロジーによって完成した。藤田のなかにはバスロッドの明確な理想像があり、それを具現するために必要なテクノロジーはどれなのか、一つ一つ吟味しながら開発は進められた。例えば、リング以外をカーボンで構成するAGS＋CWSの高感度ガイドシステムも、同じブランクに金属フレーム＋スレッドラップで組んだプロトタイプと藤田自身があらためて比較検討したうえで、「前者しかない」という結論に至っている。 「このS510XUL-SV・STは、さんざんテストしてきた僕が、使うたびにいまだに感動しちゃう、それくらい凄いフィネススペシャルです。手にするだけでワクワクします。これは、最初にプロトタイプを触ったときから凄かった。軽くてシャープなのに、しなやかできれいに曲がって、反発力で魚を浮かせられるパワーまである。 感度は感動しますよ、シャレじゃなくて（笑）。ラインの重さがすごく伝わってくるんです。空中でたるんだラインの重さ、水中でラインに掛かる水圧の重さ、ダウンショットリグだったらシンカーの重みの手前にワームの存在をはっきり感じます。ライン、シンカー、ルアーの状態が把握できるから、イメージしたとおりに操ることもできる。 プロトタイプを触った時点で理想の実現を予感した藤田は、このロッドの目標を「水深10mオーバーで0.9gのリグを自在にコントロールできるロッド」とし、完成させた。 「水深10mで0.9gだと何をしているのかわからないのが普通です。ちょっとでも風が吹いていたり、ボートに乗っていたりすると、とくに。でも、このロッドならわかっちゃう。ボトムの状態はもちろんわかる。そこが砂地で引っ掛かるものがないフラットだとしても、釣りをしていて楽しくなる。すべてを把握して“操縦”できるからです」 繊細かつ操作性に優れ、 手感度を司るメガトップソリッドティップと ULクラスのバットパワーを兼備</v>
       </c>
+      <c r="AH143" t="str">
+        <v/>
+      </c>
+      <c r="AI143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -17028,6 +17886,12 @@
       <c r="AG144" t="str">
         <v>正確無比なキャスト性能、水中を見ているかのような感度、意のままにルアーを操る操作性、スピニングに求められるあらゆる要素を高次元で持ち併せた、フィネスワーミングロッド。ネコリグ、ダウンショットリグ、ノーシンカーリグなどのフィネスリグ全般を使用できるオールマイティーさを持つ。現代のバスフィッシングにおいて、金字塔となるスピニングロッドが完成した。 「藤田が『61L』というスペックに強くこだわり、長期間のテストで徹底的に作り込まれたロッド」……とはならなかった。藤田とDAIWAワークスエンジニアが密に連携することで、互いの理想と技術を共有した結果、試作した数タイプの初期プロトのなかに「奇跡の一本」が混ざったのである。 藤田「 最初からイメージどおりだったので、コスメ以外はほぼ変えていませんよね」 エンジニアA「 はい。藤田さんは“理想のイメージ”が明確なんです。だから、それにピタリと重なれば一発OKもある。逆にちょっとでもズレがあると『違いますね』と言われ続ける。いずれにせよ、開発の方向性がブレたり、後戻りしたりすることがない。道具に対する感性も鋭くて、テストの状況に左右されずにモノ単体で評価できる。『いまの状況だと前のサンプルのほうが……』とはならない」 エンジニアB「 印象に残っているのが細かな修正点を洗い出しているとき、藤田さんに『Bさんならどうしますか？』と聞かれたことです。モノを良くするために謙虚で貪欲だなと。この聞き方って要は、DAIWAと私には何ができますか？ってことですよね。かるく挑発された気になって燃えました（笑）」 藤田「 そんなつもりはありませんでしたよ（笑）。ただDAIWAには僕の知らない製竿技術がまだまだあるんだろうなって」 ―― JBトップ50優勝とB.A.S.S.エリート昇格 S61L-SVは、あらゆる軽量級リグの“操縦”を可能とし、シャッドなどのプラッギングにも対応するライトバーサタイル機なのだが、その汎用性を語るうえでは藤田の日米における活躍も欠かせない。 2022年の藤田はJBトップ50とB.A.S.S.オープンにダブルエントリーした。そして、トップ50では遠賀川での開幕戦を勝ち、年間ランキングは1戦欠場しながらも5位。オープン・ノーザン地区では年間2位に入り、参戦初年度でエリート行きのチケットを獲得するという偉業を成した。 フィールド環境、魚のサイズやクセ、組み合わせるラインやルアー、何もかもがバリエーションに富む日米すべての試合において、藤田はこのS61L-SVでバスを手にしたのである。 ティップに張りを持たせつつも、 先端から曲がり、負荷に応じベリー～バットへ スムーズにベントするテーパーを採用</v>
       </c>
+      <c r="AH144" t="str">
+        <v/>
+      </c>
+      <c r="AI144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -17129,6 +17993,12 @@
       <c r="AG145" t="str">
         <v>PEラインを使用し、表層から水面下1mの攻略、そしてサイトフィッシングにて魚を確実に仕留めるモデル、それがS63UL-SV。軽量且つ張りを持ち、負荷に応じて素直に曲がり込むブランクは、正確無比なキャスト性能とルアー操作性を持ちながら、フッキング時には、魚と近距離且つ低伸度ラインを使用することにより発生する強い衝撃を受け止め、ラインブレイクすることなくランディングまで持ち込む。素直なテーパーを採用することで、ノーシンカーリグや表層系ルアーをはじめ、シャッドなどの小型プラグ、ミドストやホバストといった釣法にも高次元に対応。 代えの利かないサイトスペシャル RCシリーズのスピニングロッドで6ft.3in.のウルトラライトパワー、素材が「SVFコンパイルXナノプラス」とくれば、水中の変化に指先で触れているかのごとき高感度を期待されるかもしれない。しかし、このS63UL-SVは、23モデルのS510XUL-ST・STやS61L-SVとは違う。 素材は低レジン・高密度カーボン繊維のSVFコンパイルXナノプラスだが、全体的にしなるテーパーに仕上げた。そのULブランクのなかで、ティップだけはワンランク上のパワーのS61L-SVに近い設定だ。強めのティップと、よくしなるバットを、ベリーでなめらかに繋いだS63UL-SVのテーパー表記はレギュラーだが、見る人によってはスローと表現しそうなほど緩やかなカーブを描く。 ボトム感度にあまり期待してはいけない。S63UL-SVを使う時、感度を担うのはアングラーの“目”であり、このロッドは藤田京弥のザ・サイトスペシャルだからだ。 「このロッドはPEライン使用が前提。本来の用途であるサイトでは0.3号や0.4号と組みます。サイトではキャストモーションをコンパクトにしたいし、ねらったスポットにねらったタイミングでスムーズにルアーを送り込みたい。もちろん飛距離を出したい状況もあります。　また、サイトではルアーの操縦性がとても大事。ルアーをパパパッと動かすにはティップにある程度の強さが必要です。これらのキャスト性能や操縦性と同時に叶えたかったのが、しっかりアワセが利きつつラインブレイクを防いでくれること。サイトでは警戒心の強い魚が相手なのでショートバイトが多くなります。ルアーが口に入った瞬間の鋭いアワセでも細いPEをブレイクさせたくない。どうにかなりませんか？とDAIWAワークスに相談して、テスト合宿も組んでカタチにしたのがこのロッドです」 “超”のつく高感度モデルが揃うRCスピニングロッド群で、S63UL-SVの使用感は例外的だ。STEEZ RCにおいて最も先鋭的な藤田京弥の武器ともいえる。 このロッドが完成したとき藤田は、「日本でもアメリカでも、サイトフィッシングにはもうこのロッドしか考えられない」と語った。そのS63UL-SVが藤田に、B.A.S.S.エリート第2戦のレイク・セミノールで初めての入賞（準優勝）をもたらした。  硬めのティップセクションと、急な負荷に追従するようにバットまで曲がり込むテーパーを採用</v>
       </c>
+      <c r="AH145" t="str">
+        <v/>
+      </c>
+      <c r="AI145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -17230,6 +18100,12 @@
       <c r="AG146" t="str">
         <v>610M-、バスロッドにおける定番のバーサタイルモデルの番手だが、Real Controlの610Mは単なるバーサタイルロッドではない。適合ウェイト内のルアーであれば、100点に迫る使用感をもたらし、特にラインスラックを操るルアー、ラインスラックを出しながら巻くルアー、引き抵抗の少ないルアーを使用した際はかつてない操作性を体感することが可能。ひとたび手にすれば、持った瞬間その軽さとバランスに、キャストをすれば、そのアキュラシー、キャッチキャストフィールに驚くことだろう。ベイトロッドにおける「操縦性」を体感することが出来る、真のバーサタイルロッドが完成した。 この610M、独特です 610Mはバーサタイル・ベイトロッドを象徴するナンバーであり、その位置づけはSTEEZ RealControlでも変わらない。ただし、藤田京弥のバーサタイルロッド観は一般的なそれとはやや異なる。 「日本でよく釣れる、出番の多いルアーに対して汎用性の高いロッドが、僕が必要とするバーサタイルロッドです。得意なのは、Mパワーの範囲で用いられるリグ全般、プラグではトップウォーターやジャークベイトなど、いずれもラインテンションにON/OFFが生じる“ラインスラックをコントロールする釣り”です。スピナーベイトを使うことはありますが、基本的にこのロッドはリール巻きっぱなしのルアー（※クランクベイトなど）を想定していません。操縦性に富んだ、RCらしい610Mです」 藤田にとって必要性が高いロッドであるだけに、開発に着手したのはRCシリーズで最も早かった。 設計を担当したDAIWAワークスエンジニアは、「あくまでもイメージですが、スピニングロッドのS61L-SVを長く、強くしたサンプルで藤田さんから好感触を得られたので、設計者としては割とスッとストライクゾーンには入れることができたロッドです」と話す。 昨年発売の4アイテムと同時に開発をスタートして、進捗もスムーズに思われた。が、そこからほんの少しのフッキングパワー増や、ほんの少しのキャストフィール修正が相次ぎ、C610M-SVの開発は最終段階で難航した。藤田は言う。 「開発の初期段階では“従来の610M”という感じでした。RCの素材と製法なので上位互換ではあったけれど、想像の範疇というか、オドロキがあるロッドではなかった。充分いいロッドではあったんですよ。でも、そこで完成させなくてよかったです。 とくに、最後の最後までこだわったキャストフィールが素晴らしい。独特です。テイクバックでブランクをしならせたあと、ルアーを弾き出すパワーの出力が高い。“ロッドがルアーを飛ばしてくれている感”がすごくあります。従来のロッドで10のチカラを使っていたキャストが、このC610M-SVなら7のチカラでできる感じです。残りの3をアキュラシー（精度）にまわせるので、キャストに余裕が生まれます。もちろん感度と操縦性は申し分ありません。とても実用性の高い610Mをつくることができました」  RCらしさを体感することの出来る、ティップ～ベリー～バットへとスムーズにベントするテーパーを採用</v>
       </c>
+      <c r="AH146" t="str">
+        <v/>
+      </c>
+      <c r="AI146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -17331,6 +18207,12 @@
       <c r="AG147" t="str">
         <v>低弾性カーボン”Low Modulus”を採用し、引き抵抗のあるムービングルアーを幅広く使用できるロッド「C70MH-LM」。低弾性カーボンを採用しながらも、軽量に仕上げられたブランクは、高いキャストアキュラシーと遠投性を兼ね備える。バイト時のフッキング性能、掛けてからの追従性も高く、確実なランディングを約束。スピナーベイトやバズベイトなどのワイヤーベイトはもちろん、巻き抵抗の強いクランクベイト、クローラーベイト、大型トップウォータープラグに対応。ムービングルアータックルで操縦性を体感できる唯一無二のロッドが完成した。 巻きモノが俄然楽しくなる 「PEライン3号と組み合わせてバズベイトにマッチする、硬めのグラステイストのロッド」。藤田京弥のこの要求がC70MH-LMの出発点だった。「LM」はLow Modulus（ローモデュラス＝低弾性カーボン）の略である。その背景には、DAIWAワークスエンジニアが藤田と充分なコミュニケーションを取り、彼の好みを理解していることがある。エンジニアは言う。 「藤田さんの要求を聞いて、まずはサンプルをいくつか作りました。彼が言う“硬めのグラステイスト”に仕上げるために、グラスを主材料とし、カーボン比率の高いコンポジットも制作したのですが、とはいえReal Controlなので、巻きモノ用であっても操縦性や感度はできるだけ高めたい。そこで1本だけ、グラスを一切使わずLow Modulusに中弾性カーボンをブレンドし、さらに高弾性SVFをコンポジットして作ったサンプルを交ぜて藤田さんに渡しました」 そのサンプルロッドの中から、素材にこだわらず使用感だけで藤田が選び取ったのが「LM」だった。 「最初はグラスコンポジットだと思って使っていました」と藤田は言う。「軽めのチャターベイト系にはREBELLION 701MFB-Gを気に入っているので、C70MH-LMはバズベイト、重めのチャター、1/2oz.以上のスピナーベイト、クランクならマグナム系、大型のトップウォータープラグなどが担当。 このロッドは、基本的にはシングルフックの巻きモノ用ですが、とてもしなやかで追従性が高いのにフッキングパワーもあるので、大型のトレブルフックがセットされたプラグにもマッチします。それと、引き抵抗重めのルアーをグリグリ巻くのに適したロッドではあるのですが、めちゃくちゃ軽いので操作系のプラグを使ってもかなり気持ちイイです」 2022年のJBトップ50桧原湖戦で準優勝した際、藤田がジョイントタイプのビッグトップウォーターに使用し、2kg級・50cmアップのラージマウスバスを釣っていたのがC70MH-LMのサンプルだった。年が明けて2023年、B.A.S.S.エリートでは、バズベイトだけでなくマグナムクランクにも使っている。すでに日米での実績は充分だ。「この手のロッドでスポイルされがちな巻き感度も充分。追従性が高くてバイトのノリがよく、なのにアワセも決まる。巻きモノで釣っていて本当に楽しくなるロッドです」  ムービングルアーロッドながら、追従性を持たせるために、ティップの入るファストテーパーを採用</v>
       </c>
+      <c r="AH147" t="str">
+        <v/>
+      </c>
+      <c r="AI147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -17432,6 +18314,12 @@
       <c r="AG148" t="str">
         <v>PEラインを使用し、表層のワーミングから中層、ボトムの釣りまで、S61L-SVでは扱いにくい中量級ルアーを意のままに操るバーサタイルモデル。キャスト性能、ルアーの状態を感じ取る感度、操作する際は硬めのティップでルアーを操り、掛けてからはバットまで曲がり込む、ロッドの基本性能はS61L-SVを継承。掛けてからの曲がりを持たせるため、また枝にラインを掛けて魚を誘う際の操作性、フッキング性能の向上のためにレングスは6ft5inchに設定。言うならば、ライトパワーフィネスを極めるロッドが完成した。 使えば使うほど信頼が増す このS65ML-SVは、言わばS61L-SVの兄貴分的ロッドだ。藤田もDAIWAワークスエンジニアも「61Lより長くて、61Lより強い」と、たったふた言でこのロッドの特徴を語る。用途も「61Lで扱うにはちょっと重いルアーの担当で、ラインもPE0.8～1号とちょっと太めがマッチする」という。 「S61L-SVで扱いにくいルアー全般を担当する、基本的にはライトリグロッドなんですけど、S68MH-SV（パワーフィネスロッド）の弟分でもあるんです。つまりS65ML-SVはライトパワーフィネスロッドでもある。本当に単純にS61L-SVのちょいロング＆ちょいパワーアップVer.なんですけど、ベースのロッドが奇跡みたいに素晴らしいロッドなのでS65ML-SVもめちゃくちゃ完成度が高い。とっても気に入っています」と藤田。 S63UL-SVとは違い、このS65ML-SVは感度と操縦性みなぎるRCらしい使用感だ。テーパーもレギュラー寄りのファストで、張りがあるが深くスムーズに曲がり込む。その素直な特性ゆえに応用が利き、藤田にとってはS61L-SVと並んで出番が多い。いや、2023年に関しては、使用頻度も試合での貢献度もS65ML-SVが頭抜けていた。 「パワーミドストには100％このロッドです。エラストマーフロッグにも、ライトパワーフィネスにもこのロッド。S65ML-SVは、使うルアーやテクニックによって出番がある訳ではなく、1号前後のPEでやる釣りすべてにマッチします。レイク・マーレイ戦でビッグフィッシュ賞を獲ったのも、シャンプレインで勝ったミドスト用のウイニングロッドもこれです」 そのシャンプレイン戦のLIVE中継で、藤田がバスを掛けてから取り込むまでの驚異的スピードが話題になった。1,500g程度のスモールマウスが相手なら、掛けたあとは有無を言わさず強引に浮かせて抜き上げ、即リリース。ラインは、メインがPE0.8号、リーダーはフロロ3号（≒12lb.）。このシステムは米北部スモール戦の標準だが、22 EXISTのなめらかなドラグとS65ML-SVのパワーにより、大げさではなく藤田のファイトタイムは他選手の半分ほどに抑えられていた。これらはいずれも藤田自身が開発に携わったタックルだ。 「ミスらしいミスは一度もなかった。使うほどに信頼が増す、素晴らしいロッド、素晴らしいリールの組み合わせです」  ティップに張りを持たせつつも、先端から曲がり、負荷に応じてベリー～バットへスムーズにベントするテーパーを採用</v>
       </c>
+      <c r="AH148" t="str">
+        <v/>
+      </c>
+      <c r="AI148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -17533,6 +18421,12 @@
       <c r="AG149" t="str">
         <v>パワーフィネスに新たな世界をもたらすロッド。今や定番のメソッドとなったパワーフィネス。スピニングタックルながら、そのロッドパワーを保つために操作性が犠牲になっていた。しかし、このRC S68MHは、正確にカバー奥のポイントを射抜き、まるでフィネスロッドを操作するかの如くリグを操ることが可能。ひとたびバイトを捉えれば、そのバットパワーで魚に主導権を与えることなくランディングへと持ち込む。高次元にパワーフィネスを完遂するロッドが完成した。 STEEZ Real Controlの展開に関して、藤田とDAIWAワークスエンジニアは「“ないものを創る”のが先でした」と口を揃える。 「これまでのパワーフィネスロッドでは、釣りをしていて“カバーを撃っている”という以上の感覚が得られなかった。ラインをカバーに引っ掛けてやらないと、ルアー自体の操作性はほぼゼロでした」 藤田にとってパワーフィネスロッドは、言葉だけの存在だったのかもしれない。欠けていたのはフィネス（技巧的）な操作性だ。 「パワーは必須、長めのレングスも欠かせない。枝越しのフッキングになるので、テーパーはティップが入りすぎないレギュラー寄り。棒（硬いだけ）ではダメで、反発力でバスとファイトしたい。そのうえでフィネスであることを求めました」 ―― 優美にして凶暴 例えば鉄の棒にガイドとリールシートを取り付けて、そのロッドに「パワーがある」と感じるだろうか。「硬い」とは感じても、パワフルであることとは違うはずだ。ロッドとしてのパワーとは「反発（復元）する力」であり、それが発揮されるには「曲がる」ことが前提になる。藤田が手掛けるロッドはどれも、ティップからバットまでが連動して美しい弧を描くという共通した特徴がある。 S68MH-SVも、ただ硬いロッドではない。しかし、そのパワーは凶暴だ。カーボン繊維密度が極めて高いSVFコンパイルXナノプラスを用いて、藤田が理想とするアクションに設計したところ、完成したロッドは3回連続で藤田のフックを伸ばした。 「ものすごいパワーなので使うフックは注意です。僕は以前より1、2ランク太軸を使うようになりました。それほどパワーがあるのに、従来の短めのLパワーロッド並みの操作性と軽さです。ボートに乗っていて、自分とバンクの間に立木やカバーがあるとしますよね。このロッドなら、ルアーをバンクに投げて誘って、途中でカバーを探って、さらに沖へダウンヒルで引いてくる、そのすべての過程でルアーをコントロールしてバイトを得ることができるんです。理想どおりではなく、理想を超えた出来です！」 ロッド全体に張りを持たせながら、 ティップ部からバットまで負荷に応じて スムーズにベントするテーパーを採用</v>
       </c>
+      <c r="AH149" t="str">
+        <v/>
+      </c>
+      <c r="AI149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -17634,6 +18528,12 @@
       <c r="AG150" t="str">
         <v>他のロッドには無い、MHながら操縦性を持つロッドC611MH。 610よりも1インチ伸ばしたことで、キャスト、ルアー操作、フッキングやファイト時の狙った曲がりを生み出した。調子や使用感はC610Mを継承しながら、C610Mでは扱いにくい中重量級ルアーを意のままに操ることが可能。フロッグ、大型トップやジャークベイト、そしてバックスライドワームやフォールの釣りといった、ラインスラックを操るルアーを得意としながら、巻物にも高次元に対応。王道番手にReal Controlのこだわりを宿した一本が生まれた。</v>
       </c>
+      <c r="AH150" t="str">
+        <v/>
+      </c>
+      <c r="AI150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -17735,6 +18635,12 @@
       <c r="AG151" t="str">
         <v>従来のソリッドと一線を画す「メガトップR」を採用した高感度ロッドS61UL-SV･ST。 ラインはフロロ3lb、シンカーウェイトは1/16ozを基準とし、ダウンショットを中心としたライトリグから、小型プラグのスローな展開と、ライトウェイトルアーに高次元に対応。ティップ部に採用したメガトップRは、ラインの重みを捉え操る操縦性と、確実なボトムトレースを実現する追従性、ボトム変化をチューブラー同等に伝える手感度という、相反する性能をもたらした。 ファイト時にはReal Controlの他番手同様、素直に曲がり込むことで魚をコントロールする独自のテーパーを採用。ライトリグの基準となるロッドが完成した。</v>
       </c>
+      <c r="AH151" t="str">
+        <v/>
+      </c>
+      <c r="AI151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -17836,6 +18742,12 @@
       <c r="AG152" t="str">
         <v>従来のソリッドと一線を画す感度と操作性を持つ「メガトップR」を採用したソリッドティップロッドC67M-SV･ST。 3.5gシンカーを中心としたヘビダン、フリーリグ、10gまでの高比重ノーシンカー、ネコリグ等を用い、縦ストラクチャーやライトカバーに対しタイトにアプローチ、バスとの距離を縮める。高感度のメガトップRは、着底までのラインの変化、着底後のボトムの状況、更にはラインのもたれ感までもを明確にアングラーに伝えながら、ソリッドティップならではのストラクチャーのトレース性能も有する。また、ソリッドティップの恩恵により、シャッドなどの軽量プラグへの対応力の高さも併せ持つ。ベイトフィネスに踏み込む領域をもカバーする、ベイトタックルでのアプローチの幅を広げるロッドが完成した。</v>
       </c>
+      <c r="AH152" t="str">
+        <v/>
+      </c>
+      <c r="AI152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -17937,6 +18849,12 @@
       <c r="AG153" t="str">
         <v>従来のソリッドと一線を画す感度と操作性を持つ「メガトップR」を採用したソリッドティップロッドC67M-SV･ST。 3.5gシンカーを中心としたヘビダン、フリーリグ、10gまでの高比重ノーシンカー、ネコリグ等を用い、縦ストラクチャーやライトカバーに対しタイトにアプローチ、バスとの距離を縮める。高感度のメガトップRは、着底までのラインの変化、着底後のボトムの状況、更にはラインのもたれ感までもを明確にアングラーに伝えながら、ソリッドティップならではのストラクチャーのトレース性能も有する。また、ソリッドティップの恩恵により、シャッドなどの軽量プラグへの対応力の高さも併せ持つ。ベイトフィネスに踏み込む領域をもカバーする、ベイトタックルでのアプローチの幅を広げるロッドが完成した。</v>
       </c>
+      <c r="AH153" t="str">
+        <v/>
+      </c>
+      <c r="AI153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -18038,6 +18956,12 @@
       <c r="AG154" t="str">
         <v>7ft6inchという長さを持ちながら、軽快にリグを操り、ルアーを操縦するロッドC76MH+。 レングスを感じさせない操縦性は、かつてないバーサタイル性能をもたらした。30g前後のシンカーを用いたパンチングを始めとしたベジテーション攻略はもちろん、ビッグスプーンやアラバマリグ、ビッグベイトと幅広いルアーに高次元に対応。ロングレングスと高反発ながら曲がり込むテーパーがもたらす異次元のロングキャスト性能は、ディープクランクを使用した際には容易に最高深度に到達させストライクゾーンを広範囲に攻略することが可能に。シャローからディープ、ピンスポットからビッグレイクまでエリアを問うことなく使用可能な、真のヘビーバサータイルロッドが完成した。</v>
       </c>
+      <c r="AH154" t="str">
+        <v/>
+      </c>
+      <c r="AI154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -18139,6 +19063,12 @@
       <c r="AG155" t="str">
         <v>冴掛の最大の特徴であるチューブラーパワースリムの細身肉厚ブランクと近年のハートランドの 作品では見られることがなくなった掛け調子が再び蘇る。ブランクマテリアルにHVFナノプラス 素材を採用し、初代冴掛には採用されていなかったＸ45や3DXという補強構造を搭載する ことでネジレやパワーロスの抑制の他に竿がベントしたときの反発スピードがさらに高速化 され、スイングスピードが向上。初代冴掛とはまた異なるテイストに仕上がっており、まるで 柔と剛という相反する要素を両立した仕上がりになっている。</v>
       </c>
+      <c r="AH155" t="str">
+        <v/>
+      </c>
+      <c r="AI155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -18240,6 +19170,12 @@
       <c r="AG156" t="str">
         <v>村上晴彦プロデュース。ハートランド史上最軟調子の冴掛 MIDGE DIRECTION ST、あの唯一無二のテーパーを継承し、フィネスリグをより楽しむ為のロッドが出来上がった、それがHL 702UL+FS-ST23。冴掛 MIDGE DIRECTION STよりもハーフランクパワーアップさせたブランクは、極小ワームのノーシンカーなどのノー感じの釣りはもちろんシンカーを用いたリグへの対応力も兼ね備えた。掛けるまでの楽しさ、掛けてからの楽しさを併せ持つ唯一無二のフィネスロッドに仕上がった。</v>
       </c>
+      <c r="AH156" t="str">
+        <v/>
+      </c>
+      <c r="AI156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -18341,6 +19277,12 @@
       <c r="AG157" t="str">
         <v>村上晴彦が提唱したフワ釣りを形にした初代冴掛ミッジディレクション、それをさらに昇華させた冴掛レベルディレクション。これらの釣りを現代の釣りにアジャストし、誰もが扱いやすい竿を村上晴彦が創り上げた。初代ミッジディレクションのフルチューブラーのテーパーバランスをベースにキャスタビリティーの向上を図り6”延長。冴掛レベルディレクションクラスのパワー感を持たせることで、遠投先でもMデレ独特のチューブラーティップでのラインスラックコントロールを実現し、初代MデレともLデレとも一味異なるフワ釣りロッドが完成した。</v>
       </c>
+      <c r="AH157" t="str">
+        <v/>
+      </c>
+      <c r="AI157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -18442,6 +19384,12 @@
       <c r="AG158" t="str">
         <v>ハートランドの中で、浜に立ち込みライトリグ、ダウンショットやジグヘッド、ノーシンカーを遠投し、自在にアクションするために開発された名作「ハマスピニングスペシャル」。この名竿「ハマスピ」を7ft2inchにロングレングス化、そして最先端のテクノロジーを纏い、現代のスペックに昇華させたロッド、それがHL 722MLRSS-24。ハマスピよりも4inch伸ばすことで遠投性能が向上。新たに設計されたブランクは、ロングレングス化を感じることの無い使用感をもたらし、今まで以上のキャストアキュラシー、ルアーの操作感をもたらし、魚を掛けてからは気持ちよく曲がり込む。HLハートランドの歴史に残る名竿を超える一本に仕上がった。</v>
       </c>
+      <c r="AH158" t="str">
+        <v/>
+      </c>
+      <c r="AI158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -18543,6 +19491,12 @@
       <c r="AG159" t="str">
         <v>ハートランド歴代の作品の中で、長尺ロッド＋PEラインの組み合わせを定着させ、その汎用性の高さから未だに支持される「08白震斬」の調子が今蘇る。HVFナノプラスを採用したブランクは、より細身、肉厚、粘強に仕上げられ、最外層にX45フルシールドを纏うことによりロッドのネジレを徹底排除。今まで以上のキャストアキュラシーとロッドが持つ本来の性能を引き出した。ハートランド独自のヘラ合わせとVジョイント搭載のセンターカット2ピース構造は1ピースロッドと遜色ないベントカーブを描き、誰もが扱い易く、幅広いルアーに対応する懐の深いロッドに仕上がった。</v>
       </c>
+      <c r="AH159" t="str">
+        <v/>
+      </c>
+      <c r="AI159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -18644,6 +19598,12 @@
       <c r="AG160" t="str">
         <v>初期ハートランドの中で、フルソリッドのブランクを採用し、フィネスプラッギングを世に広めた名作「スモールプラグスペシャル」。このスモールプラグスペシャルをチューブラー化し、最先端のテクノロジーを纏い、現代のスペックに昇華させたロッド、それがHL 722LRSB-24。 チューブラー化することで軽量となったブランクに、硬めのティップを採用することで、操作性とキャスタビリティが向上。現代テクノロジーを纏った細身肉厚のチューブラーブランクは、ひとたび魚を掛けるとフルソリッドであったスモールプラグスペシャルを彷彿とさせる曲がりを魅せる。スモールプラグを気持ちよく遊び尽くすための一本が誕生した。</v>
       </c>
+      <c r="AH160" t="str">
+        <v/>
+      </c>
+      <c r="AI160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -18745,6 +19705,12 @@
       <c r="AG161" t="str">
         <v>バスフィッシングの世界に常に独自の発想で新しい釣法を提案し続けるハートランドの20モデル、それがHL 722ML+FB-ST20。今や一つのカテゴリーとして存在するスモラバを初めて世に出した村上晴彦が、PE PERFORMANCEコンセプトの元、DAIWA最先端テクノロジーで現代の村上流ベイトフィネススタイルを体現したスモラバロッドを創り上げた。嘗てのハートランドにはない、硬めの高弾性メガトップソリッドティップとチューブラーパワースリムの細身肉厚ブランクでベイトフィネスでのふわ釣りを実現させた。未だハートランドの作品では見たことのないテイストに仕上がっており、まるで柔と剛という相反する要素を両立した仕上がりになっている。</v>
       </c>
+      <c r="AH161" t="str">
+        <v/>
+      </c>
+      <c r="AI161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -18846,6 +19812,12 @@
       <c r="AG162" t="str">
         <v>バスフィッシングの世界に常に独自の発想で新しい釣法を提案し続けるハートランドの20モデル、それがHL 722MRB-20。軟疾風のコンセプトで1／4ozクラスのラバージグをメインに村上流ベイトフィネスを体現した二代目ドットスリー（・・・）をベースに、今や一つのカテゴリーとして存在するスモラバを初めて世に出した村上晴彦が、PE PERFORMANCEコンセプトの元、DAIWA最先端テクノロジーで現代のスモラバロッド創り上げた。二代目ドットスリーにはなかった遠投性能とストロークを備えた。チューブラーパワースリムのセンターカット2PCS仕様にハートランド伝統のへら合わせとVジョイントを搭載し1PCと遜色ない綺麗なベントカーブを見せる村上調子となっている。</v>
       </c>
+      <c r="AH162" t="str">
+        <v/>
+      </c>
+      <c r="AI162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -18947,6 +19919,12 @@
       <c r="AG163" t="str">
         <v>ハートランド歴代の作品の中で高く支持された04白疾風と07白疾風をベースにメインマテリアルをHVFからHVFナノプラスに昇華させ、チューブラーパワースリムのセンターカット2ピース仕様。ハートランド伝統のへら合わせとV-ジョイントを搭載し1ピースと遜色ない綺麗なベントカーブを見せる村上調子となっている。チューブラーパワースリムの細径肉厚ブランクは筋肉質なブランクでありながら径が細い故にねじれやすいというウィークポイントをもっていたがX45でアシストされ捻れにくいブランクに生まれ変わり、しなってから戻りの早い3DXのサポーター効果によりレスポンスが向上。キャストやフッキング、ファイトなどのダイナミックなアクションに対し、遊びやパワーロスといったものを一切排除したブランクとなっている。 ノーシンカーやテキサスリグ、ラバージグの掛けものはもとよりバイブレーション、クランクベイト、ミノーまで扱え、04&amp;07白疾風とは異なる仕上りとなっている。</v>
       </c>
+      <c r="AH163" t="str">
+        <v/>
+      </c>
+      <c r="AI163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -19048,6 +20026,12 @@
       <c r="AG164" t="str">
         <v>疾風七弐TYPE-EやTYPE-W、センターカット2ピースである疾風 BIWAKO SPEC.、そして疾風シリーズの集大成的存在である疾風七伍 AGS。これらSVFコンパイルXの細身肉厚ブランクはリリースポイントは狭いながらもハマったときの遠投性能は言うまでもない。その玄人好みのセッティングは、ある種使い手を選ぶロッドにもなっている。HL752HRB-21はSVFコンパイルXではなく敢えてHVFナノプラスを採用することでHVFの良さを最大限引き出すことで、余裕が生まれ、誰が投げても平均飛距離を叩き出せるロッドに仕上がった。ハートランド独自のコンストラクションである、チューブラーパワースリムでデザインすることで、軽量ロッドとは異なる独特のテイストが生まれ、シャープさの中に安心感とモチッとした粘りを両立させた。ハートランド独自のへら合わせとVジョイント搭載のセンターカット2ピース構造にすることで、1ピースと遜色ないベントカーブを描き、見ても美しく誰もが扱いやすい疾風となっている。</v>
       </c>
+      <c r="AH164" t="str">
+        <v/>
+      </c>
+      <c r="AI164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -19149,6 +20133,12 @@
       <c r="AG165" t="str">
         <v>8'の長さを持ちながら、使い手を選ばない長尺バーサタイルロッドHEARTLAND 802MHRB-21。この802MHRB-21をベースにMパワーへ変更し、軽量～中量級まで幅広く対応するバーサタイル性能を持たせたロッド、それが7112MRB-25。7'11"のレングスは、遠投性能を持ちながら、操作性をも併せ持つ。名竿「･･･」（ドットスリー）を彷彿とさせるベンディングカーブは、スモラバからムービングベイト、ボトムルアーまで幅広く対応する、懐の深いロッドに仕上がった。 &lt;村上晴彦 PRODUCE MODEL&gt;</v>
       </c>
+      <c r="AH165" t="str">
+        <v/>
+      </c>
+      <c r="AI165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -19250,6 +20240,12 @@
       <c r="AG166" t="str">
         <v>「究極の岸釣りバーサタイル」と呼び声の高い04白疾風、07白疾風、そしてそれらに継ぐ「次世代の究極の岸釣りバーサタイル」疾風七四 MH AGS。それらをベースにフォールトラップテクニカルシャフトや川スペ並みの遠投性能を具備させた長竿バーサタイルを村上晴彦が創りあげた。ファストムービング系ルアーからラバージグまで幅広いルアーを完璧にこなすのはもちろんのこと、レングスと8’の長さからくるバットパワーでヘビキャロの遠投までをこなす。長尺ロッドの手の負担を考慮し、3DXのサポーター効果を最大限引き出すためにバット部のみに施した使い手を選ばない長竿遠投バーサタイル。</v>
       </c>
+      <c r="AH166" t="str">
+        <v/>
+      </c>
+      <c r="AI166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -19351,6 +20347,12 @@
       <c r="AG167" t="str">
         <v>取り回しに優れたショートレングスフロッグスペシャル。BLXの設計思想を踏襲したエキストラファストテーパーに設計することで、あらゆるサイズのフロッグの投げやすさと釣れるフロッグアクションである水を絡めたアクションを出す操作性、モンスターフィッシュに主導権を握らせないバットパワーを融合。バスフィッシングにおける、フロッグや操作系ハードベイトの釣りだけでなくジグ・ワームの釣りに於いてもラインスラックを自動的に出すことが出来、釣れるロッドに仕上がっている。バスだけに留まらず、ハードロックフィッシュやボートシーバスゲームなどにも高次元に対応。</v>
       </c>
+      <c r="AH167" t="str">
+        <v/>
+      </c>
+      <c r="AI167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -19452,6 +20454,12 @@
       <c r="AG168" t="str">
         <v>あらゆるルアーに高次元に対応するバーサタイルスペシャル。BLXの設計思想を踏襲したレギュラーテーパーに設計することで、投げやすさと操作性、感度、モンスターフィッシュに主導権を握らせないバットパワーを融合。「への字テーパー」に設計することで、トップウォーターやジャークベイトなど操作系ルアーの操作性を高め、ワーミングで必要な感度はもちろんのこと、ムービングルアーの釣りに於いてもラインスラックを自動的に出すことが出来、釣れるロッドに仕上がっている。バスだけに留まらず、ハードロックフィッシュやボートシーバス、青物などにも対応。</v>
       </c>
+      <c r="AH168" t="str">
+        <v/>
+      </c>
+      <c r="AI168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -19553,6 +20561,12 @@
       <c r="AG169" t="str">
         <v>様々な重量級ルアーに対応できるパワーバーサタイルスペシャル。BLXの設計思想を踏襲した「への字テーパー」のレギュラーファストテーパーに設計することで、あらゆるルアーの投げやすさと感度、モンスターフィッシュに主導権を握らせないバットパワーを融合。バスフィッシングにおける、ジグ・ワームの釣りだけでなくファストムービングルアーの釣りに於いてもラインスラックを自動的に出すことが出来、釣れるロッドに仕上がっている。バスだけに留まらず、ハードロックフィッシュやボートシーバスゲームなどにも高次元に対応。</v>
       </c>
+      <c r="AH169" t="str">
+        <v/>
+      </c>
+      <c r="AI169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -19654,6 +20668,12 @@
       <c r="AG170" t="str">
         <v>国内のバスフィッシングのみならず海外のプレデターフィッシングにも高次元に対応するハイパワースペック。BLXの設計思想を踏襲したファストテーパーに設計することで、重量級ルアーに口を使わなくなった場面で軽量ベイトをも投げ込めるティップと操作性、感度、モンスターフィッシュに主導権を握らせないバットパワーを高次元に融合。ワーミングで必要な感度はもちろんのこと、ラインスラックを自動的に出すテーパーがビッグベイトやムービングベイトのスラックラインリトリーブを可能にし、バスのみならずあらゆるプレデターと対峙出来る1本。</v>
       </c>
+      <c r="AH170" t="str">
+        <v/>
+      </c>
+      <c r="AI170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -19755,6 +20775,12 @@
       <c r="AG171" t="str">
         <v>10oz.までのスイムベイト・ビッグベイトに対応できるSB（スイムベイト・ビッグベイト）ロッド。BLXの設計思想を踏襲したファストテーパーに設計することで、ティップを回したキャストで打ち込んでいけるアキュラシーキャストが可能。至近距離や突発的なバイトでもアワセの間を与えつつ、強靭なベリー～バットで掛け、主導権を握らせない。スイムベイト・ビッグベイトのみならず、ジャークベイトや大型ペンシル、ワイヤーベイトまで対応する懐の深いロッドに仕上がっている。バスだけに留まらず、世界中の怪魚と対峙出来るショートレングスエキストラパワーロッド。</v>
       </c>
+      <c r="AH171" t="str">
+        <v/>
+      </c>
+      <c r="AI171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -19856,6 +20882,12 @@
       <c r="AG172" t="str">
         <v>6oz.までのスイムベイト・ビッグベイトに対応できるSB（スイムベイト・ビッグベイト）ロッド。BLXの設計思想を踏襲したレギュラーテーパーに設計することで、ショートレングスながら遠投性能を備え、重量級ルアーだけでなく、あらゆるルアーの投げやすさと操作性、主導権を握らせないバットパワーを融合。スイムベイト・ビッグベイトのみならず、ジャークベイトや大型ペンシル、ワイヤーベイト、フロッグまで対応する懐の深いロッドに仕上がっている。バスだけに留まらず、1本で世界中のモンスターと対峙出来るショートレングスパワーロッド。</v>
       </c>
+      <c r="AH172" t="str">
+        <v/>
+      </c>
+      <c r="AI172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -19957,6 +20989,12 @@
       <c r="AG173" t="str">
         <v>あらゆるルアーに高次元に対応するバーサタイルスペシャル。BLXの設計思想を踏襲した「への字テーパー」のファストテーパーに設計することで、投げやすさと操作性、感度、モンスターフィッシュに主導権を握らせないバットパワーを融合。トップウォーターやジャークベイトなど操作系ルアーの操作性とタダ巻きで水に絡めたアクションを高次元で両立。ワーミングでの感度はもちろんのこと、喰わせの間を作るラインスラックを自動的に出すことが出来、釣れるロッドに仕上がっている。さらにSTEEZスナッピーフロッグJr.の高速シェイク&amp;リトリーブにも対応し、理想のアクションを演出しつつダブルフックのフッキングも可能。バスだけに留まらず、ロックフィッシュやボートシーバス、青物などにも高次元に対応。</v>
       </c>
+      <c r="AH173" t="str">
+        <v/>
+      </c>
+      <c r="AI173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -20058,6 +21096,12 @@
       <c r="AG174" t="str">
         <v>あらゆる軽量ルアーに高次元に対応するライトバーサタイルスペシャル。BLXの設計思想を踏襲したレギュラーテーパーに設計することで、投げやすさと操作性、感度、モンスターフィッシュに主導権を握らせないバットパワーを融合。高弾性HVFナノプラスを採用し 「への字テーパー」に設計することでベイトフィネスワーミングに必要な高い感度と繊細な操作性を実現。その他にトップウォーターやジャークベイトなど操作系ハードベイトを巧みに操れる他、ワイヤーベイトやプロップベイトのスラックラインリトリーブが可能に。高弾性素材が苦手とするクランキングに於いてもルアーの振動で一度振れたティップがティップ部に搭載された大口径ダブルフットステンレスフレームガイドにより増幅し、高弾性カーボン特有の突っ張った引き感ではなく、カバーやストラクチャーに絡められる柔らかい引き感に変化し、水を絡ませた釣れる動きを出せる快適なクランキングが可能。ライトバーサタイルの名に恥じない釣れるロッドに仕上がっている。バスだけに留まらず、ボートシーバスやフラットフィッシュ、チニングなどにも高次元に対応。</v>
       </c>
+      <c r="AH174" t="str">
+        <v/>
+      </c>
+      <c r="AI174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -20159,6 +21203,12 @@
       <c r="AG175" t="str">
         <v>あらゆるルアーに高次元に対応するロングバーサタイルスペシャル。BLXの設計思想を踏襲したレギュラーファストテーパーに設計することで、投げやすさと操作性、感度、モンスターフィッシュに主導権を握らせないバットパワーを融合。高弾性HVFナノプラスを採用し「への字テーパー」に設計することでワーミングに必要な高い感度と繊細な操作性を実現。トップウォーターやジャークベイトなど操作系ハードベイトの操作性を高め、ラインスラックを自動的に出すテーパーデザインによりムービングルアーのスラックラインリトリーブが容易に。高負荷に負けない強いティップと乗せどころのあるベリーセクション、強靭なバットセクションにより投げやすさと遠投性能を発揮し、重量級ルアーへの対応力が大幅アップ。バスだけに留まらず、ハードロックフィッシュやボートシーバス、青物などにも対応。</v>
       </c>
+      <c r="AH175" t="str">
+        <v/>
+      </c>
+      <c r="AI175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -20260,6 +21310,12 @@
       <c r="AG176" t="str">
         <v>あらゆるルアーに高次元に対応するロングパワーバーサタイルスペシャル。高弾性HVFナノプラスを採用しBLXの設計思想を踏襲した「への字テーパー」のファストテーパーに設計することで、ワーミングでの高い感度と繊細な操作感を実現しつつ、3.5g～5gのジグヘッドを用いた5”～6”スティックベイトのパワーミドストでも最高のパフォーマンスを発揮。「への字テーパー」のティップがトップウォーターやジャークベイトなどアクション系プラグを自在に操り、高弾性素材が苦手とするファストムービングルアーのストレートリトリーブでも引っ張り過ぎないスラックラインリトリーブを可能にし、水に絡めた高い巻き感度も実現。Mパワー以上の強靭なバットを組み合わせることで、1オンス級のルアーの遠投も可能。バスだけに留まらず、ボートシーバスや小型青物のキャスティングゲーム、フラットフィッシュ、チニングなどにも高次元に対応。大物と対峙できるロンググリップ、大口径ガイド、ファストテーパーデザインにより、向かい風を切り裂く低弾道の遠投を可能にする。</v>
       </c>
+      <c r="AH176" t="str">
+        <v/>
+      </c>
+      <c r="AI176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -20359,6 +21415,12 @@
         <v/>
       </c>
       <c r="AG177" t="str">
+        <v/>
+      </c>
+      <c r="AH177" t="str">
+        <v/>
+      </c>
+      <c r="AI177" t="str">
         <v/>
       </c>
     </row>
@@ -20468,6 +21530,12 @@
 このファイヤーフラッシュの性能を維持したまま、センターカット2PCS化することで携行性を高めつつVジョイントαを搭載することで、
 通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上。釣り勝てるセンターカット2PCSに仕上がった。 ■LURE APPLICATION Small Rubber Jig /No Sinker Rig /Down Shot Rig /Neko Rig /Jighead Rig /Wacky Jighead Rig /Stick Bait /Shad /Minnow /Prop bait /Bug lure ■TECHNOLOGY SVFコンパイルX/ X45フルシールド/ Vジョイントα/ メガトップ</v>
       </c>
+      <c r="AH178" t="str">
+        <v/>
+      </c>
+      <c r="AI178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179" xml:space="preserve">
       <c r="A179" t="str">
@@ -20575,6 +21643,12 @@
 このファイヤーフラッシュの性能を維持したまま、センターカット2PCS化することで携行性を高めつつVジョイントαを搭載することで、
 通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上。釣り勝てるセンターカット2PCSに仕上がった。 ■LURE APPLICATION Small Rubber Jig /No Sinker Rig /Down Shot Rig /Neko Rig /Jighead Rig /Wacky Jighead Rig /Stick Bait /Shad /Minnow /Prop bait /Bug lure ■TECHNOLOGY SVFコンパイルX/ X45フルシールド/ Vジョイントα/ メガトップ</v>
       </c>
+      <c r="AH179" t="str">
+        <v/>
+      </c>
+      <c r="AI179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -20676,6 +21750,12 @@
       <c r="AG180" t="str">
         <v/>
       </c>
+      <c r="AH180" t="str">
+        <v/>
+      </c>
+      <c r="AI180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -20777,6 +21857,12 @@
       <c r="AG181" t="str">
         <v>C65MH-FRはレンタルボートやオカッパリなどで、小場所やオーバーハングの下など込み入った場所でのアキュラシーキャストと操作性、パワーを高次元に融合させたテクニカルフロッギングロッド。 「への字テーパー」のエキストラファストテーパーにより、あらゆるウェイトであれ、どのアングルから振り抜いてもウェイトを一箇所に乗せて投げやすく、低弾道で奥の奥にフロッグをシュート出来る他、クイックなアクションからネチネチ焦らす様なアクションまで多彩なアクションに対応出来る。 フロッグが水を押す時と抜ける時の緩急の差を竿で感じ取れる手感度の良さも「への字テーパー」の最大の特徴。オーバーハングの裏にシュートしてフロッグが見えない時もフロッグが思い通りに動いているかがわかる。 フロッグのみならず、ショートレングスの取り回しの良さを生かして、正確なピッチングでカバー撃つワーミングの他、「への字テーパー」によりリーリングベイトの弛ませ引きがしやすくワイヤーベイトやスイムジグ、スイムベイトにも高次元に対応。さらに小刻みなトゥイッチでテクニカルに操作する1oz強のジョイントベイトにも高次元に対応し、エキサイティングなゲームを完遂する一本。 Application：Frog / Jointed Swimbait / Texas Rig / Leaderless Down Shot Rig / Free Rig / Finesse Jig / Swim Jig / No Sinker Rig / Swimbait / Spinnerbait HVFナノプラス/X45フルシールド（X45コブラシールド）/エアセンサ―シート</v>
       </c>
+      <c r="AH181" t="str">
+        <v/>
+      </c>
+      <c r="AI181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -20878,6 +21964,12 @@
       <c r="AG182" t="str">
         <v>C66L-LMは多くのバスアングラーを覚醒させるクランキングにフォーカスしたアイテム。 C66ML-LM同様に、ロッドの調子を司る軸長方向の繊維を全て低弾性カーボン“Low Modulus”で構成。 先端に「への字テーパー」を組み込むことで、リトリーブ時はへの字のティップが踊り、ラインスラックを出したグラスの様な突っ張らない巻き感とグラスには出せない性能であるラインがカバーに触れた時の抵抗感やボトムやカバーのタッチ感を両立し、タフなフィールドでのフィネスなクランキングに完全対応。 一見すると、投げにくいイメージのファストテーパーでありながら、軸長方向全て“Low Modulus”の構成に若干先重りのセッティングにすることより、素材の粘り感とブランク自重でロッドをしならせ、への字テーパーの特性も相まって軽量ルアーを投げやすくしている。 この低反発材料+ファストテーパーの組み合わせが、パラボリックにベントする低反発材料のロッドでは不可能なコンパクトスウィングによるハイスピードキャストが可能になり、風の中でも低弾道のアキュラシーキャストと遠投が可能。 軽量ルアーをオーバーハングの奥の奥へ滑り込ませつつ、着水直前に先端のへの字ティップがスッとお辞儀することでソフトなプレゼンテーションを実現。 カバーのコンタクト時にはへの字ティップがショックアブソーバーの役目を果たし、スタックは躱すものの、バイト時はティップがスコンッと入ることでバイトを弾くことなく乗せ、強靭なバットで掛け、主導権を握ったファイトが可能。 クランキングにおける相反する要素を一本に纏め上げ、真のハードベイトエキスパート達をも納得させる“釣れる”クランキングロッドに仕上がった。 Application :Tiny Crankbait /Flat Sided Crankbait /Shad Plug /Tiny Topwater Plug Low Modulus/X45フルシールド（X45コブラシールド）/エアセンサ―シート</v>
       </c>
+      <c r="AH182" t="str">
+        <v/>
+      </c>
+      <c r="AI182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -20979,6 +22071,12 @@
       <c r="AG183" t="str">
         <v>C66ML-LMは多くのバスアングラーを覚醒させるクランキングにフォーカスしたアイテム。 目指したのは、どんなにキャストが困難なスポットでも極限の精度で撃ち込み、リトリーブしながらもルアーを引っ張り過ぎず、しっかりスラックラインを出した状態でルアーをイキイキと泳がせバイトに持ち込むこと。そして、バイトをしっかり掛け、バラさず確実にキャッチすること。 それを実現するために、ロッドの調子を司る軸長方向の繊維を全て低弾性カーボン“Low Modulus”にし、強靭なバットをもつファストテーパーのティップを「への字テーパー」に仕上げ、Ｘ45フルシールドで締め上げた唯一無二のブランク。 ティップを「への字テーパー」にすることで、ルアーの重さや空気抵抗、アングラーのスウィングスピードに関わらず、ルアーの重みを乗せる部分を一極集中させることで投げやすく、軽量ルアーでもスウィングスピードを上げることなくスローなスウィングでルアーの弾道が上がることなく低い弾道でルアーを優しい着水音でピタピタ入れていける。リトリーブ始めるとへの字のティップが踊り、ラインスラックを出したリトリーブが可能。ルアーがイキイキ泳ぐばかりでなく、リトリーブ時の巻き感度も高く、バイト時はティップがスコンッと入ることでバイトを弾くことなく乗せ、強靭なバットで掛けていける。一方でカバーのコンタクト時にはへの字テーパーのティップがショックアブソーバーの役目を果たし、スタックは躱す。クランキングおける相反する要素を一本に纏め上げ、真のハードベイトエキスパート達をも納得させる“釣れる”クランキングロッドに仕上がった。 Application：Shallow Diving Crankbait / Medium Diving Crankbait / Tiny Crankbait / Flat Sided Crankbait / Shad Plug Low Modulus/X45フルシールド（X45コブラシールド）/エアセンサ―シート</v>
       </c>
+      <c r="AH183" t="str">
+        <v/>
+      </c>
+      <c r="AI183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -21080,6 +22178,12 @@
       <c r="AG184" t="str">
         <v>C66ML+は、ハードベイトに息吹を吹き込み、自分が想い描いたアクションでバイトに持ち込む、一匹と向き合うバスフィッシングが堪能できるテクニカルモデル。 アキュラシーキャストとロングキャストどちらもこなせる長さに「への字テーパー」を採用することで、ルアーの重さや空気抵抗、アングラーのスウィングスピードに関わらず、ルアーの重みを乗せる部分を一極集中させることで投げやすく、キャスト時に回転しやすいルアーでも低弾道でオーバーハングの奥に入れ込むアキュラシーキャストが容易。 さらに着水直前に「への字テーパー」のティップがスッとお辞儀することで高度なサミングワークが無くともソフトなプレゼンテーションが可能。 また操作時にティップが曲がらないことで入力がスポイルせず、ルアーに想い通りのアクションを演出させ、水中のルアー状態が手元に伝わる。 操作系ハードベイトのみならず、ストレートリトリーブ系でも真価を発揮し、ワイヤーベイトの弛ませ引きが秀逸でヒラを打たせながらバイトチャンスを作るリトリーブができる。 さらにハイパークランクのテロテロ引きでもへの字のティップが踊り、ロッドが共振することでハイパーな状態を創りだす。 ハイパーのガツンバイトもへの字のティップがスコンッと入り反転の間を作る出すことで弾かず乗せ、リアフックをパクッとバイトし反転しない魚に対しても針先を口に残しつつ、強靭なバットで掛けることができるのも「への字テーパー」の真骨頂。 静と動、双方の釣りを完遂できる芸達者な一本。 Application :Jerkbait /Topwater Plug /Spinnerbait /Buzzbait /Crankbait /Vibration /Neko Rig /Small Rubber Jig/No Sinker Rig /Down Shot Rig HVF/X45フルシールド（X45コブラシールド）/エアセンサ―シート</v>
       </c>
+      <c r="AH184" t="str">
+        <v/>
+      </c>
+      <c r="AI184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -21181,6 +22285,12 @@
       <c r="AG185" t="str">
         <v>C66M-5はタフな現代のフィールドでこそ真価を発揮するバーサタイルモデル。 ルアー対応幅の広いテーパーに、ティップの先端を「”へ”の字テーパー」にすることで、ルアーの重みを乗せる部分を一極集中させ、投げやすく、トリプルフックの付いたルアーのキャストを躊躇するようなオーバーハングの下やカバー際に低弾道でピタピタに入れていくアキュラシーキャストから高精度なロングキャストまで可能。 リーリングベイトに於いては「”へ”の字テーパー」によりラインスラックを出したスラックラインリトリーブが容易になり、ルアーがイキイキ泳ぐばかりか、バイト時に反転の間を与えしっかり吸い込ませる。 その「”へ”の字テーパー」は水中からの情報をティップでスポイルせず、手元に伝え、ワーミングに於いてもラインスラックを作りだし、先端の硬さで繊細な操作が可能。 ネコリグやダウンショットのみならず、抵抗の有るラバージグでもティップがモタレ過ぎることなく、スタックを躱し、カバーやベジテーションを不用意に揺らすことなくバイトに持ち込む。 シングルフックを貫通させる強靭なバットパワーを備え、バスだけに留まらず、あらゆるフィッシュイーターにも対応するマルチパーパスロッド。 Application :Spinnerbait /Buzzbait /Vibration /Jerkbait /Crankbait /Bladed Jig/Crawlerbait /Snagless Neko Rig /No Sinker Rig /Down Shot Rig /Texas Rig/Leaderless Down Shot Rig /Free Rig /Rubber Jig HVFナノプラス/X45フルシールド（X45コブラシールド）</v>
       </c>
+      <c r="AH185" t="str">
+        <v/>
+      </c>
+      <c r="AI185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -21282,6 +22392,12 @@
       <c r="AG186" t="str">
         <v>C68MH-SBは一匹と向き合う釣りの一つである、スイムベイト・ビッグベイトロッド。中でもマグナムクランクや2ozクラスのスイムベイト・ビッグベイトにフォーカスしたアイテム。 ７‘超えのアイテムが乱立する中で、目指したのは、どんなにキャストが困難なスポットでも極限の精度で撃ち込めること。 そしてリトリーブしながらもルアーを引っ張り過ぎず、スラックラインを出した状態でルアーをイキイキと泳がせバイトに持ち込み、しっかり反転させて掛け、バラさず確実にキャッチすること。 それを実現したのが、「“へ”の字テーパー」のティップとファストテーパーの強靭なバット。ティップをへの字テーパーにすることで、投げやすさとリトリーブを始めるとルアーの振動でへの字のティップが踊り、ラインスラックを出したリトリーブが可能。 ルアーがイキイキ泳ぐばかりでなく、リトリーブ時の巻き感度も高く、バイト時はティップがスコンッと入ることで反転の間を与え、SBロッドの特長でもある急激に立ち上がる強靭なバットで掛けていける。 ジョイントベイトのトゥイッチやリーリングジャークでルアーをナチュラルにアクションさせるティップでありながら、抵抗のある5ｍダイバー・7ｍダイバーのマグナムクランクでもティップが負けることなくスラックを出して巻けるのが「“へ”の字テーパー」の真骨頂。 リップ付きハードベイトだけでなく、ワイヤーベイトにも好相性で、ヘビースピナーベイトのスローロールや高速リトリーブにも高次元に対応する。 Application : Magnum Crankbait /Swim bait /Big bait /Crawler bait /Spinnerbait /Buzzbait /Bladed Jig /Swim Jig /Frog /No Sinker Rig /Texas Rig /Leaderless Down Shot Rig /Rubber Jig / HVFナノプラス/X45フルシールド（X45コブラシールド）/エアセンサ―シート</v>
       </c>
+      <c r="AH186" t="str">
+        <v/>
+      </c>
+      <c r="AI186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -21383,6 +22499,12 @@
       <c r="AG187" t="str">
         <v>C610Mはタフな現代のフィールドでこそ真価を発揮するバーサタイルモデル。 ルアー対応幅の広いテーパーに、ティップの先端を「への字テーパー」にすることで、ルアーの重さや空気抵抗、アングラーのスウィングスピードに関わらず、ルアーの重みをロッドに乗せる部分を一極集中させることで投げやすく、3/8～1/2ozスピナーベイトやバスベイト、トリプルフックのついたハードベイトを臆することなくカバーやストラクチャー、オーバーハングの下に入れ込むことが出来る。 リーリングベイトに於いては「への字テーパー」によりラインスラックを出したスラックラインリトリーブが容易になり、ルアーがイキイキ泳ぐばかりか、バイト時に反転の間を与えしっかり吸い込ませる。 一方でその「への字テーパー」がワーミングに於いても自動的にラインスラックを作りだしつつも、先端の硬さで繊細な操作が可能。ネコリグやダウンショットのみならず、抵抗の有るラバージグでもティップがモタレ過ぎることなく、スタックも躱し、カバーやベジテーションを不用意に揺らさず、プレッシャーをかけることなく探る。 水中からの情報をティップでスポイルせず、手感度も司る。それでいて、シングルフックを貫通させるバットパワーを備えるマルチパーパスロッド。 Application：Spinnerbait / Buzzbait / Vibration / Jerkbait / Crankbait / Bladed Jig / Crawlerbait / Snagless Neko Rig /No Sinker Rig / Down Shot Rig / Texas Rig / Leaderless Down Shot Rig / Free Rig / Rubber Jig HVFナノプラス/X45フルシールド（X45コブラシールド）/エアセンサ―シート</v>
       </c>
+      <c r="AH187" t="str">
+        <v/>
+      </c>
+      <c r="AI187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -21484,6 +22606,12 @@
       <c r="AG188" t="str">
         <v>C610MHは現代のタフなフィールドでこそ真価を発揮するパワーヘビーバーサタイルモデル。 ルアー対応幅の広いテーパーに、ティップの先端を「への字テーパー」にすることで、ルアーの重さや空気抵抗、アングラーのスウィングスピードに関わらず、ロッドにルアーの重みを乗せる部分を一極集中させることで投げやすく、1/2oz以上のスピナーベイトやバズベイト、ブレイデッドジグ、スイムジグ、トリプルフックのついたハードベイトを臆することなくカバーやストラクチャー際、オーバーハングの下に入れ込むことが出来る。 リーリングベイトに於いては「への字テーパー」によりラインスラックを出したスラックラインリトリーブが秀逸で、ルアーがイキイキ泳ぐばかりか、バイト時に反転の間を与えしっかり吸い込ませる。さらにジョイントベイトなどの操作でもティップでスポイルすることなくアングラーの意思をしっかりルアーに伝える。 一方でワーミングに於いてはテキサスリグやリーダーレスダウンショットのみならず、抵抗の有るラバージグでもティップがモタレ過ぎることなく、スタックも躱し、カバーやベジテーションを不用意に揺らさず、プレッシャーをかけることなく強く、繊細に操作できる。その「への字テーパー」によりワーミングに於いても自動的にラインスラックを作りだしつつも、水中からの情報をティップでスポイルせず、手元に伝える高い手感度を誇る。ディスタンスを取ったアプローチでもシングルフックを貫通させるバットパワーを備えるマルチパーパスロッド。 Application：Spinnerbait / Buzzbait / Bladed Jig / Crawlerbait / Jointed Swimbait / Texas Rig / Leaderless Down Shot Rig / Free Rig/ Rubber Jig / Swim Jig / No Sinker Rig HVFナノプラス/X45フルシールド（X45コブラシールド）/エアセンサ―シート</v>
       </c>
+      <c r="AH188" t="str">
+        <v/>
+      </c>
+      <c r="AI188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -21585,6 +22713,12 @@
       <c r="AG189" t="str">
         <v>バスフィッシングをやり続けていると釣果だけではない、もっと面白い釣り、もっと刺激のある釣りを追求したくなるはず。その一匹でしか得られない感動や達成感、気持ちよさを享受する釣りの一つがスイムベイト・ビッグベイトゲーム。 C611XH-2・SBは4ozクラスのスイムベイト＆ビッグベイトをロッドワークやリーリングで操るビッグベイトゲームを今まで以上に楽しくさせてくれるスイムベイト・ビッグベイトスペシャル。 XHパワーのスティッフなティップに「”へ”の字テーパー」を施すことにより、バンクやシャローのカバー際、オーバーハングの下に重量級ルアーを正確に、小さな着水音で撃ち込むことが容易になり、トゥイッチやリーリングジャーク、シェイク巻きでルアーを繊細かつ正確に操り、グリフワの高速リトリーブではルアーを引っ張り過ぎることなく艶めかしいアクションを演出させ、止めた時にラインスラックを作りやすくなっている。 さらに、突発的なバイトもティップがスコンッと入ることで反転の間を与え,弾かずしっかり絡めとる。 並継構造を採用することで、強靭なバットパワーを生み出すことはもとより、超高弾性カーボンをコンポジットすることで重量級ルアーの遠投性能が向上。 太軸フックを瞬間的に貫通させカバ一から一気に引き剥がしつつ、強さの中に適度なしなやかさを残すことで安心して魚とファイト出来る。 Application ：Swimbait /Big Bait /Crawler bait /Topwater Plug /Spinnerbait/Buzzbait /Bladed Jig /Swim Jig /Rubber Jig /Texas Rig /Leaderless Down ShotRig /No Sinker Rig HVF/X45フルシールド（X45コブラシールド）</v>
       </c>
+      <c r="AH189" t="str">
+        <v/>
+      </c>
+      <c r="AI189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -21686,6 +22820,12 @@
       <c r="AG190" t="str">
         <v>C70MH-5は現代のタフなフィールドでこそ真価を発揮するヘビーバーサタイルモデル。 ルアー対応幅の広いテーパーに、ティップの先端を「への字テーパー」にすることで、ルアーの重みを乗せる部分を一極集中させることで投げやすく、キャストを躊躇するようなオーバーハングの下やカバー際に低弾道でピタピタに入れていくアキュラシーキャストが可能。さらにスイムベイト＆ビッグベイトロッドのテーパーデザインを取り入れ、バットのテーパーを急激に立ち上げることで、ルアーウェイトの上限がアップし、2ozクラスのビッグベイトにも対応出来るだけでなく、遠投性能が飛躍的に向上。 リーリングベイトに於いては「への字テーパー」によりスラックラインリトリーブが秀逸で、ルアーがイキイキ泳ぐばかりか、バイト時に反転の間を与えしっかり吸い込ませる。 さらに操作系ハードベイトでもティップでスポイルすることなくルアーにしっかり伝える。 一方でワーミングに於いてはその「への字」ティップにより繊細に操作でき、自動的にラインスラックを作りだしつつも、水中からの情報をティップでスポイルせず、手元に伝える高い手感度を誇る。 抵抗の有るラバージグやヘビーテキサスでもティップがモタレることなく、スタックも躱す。強靭なバットパワーでシングルフックを貫通させるバットパワーを備え、バスだけに留まらず、あらゆるフィッシュイーターにも対応するマルチパーパスロッド。 Application :Spinnerbait /Buzzbait /Bladed Jig /Swim Jig /Vibration /MagnumCrankbait /Swimbait /Big bait /Topwater Plug /Frog /Rubber Jig /Texas Rig /Leaderless Down Shot Rig /No Sinker Rig HVF/X45フルシールド（X45コブラシールド）</v>
       </c>
+      <c r="AH190" t="str">
+        <v/>
+      </c>
+      <c r="AI190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -21787,6 +22927,12 @@
       <c r="AG191" t="str">
         <v>C72Hはバスフィッシングの中でも最もエキサイティングなゲームを展開するのに必要不可欠なロッド。バスフィッシングをやり続けていると釣果だけではない、もっと面白い釣り、もっと刺激のある釣りを追求したくなるはず。 難攻不落のヘビーカバーに潜むモンスターを攻略するフリップ&amp;パンチング。ここぞという時にパワーを発揮するジグフィッシング。そして、スイムベイト&amp;ビッグベイト。その一匹でしか得られない感動や達成感、気持ちよさを享受するための釣り。これらを完遂させるのがストロングゲームスペシャル。 リグのウェイトを感じながらヘビーカバーに臆することなく低い弾道で高精度に撃ち込み、カバーの中でのバイトを確実に捕らえる感度と掛けてから一気に引き剥がすパワー。 バンクやシャローのカバー際、オーバーハング下に重量級ルアーを正確に撃ち込み、小さな着水音を作る。トゥイッチやリーリングジャーク、シェイク巻きで自在にルアーを操り、バイトに持ち込むテクニカルなビッグベイティング。 これら相反する静と動の釣りを1本で完遂させた立役者が「への字テーパー」。リグをカバーに撃ち込み、ブッシュやベジテーション等に絡めつつもスタックさせずに操作出来、且つラインスラックも自動的に作り、水中の情報をスポイルせず手元まで伝える。 またスイムベイト＆ビッグベイトの投げやすさとフィネスな操作性にも一役買っている。Hパワーの「への字テーパー」はヘビースピナーベイトのスローロールにも秀逸。グラスやストラクチャーを綺麗に躱しつつ、バイトは弾かずフックアップさせるポテンシャルを秘めている。 Application：Rubber Jig / Texas Rig / Leaderless Down Shot Rig / Free Rig / No Sinker Rig / Swim jig / Swimbait / Big Bait / Spinnerbait / Crawlerbait HVFナノプラス/X45フルシールド（X45コブラシールド）/エアセンサ―シート</v>
       </c>
+      <c r="AH191" t="str">
+        <v/>
+      </c>
+      <c r="AI191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -21888,6 +23034,12 @@
       <c r="AG192" t="str">
         <v>S64UL-2は誰が振ってもキレイなシェイクが出来、タフな状況下でも食わせるハイピッチなシェイクも可能にし、高弾性フルチューブラーならではの手感度とあらゆるリグへの対応力、遠投性能を併せ持ち、全国ワカサギレイクで威力を発揮するホバスト、ミドスト、ボトストにも対応したバーサタイルULスピン。 ULパワーのセンターカット2PCS構造でありながら、継部の突っ張りがなく、センターカット2PCSと感じさせない投げやすさと軽量リグの遠投性能、感度、操作性を実現したアイテム。 ミドスト系ULパワーのセンターカット2PCS化ではなく、センターカット2PCS構造でありながら求められる機能を具備させるためにテーパーバランスを一から見直し、独自 に設計。 ティップに「”へ”の字テーパー」を施すことで感度と操作性を生み出し、スラックラインシェイクでのラインの緩急をも感じ取れ、強風下でもティップが負けることなく、操作出来、集中力を切らさず一定のリズムでシェイクを刻む事が可能。ボトムの釣りでは、センターカット2PCSとは思えないボトムやウィードのタッチ感と躱したときの抜け感も秀逸で、強靭なバットパワーを生む並継構造に、さらにバットパワーを上げる事で、強風下でも風に負けない直進性と遠投性能が向上。 ホバストの様なハイピッチシェイクでも胴ブレすることなく、シェイクピッチとティップの振れ幅を自在にコントロール出来る未だかつて体感したことのないセンターカット2PCSのULスピニングに仕上がった。 Application :Hover Strolling /Mid Strolling/Bottom Strolling/Neko Rig /SmallRubber Jig/Wacky Jighead Rig/No Sinker Rig /Down Shot Rig /Small Plug HVFナノプラス/X45フルシールド（X45コブラシールド）</v>
       </c>
+      <c r="AH192" t="str">
+        <v/>
+      </c>
+      <c r="AI192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -21989,6 +23141,12 @@
       <c r="AG193" t="str">
         <v>S64Lは、タフな現代のフィールドでこそ真価を発揮するバーサタイルモデル。 ルアー対応幅の広いテーパーに、ティップの先端を「への字テーパー」にすることで、ルアーの重さや空気抵抗、アングラーのスウィングスピードに関わらず、ルアーの重みを乗せる部分を一極集中させることで投げやすく、トリプルフックの付いたルアーのキャストを躊躇するようなオーバーハングの下やカバー際に低弾道でピタピタに入れていくアキュラシーキャストから高精度なロングキャストまで可能。 高弾性のソフトなティップでありながら先端を「への字テーパー」にすることで、ストレートリトリーブでの高弾性特有の突っ張る巻き感も無く、ティップが踊りラインを弛ませて引くことが出来る。 ボトムに当たってもバウンドして軌道が狂うことなく、ガツッとスタックすることもなく、綺麗に躱すリーリングが可能。 バイトの瞬間は、への字のティップがスコンッと入り込むことで、弾くことなく針先を口の中に残し反転の間を持たせ、ベリー～バットでオートマチックなフッキングが可能。 一方で「への字テーパー」がワーミングに於いては、自動的にラインスラックを作りだしつつも、ボトムの小さな起伏を鋭敏に感じとれる感度と繊細さがあり、高弾性チューブラーながらもまるで硬いソリッドティップの様なモタレ感もあり、プレッシャーをかけることなく半スタック状態で誘える操作感もあるマルチパーパスロッド。 Application :Shad /Propbait /Bug lure /Jerkbait /Topwater Plug /Crankbait /Metal Vibration /Neko Rig /Small Rubber Jig /No Sinker Rig /Down Shot Rig /Jighead Rig /Wacky Jighead Rig HVFナノプラス/X45フルシールド（X45コブラシールド）/エアセンサ―シート</v>
       </c>
+      <c r="AH193" t="str">
+        <v/>
+      </c>
+      <c r="AI193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -22090,6 +23248,12 @@
       <c r="AG194" t="str">
         <v>S66L-5は、タフな現代のフィールドでこそ真価を発揮するバーサタイルモデル。 ルアー対応幅の広いテーパーに、ティップの先端を「への字テーパー」にすることで、ルアーの重みを乗せる部分を一極集中させることで投げやすく、トリプルフックの付いたルアーのキャストを躊躇するようなオーバーハングの下やカバー際に低弾道でピタピタに入れていくアキュラシーキャストから高精度なロングキャストまで可能。 ソフトなティップの先端を「への字テーパー」にすることで、ワーミングに於いては、スタックを躱しつつ自動的にラインスラックを作りだし、ボトムの小さな起伏を鋭敏に感じとれる感度と繊細さがある。 また操作時は「への字」ティップによりアクションをスポイルすることなくルアーに伝える高精度な操作感もあり、ワーミングだけでなく操作系ハードベイトにも秀逸。 リーリングベイトのストレートリトリーブでは「への字」のティップにより、高弾性特有の突っ張る巻き感も無く、ティップが踊りラインを弛ませて引くことが出来、スタックもすることなく綺麗に躱す一方でバイトの瞬間は、への字のティップがスコンッと入り込むことで、反転の間を持たせ、ベリー～バットでオートマチックなフッキングが可能。 バスだけに留まらず、あらゆるフィッシュイーターにも対応するマルチパーパスロッド。 Application:Shad /Minnow /Propbait /Crankbait /Small Wire Bait /Bug lure/Topwater Plug /Jerkbait /Metal Vibration /Neko Rig /Small Rubber Jig /NoSinker Rig /Down Shot Rig /Jighead Rig /Wacky Jighead Rig HVFナノプラス/X45フルシールド（X45コブラシールド）</v>
       </c>
+      <c r="AH194" t="str">
+        <v/>
+      </c>
+      <c r="AI194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -22191,6 +23355,12 @@
       <c r="AG195" t="str">
         <v>S66MLは、タフな現代のフィールドでこそ真価を発揮するバーサタイルモデル。 強靭なバットを備えたファストテーパーのティップを「への字テーパー」にすることで、ルアーの重みを一極集中させ投げやすく、胴ブレしない強靭なバットにより直進性の優れた鋭いキャストが可能。 特に軽量でキャスト時に空中回転しやすい、バルサ製のシャッドプラグや風に流されやすくキャストが決まりにくいフラットサイドクランクなど投げにくいルアーも鋭いスピードとパワーでロング＆アキュラシーキャストが可能。 キャスト時はシャキッとした高弾性特性を感じられるテイストでありながら、先端を「への字テーパー」にすることで、ストレートリトリーブでは高弾性特有の突っ張る巻き感も無く、ティップが踊りラインを弛ませて引くことが出来る。 ボトムにコンタクトした際もバウンドして軌道が狂うことなく、ガツッとスタックすることもなく、綺麗に躱すリーリングが可能。 バイトの瞬間は、への字のティップがスコンッと入り込むことで、弾くことなく針先を口の中に残し反転の間を持たせ、強靭なベリー～バットでオートマチックにフッキングさせる。 一方でワーミングに於いては、高弾性特性が一気にあらわになり、ボトムの小さな起伏を鋭敏に感じとれる感度と繊細さが突出。「への字テーパー」との組み合わせで操作性も向上し、ラインスラックを自動的に作りだすことでリグをより釣れる状態に。またこれらの特性がメタル系ルアーでも威力を発揮。 リアクションを誘発する操作性とバイトの吸い込みやすさ、そしてフッキング性能がミスの多いメタルゲームを完遂させる。 鋭いアキュラシーキャストと操作性、自動的にスラックを出せるへの字テーパーがスモールフロッグにも抜群の性能を発揮。ありとあらゆるルアー・リグに対応するマルチパーパススピニング。 Application :Shad /Flat Sided Crankbait /Propbait /Bug lure /Jerkbait /Topwater Plug /Small Frog /Metal Vibration /Metal Jig /Neko Rig /Small Rubber Jig /No Sinker Rig /Down Shot Rig /Jighead Rig /Light Texas Rig HVFナノプラス/X45フルシールド（X45コブラシールド）/エアセンサ―シート</v>
       </c>
+      <c r="AH195" t="str">
+        <v/>
+      </c>
+      <c r="AI195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -22292,6 +23462,12 @@
       <c r="AG196" t="str">
         <v>S70ML+　-5は、あらゆるルアーに高次元に対応するロングパワーバーサタイルモデル。 ファストテーパーのティップを「への字テーパー」にすることで、ルアーの重みを一極集中させ投げやすく、ヘビールアーでも胴ブレしないMパワー以上の強靭なバットにより直進性の優れた鋭いキャストが可能。 特にキャスト時に空中回転しやすいバルサ製のミノーやシャッド、風に流されやすいフラットサイドクランクなど、鋭いスピードとパワーでロング＆アキュラシーキャストが可能。 キャスト時はシャキッとした高弾性特性を感じられるテイストでありながら、先端の「への字テーパー」が機能し、ストレートリトリーブでは高弾性特有の突っ張る巻き感も無く、ティップが踊りラインを弛ませて引くことが出来、スタックも綺麗に躱すリーリングが可能。バイトの瞬間は、「への字」のティップがスコンッと入り込むことで、反転の間を持たせ、強靭なベリー～バットでオートマチックにフッキングさせる。 一方でワーミングに於いては、高弾性特性が一気にあらわになり、「への字テーパー」との組み合わせでボトムの小さな起伏を鋭敏に感じとれる感度と操作性も向上。 太糸にも対応する大口径ガイド、大物と対峙できるロンググリップを搭載することでバスだけに留まらず、あらゆるフィッシュイーターにも対応するマルチパーパススピニング。 Application:Shad /Minnow /Propbait /Crankbait /Small Wire Bait /Bug lure/Jerkbait /Topwater Plug /Small Frog /Metal Vibration /Metal Jig /Neko Rig/Small Rubber Jig /No Sinker Rig /Down Shot Rig /Jighead Rig /Light Texas Rig HVFナノプラス/X45フルシールド（X45コブラシールド）</v>
       </c>
+      <c r="AH196" t="str">
+        <v/>
+      </c>
+      <c r="AI196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -22393,6 +23569,12 @@
       <c r="AG197" t="str">
         <v>入り組んだブッシュへ正確に撃ち込むアキュラシー性能と操作性、そしてパワーを高次元に融合させたテクニカルフロッギングモデル。 ウェイトを乗せた軽快なキャスト性能を追求した中弾性カーボン・19BLX LG 631MHFB-FRの血統を汲み、ティップに「“へ”の字テーパー」を採用し、超高弾性カーボンをコンポジットしたことでユーザビリティが飛躍的に向上。ピンスポットを撃ち抜く低弾道のアキュラシーキャストはもちろん、「“へ”の字」ティップはサミングでティップがお辞儀することでソフトな着水音を可能に。 ベリー～バットには超高弾性カーボンを採用して、小さなモーションでもしっかりとアクションさせ、PEの水切り音も抑えてプレッシャーを軽減する。1アクション目から艶めかしい動きを見せ、操作時のラインテンションの緩急も感じ取りながらの操作は秀逸。 また大型トップウォーターやジャークベイト、1oz強のジョイントベイトなど操作系ハードベイトの他、リーリングベイトにも抜群の相性を魅せ、ワーミングにも高次元に対応する。 ■LURE APPLICATION:Frog /Jointed Swimbait /Topwater Plug /Jerkbait /Crawler bait /Spinnerbait /Buzzbait /Bladed Jig /Swim Jig /Swimbait /No Sinker Rig /Rubber Jig /Texas Rig / Leaderless Down Shot Rig /Free Rig ■TECHNOLOGY:HVF、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH197" t="str">
+        <v/>
+      </c>
+      <c r="AI197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -22494,6 +23676,12 @@
       <c r="AG198" t="str">
         <v>STEEZ RCを彷彿とさせる超細身かつ高反発のブランクスは、シャープな操作性と高感度を実現。 ベイトフィネスロッド・19BLX SG 641LFBの血統を汲み、ベリー〜バットをややマイルドなテーパーに仕上げたことで軽量ルアーのウェイトを乗せて投げやすく、キャスタビリティを飛躍的に向上。 ティップには「“へ”の字テーパー」を採用して、全身を超高弾性SVFでビルドアップ。狙ったスポットを正確に撃ち込むことを可能にした一方で、ボトムのタッチ感を始めとする感度と操作性がさらに突き抜ける。 ひとたび掛ければその細身ブランクからは想像できないリフトパワーを発揮して、ベイトロッドならではの安心したファイトが可能。操作性重視のネコリグ、スモラバ等での優れた操作性を始め、プロップベイトのストレートリトリーブではペラの回転を感じ獲れる巻き感度を発揮。 撃ちと巻きを両立して、ベイトフィネスを次なる次元へと導いていく。 ■LURE APPLICATION:Neko Rig /No Sinker Rig /Down Shot Rig /Small Rubber Jig /Small Plug ■TECHNOLOGY:SVF、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH198" t="str">
+        <v/>
+      </c>
+      <c r="AI198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -22595,6 +23783,12 @@
       <c r="AG199" t="str">
         <v>近年のハイプレッシャー化によりスモラバのパワーフィネスには口を使わなくなったバスを攻略する為に繊細さを併せ持ったパワーフィネスロッド。 MHやHパワーのパワーフィネスロッドのキャストはロッドにウェイトを乗せるという感覚は皆無であったが、MLパワーのティップを搭載することでティップセクションにウェイトを乗せてピッチングすることが可能になり、誰もが正確にシャローカバーを射抜くことが可能。またティップに「”へ”の字テーパー」を施すことによって、今までとは一線を画した繊細な操作感と手感度を手に入れ、レイダウン等を跨いで吊るした状態でもリグの状態が把握でき、繊細に操作できる。繊細なティップとは相反する強靭なバットがパワーフィネス特有の一瞬のバイトを鋭くアワせて、カバーからブッコ抜くことが可能。またパワーフィネスで有能な「”へ”の字テーパー」のティップが3.5ｇ～７ｇのジグヘッドを用いた5”～6”スティックベイトのミドストでも最高のパフォーマンスを発揮。湖面が波っ気が立った強風下でもラインテンションを巧みにコントロール出来、無になりがちな中層の釣りに於いても水中のリグの挙動が手に取るようにわかる手感度で、ラインテンションの緩急を感じながら、一定のリズムを刻むことでバイトに持ち込むことが出来る。 ■LURE APPLICATION:Neko Rig /Small Rubber Jig /No Sinker Rig /Down Shot Rig /Jighead Rig /Wacky Jighead Rig /Light Texas Rig /Small Plug ■TECHNOLOGY:SVF、X45X、3DX、ZEROSEAT</v>
       </c>
+      <c r="AH199" t="str">
+        <v/>
+      </c>
+      <c r="AI199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -22696,6 +23890,12 @@
       <c r="AG200" t="str">
         <v>C66L-LMは、多くのバスアングラーを覚醒させるクランキングにフォーカスしたアイテム。 アキュラシーとロングキャスト、どちらもこなせるレングスに、ロッドの調子を司る軸長方向の繊維を全て低弾性カーボン“Low Modulus”で構成。長めのティップセクションで曲がり代を長くしつつ、急激に立ち上がる強靭なバットを併せ持つ緩急のはっきりしたレギュラーファストテーパーのティップに「”へ”の字テーパー」に施したLパワーのブランク。曲がり代を長くしたティップセクションにより、手首を返すだけでロッドにウェイトを乗せやすく、ルアーの弾道が上がることなく低い弾道で運び、キャストが困難なスポットでもサイドハンドやバックハンドなどあらゆる角度から極限の精度で撃ち込むことが出来る。また着水直前のサミングで先端の「”へ”の字」ティップがスッとお辞儀することでソフトな着水音のキャストを実現。ティップを「”へ”の字テーパー」にすることで、ラインスラックを出したグラスの様な突っ張らない巻き感とグラスには出せない、ラインがカバーに触れた時の抵抗感や、ボトムやカバーのタッチ感を両立し、カバーのコンタクト時には「”へ”の字」ティップがショックアブソーバーの役目を果たし、スタックは躱すものの、バイト時はティップがスコンッと入ることでバイトを弾くことなく乗せ、強靭なバットで掛け、主導権を握ったファイトが可能。長めのティップセクションで曲がり代を長くし、「”へ”の字テーパー」を施したティップにより、フラットサイドクランクのシャイキーやクラストといったメソッドにも完全対応。「ユーザビリティー」が開発コンセプトの25ＢＬＸらしく、誰もがシェイキーアクションを出せるテーパーデザインで、ロッドが仕事をすることで腕の疲労を軽減。タフなフィールドでのフィネスなクランキングに完全対応した“釣れる”クランキングロッド。 ■LURE APPLICATION:Shallow Diving Crankbait /Tiny Crankbait /Flat Sided Crankbait /Shad Plug /Tiny Topwater Plug ■TECHNOLOGY:Low Modulus、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH200" t="str">
+        <v/>
+      </c>
+      <c r="AI200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -22797,6 +23997,12 @@
       <c r="AG201" t="str">
         <v>C66L-LMは、多くのバスアングラーを覚醒させるクランキングにフォーカスしたアイテム。 アキュラシーとロングキャスト、どちらもこなせるレングスに、ロッドの調子を司る軸長方向の繊維を全て低弾性カーボン“Low Modulus”で構成。長めのティップセクションで曲がり代を長くしつつ、急激に立ち上がる強靭なバットを併せ持つ緩急のはっきりしたレギュラーファストテーパーのティップに「”へ”の字テーパー」に施したLパワーのブランク。曲がり代を長くしたティップセクションにより、手首を返すだけでロッドにウェイトを乗せやすく、ルアーの弾道が上がることなく低い弾道で運び、キャストが困難なスポットでもサイドハンドやバックハンドなどあらゆる角度から極限の精度で撃ち込むことが出来る。また着水直前のサミングで先端の「”へ”の字」ティップがスッとお辞儀することでソフトな着水音のキャストを実現。ティップを「”へ”の字テーパー」にすることで、ラインスラックを出したグラスの様な突っ張らない巻き感とグラスには出せない、ラインがカバーに触れた時の抵抗感や、ボトムやカバーのタッチ感を両立し、カバーのコンタクト時には「”へ”の字」ティップがショックアブソーバーの役目を果たし、スタックは躱すものの、バイト時はティップがスコンッと入ることでバイトを弾くことなく乗せ、強靭なバットで掛け、主導権を握ったファイトが可能。長めのティップセクションで曲がり代を長くし、「”へ”の字テーパー」を施したティップにより、フラットサイドクランクのシャイキーやクラストといったメソッドにも完全対応。「ユーザビリティー」が開発コンセプトの25ＢＬＸらしく、誰もがシェイキーアクションを出せるテーパーデザインで、ロッドが仕事をすることで腕の疲労を軽減。タフなフィールドでのフィネスなクランキングに完全対応した“釣れる”クランキングロッド。 ■LURE APPLICATION:Shallow Diving Crankbait /Tiny Crankbait /Flat Sided Crankbait /Shad Plug /Tiny Topwater Plug ■TECHNOLOGY:Low Modulus、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH201" t="str">
+        <v/>
+      </c>
+      <c r="AI201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -22898,6 +24104,12 @@
       <c r="AG202" t="str">
         <v>C66M-LMは多くのバスアングラーを覚醒させるクランキングにフォーカスしたアイテム。 アキュラシーとロングキャスト、どちらもこなせるレングスに、ロッドの調子を司る軸長方向の繊維を全て低弾性カーボン“Low Modulus”で構成。長めのティップセクションで曲がり代を長くし、強靭なバットを併せ持つ緩急のはっきりしたレギュラーファストテーパーのティップに「”へ”の字テーパー」を施した唯一無二のブランク。「”へ”の字テーパー」の長めのティップセクションが、手首を返すだけでウェイトを乗せやすく、ルアーの弾道が上がることなく低い弾道でルアーを運び、ソフトな着水音のキャストが可能。キャストが困難なスポットでもサイドハンドやバックハンドなどあらゆる角度からでも極限の精度で撃ち込むことが出来る。急激に立ち上がる強靭なバットパワーでワイヤーベイトのシングルフックを上顎に貫通させるパワーを誇り、より重量級のルアーにも対応。リトリーブを始めると「”へ”の字」のティップが踊り、ラインスラックを出したリトリーブが可能。誰が使ってもユーザビリティーの高さを感じられる“釣れる”クランキングロッド。 ■LURE APPLICATION:Spinnerbait /Buzzbait /Bladed Jig /Vibration /Crankbait /Topwater Plug /Jerkbait ■TECHNOLOGY:Low Modulus、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH202" t="str">
+        <v/>
+      </c>
+      <c r="AI202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -22999,6 +24211,12 @@
       <c r="AG203" t="str">
         <v>C66M-LMは多くのバスアングラーを覚醒させるクランキングにフォーカスしたアイテム。 アキュラシーとロングキャスト、どちらもこなせるレングスに、ロッドの調子を司る軸長方向の繊維を全て低弾性カーボン“Low Modulus”で構成。長めのティップセクションで曲がり代を長くし、強靭なバットを併せ持つ緩急のはっきりしたレギュラーファストテーパーのティップに「”へ”の字テーパー」を施した唯一無二のブランク。「”へ”の字テーパー」の長めのティップセクションが、手首を返すだけでウェイトを乗せやすく、ルアーの弾道が上がることなく低い弾道でルアーを運び、ソフトな着水音のキャストが可能。キャストが困難なスポットでもサイドハンドやバックハンドなどあらゆる角度からでも極限の精度で撃ち込むことが出来る。急激に立ち上がる強靭なバットパワーでワイヤーベイトのシングルフックを上顎に貫通させるパワーを誇り、より重量級のルアーにも対応。リトリーブを始めると「”へ”の字」のティップが踊り、ラインスラックを出したリトリーブが可能。誰が使ってもユーザビリティーの高さを感じられる“釣れる”クランキングロッド。 ■LURE APPLICATION:Spinnerbait /Buzzbait /Bladed Jig /Vibration /Crankbait /Topwater Plug /Jerkbait ■TECHNOLOGY:Low Modulus、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH203" t="str">
+        <v/>
+      </c>
+      <c r="AI203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -23100,6 +24318,12 @@
       <c r="AG204" t="str">
         <v>C66M-LMは多くのバスアングラーを覚醒させるクランキングにフォーカスしたアイテム。 アキュラシーとロングキャスト、どちらもこなせるレングスに、ロッドの調子を司る軸長方向の繊維を全て低弾性カーボン“Low Modulus”で構成。長めのティップセクションで曲がり代を長くし、強靭なバットを併せ持つ緩急のはっきりしたレギュラーファストテーパーのティップに「”へ”の字テーパー」を施した唯一無二のブランク。「”へ”の字テーパー」の長めのティップセクションが、手首を返すだけでウェイトを乗せやすく、ルアーの弾道が上がることなく低い弾道でルアーを運び、ソフトな着水音のキャストが可能。キャストが困難なスポットでもサイドハンドやバックハンドなどあらゆる角度からでも極限の精度で撃ち込むことが出来る。急激に立ち上がる強靭なバットパワーでワイヤーベイトのシングルフックを上顎に貫通させるパワーを誇り、より重量級のルアーにも対応。リトリーブを始めると「”へ”の字」のティップが踊り、ラインスラックを出したリトリーブが可能。誰が使ってもユーザビリティーの高さを感じられる“釣れる”クランキングロッド。 ■LURE APPLICATION:Spinnerbait /Buzzbait /Bladed Jig /Vibration /Crankbait /Topwater Plug /Jerkbait ■TECHNOLOGY:Low Modulus、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH204" t="str">
+        <v/>
+      </c>
+      <c r="AI204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -23201,6 +24425,12 @@
       <c r="AG205" t="str">
         <v>C66M-LMは多くのバスアングラーを覚醒させるクランキングにフォーカスしたアイテム。 アキュラシーとロングキャスト、どちらもこなせるレングスに、ロッドの調子を司る軸長方向の繊維を全て低弾性カーボン“Low Modulus”で構成。長めのティップセクションで曲がり代を長くし、強靭なバットを併せ持つ緩急のはっきりしたレギュラーファストテーパーのティップに「”へ”の字テーパー」を施した唯一無二のブランク。「”へ”の字テーパー」の長めのティップセクションが、手首を返すだけでウェイトを乗せやすく、ルアーの弾道が上がることなく低い弾道でルアーを運び、ソフトな着水音のキャストが可能。キャストが困難なスポットでもサイドハンドやバックハンドなどあらゆる角度からでも極限の精度で撃ち込むことが出来る。急激に立ち上がる強靭なバットパワーでワイヤーベイトのシングルフックを上顎に貫通させるパワーを誇り、より重量級のルアーにも対応。リトリーブを始めると「”へ”の字」のティップが踊り、ラインスラックを出したリトリーブが可能。誰が使ってもユーザビリティーの高さを感じられる“釣れる”クランキングロッド。 ■LURE APPLICATION:Spinnerbait /Buzzbait /Bladed Jig /Vibration /Crankbait /Topwater Plug /Jerkbait ■TECHNOLOGY:Low Modulus、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH205" t="str">
+        <v/>
+      </c>
+      <c r="AI205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -23302,6 +24532,12 @@
       <c r="AG206" t="str">
         <v>タフ化が進む現代のフィールドで釣り勝つべく、オカッパリのベイトフィネスで求められる要素を具備したベイトフィネスロッド。 STEEZ SC 24ウェアウルフをベースにユーザビリティーの向上を目指したアイテム。ティップにはSC24ウェアウルフ同様チューブラーに匹敵する硬さの「”へ”の字テーパー」を施したメガトップRソリッドを搭載することで、優れた感度と操作性を有し、トレース時には小さな変化を感じつつもスタックは躱し、ボトムやストラクチャーにモタレさせながら誘う事が出来る。またSVFコンパイルXのチューブラーをSVF化することで、高反発力な筋肉質ブランクに粘りが加わることでキャスト時のスイートスポットが広がり、投げやすさが向上。ブランク素材の変更により汎用性が拡大し、使い手を選ばないだけでなく、ルアーやリグの対応幅も広がり、ライトバーサタイルロッドとしての顔も覗かせるベイトフィネスロッド。 ■LURE APPLICATION:Snagless Neko Rig /Small Rubber Jig /No Sinker Rig /Down Shot Rig /Jerkbait /Topwater Plug /Spinnerbait ■TECHNOLOGY:SVF、X45X、3DX、MEGATOP R、ZEROSEAT</v>
       </c>
+      <c r="AH206" t="str">
+        <v/>
+      </c>
+      <c r="AI206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -23403,6 +24639,12 @@
       <c r="AG207" t="str">
         <v>柔軟なソリッドとは一線を画した高弾性メガトップの硬いソリッドティップに、強靭なチューブラーブランクを融合させ、”もたれ感”と高感度を両立したソリッドティップロッド。 感度だけでなく、カバーやボトム、ストラクチャーへの”もたれ感”を出すために高弾性メガトップのソリッドティップに強靭なSVFチューブラーブランクを組み合わせた特殊構造を採用。硬いソリッドティップの最大の特長である、チューブラーティップでは躱してしまい、感じ取れないボトムやカバー、ストラクチャーの小さな変化を感じ取れるのと同時に、リグをタイトにトレースすることカバーやストラクチャーにもたれさせたまま揺する操作が出来る繊細さとカバーから引きずり出すパワーを兼備。また、ソリッドティップではスタックしそうなハードボトムでもその前兆を感じとり、躱す操作を誘導。ラインスラックが出た状態でもラインの重みの差を感じ取れ、ソリッドティップで捉えた細かな振動を吸収することなく手元に伝達させ、今まで獲れなかった一本を絞り出すことが出来る。 ■LURE APPLICATION:Free Rig/ Texas Rig / Leaderless Down Shot Rig /Rubber Jig /Heavy Carolina Rig /Heavy Down Shot Rig /No Sinker Rig ■TECHNOLOGY:SVF、X45X、3DX、MEGATOP、ZEROSEAT</v>
       </c>
+      <c r="AH207" t="str">
+        <v/>
+      </c>
+      <c r="AI207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -23504,6 +24746,12 @@
       <c r="AG208" t="str">
         <v>優れた遠投性能はもちろん、シャローカバーや沖のピンスポットへ正確に送り込むアキュラシー性能、感度や操作性、そしてパワーさえも高次元に融合させたワイヤーベイトスペシャル。 19BLX LG 6101MRBの血統を汲み、ブランクには中弾性カーボンをベースに超高弾性カーボンでアシストした特殊構造を採用。強靭なバットで急激に立ち上げたテーパーを採用するスイムベイト・ビッグベイトロッドの設計思想を取り入れ、ルアーウェイトの上限を底上げすると共に、遠投性能が飛躍的に向上した。 テーパーはレギュラーファスト、かつティップには「“へ”の字テーパー」を採用することで、アキュラシー性能と投げやすさが昇華。 ルアー本来の泳ぎを出せるスラックラインリトリーブを自動的に実現して、不用意なスタックを躱せる一方でバイトは確実に乗せて掛ける。 ワイヤーベイトに求めたポテンシャルは、クランキング、そしてワーミングの対応レベルを大幅にアップすることに成功している。フルチューブラーのバーサタイルロッドとしても秀逸。 ■LURE APPLICATION:Spinnerbait /Buzzbait /Bladed Jig /Vibration /Swimbait /Crawler bait /Swim Jig /Prop bait /Topwater Plug /Jerkbait /Crankbait /Snagless Neko Rig /No Sinker Rig /Down Shot Rig /Texas Rig /Leaderless Down Shot Rig /Free Rig /Rubber Jig ■TECHNOLOGY:HVF、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH208" t="str">
+        <v/>
+      </c>
+      <c r="AI208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -23605,6 +24853,12 @@
       <c r="AG209" t="str">
         <v>狙いのピンスポットへ正確に送り込むアキュラシー性能のみならず、遠投性能を兼ね備え、感度・操作性・パワーを高次元に融合させたワイヤーベイト・スイムベイト&amp;ビッグベイトスペシャリティ。 中弾性カーボンで作り上げた19BLX LG 6101MHFBの血統を汲み、超高弾性カーボンでアシストした特殊構造を採用。バットのテーパーを急激に立ち上げるスイムベイト・ビッグベイトロッドのテーパーデザインを採用することでルアーウェイトの上限が高まり、マグナムクランクや2ozクラスのビッグベイトにも磐石の対応を見せるモデルに仕上がった。 先端が曲がらない「“へ”の字」ティップを採用することで、感度と操作性が劇的に向上するのみならず、ワーミングへの対応レベルが大幅にアップ。 ハードベイトだけでなくワーミングにも対応するフルチューブラーバーサタイルモデル。共にレギュラーファストテーパーのC610Mとはパワー違いで使い分けの幅を広げる。 ■LURE APPLICATION:Spinnerbait /Buzzbait /Bladed Jig /Swim Jig /Vibration /Magnum Crankbait /Swimbait /Big Bait /Crawler bait /Topwater Plug /Frog /Rubber Jig /Texas Rig /Leaderless Down Shot Rig /No Sinker Rig ■TECHNOLOGY:HVF、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH209" t="str">
+        <v/>
+      </c>
+      <c r="AI209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -23706,6 +24960,12 @@
       <c r="AG210" t="str">
         <v>現代のタフ化が進むフィールドでビッグベイト・スイムベイトの実釣性能を最大限引き出し、4ozクラスのスイムベイト＆ビッグベイトに対応したSB（スイムベイト・ビッグベイト）ロッド。 重量級ルアーでもサイドハンドの低弾道キャストでオーバーハングの下にビッグベイトを入れ込み、ソフトな着水音でキャストを決め、ロッドワークやリーリングで操り、バイトに持ち込むビッグベイトゲームを完遂できるアイテム。XHパワーのスティッフなティップに「”へ”の字テーパー」を施すことにより、バンクやシャローのカバー際、オーバーハングの下に重量級ルアーを正確に入れ込むことが容易になり、着水直前のサミングで先端の「”へ”の字」ティップがスッとお辞儀することでソフトな着水音のキャストを実現。トゥイッチやリーリングジャーク、シェイク巻きでルアーを繊細かつ正確に操り、グリフワの高速リトリーブではルアーを引っ張り過ぎることなく艶めかしいアクションを演出させ、止めた時にラインスラックを作りやすくなっているのも「”へ”の字テーパー」の真骨頂。さらに、突発的なバイトもティップがスコンッと入ることで反転の間を与え、弾かずしっかり絡めとり、強靭なバットパワーで太軸フックを貫通させる。強さの中に適度なしなやかさを残すことで安心して魚とファイト出来る。 ■LURE APPLICATION:Swim Bait /Big Bait /Crawlerbait /Alabama Rig /Spinnerbait /Topwater Plug /Buzzbait /Bladed Jig /Swim Jig /Rubber Jig /Texas Rig /Leaderless Down Shot Rig /No Sinker Rig ■TECHNOLOGY:HVF、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH210" t="str">
+        <v/>
+      </c>
+      <c r="AI210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -23807,6 +25067,12 @@
       <c r="AG211" t="str">
         <v>ヘビキャロをはじめとしたボトム探査系の釣りからテキサスリグのカバー撃ちまで幅広く対応して、究極の感度と操作性を誇るジグ＆ワーミングのヘビーバーサタイルモデル。 繊細なティップを持ちボトム感知能力に優れる19BLX SG 701MHXB及びSTEEZストライクフォースの血統を汲み、素材に高弾性SVF、ティップに「“へ”の字テーパー」を採用することでその機能はさらに昇華。 手感度の向上のみならず、ハードボトムやグラス、ヘビーカバーのスタックを躱して誘うことさえも可能にした。またシャローのピンスポットを正確に撃ち抜くピッチング性能と、フラットに点在するストラクチャーやブレイクのエッジに正確にリグを送り込むキャスト性能も飛躍的に向上。 ヘビキャロにおいてはヘビーシンカーにも負けないシャープなティップが、ワームを自在に踊らせる操作性、フックに葉っぱ1枚が付いた状態さえも伝える優れた高感度を実現している。 カバー撃ちや沖のグラスを探る釣りでも同様に繊細な操作を可能にする。 ■LURE APPLICATION:Heavy Carolina Rig /Texas Rig /Rubber Jig /Leaderless Down Shot Rig /Free Rig /No Sinker Rig /Swim Jig /Spinnerbait /Swimbait /Frog ■TECHNOLOGY:SVF、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH211" t="str">
+        <v/>
+      </c>
+      <c r="AI211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -23908,6 +25174,12 @@
       <c r="AG212" t="str">
         <v>タフ化が進む現代のフィールドで釣り勝つべく、オカッパリのベイトフィネスで求められる要素を具備したベイトフィネスロッド。 STEEZ SC 24ウェアウルフをベースにユーザビリティーの向上を目指したアイテム。ティップにはSC24ウェアウルフ同様チューブラーに匹敵する硬さの「”へ”の字テーパー」を施したメガトップRソリッドを搭載することで、優れた感度と操作性を有し、トレース時には小さな変化を感じつつもスタックは躱し、ボトムやストラクチャーにモタレさせながら誘う事が出来る。またSVFコンパイルXのチューブラーをSVF化することで、高反発力な筋肉質ブランクに粘りが加わることでキャスト時のスイートスポットが広がり、投げやすさが向上。ブランク素材の変更により汎用性が拡大し、使い手を選ばないだけでなく、ルアーやリグの対応幅も広がり、ライトバーサタイルロッドとしての顔も覗かせるベイトフィネスロッド。 ■LURE APPLICATION:Snagless Neko Rig /Small Rubber Jig /No Sinker Rig /Down Shot Rig /Jerkbait /Topwater Plug /Spinnerbait ■TECHNOLOGY:SVF、X45X、3DX、MEGATOP R、ZEROSEAT</v>
       </c>
+      <c r="AH212" t="str">
+        <v/>
+      </c>
+      <c r="AI212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -24009,6 +25281,12 @@
       <c r="AG213" t="str">
         <v>近年のハイプレッシャー化によりスモラバのパワーフィネスには口を使わなくなったバスを攻略する為に繊細さを併せ持ったパワーフィネスロッド。 MHやHパワーのパワーフィネスロッドのキャストはロッドにウェイトを乗せるという感覚は皆無であったが、MLパワーのティップを搭載することでティップセクションにウェイトを乗せてピッチングすることが可能になり、誰もが正確にシャローカバーを射抜くことが可能。またティップに「”へ”の字テーパー」を施すことによって、今までとは一線を画した繊細な操作感と手感度を手に入れ、レイダウン等を跨いで吊るした状態でもリグの状態が把握でき、繊細に操作できる。繊細なティップとは相反する強靭なバットがパワーフィネス特有の一瞬のバイトを鋭くアワせて、カバーからブッコ抜くことが可能。またパワーフィネスで有能な「”へ”の字テーパー」のティップが3.5ｇ～７ｇのジグヘッドを用いた5”～6”スティックベイトのミドストでも最高のパフォーマンスを発揮。湖面が波っ気が立った強風下でもラインテンションを巧みにコントロール出来、無になりがちな中層の釣りに於いても水中のリグの挙動が手に取るようにわかる手感度で、ラインテンションの緩急を感じながら、一定のリズムを刻むことでバイトに持ち込むことが出来る。 ■LURE APPLICATION:Neko Rig /Small Rubber Jig /No Sinker Rig /Down Shot Rig /Jighead Rig /Wacky Jighead Rig /Light Texas Rig /Small Plug ■TECHNOLOGY:SVF、X45X、3DX、ZEROSEAT</v>
       </c>
+      <c r="AH213" t="str">
+        <v/>
+      </c>
+      <c r="AI213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -24110,6 +25388,12 @@
       <c r="AG214" t="str">
         <v>「“へ”の字テーパー」のティップに強靭なバットパワーを備え、巻きと撃ちの双方を自在にこなせるビッグレイク対応のロング&amp;パワーバーサタイルロッド。 ティップに「“へ”の字」を採用したSVFでビルドアップした筋肉質ブランクは圧倒的な飛距離を叩き出し、より広範囲を探ることを可能にする。また水中の情報を手元まで伝達する優れた感度も特筆で、ウィードとグラスの硬軟を問わずタッチ感と抜け感が向上して、ラインスラックを自動的に作り出すティップはウィードやグラスを揺らすことなく躱し、よりナチュラルな操作を可能にする。 ロングレングスを生かしてスラックを出しやすく、高さのあるグラスでは縦方向の操作が容易に。巻きではスラックラインリトリーブを可能にして、スタックを躱せるストレスフリーの巻きを実現。遠投した先でも回転角の狭いブレードを持つスピナーベイトの振動、スイムジグのシャッドテールのロールさえも手元に伝え集中力を高めてくれる。 ■LURE APPLICATION:Rubber Jig /Texas Rig /Leaderless Down Shot Rig /Free Rig /Heavy Carolina Rig /No Sinker Rig /Swim Jig /Spinnerbait /Swimbait /Big Bait /Crawlerbait ■TECHNOLOGY:SVF、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH214" t="str">
+        <v/>
+      </c>
+      <c r="AI214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -24211,6 +25495,12 @@
       <c r="AG215" t="str">
         <v>C66M-LMは多くのバスアングラーを覚醒させるクランキングにフォーカスしたアイテム。 アキュラシーとロングキャスト、どちらもこなせるレングスに、ロッドの調子を司る軸長方向の繊維を全て低弾性カーボン“Low Modulus”で構成。長めのティップセクションで曲がり代を長くし、強靭なバットを併せ持つ緩急のはっきりしたレギュラーファストテーパーのティップに「”へ”の字テーパー」を施した唯一無二のブランク。「”へ”の字テーパー」の長めのティップセクションが、手首を返すだけでウェイトを乗せやすく、ルアーの弾道が上がることなく低い弾道でルアーを運び、ソフトな着水音のキャストが可能。キャストが困難なスポットでもサイドハンドやバックハンドなどあらゆる角度からでも極限の精度で撃ち込むことが出来る。急激に立ち上がる強靭なバットパワーでワイヤーベイトのシングルフックを上顎に貫通させるパワーを誇り、より重量級のルアーにも対応。リトリーブを始めると「”へ”の字」のティップが踊り、ラインスラックを出したリトリーブが可能。誰が使ってもユーザビリティーの高さを感じられる“釣れる”クランキングロッド。 ■LURE APPLICATION:Spinnerbait /Buzzbait /Bladed Jig /Vibration /Crankbait /Topwater Plug /Jerkbait ■TECHNOLOGY:Low Modulus、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH215" t="str">
+        <v/>
+      </c>
+      <c r="AI215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216" xml:space="preserve">
       <c r="A216" t="str">
@@ -24313,6 +25603,12 @@
         <v xml:space="preserve">現代のタフ化が進むフィールドで釣り勝つべく、ビッグベイト・スイムベイトの実釣性能を最大限引き出したショアコンペティション(SC）のSB（スイムベイト・ビッグベイト）ロッド。 STEEZ SC ストラトフォートレス68をベースにユーザビリティーの向上を目指したアイテム。 ビッグベイト・スイムベイトの遠投性能、近距離を高精度に撃ち込むピッチング性能、バイトに持ち込むために水中のルアーを水に絡ませた艶めかしいアクションを繊細かつ正確に演出させる操作性、そして水中のルアーの状態をアングラー側に伝える感度、突発的なバイトも弾かずしっかり絡めながらも太軸フックを貫通させるバットパワー、強さの中に安心して魚とファイト出来る適度なしなやかさ。
 これら相反する要素を絶妙なバランスで一本に纏め上げた、ストラトフォートレス68をベースにステンレスフレームガイドをセッティング。耐久性が増すだけでなく、ガイドの重みで竿がしなってくれるおかげで投げやすくなっており、スローなスウィングでもルアーを弾き飛ばしてくれ、遠投性能やオーバーハングの奥の奥までルアーを運んでくれる。ティップをスティッフにすることで近距離のピッチング性能を向上させた一方で、硬い高弾性ソリッドティップの先端に「”へ”の字テーパー」を施すことにより手感度とリニアな操作性、さらにビッグベイトのノリの良さを大幅に向上。チューブラーは中弾性カーボンを採用することで硬さの中にもしなやかさを持たせつつ、バットを3DXでアシストする事で、遠投性能を引き出した。1PCモデルの性能を維持したまま、携行性を高めつつもVジョイントを搭載することで、通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上したハイレベルなセンターカット2PCS。 ■LURE APPLICATION:Swim Bait /Big Bait /Crawlerbait /Alabama Rig /Rubber Jig /Texas Rig /Leaderless Down Shot Rig /No Sinker Rig /Spinnerbait ■TECHNOLOGY:SVF、X45X、3DX、MEGATOP、ZEROSEAT、V-JOINT</v>
       </c>
+      <c r="AH216" t="str">
+        <v/>
+      </c>
+      <c r="AI216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217" xml:space="preserve">
       <c r="A217" t="str">
@@ -24415,6 +25711,12 @@
         <v xml:space="preserve">現代のタフ化が進むフィールドで釣り勝つべく、ビッグベイト・スイムベイトの実釣性能を最大限引き出したショアコンペティション(SC）のSB（スイムベイト・ビッグベイト）ロッド。 STEEZ SC ストラトフォートレス68をベースにユーザビリティーの向上を目指したアイテム。 ビッグベイト・スイムベイトの遠投性能、近距離を高精度に撃ち込むピッチング性能、バイトに持ち込むために水中のルアーを水に絡ませた艶めかしいアクションを繊細かつ正確に演出させる操作性、そして水中のルアーの状態をアングラー側に伝える感度、突発的なバイトも弾かずしっかり絡めながらも太軸フックを貫通させるバットパワー、強さの中に安心して魚とファイト出来る適度なしなやかさ。
 これら相反する要素を絶妙なバランスで一本に纏め上げた、ストラトフォートレス68をベースにステンレスフレームガイドをセッティング。耐久性が増すだけでなく、ガイドの重みで竿がしなってくれるおかげで投げやすくなっており、スローなスウィングでもルアーを弾き飛ばしてくれ、遠投性能やオーバーハングの奥の奥までルアーを運んでくれる。ティップをスティッフにすることで近距離のピッチング性能を向上させた一方で、硬い高弾性ソリッドティップの先端に「”へ”の字テーパー」を施すことにより手感度とリニアな操作性、さらにビッグベイトのノリの良さを大幅に向上。チューブラーは中弾性カーボンを採用することで硬さの中にもしなやかさを持たせつつ、バットを3DXでアシストする事で、遠投性能を引き出した。1PCモデルの性能を維持したまま、携行性を高めつつもVジョイントを搭載することで、通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上したハイレベルなセンターカット2PCS。 ■LURE APPLICATION:Swim Bait /Big Bait /Crawlerbait /Alabama Rig /Rubber Jig /Texas Rig /Leaderless Down Shot Rig /No Sinker Rig /Spinnerbait ■TECHNOLOGY:SVF、X45X、3DX、MEGATOP、ZEROSEAT、V-JOINT</v>
       </c>
+      <c r="AH217" t="str">
+        <v/>
+      </c>
+      <c r="AI217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -24516,6 +25818,12 @@
       <c r="AG218" t="str">
         <v>タフな現代のフィールドで釣り勝つために、更なる汎用性を具現。ショアコンペティションの中核を成す究極のバーサタイルロッド。 「”へ”の字テーパー」の中弾性ソリッドと、高弾性SVFのチューブラーで、レギュラーファストテーパーに纏め上げたSTEEZ 22ファイヤーウルフをベースに、ユーザビリティーを向上させた25BLX SC C69M+ -STのセンターカット2PCSモデル。先端「”へ”の字テーパー」のソリッドティップは、水中の変化を捉え、手元まで伝達する高い感度と繊細な操作を実現。ハードベイトに於いては中弾性ソリッドと相まって、ラインテンションを抜いたスラックラインリトリーブが出来、ルアー本来のアクションを引き出し、ノセ感にも優れる。またレギュラーファストテーパーにすることで、ラバージグなどの抵抗が大きなリグでもティップがもたれることなく思い通りの操作が可能。ステンレスフレームガイドをセッティングすることでガイドの重みで竿がしなりやすくなり、投げやすくなっているだけでなく、スローなスウィングでもルアーを低弾道で弾き飛ばす。1PCモデルの性能を維持したまま、携行性を高めつつもVジョイントを搭載することで、通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上。釣り勝てるセンターカット2PCSに仕上がった。 ■LURE APPLICATION:Snagless Neko Rig /No Sinker Rig /Down Shot Rig /Texas Rig /Leaderless Down Shot Rig /Free Rig /Rubber Jig /Spinnerbait /Vibration /Crankbait /Crawlerbait ■TECHNOLOGY:SVF、X45X、MEGATOP、ZEROSEAT、V-JOINT</v>
       </c>
+      <c r="AH218" t="str">
+        <v/>
+      </c>
+      <c r="AI218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -24617,6 +25925,12 @@
       <c r="AG219" t="str">
         <v>タフな現代のフィールドで釣り勝つために、更なる汎用性を具現。ショアコンペティションの中核を成す究極のバーサタイルロッド。 「”へ”の字テーパー」の中弾性ソリッドと、高弾性SVFのチューブラーで、レギュラーファストテーパーに纏め上げたSTEEZ 22ファイヤーウルフをベースに、ユーザビリティーを向上させた25BLX SC C69M+ -STのセンターカット2PCSモデル。先端「”へ”の字テーパー」のソリッドティップは、水中の変化を捉え、手元まで伝達する高い感度と繊細な操作を実現。ハードベイトに於いては中弾性ソリッドと相まって、ラインテンションを抜いたスラックラインリトリーブが出来、ルアー本来のアクションを引き出し、ノセ感にも優れる。またレギュラーファストテーパーにすることで、ラバージグなどの抵抗が大きなリグでもティップがもたれることなく思い通りの操作が可能。ステンレスフレームガイドをセッティングすることでガイドの重みで竿がしなりやすくなり、投げやすくなっているだけでなく、スローなスウィングでもルアーを低弾道で弾き飛ばす。1PCモデルの性能を維持したまま、携行性を高めつつもVジョイントを搭載することで、通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上。釣り勝てるセンターカット2PCSに仕上がった。 ■LURE APPLICATION:Snagless Neko Rig /No Sinker Rig /Down Shot Rig /Texas Rig /Leaderless Down Shot Rig /Free Rig /Rubber Jig /Spinnerbait /Vibration /Crankbait /Crawlerbait ■TECHNOLOGY:SVF、X45X、MEGATOP、ZEROSEAT、V-JOINT</v>
       </c>
+      <c r="AH219" t="str">
+        <v/>
+      </c>
+      <c r="AI219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220" xml:space="preserve">
       <c r="A220" t="str">
@@ -24719,6 +26033,12 @@
         <v xml:space="preserve">タフ化が進む現代のフィールドで釣り勝つ為の要素を凝縮し、一本で幅広いルアーに対応するバーサタイル性を兼ね備えたヘビーバーサタイルモデル。 繊細な操作性と感度を生み出す「”へ”の字テーパー」をティップに施したレギュラーテーパーとあらゆるウェイトのキャストでも打点がブレないスローテーパーをマルチテーパーデザインにより１本に纏め上げたSTEEZ SC 24キングヴァイパーをベースにユーザビリティーを向上させた25BLX SC C69MHのセンターカット2PCSモデル。使用頻度の高い3/8oz.クラスのジグ＆ワームから2oz.クラスのビッグベイトに焦点を合わせ、さらにヘビーウェイトのスピナーベイト、そしてマグナムクランクといったファストムービングルアーにも対応。
 キャスタビリティー、フルベンドならではの粘り感を残しつつ、感度、操作性、瞬時のフッキングレスポンスを兼備している。ステンレスフレームガイドをセッティングすることでガイドの重みで竿がしなりやすくなり、投げやすくなっているだけでなく、スローなスウィングでもルアーを低弾道で弾き飛ばす。1PCモデルの性能を維持したまま、携行性を高めつつもVジョイントを搭載することで、通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上。釣り勝てるセンターカット2PCSに仕上がった。 ■LURE APPLICATION:Rubber Jig /Texas Rig /Leaderless Down Shot Rig /No Sinker Rig / Spinnerbait /Crawler bait /Swim bait /Big Bait /Magnum Crankbait / Frog ■TECHNOLOGY:SVF、X45X、3DX、ZEROSEAT、V-JOINT</v>
       </c>
+      <c r="AH220" t="str">
+        <v/>
+      </c>
+      <c r="AI220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221" xml:space="preserve">
       <c r="A221" t="str">
@@ -24821,6 +26141,12 @@
         <v xml:space="preserve">タフ化が進む現代のフィールドで釣り勝つ為の要素を凝縮し、一本で幅広いルアーに対応するバーサタイル性を兼ね備えたヘビーバーサタイルモデル。 繊細な操作性と感度を生み出す「”へ”の字テーパー」をティップに施したレギュラーテーパーとあらゆるウェイトのキャストでも打点がブレないスローテーパーをマルチテーパーデザインにより１本に纏め上げたSTEEZ SC 24キングヴァイパーをベースにユーザビリティーを向上させた25BLX SC C69MHのセンターカット2PCSモデル。使用頻度の高い3/8oz.クラスのジグ＆ワームから2oz.クラスのビッグベイトに焦点を合わせ、さらにヘビーウェイトのスピナーベイト、そしてマグナムクランクといったファストムービングルアーにも対応。
 キャスタビリティー、フルベンドならではの粘り感を残しつつ、感度、操作性、瞬時のフッキングレスポンスを兼備している。ステンレスフレームガイドをセッティングすることでガイドの重みで竿がしなりやすくなり、投げやすくなっているだけでなく、スローなスウィングでもルアーを低弾道で弾き飛ばす。1PCモデルの性能を維持したまま、携行性を高めつつもVジョイントを搭載することで、通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上。釣り勝てるセンターカット2PCSに仕上がった。 ■LURE APPLICATION:Rubber Jig /Texas Rig /Leaderless Down Shot Rig /No Sinker Rig / Spinnerbait /Crawler bait /Swim bait /Big Bait /Magnum Crankbait / Frog ■TECHNOLOGY:SVF、X45X、3DX、ZEROSEAT、V-JOINT</v>
       </c>
+      <c r="AH221" t="str">
+        <v/>
+      </c>
+      <c r="AI221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -24922,6 +26248,12 @@
       <c r="AG222" t="str">
         <v>STEEZ　RCを彷彿させる細身で高反発、シャープで高感度なブランクに仕上げたフィネススピニングロッド。ベースとなったのはＬパワーのティップにMLパワーのバットを備えた強めのフィネススピニング・19BLX  SG 6011L/MLXS、その硬さで掛け感やキャスト性能を引き出したモデル。 一方、25BLX S61Lはバットパワーをマイルドに仕上げる事で軽量ルアーウェイトを乗せて投げやすくなり、超高弾性SVFの反発力で掛け感やキャスト性能を引き出したモデル。 感度と操作性を生み出す「“へ”の字テーパー」と超高弾性SVFにより、狙ったスポットへ正確に撃ち込む精度と感度が飛躍的に向上。そのタッチ感、操作感度はフラッグシップモデルに匹敵。掛けてからはその細身ブランクからは想像できないリフトパワーを発揮する。 操作性重視のネコリグやスモラバ等の軽量リグを主軸に、プロップベイトではスラックラインリトリーブも自在。シャープなブランク特性を生かして 、操作系プラグにも対応。 ■LURE APPLICATION:Small Rubber Jig /Neko Rig /Down Shot Rig /Jighead Rig /Wacky Jighead Rig /No Sinker Rig /Small Plug ■TECHNOLOGY:SVF、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH222" t="str">
+        <v/>
+      </c>
+      <c r="AI222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -25023,6 +26355,12 @@
       <c r="AG223" t="str">
         <v>全国ワカサギレイクの中層攻略には無くてはならないホバスト、ミドスト、ボトストスペシャル。 19BLX SG641ULFSの設計思想を昇華させ、SVFでビルドアップすることで操作性、感度を飛躍的に向上させた25BLX S64ULのセンターカット2PCSモデル。スラックラインシェイクでのラインの緩急をも感じ取れ、強風下でもティップが負けることなく操作出来、集中力を切らさず一定のリズムでシェイクを刻む事で容易にレンジをキープすることが可能。「”へ”の字テーパー」の繊細なティップにより感度と操作性を生み出し、3DXをプライアップした並継構造のバットにより、強風下でも風に負けない直進性と遠投性能が向上し、ホバストの様なハイピッチシェイクでも胴ブレすることなく、シェイクピッチとティップの振れ幅を自在にコントロール出来る。また、ボトムストローリングに於いても「”へ”の字」のティップが感度を生み、スタックを躱しつつも、バイトは弾かないオートマチック且つ繊細な操作が可能。シェイクピッチの細かいボトスト、ホバストだけでなく、ロールさせるミドストにも高次元に対応。スモラバやダウンショットなどのマイクロピッチシェイクにも対応し、あらゆるライトリグのバーサタイル性も向上。1PCモデルの性能を維持したまま、携行性を高めつつもVジョイントを搭載することで、通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上したハイレベルなセンターカット2PCS。 ■LURE APPLICATION:Hover Strolling /Mid Strolling /Bottom Strolling /Down Shot Rig /Neko Rig /No Sinker Rig /Small Rubber Jig /Jighead Rig /Wacky Jighead Rig /Small Plug ■TECHNOLOGY:SVF、X45X、3DX、ZEROSEAT、V-JOINT</v>
       </c>
+      <c r="AH223" t="str">
+        <v/>
+      </c>
+      <c r="AI223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -25124,6 +26462,12 @@
       <c r="AG224" t="str">
         <v>全国ワカサギレイクの中層攻略には無くてはならないホバスト、ミドスト、ボトストスペシャル。 19BLX SG641ULFSの設計思想を昇華させ、SVFでビルドアップすることで操作性、感度を飛躍的に向上させた25BLX S64ULのセンターカット2PCSモデル。スラックラインシェイクでのラインの緩急をも感じ取れ、強風下でもティップが負けることなく操作出来、集中力を切らさず一定のリズムでシェイクを刻む事で容易にレンジをキープすることが可能。「”へ”の字テーパー」の繊細なティップにより感度と操作性を生み出し、3DXをプライアップした並継構造のバットにより、強風下でも風に負けない直進性と遠投性能が向上し、ホバストの様なハイピッチシェイクでも胴ブレすることなく、シェイクピッチとティップの振れ幅を自在にコントロール出来る。また、ボトムストローリングに於いても「”へ”の字」のティップが感度を生み、スタックを躱しつつも、バイトは弾かないオートマチック且つ繊細な操作が可能。シェイクピッチの細かいボトスト、ホバストだけでなく、ロールさせるミドストにも高次元に対応。スモラバやダウンショットなどのマイクロピッチシェイクにも対応し、あらゆるライトリグのバーサタイル性も向上。1PCモデルの性能を維持したまま、携行性を高めつつもVジョイントを搭載することで、通常のセンターカット2PCSに比べ、パワー・レスポンス・感度が向上したハイレベルなセンターカット2PCS。 ■LURE APPLICATION:Hover Strolling /Mid Strolling /Bottom Strolling /Down Shot Rig /Neko Rig /No Sinker Rig /Small Rubber Jig /Jighead Rig /Wacky Jighead Rig /Small Plug ■TECHNOLOGY:SVF、X45X、3DX、ZEROSEAT、V-JOINT</v>
       </c>
+      <c r="AH224" t="str">
+        <v/>
+      </c>
+      <c r="AI224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -25225,6 +26569,12 @@
       <c r="AG225" t="str">
         <v>ウィードフラットを広く探る釣りから、ピンスポットを射貫いてターゲットの目の前に送り込む釣りまで幅広く対応するテクニカルスピン。 Ｌパワーのティップに、Mパワーに迫るML+パワーのバットを繋いだ19BLX SG 641L/ML+XSの設計思想を踏襲し、さらなる進化を遂げたビッグレイク対応のフィネススピンがこのモデル。 ブランクをSVFでビルドアップし、「“へ”の字テーパー」を採用することで、感度と操作性が飛躍的に向上。ウィードやグラスにスタックすることなくトレースを可能にした上で、水中のごく小さな変化を捉えてよりテクニカルな操作を可能にする。 適度に張りのあるティップはリアクションダウンショットなどに最適。リザーバーのレイダウンやブッシュにリグを正確に撃ち込み食わせる攻めのダウンショットにも威力を発揮。 掛けてからはML+パワーのバットが60ＵＰをも容易にリフティングする。 ■LURE APPLICATION:Neko Rig /Down Shot Rig /No Sinker Rig /Jighead Rig /Wacky Jighead Rig /Small Rubber Jig /Small Plug /Prop Bait /Bug lure /Small Frog ■TECHNOLOGY:SVF、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH225" t="str">
+        <v/>
+      </c>
+      <c r="AI225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -25326,6 +26676,12 @@
       <c r="AG226" t="str">
         <v>3"クラスのホバスト、ミドスト、ボトストに秀逸なS64ULに対し、S67L+は3.5"以上のスティックベイトのミドストだけでなく、様々なルアーにも対応したテクニカルフィネスロングスピン。 25BLX S64ULの設計思想を踏襲し、ティップに「”へ”の字テーパー」を搭載。操作性、感度が飛躍的に向上し、スラックラインシェイクでのラインの緩急をも感じ取れ、強風下でもティップが負けることなく、操作感に優れ、集中力を切らさず一定のリズムでシェイクを刻む事で一定のレンジコントロールが可能。加えてレングスを6'7"にレングスをアップすることで、遠投性能が昇華。そのレングスの長さからキャスト後のラインメンディングのしやすさもプラス。ミドストだけに留まらず、ULクラスのロッドではオーバースペックなi字系ルアーやシャッド、様々なライトリグにも高次元に対応。バットパワーもアップすることで、グラスレイクやリザーバーのカバー際でも主導権をキープしたファイトが可能。 ■LURE APPLICATION:Mid Strolling /Bottom Strolling /Down Shot Rig /Neko Rig /No Sinker Rig /Small Rubber Jig /Jighead Rig /Wacky Jighead Rig /Small Plug /Prop Bait /Bug lure ■TECHNOLOGY:SVF、X45X、ZEROSEAT</v>
       </c>
+      <c r="AH226" t="str">
+        <v/>
+      </c>
+      <c r="AI226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -25427,6 +26783,12 @@
       <c r="AG227" t="str">
         <v>あらゆる軽量ルアーを幅広く扱えるバーサタイル性に遠投性能を兼ね備え、さらに繊細な操作を可能にしたフィネスロングスピン。 19BLX SG 681ULFSの設計思想を踏襲し、チューブラーの硬さ同等の中弾性ソリッドティップをSVFと3DXでビルドアップしたチューブラーに組み込んだ特殊ブランク構造を採用。 軽量でハンドリングしにくいルアーをロッドが仕事することでユーザビリティを昇華。ソリッドの自重を利用してロッドを曲げ込み、SVFと3DXの反発力で軽量ルアーを弾き飛ばす。 ソリッドの先端に採用された「”へ”の字テーパー」は、操作性と感度を向上。各種ライトリグの自在な操作を実現する一方で、i字系ではラインを弛ませた状態を作りラインの重みを感じながら一定のリトリーブを、テンションのかかりやすいハードベイトや巻きキャロではスラックラインリトリーブを、いずれも可能にする。 また表層ピクピクやミドスト、ボトストなどシェイクが必要な釣法においても、3DXが胴ブレを抑えティップの振れ幅をコントロールして繊細な操作が可能。 ■LURE APPLICATION:Neko Rig /Small Rubber Jig /Wacky Jighead Rig /Jighead Rig /No Sinker Rig /Down Shot Rig /Light Carolina Rig/Split Shot Rig /Mid Strolling /Bottom Strolling /Small Plug ■TECHNOLOGY:SVF、X45X、3DX、MEGATOP、ZEROSEAT</v>
       </c>
+      <c r="AH227" t="str">
+        <v/>
+      </c>
+      <c r="AI227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -25528,6 +26890,12 @@
       <c r="AG228" t="str">
         <v>近年のハイプレッシャー化によりスモラバのパワーフィネスには口を使わなくなったバスを攻略する為に繊細さを併せ持ったパワーフィネスロッド。 MHやHパワーのパワーフィネスロッドのキャストはロッドにウェイトを乗せるという感覚は皆無であったが、MLパワーのティップを搭載することでティップセクションにウェイトを乗せてピッチングすることが可能になり、誰もが正確にシャローカバーを射抜くことが可能。またティップに「”へ”の字テーパー」を施すことによって、今までとは一線を画した繊細な操作感と手感度を手に入れ、レイダウン等を跨いで吊るした状態でもリグの状態が把握でき、繊細に操作できる。繊細なティップとは相反する強靭なバットがパワーフィネス特有の一瞬のバイトを鋭くアワせて、カバーからブッコ抜くことが可能。またパワーフィネスで有能な「”へ”の字テーパー」のティップが3.5ｇ～７ｇのジグヘッドを用いた5”～6”スティックベイトのミドストでも最高のパフォーマンスを発揮。湖面が波っ気が立った強風下でもラインテンションを巧みにコントロール出来、無になりがちな中層の釣りに於いても水中のリグの挙動が手に取るようにわかる手感度で、ラインテンションの緩急を感じながら、一定のリズムを刻むことでバイトに持ち込むことが出来る。 ■LURE APPLICATION:Neko Rig /Small Rubber Jig /No Sinker Rig /Down Shot Rig /Jighead Rig /Wacky Jighead Rig /Light Texas Rig /Small Plug ■TECHNOLOGY:SVF、X45X、3DX、ZEROSEAT</v>
       </c>
+      <c r="AH228" t="str">
+        <v/>
+      </c>
+      <c r="AI228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -25629,6 +26997,12 @@
       <c r="AG229" t="str">
         <v>タフ化が進む現代のフィールドで釣り勝つべく、オカッパリのベイトフィネスで求められる要素を具備したベイトフィネスロッド。 STEEZ SC 24ウェアウルフをベースにユーザビリティーの向上を目指したアイテム。ティップにはSC24ウェアウルフ同様チューブラーに匹敵する硬さの「”へ”の字テーパー」を施したメガトップRソリッドを搭載することで、優れた感度と操作性を有し、トレース時には小さな変化を感じつつもスタックは躱し、ボトムやストラクチャーにモタレさせながら誘う事が出来る。またSVFコンパイルXのチューブラーをSVF化することで、高反発力な筋肉質ブランクに粘りが加わることでキャスト時のスイートスポットが広がり、投げやすさが向上。ブランク素材の変更により汎用性が拡大し、使い手を選ばないだけでなく、ルアーやリグの対応幅も広がり、ライトバーサタイルロッドとしての顔も覗かせるベイトフィネスロッド。 ■LURE APPLICATION:Snagless Neko Rig /Small Rubber Jig /No Sinker Rig /Down Shot Rig /Jerkbait /Topwater Plug /Spinnerbait ■TECHNOLOGY:SVF、X45X、3DX、MEGATOP R、ZEROSEAT</v>
       </c>
+      <c r="AH229" t="str">
+        <v/>
+      </c>
+      <c r="AI229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -25730,6 +27104,12 @@
       <c r="AG230" t="str">
         <v>タフ化が進む現代のフィールドで釣り勝つべく、オカッパリのベイトフィネスで求められる要素を具備したベイトフィネスロッド。 STEEZ SC 24ウェアウルフをベースにユーザビリティーの向上を目指したアイテム。ティップにはSC24ウェアウルフ同様チューブラーに匹敵する硬さの「”へ”の字テーパー」を施したメガトップRソリッドを搭載することで、優れた感度と操作性を有し、トレース時には小さな変化を感じつつもスタックは躱し、ボトムやストラクチャーにモタレさせながら誘う事が出来る。またSVFコンパイルXのチューブラーをSVF化することで、高反発力な筋肉質ブランクに粘りが加わることでキャスト時のスイートスポットが広がり、投げやすさが向上。ブランク素材の変更により汎用性が拡大し、使い手を選ばないだけでなく、ルアーやリグの対応幅も広がり、ライトバーサタイルロッドとしての顔も覗かせるベイトフィネスロッド。 ■LURE APPLICATION:Snagless Neko Rig /Small Rubber Jig /No Sinker Rig /Down Shot Rig /Jerkbait /Topwater Plug /Spinnerbait ■TECHNOLOGY:SVF、X45X、3DX、MEGATOP R、ZEROSEAT</v>
       </c>
+      <c r="AH230" t="str">
+        <v/>
+      </c>
+      <c r="AI230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -25831,6 +27211,12 @@
       <c r="AG231" t="str">
         <v>タフなフィールドで釣り勝つための要素を凝縮し、ライトリグ全般を1本でこなすバーサタイル性を兼ね備えたフィネスバーサタイルスピニング、STEEZ SC ファイヤーフラッシュの設計をBLXに踏襲。 ティップには「“へ”の字テーパー」の中弾性ソリッドを採用することで、操作性と感度が飛躍的に向上。ボトムトレース時には小さな変化を感じつつスタックを躱し、カバーやストラクチャーにモタれさせながら1点で誘うことを可能に。 チューブラー部はSVF化したことで、高反発力な筋肉質ブランクに粘りが加わり、ステンレスフレームガイドのガイド自重により竿が曲がりやすく、投げやすくなりリリースポイントが取りやすくなっている。 軽快なキャスタビリティが即ち、キャストアキュラシーへと繋げている。中弾性ソリッドとSVFのブランク素材が導いたのはさらなるバーサタイル性の拡大。 使い手を選ばず、ルアーやリグをも選ばない真のバーサタイルスピンがここに。 ■LURE APPLICATION:Small Rubber Jig /No Sinker Rig /Down Shot Rig /Neko Rig /Jighead Rig /Wacky Jighead Rig /Stick Bait /Shad /Minnow /Prop bait /Bug lure /Small Wire Bait ■TECHNOLOGY:SVF、X45X、MEGATOP、ZEROSEAT</v>
       </c>
+      <c r="AH231" t="str">
+        <v/>
+      </c>
+      <c r="AI231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -25932,6 +27318,12 @@
       <c r="AG232" t="str">
         <v>タフなフィールドで釣り勝つための要素を凝縮し、ライトリグ全般を1本でこなすバーサタイル性を兼ね備えたフィネスバーサタイルスピニング、STEEZ SC ファイヤーフラッシュの設計をBLXに踏襲。 ティップには「“へ”の字テーパー」の中弾性ソリッドを採用することで、操作性と感度が飛躍的に向上。ボトムトレース時には小さな変化を感じつつスタックを躱し、カバーやストラクチャーにモタれさせながら1点で誘うことを可能に。 チューブラー部はSVF化したことで、高反発力な筋肉質ブランクに粘りが加わり、ステンレスフレームガイドのガイド自重により竿が曲がりやすく、投げやすくなりリリースポイントが取りやすくなっている。 軽快なキャスタビリティが即ち、キャストアキュラシーへと繋げている。中弾性ソリッドとSVFのブランク素材が導いたのはさらなるバーサタイル性の拡大。 使い手を選ばず、ルアーやリグをも選ばない真のバーサタイルスピンがここに。 ■LURE APPLICATION:Small Rubber Jig /No Sinker Rig /Down Shot Rig /Neko Rig /Jighead Rig /Wacky Jighead Rig /Stick Bait /Shad /Minnow /Prop bait /Bug lure /Small Wire Bait ■TECHNOLOGY:SVF、X45X、MEGATOP、ZEROSEAT</v>
       </c>
+      <c r="AH232" t="str">
+        <v/>
+      </c>
+      <c r="AI232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -26033,6 +27425,12 @@
       <c r="AG233" t="str">
         <v>低弾性カーボンを採用した、小型トップウォーター、ジャークベイト対応モデル。ジャークしやすいレングス、グリップ長を採用し、軽量且つしなやかなブランクは、軽量プラグ全般の扱いやすさをもたらす。</v>
       </c>
+      <c r="AH233" t="str">
+        <v/>
+      </c>
+      <c r="AI233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -26134,6 +27532,12 @@
       <c r="AG234" t="str">
         <v>柔軟さと強靭さを持ち併せたムービングベイトスペシャル。1/4～1/2ozのスピナーベイトをカバーにタイトに打ち込むことをメインに、ポッパー、ペンシルといった操作系のプラグからムービングベイトまで、幅広く対応するロッド。</v>
       </c>
+      <c r="AH234" t="str">
+        <v/>
+      </c>
+      <c r="AI234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -26235,6 +27639,12 @@
       <c r="AG235" t="str">
         <v>SVFナノプラスを軸にX45で締め上げたブランクは狙いのスポットへジグ＆テキサスをピッチ&amp;フリップが可能。このロッドでノーシンカーからヘビキャロまでを対応し、バイトを瞬時に捕らえる高感度、掛けてからのリフティングパワーにも注目。</v>
       </c>
+      <c r="AH235" t="str">
+        <v/>
+      </c>
+      <c r="AI235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -26336,6 +27746,12 @@
       <c r="AG236" t="str">
         <v>大森貴洋が得意とするシャロークランキングはもとより、この一本のロッドでリップレスクランク、ワイヤーベイト、ブレイデッドジグ、スイムベイト、ディープクランクまでを全て対応。グラスコンポジットロッドの中では珍しい7：3調子のテーパーを採用。高いアキュラシー性能とフッキング性能をもたらした。</v>
       </c>
+      <c r="AH236" t="str">
+        <v/>
+      </c>
+      <c r="AI236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -26437,6 +27853,12 @@
       <c r="AG237" t="str">
         <v>ダウンショットスペシャリティ。沖の水中のストラクチャー回りやフラットをダウンショットで狙うモデルだが、素直に曲がり込むテーパーは、ノーシンカーから軽量プラグまで、幅広いリグに対応。レングスを活かした遠投力も魅力的なモデルに仕上がっている。</v>
       </c>
+      <c r="AH237" t="str">
+        <v/>
+      </c>
+      <c r="AI237" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -26538,6 +27960,12 @@
       <c r="AG238" t="str">
         <v>ノーシンカーやネコリグ、スモラバなどのライトリグから小型ハードベイトまで対応し、キャスト性能にも優れたベイトフィネスアイテム。</v>
       </c>
+      <c r="AH238" t="str">
+        <v/>
+      </c>
+      <c r="AI238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -26639,6 +28067,12 @@
       <c r="AG239" t="str">
         <v>ヘビタン、テキサスなどのワーミングから巻物や操作系プラグまでと幅広いルアーに対応する、操作性に優れた6'5"レングスアイテム。</v>
       </c>
+      <c r="AH239" t="str">
+        <v/>
+      </c>
+      <c r="AI239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -26740,6 +28174,12 @@
       <c r="AG240" t="str">
         <v>軽量リグでのワーミングや小型～中型プラグを繊細に操作することが可能で、カバー周りのフィネスアプローチにも対応するアイテム。</v>
       </c>
+      <c r="AH240" t="str">
+        <v/>
+      </c>
+      <c r="AI240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -26841,6 +28281,12 @@
       <c r="AG241" t="str">
         <v>水中でのルアーの操作性に長け、高比重ワームやテキサスリグ、ジグはもちろん、中～重量級ハードプラグにも対応するアイテム。</v>
       </c>
+      <c r="AH241" t="str">
+        <v/>
+      </c>
+      <c r="AI241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -26942,6 +28388,12 @@
       <c r="AG242" t="str">
         <v>クランクベイトやスピナーベイト等のハードベイトからダウンショットやテキサス、高比重ワームと幅広い用途に対応するアイテム。</v>
       </c>
+      <c r="AH242" t="str">
+        <v/>
+      </c>
+      <c r="AI242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -27043,6 +28495,12 @@
       <c r="AG243" t="str">
         <v>Ｓ字形ビッグベイトやスイムベイトに適応するパワーを備え、スイムジグやスピナーベイト、水に絡ませる羽根モノにも対応するアイテム。</v>
       </c>
+      <c r="AH243" t="str">
+        <v/>
+      </c>
+      <c r="AI243" t="str">
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -27144,6 +28602,12 @@
       <c r="AG244" t="str">
         <v/>
       </c>
+      <c r="AH244" t="str">
+        <v/>
+      </c>
+      <c r="AI244" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -27245,6 +28709,12 @@
       <c r="AG245" t="str">
         <v/>
       </c>
+      <c r="AH245" t="str">
+        <v/>
+      </c>
+      <c r="AI245" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -27346,6 +28816,12 @@
       <c r="AG246" t="str">
         <v/>
       </c>
+      <c r="AH246" t="str">
+        <v/>
+      </c>
+      <c r="AI246" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -27447,6 +28923,12 @@
       <c r="AG247" t="str">
         <v/>
       </c>
+      <c r="AH247" t="str">
+        <v/>
+      </c>
+      <c r="AI247" t="str">
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -27548,6 +29030,12 @@
       <c r="AG248" t="str">
         <v>フィネスリグを緻密に操り、ストラクチャーに絡めバイトを誘発することも可能な、食わせ性能と操作性を兼ね備えたソリッドティップアイテム。</v>
       </c>
+      <c r="AH248" t="str">
+        <v/>
+      </c>
+      <c r="AI248" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -27649,6 +29137,12 @@
       <c r="AG249" t="str">
         <v>一定のリズムで容易に振り続ける事が可能なティップセクションを有し、表層、中層、ボトム問わず様々なフィネスリグに対応するアイテム。</v>
       </c>
+      <c r="AH249" t="str">
+        <v/>
+      </c>
+      <c r="AI249" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -27750,6 +29244,12 @@
       <c r="AG250" t="str">
         <v>クセの無いテーパーを持ち、ライトリグ全般から小型プラグまで、幅広いルアー、アプローチに対応するフィネスバーサタイルアイテム。</v>
       </c>
+      <c r="AH250" t="str">
+        <v/>
+      </c>
+      <c r="AI250" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -27851,6 +29351,12 @@
       <c r="AG251" t="str">
         <v>ライトリグの遠投性能とフッキング性能を持ち、トゥイッチやジャークで小型プラグを操作することも可能なバーサタイルアイテム。</v>
       </c>
+      <c r="AH251" t="str">
+        <v/>
+      </c>
+      <c r="AI251" t="str">
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -27952,6 +29458,12 @@
       <c r="AG252" t="str">
         <v/>
       </c>
+      <c r="AH252" t="str">
+        <v/>
+      </c>
+      <c r="AI252" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -28053,6 +29565,12 @@
       <c r="AG253" t="str">
         <v>ノーシンカーやネコリグ、スモラバなどのライトリグから小型ハードベイトまで対応し、キャスト性能にも優れたベイトフィネスアイテム。</v>
       </c>
+      <c r="AH253" t="str">
+        <v/>
+      </c>
+      <c r="AI253" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -28154,6 +29672,12 @@
       <c r="AG254" t="str">
         <v>ヘビタン、テキサスなどのワーミングから巻物や操作系プラグまでと幅広いルアーに対応する、操作性に優れた6'5"レングスアイテム。</v>
       </c>
+      <c r="AH254" t="str">
+        <v/>
+      </c>
+      <c r="AI254" t="str">
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -28255,6 +29779,12 @@
       <c r="AG255" t="str">
         <v>軽量リグでのワーミングや小型～中型プラグを繊細に操作することが可能で、カバー周りのフィネスアプローチにも対応するアイテム。</v>
       </c>
+      <c r="AH255" t="str">
+        <v/>
+      </c>
+      <c r="AI255" t="str">
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -28356,6 +29886,12 @@
       <c r="AG256" t="str">
         <v>水中でのルアーの操作性に長け、高比重ワームやテキサスリグ、ジグはもちろん、中～重量級ハードプラグにも対応するアイテム。</v>
       </c>
+      <c r="AH256" t="str">
+        <v/>
+      </c>
+      <c r="AI256" t="str">
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -28457,6 +29993,12 @@
       <c r="AG257" t="str">
         <v>クランクベイトやスピナーベイト等のハードベイトからダウンショットやテキサス、高比重ワームと幅広い用途に対応するアイテム。</v>
       </c>
+      <c r="AH257" t="str">
+        <v/>
+      </c>
+      <c r="AI257" t="str">
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -28558,6 +30100,12 @@
       <c r="AG258" t="str">
         <v>Ｓ字形ビッグベイトやスイムベイトに適応するパワーを備え、スイムジグやスピナーベイト、水に絡ませる羽根モノにも対応するアイテム。</v>
       </c>
+      <c r="AH258" t="str">
+        <v/>
+      </c>
+      <c r="AI258" t="str">
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -28659,6 +30207,12 @@
       <c r="AG259" t="str">
         <v>フィネスリグを緻密に操り、ストラクチャーに絡めバイトを誘発することも可能な、食わせ性能と操作性を兼ね備えたソリッドティップアイテム。</v>
       </c>
+      <c r="AH259" t="str">
+        <v/>
+      </c>
+      <c r="AI259" t="str">
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -28760,6 +30314,12 @@
       <c r="AG260" t="str">
         <v>一定のリズムで容易に振り続ける事が可能なティップセクションを有し、表層、中層、ボトム問わず様々なフィネスリグに対応するアイテム。</v>
       </c>
+      <c r="AH260" t="str">
+        <v/>
+      </c>
+      <c r="AI260" t="str">
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -28861,6 +30421,12 @@
       <c r="AG261" t="str">
         <v>クセの無いテーパーを持ち、ライトリグ全般から小型プラグまで、幅広いルアー、アプローチに対応するフィネスバーサタイルアイテム。</v>
       </c>
+      <c r="AH261" t="str">
+        <v/>
+      </c>
+      <c r="AI261" t="str">
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -28962,6 +30528,12 @@
       <c r="AG262" t="str">
         <v>ライトリグの遠投性能とフッキング性能を持ち、トゥイッチやジャークで小型プラグを操作することも可能なバーサタイルアイテム。</v>
       </c>
+      <c r="AH262" t="str">
+        <v/>
+      </c>
+      <c r="AI262" t="str">
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -29063,6 +30635,12 @@
       <c r="AG263" t="str">
         <v>「ライトバーサタイルモデル」軽量リグでのワーミングや小型～中型プラグを繊細に操作することが可能で、カバー周りのフィネスアプローチにも対応するマルチピースモデル。</v>
       </c>
+      <c r="AH263" t="str">
+        <v/>
+      </c>
+      <c r="AI263" t="str">
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -29164,6 +30742,12 @@
       <c r="AG264" t="str">
         <v>「バーサタイルモデル」クランクベイトやスピナーベイト等のハードベイトからダウンショットやテキサス、高比重ワームと幅広い用途に対応するマルチピースモデル。</v>
       </c>
+      <c r="AH264" t="str">
+        <v/>
+      </c>
+      <c r="AI264" t="str">
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -29265,6 +30849,12 @@
       <c r="AG265" t="str">
         <v>「パワーバーサタイルモデル」テキサス＆ジグなどの撃ちモノはもちろん、スイムジグやスピナーベイトなどの中、重量級ハードプラグにも対応するマルチピースモデル。</v>
       </c>
+      <c r="AH265" t="str">
+        <v/>
+      </c>
+      <c r="AI265" t="str">
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -29366,6 +30956,12 @@
       <c r="AG266" t="str">
         <v/>
       </c>
+      <c r="AH266" t="str">
+        <v/>
+      </c>
+      <c r="AI266" t="str">
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -29467,6 +31063,12 @@
       <c r="AG267" t="str">
         <v>「バーサタイルモデル」ライトリグの遠投性能とフッキング性能を持ち、トゥイッチやジャークで小型プラグを操作することも可能なマルチピースモデル。</v>
       </c>
+      <c r="AH267" t="str">
+        <v/>
+      </c>
+      <c r="AI267" t="str">
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -29568,6 +31170,12 @@
       <c r="AG268" t="str">
         <v>中・小型ファストムービングルアーを始め、中型トップウォータープラグやライトテキサスリグ、ライトラバージグ＆ワーミングまで自在に操ることが可能なオールラウンダー。元ガイドはKガイド仕様。</v>
       </c>
+      <c r="AH268" t="str">
+        <v/>
+      </c>
+      <c r="AI268" t="str">
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -29669,6 +31277,12 @@
       <c r="AG269" t="str">
         <v>ノーシンカーリグやキャロライナリグなどのライトワーミングだけでなく、小型トップウォータープラグやミノーを使用したプラッギングまで自在に操ることが可能なオールラウンダー。元ガイドはKガイド仕様。</v>
       </c>
+      <c r="AH269" t="str">
+        <v/>
+      </c>
+      <c r="AI269" t="str">
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -29770,6 +31384,12 @@
       <c r="AG270" t="str">
         <v>最も扱いやすい長さ・硬さでスーパーバーサタイルに使いこなせるテレスコピック・ベイトキャスティングロッド。中・重量級のファストムービングルアーのロングキャストからピッチング、テキサスリグなどの撃ちモノまで自在に操ることが可能なオールラウンダー。</v>
       </c>
+      <c r="AH270" t="str">
+        <v/>
+      </c>
+      <c r="AI270" t="str">
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -29871,6 +31491,12 @@
       <c r="AG271" t="str">
         <v>最も扱いやすい長さ・硬さでスーパーバーサタイルに使いこなせるスピニングロッド。様々なフィールドで多様な軽量ルアー・軽量リグを自在に扱えるオールラウンダー。</v>
       </c>
+      <c r="AH271" t="str">
+        <v/>
+      </c>
+      <c r="AI271" t="str">
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -29972,6 +31598,12 @@
       <c r="AG272" t="str">
         <v>操作性・アキュラシー性能に優れ、軽量ルアー・軽量リグを自在に操ることが可能なベイトフィネス対応モデル。</v>
       </c>
+      <c r="AH272" t="str">
+        <v/>
+      </c>
+      <c r="AI272" t="str">
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -30073,6 +31705,12 @@
       <c r="AG273" t="str">
         <v>ロングキャストとアキュラシー性能の両立を実現し、軽量ルアー・軽量リグを自在に操ることが可能なオールラウンダー。</v>
       </c>
+      <c r="AH273" t="str">
+        <v/>
+      </c>
+      <c r="AI273" t="str">
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -30174,6 +31812,12 @@
       <c r="AG274" t="str">
         <v>最も扱いやすい長さ･硬さでスーパーバーサタイルに使いこなせるテレスコピック･スピニングロッド。軽量ルアー･軽量リグのロングキャストが必要な場面で幅広く対応し、繊細に操ることが可能なオールラウンダー。</v>
       </c>
+      <c r="AH274" t="str">
+        <v/>
+      </c>
+      <c r="AI274" t="str">
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -30275,6 +31919,12 @@
       <c r="AG275" t="str">
         <v>最も扱いやすい長さ･硬さでスーパーバーサタイルに使いこなせるテレスコピック･ベイトキャスティングロッド。中･重量級のファストムービングルアーのロングキャストからピッチングまで自在に操ることが可能なオールラウンダー。</v>
       </c>
+      <c r="AH275" t="str">
+        <v/>
+      </c>
+      <c r="AI275" t="str">
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -30376,6 +32026,12 @@
       <c r="AG276" t="str">
         <v>操作性と感度に優れたメガトップを搭載。ソリッド部を硬めのセッティングにすることで、ボトムのトレース能力と、スタックを回避する能力を併せ持ち、ベイトフィネスリグの緻密なコントロールを可能とした“ベイトフィネスソリッドモデル”。</v>
       </c>
+      <c r="AH276" t="str">
+        <v/>
+      </c>
+      <c r="AI276" t="str">
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -30477,6 +32133,12 @@
       <c r="AG277" t="str">
         <v>操作性と感度に優れたメガトップを搭載。ソリッド部を硬めのセッティングにすることで、ボトムのトレース能力と、スタックを回避する能力を併せ持ち、ベイトフィネスリグの緻密なコントロールを可能とした“ベイトフィネスソリッドモデル”。</v>
       </c>
+      <c r="AH277" t="str">
+        <v/>
+      </c>
+      <c r="AI277" t="str">
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -30578,6 +32240,12 @@
       <c r="AG278" t="str">
         <v>硬めにセッティングされたメガトップ仕様のソリッドティップは、高感度かつ高い操作性を持つ。ダウンショットリグやテキサスリグなどの撃ちモノを的確にキャスト＆コントロールする“バーサタイルソリッドモデル”。</v>
       </c>
+      <c r="AH278" t="str">
+        <v/>
+      </c>
+      <c r="AI278" t="str">
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -30679,6 +32347,12 @@
       <c r="AG279" t="str">
         <v>硬めにセッティングされたメガトップ仕様のソリッドティップは、高感度かつ高い操作性を持つ。ダウンショットリグやテキサスリグなどの撃ちモノを的確にキャスト＆コントロールする“バーサタイルソリッドモデル”。</v>
       </c>
+      <c r="AH279" t="str">
+        <v/>
+      </c>
+      <c r="AI279" t="str">
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -30780,6 +32454,12 @@
       <c r="AG280" t="str">
         <v>硬めにセッティングされたメガトップ仕様のソリッドティップは、高感度かつ高い操作性を持つ。ダウンショットリグやテキサスリグなどの撃ちモノを的確にキャスト＆コントロールする“バーサタイルソリッドモデル”。</v>
       </c>
+      <c r="AH280" t="str">
+        <v/>
+      </c>
+      <c r="AI280" t="str">
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -30881,6 +32561,12 @@
       <c r="AG281" t="str">
         <v>硬めにセッティングされたメガトップ仕様のソリッドティップは、高感度かつ高い操作性を持つ。ダウンショットリグやテキサスリグなどの撃ちモノを的確にキャスト＆コントロールする“バーサタイルソリッドモデル”。</v>
       </c>
+      <c r="AH281" t="str">
+        <v/>
+      </c>
+      <c r="AI281" t="str">
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -30982,6 +32668,12 @@
       <c r="AG282" t="str">
         <v>硬めにセッティングされたメガトップ仕様のソリッドティップと強靭なバットという、繊細さとパワーを持ち併せたロッド。カバー周りやピンスポットをテキサスリグ、フリーリグなどの撃ちモノで確実にトレースし、意のままに操ることが可能な“パワーソリッドモデル”。</v>
       </c>
+      <c r="AH282" t="str">
+        <v/>
+      </c>
+      <c r="AI282" t="str">
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -31083,6 +32775,12 @@
       <c r="AG283" t="str">
         <v>緻密なアクションを生み出すソフトなティップにカバーから強引に引きずり出す強靭なバットパワーを高次元で融合させた“フロッグモデル”。</v>
       </c>
+      <c r="AH283" t="str">
+        <v/>
+      </c>
+      <c r="AI283" t="str">
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -31184,6 +32882,12 @@
       <c r="AG284" t="str">
         <v>ノーシンカーやスモラバを中心としたライトリグから小型ハードベイトまで適応する“ベイトフィネスモデル”。</v>
       </c>
+      <c r="AH284" t="str">
+        <v/>
+      </c>
+      <c r="AI284" t="str">
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -31285,6 +32989,12 @@
       <c r="AG285" t="str">
         <v>メガトップを搭載し、テキサスリグなどの重量級の撃ちモノ、ジグストにも最適な”ヘビーソリッドモデル”。</v>
       </c>
+      <c r="AH285" t="str">
+        <v/>
+      </c>
+      <c r="AI285" t="str">
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -31386,6 +33096,12 @@
       <c r="AG286" t="str">
         <v>中～大型ハードベイトから重量級テキサスやラバージグなどの撃ちモノまで適応する“パワーバーサタイルモデル”。</v>
       </c>
+      <c r="AH286" t="str">
+        <v/>
+      </c>
+      <c r="AI286" t="str">
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -31487,6 +33203,12 @@
       <c r="AG287" t="str">
         <v>中～大型ハードベイトから重量級テキサスやラバージグなどの撃ちモノまで適応する“パワーバーサタイルモデル”。</v>
       </c>
+      <c r="AH287" t="str">
+        <v/>
+      </c>
+      <c r="AI287" t="str">
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -31588,6 +33310,12 @@
       <c r="AG288" t="str">
         <v>S字系ビッグベイトやスイムベイトに適応するパワーを備えたスローテーパーの“ビッグベイトモデル”。</v>
       </c>
+      <c r="AH288" t="str">
+        <v/>
+      </c>
+      <c r="AI288" t="str">
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -31689,6 +33417,12 @@
       <c r="AG289" t="str">
         <v>ヘビーウエイトルアーを駆使したパワーゲームに最適で、マットカバーへのパンチングも容易にこなす“ハード＆パワーモデル”。</v>
       </c>
+      <c r="AH289" t="str">
+        <v/>
+      </c>
+      <c r="AI289" t="str">
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -31790,6 +33524,12 @@
       <c r="AG290" t="str">
         <v>太軸フックを貫通させる瞬発力とモンスター級をカバーから引き離すパワーを備えた“パワーストロングモデル”。</v>
       </c>
+      <c r="AH290" t="str">
+        <v/>
+      </c>
+      <c r="AI290" t="str">
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -31891,6 +33631,12 @@
       <c r="AG291" t="str">
         <v>繊細さと操作性を高次元で融合させたメガトップ仕様の張りのあるソリッドを搭載した攻めのソリッドティップロッド。繊細なティップと強靭なバットを組み合わせることで、ショートバイトを逃さず捉え一瞬で掛けてバットで寄せる、繊細でありながら強靭なロッド。</v>
       </c>
+      <c r="AH291" t="str">
+        <v/>
+      </c>
+      <c r="AI291" t="str">
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -31992,6 +33738,12 @@
       <c r="AG292" t="str">
         <v>ライトリグを緻密に操りタフコンディション下においてもバスが違和感を感じずスムースなフッキングを実現するメガトップを採用した“フィネスソリッドモデル”。</v>
       </c>
+      <c r="AH292" t="str">
+        <v/>
+      </c>
+      <c r="AI292" t="str">
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -32093,6 +33845,12 @@
       <c r="AG293" t="str">
         <v>ライトリグ全般と、「ミドスト、ボトスト、ホバスト」に高次元に対応した”フィネスモデル”。</v>
       </c>
+      <c r="AH293" t="str">
+        <v/>
+      </c>
+      <c r="AI293" t="str">
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -32194,6 +33952,12 @@
       <c r="AG294" t="str">
         <v>小型ハードベイトからライトリグまで様々な状況に適応するバーサタイル性能にソリッドの操作性を融合させた“ライトソリッドモデル”。</v>
       </c>
+      <c r="AH294" t="str">
+        <v/>
+      </c>
+      <c r="AI294" t="str">
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -32295,6 +34059,12 @@
       <c r="AG295" t="str">
         <v>小型ハードベイトからライトリグまで様々な状況に適応するバーサタイル性能にソリッドの操作性を融合させた“ライトソリッドモデル”。</v>
       </c>
+      <c r="AH295" t="str">
+        <v/>
+      </c>
+      <c r="AI295" t="str">
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -32396,6 +34166,12 @@
       <c r="AG296" t="str">
         <v>ノーシンカー、ダウンショット、ライトテキサスはもちろん、タイニークランクやミノーもこなす汎用性に優れた“バーサタイルモデル”。</v>
       </c>
+      <c r="AH296" t="str">
+        <v/>
+      </c>
+      <c r="AI296" t="str">
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -32497,6 +34273,12 @@
       <c r="AG297" t="str">
         <v>ヘビーカバーで口を使わないバスをスモラバをはじめとするライトリグで攻略する“パワーフィネスモデル”。</v>
       </c>
+      <c r="AH297" t="str">
+        <v/>
+      </c>
+      <c r="AI297" t="str">
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -32598,6 +34380,12 @@
       <c r="AG298" t="str">
         <v>ノーシンカーやスモラバなどのライトリグから小～中型ハードベイトまでオールラウンドに適応する“ライトバーサタイルモデル”。</v>
       </c>
+      <c r="AH298" t="str">
+        <v/>
+      </c>
+      <c r="AI298" t="str">
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -32699,6 +34487,12 @@
       <c r="AG299" t="str">
         <v>操作性と感度に優れたメガトップを搭載。ソリッド部を硬めのセッティングにすることで、ボトムのトレース能力と、スタックを回避する能力を併せ持ち、ベイトフィネスリグの緻密なコントロールを可能とした“ベイトフィネスソリッドモデル”。</v>
       </c>
+      <c r="AH299" t="str">
+        <v/>
+      </c>
+      <c r="AI299" t="str">
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -32800,6 +34594,12 @@
       <c r="AG300" t="str">
         <v>操作性と感度に優れたメガトップを搭載。ソリッド部を硬めのセッティングにすることで、ボトムのトレース能力と、スタックを回避する能力を併せ持ち、ベイトフィネスリグの緻密なコントロールを可能とした“ベイトフィネスソリッドモデル”。</v>
       </c>
+      <c r="AH300" t="str">
+        <v/>
+      </c>
+      <c r="AI300" t="str">
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -32901,6 +34701,12 @@
       <c r="AG301" t="str">
         <v>硬めにセッティングされたメガトップ仕様のソリッドティップは、高感度かつ高い操作性を持つ。ダウンショットリグやテキサスリグなどの撃ちモノを的確にキャスト＆コントロールする“バーサタイルソリッドモデル”。</v>
       </c>
+      <c r="AH301" t="str">
+        <v/>
+      </c>
+      <c r="AI301" t="str">
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -33002,6 +34808,12 @@
       <c r="AG302" t="str">
         <v>硬めにセッティングされたメガトップ仕様のソリッドティップは、高感度かつ高い操作性を持つ。ダウンショットリグやテキサスリグなどの撃ちモノを的確にキャスト＆コントロールする“バーサタイルソリッドモデル”。</v>
       </c>
+      <c r="AH302" t="str">
+        <v/>
+      </c>
+      <c r="AI302" t="str">
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -33103,6 +34915,12 @@
       <c r="AG303" t="str">
         <v>硬めにセッティングされたメガトップ仕様のソリッドティップは、高感度かつ高い操作性を持つ。ダウンショットリグやテキサスリグなどの撃ちモノを的確にキャスト＆コントロールする“バーサタイルソリッドモデル”。</v>
       </c>
+      <c r="AH303" t="str">
+        <v/>
+      </c>
+      <c r="AI303" t="str">
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -33204,6 +35022,12 @@
       <c r="AG304" t="str">
         <v>硬めにセッティングされたメガトップ仕様のソリッドティップは、高感度かつ高い操作性を持つ。ダウンショットリグやテキサスリグなどの撃ちモノを的確にキャスト＆コントロールする“バーサタイルソリッドモデル”。</v>
       </c>
+      <c r="AH304" t="str">
+        <v/>
+      </c>
+      <c r="AI304" t="str">
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -33305,6 +35129,12 @@
       <c r="AG305" t="str">
         <v>硬めにセッティングされたメガトップ仕様のソリッドティップと強靭なバットという、繊細さとパワーを持ち併せたロッド。カバー周りやピンスポットをテキサスリグ、フリーリグなどの撃ちモノで確実にトレースし、意のままに操ることが可能な“パワーソリッドモデル”。</v>
       </c>
+      <c r="AH305" t="str">
+        <v/>
+      </c>
+      <c r="AI305" t="str">
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -33406,6 +35236,12 @@
       <c r="AG306" t="str">
         <v>緻密なアクションを生み出すソフトなティップにカバーから強引に引きずり出す強靭なバットパワーを高次元で融合させた“フロッグモデル”。</v>
       </c>
+      <c r="AH306" t="str">
+        <v/>
+      </c>
+      <c r="AI306" t="str">
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -33507,6 +35343,12 @@
       <c r="AG307" t="str">
         <v>ノーシンカーやスモラバを中心としたライトリグから小型ハードベイトまで適応する“ベイトフィネスモデル”。</v>
       </c>
+      <c r="AH307" t="str">
+        <v/>
+      </c>
+      <c r="AI307" t="str">
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -33608,6 +35450,12 @@
       <c r="AG308" t="str">
         <v>メガトップを搭載し、テキサスリグなどの重量級の撃ちモノ、ジグストにも最適な”ヘビーソリッドモデル”。</v>
       </c>
+      <c r="AH308" t="str">
+        <v/>
+      </c>
+      <c r="AI308" t="str">
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -33709,6 +35557,12 @@
       <c r="AG309" t="str">
         <v/>
       </c>
+      <c r="AH309" t="str">
+        <v/>
+      </c>
+      <c r="AI309" t="str">
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -33810,6 +35664,12 @@
       <c r="AG310" t="str">
         <v>中～大型ハードベイトから重量級テキサスやラバージグなどの撃ちモノまで適応する“パワーバーサタイルモデル”。</v>
       </c>
+      <c r="AH310" t="str">
+        <v/>
+      </c>
+      <c r="AI310" t="str">
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -33911,6 +35771,12 @@
       <c r="AG311" t="str">
         <v>S字系ビッグベイトやスイムベイトに適応するパワーを備えたスローテーパーの“ビッグベイトモデル”。</v>
       </c>
+      <c r="AH311" t="str">
+        <v/>
+      </c>
+      <c r="AI311" t="str">
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -34012,6 +35878,12 @@
       <c r="AG312" t="str">
         <v>ヘビーウエイトルアーを駆使したパワーゲームに最適で、マットカバーへのパンチングも容易にこなす“ハード＆パワーモデル”。</v>
       </c>
+      <c r="AH312" t="str">
+        <v/>
+      </c>
+      <c r="AI312" t="str">
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -34113,6 +35985,12 @@
       <c r="AG313" t="str">
         <v>太軸フックを貫通させる瞬発力とモンスター級をカバーから引き離すパワーを備えた“パワーストロングモデル”。</v>
       </c>
+      <c r="AH313" t="str">
+        <v/>
+      </c>
+      <c r="AI313" t="str">
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -34214,6 +36092,12 @@
       <c r="AG314" t="str">
         <v>繊細さと操作性を高次元で融合させたメガトップ仕様の張りのあるソリッドを搭載した攻めのソリッドティップロッド。繊細なティップと強靭なバットを組み合わせることで、ショートバイトを逃さず捉え一瞬で掛けてバットで寄せる、繊細でありながら強靭なロッド。</v>
       </c>
+      <c r="AH314" t="str">
+        <v/>
+      </c>
+      <c r="AI314" t="str">
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -34315,6 +36199,12 @@
       <c r="AG315" t="str">
         <v>ライトリグを緻密に操りタフコンディション下においてもバスが違和感を感じずスムースなフッキングを実現するメガトップを採用した“フィネスソリッドモデル”。</v>
       </c>
+      <c r="AH315" t="str">
+        <v/>
+      </c>
+      <c r="AI315" t="str">
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -34416,6 +36306,12 @@
       <c r="AG316" t="str">
         <v>ライトリグ全般と、「ミドスト、ボトスト、ホバスト」に高次元に対応した”フィネスモデル”。</v>
       </c>
+      <c r="AH316" t="str">
+        <v/>
+      </c>
+      <c r="AI316" t="str">
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -34517,6 +36413,12 @@
       <c r="AG317" t="str">
         <v>小型ハードベイトからライトリグまで様々な状況に適応するバーサタイル性能にソリッドの操作性を融合させた“ライトソリッドモデル”。</v>
       </c>
+      <c r="AH317" t="str">
+        <v/>
+      </c>
+      <c r="AI317" t="str">
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -34618,6 +36520,12 @@
       <c r="AG318" t="str">
         <v>小型ハードベイトからライトリグまで様々な状況に適応するバーサタイル性能にソリッドの操作性を融合させた“ライトソリッドモデル”。</v>
       </c>
+      <c r="AH318" t="str">
+        <v/>
+      </c>
+      <c r="AI318" t="str">
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -34719,6 +36627,12 @@
       <c r="AG319" t="str">
         <v>ノーシンカー、ダウンショット、ライトテキサスはもちろん、タイニークランクやミノーもこなす汎用性に優れた“バーサタイルモデル”。</v>
       </c>
+      <c r="AH319" t="str">
+        <v/>
+      </c>
+      <c r="AI319" t="str">
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -34820,6 +36734,12 @@
       <c r="AG320" t="str">
         <v>ヘビーカバーで口を使わないバスをスモラバをはじめとするライトリグで攻略する“パワーフィネスモデル”。</v>
       </c>
+      <c r="AH320" t="str">
+        <v/>
+      </c>
+      <c r="AI320" t="str">
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -34921,6 +36841,12 @@
       <c r="AG321" t="str">
         <v>ノーシンカーやスモラバなどのライトリグから小～中型ハードベイトまでオールラウンドに適応する“ライトバーサタイルモデル”。</v>
       </c>
+      <c r="AH321" t="str">
+        <v/>
+      </c>
+      <c r="AI321" t="str">
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -35022,6 +36948,12 @@
       <c r="AG322" t="str">
         <v>遠投性、操作性、強靭性を追求。</v>
       </c>
+      <c r="AH322" t="str">
+        <v/>
+      </c>
+      <c r="AI322" t="str">
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -35123,6 +37055,12 @@
       <c r="AG323" t="str">
         <v>操作性、軽量性、遠投性を追求。</v>
       </c>
+      <c r="AH323" t="str">
+        <v/>
+      </c>
+      <c r="AI323" t="str">
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -35224,6 +37162,12 @@
       <c r="AG324" t="str">
         <v>ミノーの操作性、軽量性を追求。</v>
       </c>
+      <c r="AH324" t="str">
+        <v/>
+      </c>
+      <c r="AI324" t="str">
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -35325,6 +37269,12 @@
       <c r="AG325" t="str">
         <v/>
       </c>
+      <c r="AH325" t="str">
+        <v/>
+      </c>
+      <c r="AI325" t="str">
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -35426,6 +37376,12 @@
       <c r="AG326" t="str">
         <v/>
       </c>
+      <c r="AH326" t="str">
+        <v/>
+      </c>
+      <c r="AI326" t="str">
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -35527,6 +37483,12 @@
       <c r="AG327" t="str">
         <v/>
       </c>
+      <c r="AH327" t="str">
+        <v/>
+      </c>
+      <c r="AI327" t="str">
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -35628,6 +37590,12 @@
       <c r="AG328" t="str">
         <v/>
       </c>
+      <c r="AH328" t="str">
+        <v/>
+      </c>
+      <c r="AI328" t="str">
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -35729,6 +37697,12 @@
       <c r="AG329" t="str">
         <v/>
       </c>
+      <c r="AH329" t="str">
+        <v/>
+      </c>
+      <c r="AI329" t="str">
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -35830,6 +37804,12 @@
       <c r="AG330" t="str">
         <v/>
       </c>
+      <c r="AH330" t="str">
+        <v/>
+      </c>
+      <c r="AI330" t="str">
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -35931,6 +37911,12 @@
       <c r="AG331" t="str">
         <v/>
       </c>
+      <c r="AH331" t="str">
+        <v/>
+      </c>
+      <c r="AI331" t="str">
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -36032,6 +38018,12 @@
       <c r="AG332" t="str">
         <v/>
       </c>
+      <c r="AH332" t="str">
+        <v/>
+      </c>
+      <c r="AI332" t="str">
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -36133,6 +38125,12 @@
       <c r="AG333" t="str">
         <v/>
       </c>
+      <c r="AH333" t="str">
+        <v/>
+      </c>
+      <c r="AI333" t="str">
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -36234,6 +38232,12 @@
       <c r="AG334" t="str">
         <v/>
       </c>
+      <c r="AH334" t="str">
+        <v/>
+      </c>
+      <c r="AI334" t="str">
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -36335,6 +38339,12 @@
       <c r="AG335" t="str">
         <v/>
       </c>
+      <c r="AH335" t="str">
+        <v/>
+      </c>
+      <c r="AI335" t="str">
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -36436,6 +38446,12 @@
       <c r="AG336" t="str">
         <v/>
       </c>
+      <c r="AH336" t="str">
+        <v/>
+      </c>
+      <c r="AI336" t="str">
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -36537,6 +38553,12 @@
       <c r="AG337" t="str">
         <v/>
       </c>
+      <c r="AH337" t="str">
+        <v/>
+      </c>
+      <c r="AI337" t="str">
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -36638,6 +38660,12 @@
       <c r="AG338" t="str">
         <v/>
       </c>
+      <c r="AH338" t="str">
+        <v/>
+      </c>
+      <c r="AI338" t="str">
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -36739,6 +38767,12 @@
       <c r="AG339" t="str">
         <v>湾岸部や漁港内などの使用を想定したシャープな振りと操作性を重視したショートレングスモデル。混み合った中での強引なやり取りを可能にしたバットパワーが魅力の専用設計。</v>
       </c>
+      <c r="AH339" t="str">
+        <v/>
+      </c>
+      <c r="AI339" t="str">
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -36840,6 +38874,12 @@
       <c r="AG340" t="str">
         <v>軽快な振り抜きで従来のフィールドだけでなく、サーフエリアでも活躍。またウキルアーだけでなく食い渋り時に有効なウキフカセ釣法にも対応するオールラウンドモデル。</v>
       </c>
+      <c r="AH340" t="str">
+        <v/>
+      </c>
+      <c r="AI340" t="str">
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -36941,6 +38981,12 @@
       <c r="AG341" t="str">
         <v>磯場の立ち込みやウキルアーの長い仕掛けを遠投し、沖を回遊するフレッシュなアキアジを狙い、確実なフッキングで掛けるティップと一日振り続けても疲れない軽さが魅力の遠投スペシャルモデル。</v>
       </c>
+      <c r="AH341" t="str">
+        <v/>
+      </c>
+      <c r="AI341" t="str">
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -37042,6 +39088,12 @@
       <c r="AG342" t="str">
         <v>取り回しの良い絶妙なレングス設定のマルチピースモデル。軽量SVFグラスにカーボンをコンポジットさせ、グラスの持つ柔軟さと、カーボンの持つ操作性、感度を両立。4ピースとすることで携行性を高め、遠征や未知なる釣場へのアプローチを容易に。スプーン、スピナーのリトリーブの釣りからシンキングミノーの釣りまで幅広く対応。</v>
       </c>
+      <c r="AH342" t="str">
+        <v/>
+      </c>
+      <c r="AI342" t="str">
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -37143,6 +39195,12 @@
       <c r="AG343" t="str">
         <v>取り回しの良い絶妙なレングス設定。SVF グラスに最適なバランスでカーボンマテリアルをコンポジットすることで、ルアーを水に絡ませるグラスならではの柔軟さに、軽さとキレという相反する特性を付加している。源流、渓流域でルアーでピンポイントを射抜き、躍動させ、掛けた後は確実に獲る、攻めのグラスロッドに仕上がった。</v>
       </c>
+      <c r="AH343" t="str">
+        <v/>
+      </c>
+      <c r="AI343" t="str">
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -37244,6 +39302,12 @@
       <c r="AG344" t="str">
         <v>一般的な渓流、里川でメインとなるアイテム。テンポよく且つ軽快にルアーを打ち込むことが可能。バットにパワーを持たせることで、ロングキャスト時も腰が砕けることなくキャストが可能。</v>
       </c>
+      <c r="AH344" t="str">
+        <v/>
+      </c>
+      <c r="AI344" t="str">
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -37345,6 +39409,12 @@
       <c r="AG345" t="str">
         <v>個性豊かな美しい渓魚が生息する小渓流。時に木々に覆われ、河川規模からもプレゼンテーションできる範囲が僅かしか存在しないことも多い。攻略するためには、どの角度からも確実に打ち込めるテクニカルキャストへの対応力、ルアー着水後、流れに馴染む移動距離を抑えた繊細なアプローチ、バレやすい近距離のバイトを確実に捕らえる追従性が求められる。それらを実現するために超高密度グラスのどこまでもしなやかに曲がる追従特性を最大限いかし、カーボンのキレの良さをアクセントとして配合したグラスプログレッシブ48UL-G。個性豊かな渓流魚との出逢いを1尾、1尾、存分に楽しみたいアングラーへおすすめしたい一本。</v>
       </c>
+      <c r="AH345" t="str">
+        <v/>
+      </c>
+      <c r="AI345" t="str">
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -37446,6 +39516,12 @@
       <c r="AG346" t="str">
         <v>渓流・源流域で高いキャストアキュラシーを活かし、ピンポイントを攻めるショートレングスマルチピースベイトモデル。軽量SVFグラスにカーボンをコンポジットさせ、グラスの持つ柔軟さと、カーボンの持つ操作性、感度を両立。4ピースとすることで携行性を高め、遠征や未知なる釣場へのアプローチを容易に。クセの無いテーパーは、ミノーからスプーン、スピナーまで幅広く対応。</v>
       </c>
+      <c r="AH346" t="str">
+        <v/>
+      </c>
+      <c r="AI346" t="str">
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -37547,6 +39623,12 @@
       <c r="AG347" t="str">
         <v>渓流・源流域をミノーを中心としたプラグで攻めるショートレングスベイトモデル。SVFグラスに最適なバランスでカーボンマテリアルをコンポジットした、柔軟性がありながらもやや張りを持たせたブランクは、ピンを狙い撃つキャスト性能と意のままにルアーを操れる操作性を両立。掛けた後は、グラスの持ち味を発揮し確実なランディングを約束。</v>
       </c>
+      <c r="AH347" t="str">
+        <v/>
+      </c>
+      <c r="AI347" t="str">
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -37648,6 +39730,12 @@
       <c r="AG348" t="str">
         <v>個性豊かな美しい渓魚が生息する小渓流。時に木々に覆われ、河川規模からもプレゼンテーションできる範囲が僅かしか存在しないことも多い。攻略するためには、どの角度からも確実に打ち込めるテクニカルキャストへの対応力、ルアー着水後、流れに馴染む移動距離を抑えた繊細なアプローチ、バレやすい近距離のバイトを確実に捕らえる追従性が求められる。それらを実現するために超高密度グラスのどこまでもしなやかに曲がる追従特性を最大限いかし、カーボンのキレの良さをアクセントとして配合したグラスプログレッシブ48UL-G。個性豊かな渓流魚との出逢いを1尾、1尾、存分に楽しみたいアングラーへおすすめしたい一本。</v>
       </c>
+      <c r="AH348" t="str">
+        <v/>
+      </c>
+      <c r="AI348" t="str">
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -37749,6 +39837,12 @@
       <c r="AG349" t="str">
         <v>取り回しの良い絶妙なレングス設定のマルチピースモデル。軽量SVFグラスにカーボンをコンポジットさせ、グラスの持つ柔軟さと、カーボンの持つ操作性、感度を両立。4ピースとすることで携行性を高め、遠征や未知なる釣場へのアプローチを容易に。スプーン、スピナーのリトリーブの釣りからシンキングミノーの釣りまで幅広く対応。</v>
       </c>
+      <c r="AH349" t="str">
+        <v/>
+      </c>
+      <c r="AI349" t="str">
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -37850,6 +39944,12 @@
       <c r="AG350" t="str">
         <v>渓流・源流域で高いキャストアキュラシーを活かし、ピンポイントを攻めるショートレングスマルチピースベイトモデル。軽量SVFグラスにカーボンをコンポジットさせ、グラスの持つ柔軟さと、カーボンの持つ操作性、感度を両立。4ピースとすることで携行性を高め、遠征や未知なる釣場へのアプローチを容易に。クセの無いテーパーは、ミノーからスプーン、スピナーまで幅広く対応。</v>
       </c>
+      <c r="AH350" t="str">
+        <v/>
+      </c>
+      <c r="AI350" t="str">
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -37951,6 +40051,12 @@
       <c r="AG351" t="str">
         <v>ベイトフィネスモデルノーシンカーやスモラバを中心としたライトリグから小型ハードベイトまで適応する”ベイトフィネスモデル”</v>
       </c>
+      <c r="AH351" t="str">
+        <v/>
+      </c>
+      <c r="AI351" t="str">
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -38052,6 +40158,12 @@
       <c r="AG352" t="str">
         <v>ライトバーサタイルモデルライトリグから小～中型ハードベイトまでオールラウンドに適応する”ライトバーサタイルモデル”</v>
       </c>
+      <c r="AH352" t="str">
+        <v/>
+      </c>
+      <c r="AI352" t="str">
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -38153,6 +40265,12 @@
       <c r="AG353" t="str">
         <v>バーサタイルモデルクランクベイトやスピナーベイト等の中型ハードベイトからダウンショットやテキサスなどの撃ちモノまで幅広く適応する”バーサタイルモデル”</v>
       </c>
+      <c r="AH353" t="str">
+        <v/>
+      </c>
+      <c r="AI353" t="str">
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -38254,6 +40372,12 @@
       <c r="AG354" t="str">
         <v>パワーバーサタイルモデル中～大型ハードベイトから重量級テキサスやラバージグなどの撃ちモノまで適応する”パワーバーサタイルモデル”</v>
       </c>
+      <c r="AH354" t="str">
+        <v/>
+      </c>
+      <c r="AI354" t="str">
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -38355,6 +40479,12 @@
       <c r="AG355" t="str">
         <v>スイムベイト・ビッグベイトモデルＳ字形ビッグベイトやスイムベイトに適応するパワーを備えたスローテーパーの”ビッグベイトモデル”</v>
       </c>
+      <c r="AH355" t="str">
+        <v/>
+      </c>
+      <c r="AI355" t="str">
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -38456,6 +40586,12 @@
       <c r="AG356" t="str">
         <v>フィネスモデルノーシンカー、ダウンショット、スモラバなどのライトリグの操作性に優れ、アキュラシーキャストを得意とする”フィネスモデル”</v>
       </c>
+      <c r="AH356" t="str">
+        <v/>
+      </c>
+      <c r="AI356" t="str">
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -38557,6 +40693,12 @@
       <c r="AG357" t="str">
         <v>ライトバーサタイルモデルジグヘッドやダウンショット、ネコリグなどのライトリグ全般から小～中型ハードベイトまでオールラウンドに適応する”ライトバーサタイルモデル”</v>
       </c>
+      <c r="AH357" t="str">
+        <v/>
+      </c>
+      <c r="AI357" t="str">
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -38658,6 +40800,12 @@
       <c r="AG358" t="str">
         <v>バーサタイルモデルノーシンカー、ダウンショット、ライトテキサスはもちろん、スモールクランクやミノーもこなす汎用性に優れた”バーサタイルモデル”</v>
       </c>
+      <c r="AH358" t="str">
+        <v/>
+      </c>
+      <c r="AI358" t="str">
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -38759,6 +40907,12 @@
       <c r="AG359" t="str">
         <v>ベイトフィネスモデルノーシンカーやスモラバを中心としたライトリグから小型ハードベイトまで適応する‟ベイトフィネスモデル”</v>
       </c>
+      <c r="AH359" t="str">
+        <v/>
+      </c>
+      <c r="AI359" t="str">
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -38860,6 +41014,12 @@
       <c r="AG360" t="str">
         <v>ライトバーサタイルモデルライトリグから小〜中型ハードベイトまでオールラウンドに適応する‟ライトバーサタイルモデル”</v>
       </c>
+      <c r="AH360" t="str">
+        <v/>
+      </c>
+      <c r="AI360" t="str">
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -38961,6 +41121,12 @@
       <c r="AG361" t="str">
         <v>バーサタイルモデルクランクベイトやスピナーベイト等の中型ハードベイトからダウンショットやテキサスなどの撃ちモノまで幅広く適応する‟バーサタイルモデル”</v>
       </c>
+      <c r="AH361" t="str">
+        <v/>
+      </c>
+      <c r="AI361" t="str">
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -39062,6 +41228,12 @@
       <c r="AG362" t="str">
         <v>グラスモデルクランクベイトやスピナーベイトなど、巻物の性能を存分に引き出し、バイトを弾くことなく乗せる柔軟さを持つグラスモデル。</v>
       </c>
+      <c r="AH362" t="str">
+        <v/>
+      </c>
+      <c r="AI362" t="str">
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -39163,6 +41335,12 @@
       <c r="AG363" t="str">
         <v>フロッグモデル緻密なアクションを生み出すソフトなティップにカバーから強引に引きずり出す強靭なバットパワーを高次元で融合させた‟フロッグモデル”</v>
       </c>
+      <c r="AH363" t="str">
+        <v/>
+      </c>
+      <c r="AI363" t="str">
+        <v/>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -39264,6 +41442,12 @@
       <c r="AG364" t="str">
         <v>バーサタイルモデルクランクベイトやスピナーベイト等の中型ハードベイトからダウンショットやテキサスなどの撃ちモノまで幅広く適応する‟バーサタイルモデル”</v>
       </c>
+      <c r="AH364" t="str">
+        <v/>
+      </c>
+      <c r="AI364" t="str">
+        <v/>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -39365,6 +41549,12 @@
       <c r="AG365" t="str">
         <v>パワーバーサタイルモデル中～大型ハードベイトから重量級テキサスやラバージグなどの撃ちモノまで適応する‟パワーバーサタイルモデル”</v>
       </c>
+      <c r="AH365" t="str">
+        <v/>
+      </c>
+      <c r="AI365" t="str">
+        <v/>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -39466,6 +41656,12 @@
       <c r="AG366" t="str">
         <v>パワーストロングモデル太軸フックを貫通させる瞬発力とモンスター級をカバーから引き離すパワーを備えた‟パワーストロングモデル”</v>
       </c>
+      <c r="AH366" t="str">
+        <v/>
+      </c>
+      <c r="AI366" t="str">
+        <v/>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -39567,6 +41763,12 @@
       <c r="AG367" t="str">
         <v>スイムベイト、ビッグベイトモデルS字系ビッグベイトやスイムベイトに適応するパワーを備えたスローテーパーの‟ビッグベイトモデル”</v>
       </c>
+      <c r="AH367" t="str">
+        <v/>
+      </c>
+      <c r="AI367" t="str">
+        <v/>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -39668,6 +41870,12 @@
       <c r="AG368" t="str">
         <v>パワーバーサタイルモデル中～大型ハードベイトから重量級テキサスやラバージグなどの撃ちモノまで適応し、遠投も可能な‟ロングパワーバーサタイルモデル”</v>
       </c>
+      <c r="AH368" t="str">
+        <v/>
+      </c>
+      <c r="AI368" t="str">
+        <v/>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
@@ -39769,6 +41977,12 @@
       <c r="AG369" t="str">
         <v>パワーストロングモデル太軸フックを貫通させる瞬発力とモンスター級をカバーから引き離すパワーを備えた‟パワーストロングモデル”</v>
       </c>
+      <c r="AH369" t="str">
+        <v/>
+      </c>
+      <c r="AI369" t="str">
+        <v/>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -39870,6 +42084,12 @@
       <c r="AG370" t="str">
         <v>フィネスモデルノーシンカー、ダウンショット、スモラバなどのライトリグの操作性に優れ、アキュラシーキャストを得意とする‟フィネスモデル”</v>
       </c>
+      <c r="AH370" t="str">
+        <v/>
+      </c>
+      <c r="AI370" t="str">
+        <v/>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
@@ -39971,6 +42191,12 @@
       <c r="AG371" t="str">
         <v>フィネスソリッドモデルライトリグを緻密に操りタフコンディション下においてもバスが違和感を感じずスムースなフッキングを実現するメガトップを採用した‟フィネスソリッドモデル”</v>
       </c>
+      <c r="AH371" t="str">
+        <v/>
+      </c>
+      <c r="AI371" t="str">
+        <v/>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -40072,6 +42298,12 @@
       <c r="AG372" t="str">
         <v>ライトバーサタイルモデルジグヘッドリグやダウンショット、ネコリグなどのライトリグ全般から小〜中型ハードベイトまでオールラウンドに適応する‟ライトバーサタイルモデル”</v>
       </c>
+      <c r="AH372" t="str">
+        <v/>
+      </c>
+      <c r="AI372" t="str">
+        <v/>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
@@ -40173,6 +42405,12 @@
       <c r="AG373" t="str">
         <v>ライトバーサタイルモデルジグヘッドリグやダウンショット、ネコリグなどのライトリグ全般から小〜中型ハードベイトまでオールラウンドに適応する‟ライトバーサタイルモデル”</v>
       </c>
+      <c r="AH373" t="str">
+        <v/>
+      </c>
+      <c r="AI373" t="str">
+        <v/>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -40274,6 +42512,12 @@
       <c r="AG374" t="str">
         <v>バーサタイルモデルノーシンカー、ダウンショット、ライトテキサスはもちろん、スモールクランクやミノーもこなす汎用性に優れた‟バーサタイルモデル”</v>
       </c>
+      <c r="AH374" t="str">
+        <v/>
+      </c>
+      <c r="AI374" t="str">
+        <v/>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -40375,6 +42619,12 @@
       <c r="AG375" t="str">
         <v>パワーフィネスモデルヘビーカバーで口を使わないバスをスモラバをはじめとするライトリグで攻略する‟パワーフィネスモデル”</v>
       </c>
+      <c r="AH375" t="str">
+        <v/>
+      </c>
+      <c r="AI375" t="str">
+        <v/>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -40476,6 +42726,12 @@
       <c r="AG376" t="str">
         <v>SVF GLASS採用モデル。柔軟なティップセクションから急激に立ち上がるベリー～バット部を採用したことで、グラスの食わせ性能と掛け性能を持ち合わせ、確実なランディングを約束。マイクロクランクから放流スプーンまで幅広く対応。</v>
       </c>
+      <c r="AH376" t="str">
+        <v/>
+      </c>
+      <c r="AI376" t="str">
+        <v/>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
@@ -40577,6 +42833,12 @@
       <c r="AG377" t="str">
         <v>異次元のボトム感度超ショートSMTを搭載した、仕掛けて獲る攻撃的ロッド。PEラインと最高の相性を持つ。ラインテンションを操る、メリハリの効かせたメソッドに特に最適で、デジ巻きやリフト＆フォールの釣りで、短い距離でどれだけルアーがアクションしたか、ボトムに着底したかがまるで見ているかのように鮮明に感じ取れる。トップウォーターの釣りにおいても抜群の使いやすさを誇る。</v>
       </c>
+      <c r="AH377" t="str">
+        <v/>
+      </c>
+      <c r="AI377" t="str">
+        <v/>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
@@ -40678,6 +42940,12 @@
       <c r="AG378" t="str">
         <v>操作性と感度を両立した、ソリッドティップモデル。繊細なティップと張りのあるベリーのセッティングは、魚に違和感を与えることなく、確実なフッキングをもたらす。繊細なティップは、操作系プラグを中心にスプーンにも高次元に対応。</v>
       </c>
+      <c r="AH378" t="str">
+        <v/>
+      </c>
+      <c r="AI378" t="str">
+        <v/>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
@@ -40779,6 +43047,12 @@
       <c r="AG379" t="str">
         <v>センシティブバーサタイルモデルPRESSOプロスタッフ待望モデル。 低伸度ラインを合わせることで、真の性能を発揮。繊細なティップに強めなベリーをセッティングすることで、トラウトに違和感なくルアーを喰わせると共に、バイトを瞬時に捉え掛けることが可能に。操作性の良いテーパーセッティングは、攻めの巻きの釣りから、ボトムルアーやトップなどのルアーをアクションさせる釣りに対応。 小型のミノープラグにもオススメ。</v>
       </c>
+      <c r="AH379" t="str">
+        <v/>
+      </c>
+      <c r="AI379" t="str">
+        <v/>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
@@ -40880,6 +43154,12 @@
       <c r="AG380" t="str">
         <v>センシティブバーサタイルモデルPRESSOプロスタッフ待望モデル。 低伸度ラインを合わせることで、真の性能を発揮。繊細なティップに強めなベリーをセッティングすることで、トラウトに違和感なくルアーを喰わせると共に、バイトを瞬時に捉え掛けることが可能に。操作性の良いテーパーセッティングは、攻めの巻きの釣りから、ボトムルアーやトップなどのルアーをアクションさせる釣りに対応。 小型のミノープラグにもオススメ。</v>
       </c>
+      <c r="AH380" t="str">
+        <v/>
+      </c>
+      <c r="AI380" t="str">
+        <v/>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
@@ -40981,6 +43261,12 @@
       <c r="AG381" t="str">
         <v>二段テーパーソリッドティップモデル二段テーパーメガトップ採用の高感度ソリッドティップモデル。ソフトなソリッドティップは手感度が鈍りがちだが、二段テーパーによって今までに無い手感度をもたらした。食い渋り時でも口にフックを残しフッキングに持ち込めるソリッドの基本性能はもちろん健在。ノー感じになりがちなマイクロスプーンのアクションも手に感じながらリトリーブが可能。</v>
       </c>
+      <c r="AH381" t="str">
+        <v/>
+      </c>
+      <c r="AI381" t="str">
+        <v/>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
@@ -41082,6 +43368,12 @@
       <c r="AG382" t="str">
         <v>シビアな状況を打破するメガトップ搭載モデルエリアトラウトのレジェンド、高田達也テスター監修のシビアな状況を、スプーニングで打破する繊細なティップを持つモデル。放流から時間が経ち追いが悪くなった状況、気温の大きな変化で活性が下がった状況など、厳しい状況下でのバイトを確実に捉え、ランディングに持ち込む。繊細さを持つメガトップはルアーに起こる変化を視覚でも伝えると共に、トラウトに違和感なくルアーを喰わせる。マイクロスプーンや軽量スプーンとの相性は抜群で、マイクロクランクのデッドスローリトリーブにも対応。</v>
       </c>
+      <c r="AH382" t="str">
+        <v/>
+      </c>
+      <c r="AI382" t="str">
+        <v/>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
@@ -41183,6 +43475,12 @@
       <c r="AG383" t="str">
         <v>シビアな状況を打破するメガトップ搭載モデルエリアトラウトのレジェンド、高田達也テスター監修のシビアな状況を、スプーニングで打破する繊細なティップを持つモデル。放流から時間が経ち追いが悪くなった状況、気温の大きな変化で活性が下がった状況など、厳しい状況下でのバイトを確実に捉え、ランディングに持ち込む。繊細さを持つメガトップはルアーに起こる変化を視覚でも伝えると共に、トラウトに違和感なくルアーを喰わせる。マイクロスプーンや軽量スプーンとの相性は抜群で、マイクロクランクのデッドスローリトリーブにも対応。</v>
       </c>
+      <c r="AH383" t="str">
+        <v/>
+      </c>
+      <c r="AI383" t="str">
+        <v/>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
@@ -41284,6 +43582,12 @@
       <c r="AG384" t="str">
         <v>ショートディスタンスでの唐突なバイトに対し、柔軟なソリッドティップがフックを口に残し、スムーズに曲がるベリーで弾くことなく確実に掛けることが可能なモデル。マイクロスプーンはもちろん、マイクロクランクにも対応。</v>
       </c>
+      <c r="AH384" t="str">
+        <v/>
+      </c>
+      <c r="AI384" t="str">
+        <v/>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
@@ -41385,6 +43689,12 @@
       <c r="AG385" t="str">
         <v>操作性と感度を両立した、ソリッドティップモデル。繊細なティップと張りのあるベリーのセッティングは、魚に違和感を与えることなく、確実なフッキングをもたらす。繊細なティップは、操作系プラグを中心にスプーンにも高次元に対応。</v>
       </c>
+      <c r="AH385" t="str">
+        <v/>
+      </c>
+      <c r="AI385" t="str">
+        <v/>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
@@ -41486,6 +43796,12 @@
       <c r="AG386" t="str">
         <v>エステルライン専用モデル。バイトを弾くことなく捉える繊細なティップと、魚を暴れさせること無くランディングに持ち込む、負荷に追従するベリー～バットを持つ。小径のガイドセッティングは、感度向上とトラブルの減少を実現。</v>
       </c>
+      <c r="AH386" t="str">
+        <v/>
+      </c>
+      <c r="AI386" t="str">
+        <v/>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
@@ -41587,6 +43903,12 @@
       <c r="AG387" t="str">
         <v>操作性と感度を両立した、ソリッドティップモデル。繊細なティップと張りのあるベリーのセッティングは、魚に違和感を与えることなく、確実なフッキングをもたらす。繊細なティップは、操作系プラグを中心にスプーンにも高次元に対応。</v>
       </c>
+      <c r="AH387" t="str">
+        <v/>
+      </c>
+      <c r="AI387" t="str">
+        <v/>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
@@ -41688,6 +44010,12 @@
       <c r="AG388" t="str">
         <v>SVF GLASS採用モデル。柔軟なティップセクションから急激に立ち上がるベリー～バット部を採用したことで、グラスの食わせ性能と掛け性能を持ち合わせ、確実なランディングを約束。マイクロクランクから放流スプーンまで幅広く対応。</v>
       </c>
+      <c r="AH388" t="str">
+        <v/>
+      </c>
+      <c r="AI388" t="str">
+        <v/>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
@@ -41789,6 +44117,12 @@
       <c r="AG389" t="str">
         <v>携帯性を活かしたアプローチで、源流～渓流域を攻略。ピッチングやフリップなどテクニカルキャストを得意とする4ピースモデル。</v>
       </c>
+      <c r="AH389" t="str">
+        <v/>
+      </c>
+      <c r="AI389" t="str">
+        <v/>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
@@ -41890,6 +44224,12 @@
       <c r="AG390" t="str">
         <v>小渓流から里川まで幅広く対応する410レングスにしなやかなXULが追加。ショートバイトも弾かずフックアップ、ファイトも存分に楽しめるレギュラーテーパー。</v>
       </c>
+      <c r="AH390" t="str">
+        <v/>
+      </c>
+      <c r="AI390" t="str">
+        <v/>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
@@ -41991,6 +44331,12 @@
       <c r="AG391" t="str">
         <v>小渓流ミノーイングスペシャル。サイドやバックハンドのライナーキャスト、ハイテンポな攻略を得意とした1本。</v>
       </c>
+      <c r="AH391" t="str">
+        <v/>
+      </c>
+      <c r="AI391" t="str">
+        <v/>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
@@ -42092,6 +44438,12 @@
       <c r="AG392" t="str">
         <v>山岳渓流～開けた里川まで適応するオールラウンダー。ミノー、スピナー、スプーン、幅広く対応する1本。</v>
       </c>
+      <c r="AH392" t="str">
+        <v/>
+      </c>
+      <c r="AI392" t="str">
+        <v/>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
@@ -42193,6 +44545,12 @@
       <c r="AG393" t="str">
         <v>里川～中流の開けた流れのスタンダードモデル。レングスを活かしたロングプレゼンテーション、アップ～ダウンクロスまで幅広いアプローチを可能にする1本。</v>
       </c>
+      <c r="AH393" t="str">
+        <v/>
+      </c>
+      <c r="AI393" t="str">
+        <v/>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
@@ -42294,6 +44652,12 @@
       <c r="AG394" t="str">
         <v>渓流～中流域で、大ヤマメや大アマゴを、トルクフルなブランクで獲ることが可能。ルアーの選択肢も広く、高い操作性も魅力な一本。</v>
       </c>
+      <c r="AH394" t="str">
+        <v/>
+      </c>
+      <c r="AI394" t="str">
+        <v/>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
@@ -42395,6 +44759,12 @@
       <c r="AG395" t="str">
         <v>湖や中流域～本流域にて、幅広いルアーを駆使し、サクラマスや大型レインボーと対峙できる遠投性能も魅力な一本。</v>
       </c>
+      <c r="AH395" t="str">
+        <v/>
+      </c>
+      <c r="AI395" t="str">
+        <v/>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
@@ -42496,6 +44866,12 @@
       <c r="AG396" t="str">
         <v>携帯性を活かしたアプローチで、源流～渓流域を攻略。手返しの良いアキュラシーキャストを可能とする4ピースベイトモデル。</v>
       </c>
+      <c r="AH396" t="str">
+        <v/>
+      </c>
+      <c r="AI396" t="str">
+        <v/>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
@@ -42597,6 +44973,12 @@
       <c r="AG397" t="str">
         <v>小渓流から里川まで幅広く対応する48レングスのベイトにXULのしなやか調子が追加。フリップキャストとの相性も良く、ファイトも存分に楽しめる曲がるパラボリック調子。</v>
       </c>
+      <c r="AH397" t="str">
+        <v/>
+      </c>
+      <c r="AI397" t="str">
+        <v/>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
@@ -42698,6 +45080,12 @@
       <c r="AG398" t="str">
         <v>渓流～開けた里川まで幅広く適応するベイトモデル。ミノー、スピナー、スプーンとルアーを選ばず、レングスを活かした豊富なアプローチを可能にする1本。</v>
       </c>
+      <c r="AH398" t="str">
+        <v/>
+      </c>
+      <c r="AI398" t="str">
+        <v/>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
@@ -42799,6 +45187,12 @@
       <c r="AG399" t="str">
         <v>携帯性を活かしたアプローチで、源流～渓流域を攻略。ピッチングやフリップなどテクニカルキャストを得意とする4ピースモデル。</v>
       </c>
+      <c r="AH399" t="str">
+        <v/>
+      </c>
+      <c r="AI399" t="str">
+        <v/>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
@@ -42900,6 +45294,12 @@
       <c r="AG400" t="str">
         <v>携帯性を活かしたアプローチで、源流～渓流域を攻略。手返しの良いアキュラシーキャストを可能とする4ピースベイトモデル。</v>
       </c>
+      <c r="AH400" t="str">
+        <v/>
+      </c>
+      <c r="AI400" t="str">
+        <v/>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
@@ -43001,6 +45401,12 @@
       <c r="AG401" t="str">
         <v>小渓流のスペシャリスト。緑のアーチを潜り、木漏れ日が差し込む小渓の流れを心地よく釣っていく。変化に富んだ流れ、倒木や岩には苔が生し、僅かなピンスポットに渓魚が潜む。木々をかわしたテクニカルキャスト、ショートレングスを生かしたダイレクト感ある取り回し良いロッドでテンポよく釣っていく。オーラム48ULはサイド、バックハンドキャストが特に心地よいロッドに仕上がっている。調子はレギュラーアクション。やや細身で良く曲がるが、SVFカーボンの恩恵でブランクスには密度感がありシャープ。キャストは予想したよりも伸びる。サイド、バックハンドでストレートに抜ける軌道がとにかく心地よいロッドである。パワーはUL。水深50cm前後の小渓を軽快に楽しむにはぴったりのパワーバランス。源流、沢、小渓流のピンスポットを射抜く正確性。ルアーを緻密に操り、点で喰わせ、掛ける操作性。4’8”に求められる要素を凝縮したエキスパートモデル。</v>
       </c>
+      <c r="AH401" t="str">
+        <v/>
+      </c>
+      <c r="AI401" t="str">
+        <v/>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
@@ -43102,6 +45508,12 @@
       <c r="AG402" t="str">
         <v>小規模河川のピン打ちスペシャリストオーラム410L、調子はファーストアクション。オーラム48ULがレギュラーテーパーに対し、このオーラム410Lは穂先が入るファストテーパーに仕上がっている。410Lの穂先が入る調子はピッチングやフリップキャストとの相性が特に良い。落ち込みが続くピンスポット打ちや掌ほどのスペースに落としたいシーンも先調子の柔軟な穂先にルアーウェイトを乗せ、変動値の少ない再現性あるキャストを容易にしてくれる。また、ピンスポットに打ち込んだルアーが大雑把に動かず細かな操作が出来るのも穂先の入る調子の優位性。オーラム410Lはオーラム48ULが得意とする優しい流れだけでなく、水量豊富、押しの強い流れでも活躍する。一言に小渓流、小規模河川と言っても水量や高低差によって川の表情は全く違う。Lパワーの先調子が必要な場面は多く存在する。小渓流のピンスポットをライナー軌道で射抜く正確性。流れを捉えるクリアでシャープなルアー操作性。ハイテンポな領域にも対応するエキスパートモデル。</v>
       </c>
+      <c r="AH402" t="str">
+        <v/>
+      </c>
+      <c r="AI402" t="str">
+        <v/>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
@@ -43203,6 +45615,12 @@
       <c r="AG403" t="str">
         <v>小渓流～里川まで、渓流のオールラウンダーオーラム53UL、調子はレギュラーファスト。サイドやバックハンドキャストはもちろん、ややファストよりの調子ともありピッチングやフリップも心地よいキャストフィール。SVFの恩恵もあり優しく振ってもストレートに伸びるキャストが気持ちいい。53レングスは源流域などの小規模河川から里川まで、1本でどこでも活躍するロッドである。小規模特化型の48と比べると53はレングス由来の有意性、キャスト後のルアー操作に圧倒的な自由度がある。小規模河川であっても離れた場所からアプローチをしないと警戒をあたえる場面や、高低差があり狙う流れが一段高いポイントなど、53のレングスがいきる。また53は穂先を高い位置でルアー操作できるため、引っ張ろうとする力を抑え、トゥイッチなどでアクションさせたルアーが近寄ってきにくい特徴もある。とにかくバランスの良い総合力に優れた1本である。渓流～里川対応のオールラウンダー。キャストの心地よさ、カーブの気持ちよさ、ロッドと一体となるような操作性。総合力、バランスを極めたエキスパートモデル。</v>
       </c>
+      <c r="AH403" t="str">
+        <v/>
+      </c>
+      <c r="AI403" t="str">
+        <v/>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
@@ -43304,6 +45722,12 @@
       <c r="AG404" t="str">
         <v>小渓流をクリアな操作感でハイテンポに釣り上がるベイトモデル細身シャープな印象のオーラム46ULB。調子はスローテーパー。細身ながらSVFのカーボン密度を感じるブランクスがクリアでダイレクト感あるルアー操作感を実現してくれる。ハリのあるブランクスはブレが少なく、マニュアル感覚でルアーのアクションを自在に演出できる。流れに合わせ緩急をつけたアクションもより正確に操れる。フワフワ調子で流れに馴染ませることに優れたトラッド46ULB-4と比べると、オーラムはキリっとしたクリアな操作性のロッドとなっている。そのため豊富な流れにも負けずルアーアクションの質を損なわない。さらには瞬間的なフッキングも決まるシャープなロッドとなっている。小渓流のピンスポットをフリップで射抜く正確性とバックハンド、サイドハンドキャストの快適さ、緩急自在シャープなルアー操作性を併せ持つエキスパートモデル。</v>
       </c>
+      <c r="AH404" t="str">
+        <v/>
+      </c>
+      <c r="AI404" t="str">
+        <v/>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
@@ -43405,6 +45829,12 @@
       <c r="AG405" t="str">
         <v>マイクロスプーンからスモールプラグなどの軽量ルアーをストレスなく使用でき、シビアな状況でも確実にバイトを捉えるモデル。</v>
       </c>
+      <c r="AH405" t="str">
+        <v/>
+      </c>
+      <c r="AI405" t="str">
+        <v/>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
@@ -43506,6 +45936,12 @@
       <c r="AG406" t="str">
         <v>突き詰めたガイドセッティング、繊細なバイトを捉えるティップセクション、衝撃をいなしラインブレイクを防ぐ、負荷に応じて素直に曲がり込むベリー～バットセクションを採用と、エステルラインを用いた釣りを完遂するロッド。</v>
       </c>
+      <c r="AH406" t="str">
+        <v/>
+      </c>
+      <c r="AI406" t="str">
+        <v/>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
@@ -43607,6 +46043,12 @@
       <c r="AG407" t="str">
         <v>スプーンからプラグを使用し、キャストのしやすさ、ルアーの操作性を高次元で両立したベイトモデル。</v>
       </c>
+      <c r="AH407" t="str">
+        <v/>
+      </c>
+      <c r="AI407" t="str">
+        <v/>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
@@ -43708,6 +46150,12 @@
       <c r="AG408" t="str">
         <v>操作性と感度を両立した、ソリッドティップモデル。繊細なソリッド部と強めのベリーからバット部の組み合わせは、ボトムルアー、ミノーなどの高い操作性と確実なフッキングをもたらす。繊細なティップは、スプーンにも高次元に対応。</v>
       </c>
+      <c r="AH408" t="str">
+        <v/>
+      </c>
+      <c r="AI408" t="str">
+        <v/>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
@@ -43809,6 +46257,12 @@
       <c r="AG409" t="str">
         <v>スプーンからプラグを使用し、キャストのしやすさ、ルアーの操作性を高次元で両立したベイトモデル。</v>
       </c>
+      <c r="AH409" t="str">
+        <v/>
+      </c>
+      <c r="AI409" t="str">
+        <v/>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
@@ -43910,6 +46364,12 @@
       <c r="AG410" t="str">
         <v>取り回しの良い5.5ftのレングスに、ショートソリッドを組み合わせた高感度ソリッドモデル。軽量スプーンの泳ぎを手元に伝える感度と、マイクロクランク使用時のノリの良さを併せ持つ。操作系プラグにもおすすめの一本。</v>
       </c>
+      <c r="AH410" t="str">
+        <v/>
+      </c>
+      <c r="AI410" t="str">
+        <v/>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
@@ -44011,6 +46471,12 @@
       <c r="AG411" t="str">
         <v>操作性と感度を両立した、ソリッドティップモデル。繊細なソリッド部と強めのベリーからバット部の組み合わせは、ボトムルアー、ミノーなどの高い操作性と確実なフッキングをもたらす。繊細なティップは、スプーンにも高次元に対応。</v>
       </c>
+      <c r="AH411" t="str">
+        <v/>
+      </c>
+      <c r="AI411" t="str">
+        <v/>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
@@ -44112,6 +46578,12 @@
       <c r="AG412" t="str">
         <v>カーボン素材とは一線を画す高感度「メタルトップ」を採用し、あらゆる変化を伝える手感度、ティップ部の繊細さがもたらす目感度も持ち合わせるロッド。フォールの釣りや操作系の釣りで圧巻のパフォーマンスを発揮。</v>
       </c>
+      <c r="AH412" t="str">
+        <v/>
+      </c>
+      <c r="AI412" t="str">
+        <v/>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
@@ -44213,6 +46685,12 @@
       <c r="AG413" t="str">
         <v>突き詰めたガイドセッティング、繊細なバイトを捉えるティップセクション、衝撃をいなしラインブレイクを防ぐ、負荷に応じて素直に曲がり込むベリー～バットセクションを採用と、エステルラインを用いた釣りを完遂するロッド。</v>
       </c>
+      <c r="AH413" t="str">
+        <v/>
+      </c>
+      <c r="AI413" t="str">
+        <v/>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
@@ -44314,6 +46792,12 @@
       <c r="AG414" t="str">
         <v>スプーンからプラグを使用し、キャストのしやすさ、ルアーの操作性を高次元で両立したベイトモデル。</v>
       </c>
+      <c r="AH414" t="str">
+        <v/>
+      </c>
+      <c r="AI414" t="str">
+        <v/>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
@@ -44415,6 +46899,12 @@
       <c r="AG415" t="str">
         <v>湖のトラウトをジグで狙うための専用設計モデル。浅場から30mの水深でジグを巧みに操り、食い込みの良いソリッドティップでシビアなバイトも確実に捉え、しっかりとしたバットでトラウトを制御し、確実にランディングに持ち込むモデル。</v>
       </c>
+      <c r="AH415" t="str">
+        <v/>
+      </c>
+      <c r="AI415" t="str">
+        <v/>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
@@ -44516,6 +47006,12 @@
       <c r="AG416" t="str">
         <v>湖のトラウトをジグで狙うための専用設計モデル。浅場から30mの水深でジグを巧みに操り、食い込みの良いソリッドティップでシビアなバイトも確実に捉え、しっかりとしたバットでトラウトを制御し、確実にランディングに持ち込むモデル。</v>
       </c>
+      <c r="AH416" t="str">
+        <v/>
+      </c>
+      <c r="AI416" t="str">
+        <v/>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
@@ -44617,6 +47113,12 @@
       <c r="AG417" t="str">
         <v>源流域から渓流域における小渓流にて、ショートレンジやピンスポット攻略を得意とするショートレングスモデル。</v>
       </c>
+      <c r="AH417" t="str">
+        <v/>
+      </c>
+      <c r="AI417" t="str">
+        <v/>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
@@ -44718,6 +47220,12 @@
       <c r="AG418" t="str">
         <v>源流域から渓流域で、軽量ルアーからミノーまで対応するショートレングスモデル。</v>
       </c>
+      <c r="AH418" t="str">
+        <v/>
+      </c>
+      <c r="AI418" t="str">
+        <v/>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
@@ -44819,6 +47327,12 @@
       <c r="AG419" t="str">
         <v>源流域から渓流域をミノーでテンポよく攻略するショートレングスモデル。</v>
       </c>
+      <c r="AH419" t="str">
+        <v/>
+      </c>
+      <c r="AI419" t="str">
+        <v/>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
@@ -44920,6 +47434,12 @@
       <c r="AG420" t="str">
         <v>源流域から中流域まで幅広く使用できるオールラウンドモデル。</v>
       </c>
+      <c r="AH420" t="str">
+        <v/>
+      </c>
+      <c r="AI420" t="str">
+        <v/>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
@@ -45021,6 +47541,12 @@
       <c r="AG421" t="str">
         <v>渓流域から中流域で幅広く使用でき、大型魚にも対応するオールラウンドモデル。</v>
       </c>
+      <c r="AH421" t="str">
+        <v/>
+      </c>
+      <c r="AI421" t="str">
+        <v/>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
@@ -45122,6 +47648,12 @@
       <c r="AG422" t="str">
         <v>中流域やC&amp;R区間などで大型トラウトとも対峙できるロングキャストモデル。</v>
       </c>
+      <c r="AH422" t="str">
+        <v/>
+      </c>
+      <c r="AI422" t="str">
+        <v/>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
@@ -45223,6 +47755,12 @@
       <c r="AG423" t="str">
         <v>湖沼や中流域～本流域でミノーやスプーンを遠投し攻略するモデル。</v>
       </c>
+      <c r="AH423" t="str">
+        <v/>
+      </c>
+      <c r="AI423" t="str">
+        <v/>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
@@ -45324,6 +47862,12 @@
       <c r="AG424" t="str">
         <v>素早い手返しでアキュラシーキャストを繰り出し、ピンスポットを攻略するショートレングスベイトモデル。</v>
       </c>
+      <c r="AH424" t="str">
+        <v/>
+      </c>
+      <c r="AI424" t="str">
+        <v/>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
@@ -45425,6 +47969,12 @@
       <c r="AG425" t="str">
         <v>源流域から渓流域で、アキュラシーキャストを可能にするショートレングスベイトモデル。</v>
       </c>
+      <c r="AH425" t="str">
+        <v/>
+      </c>
+      <c r="AI425" t="str">
+        <v/>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
@@ -45526,6 +48076,12 @@
       <c r="AG426" t="str">
         <v>源流域から中流域まで幅広く使用できるオールラウンドベイトモデル。</v>
       </c>
+      <c r="AH426" t="str">
+        <v/>
+      </c>
+      <c r="AI426" t="str">
+        <v/>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
@@ -45627,6 +48183,12 @@
       <c r="AG427" t="str">
         <v>軽量ルアーの操作性に優れたしなやかなXUL。取り回しの良い小渓流のスタンダード。</v>
       </c>
+      <c r="AH427" t="str">
+        <v/>
+      </c>
+      <c r="AI427" t="str">
+        <v/>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
@@ -45728,6 +48290,12 @@
       <c r="AG428" t="str">
         <v>軽量ルアーのキャスト性に優れたしなやかなXUL。小渓流ベイトのスタンダード。</v>
       </c>
+      <c r="AH428" t="str">
+        <v/>
+      </c>
+      <c r="AI428" t="str">
+        <v/>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
@@ -45829,6 +48397,12 @@
       <c r="AG429" t="str">
         <v>硬めのティップセクションと柔軟なベリー～バットのセッティング。掛け性能を持ちながら、曲がり込むテーパーにより確実なランディングを約束。マイクロスプーンから中量級スプーン、小型クランクに対応。</v>
       </c>
+      <c r="AH429" t="str">
+        <v/>
+      </c>
+      <c r="AI429" t="str">
+        <v/>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
@@ -45930,6 +48504,12 @@
       <c r="AG430" t="str">
         <v>エステルライン専用セッティングを施した、繊細なティップと張りのあるベリー、柔軟なバットを組み合わせ、掛け性能とランディングの安心感をもたらす。小径のガイドセッティングは、感度向上とトラブルの減少を実現。</v>
       </c>
+      <c r="AH430" t="str">
+        <v/>
+      </c>
+      <c r="AI430" t="str">
+        <v/>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
@@ -46031,6 +48611,12 @@
       <c r="AG431" t="str">
         <v>繊細なソリッドティップに強めのベリーセクションを採用することで、マイクロスプーンからマイクロクランクの巻きの釣りにて、あらゆるバイトを確実に捉えることが可能。小型操作系プラグにも高次元に対応する。</v>
       </c>
+      <c r="AH431" t="str">
+        <v/>
+      </c>
+      <c r="AI431" t="str">
+        <v/>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
@@ -46132,6 +48718,12 @@
       <c r="AG432" t="str">
         <v>繊細なソリッドティップに強めのベリーセクションを採用することで、マイクロスプーンからマイクロクランクの巻きの釣りにて、あらゆるバイトを確実に捉えることが可能。小型操作系プラグにも高次元に対応する。</v>
       </c>
+      <c r="AH432" t="str">
+        <v/>
+      </c>
+      <c r="AI432" t="str">
+        <v/>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
@@ -46233,6 +48825,12 @@
       <c r="AG433" t="str">
         <v>張りのあるティップと曲がるバットセクションを持ち、中量級スプーンから放流スプーン、そしてフルサイズクランクと、ウェイトのあるルアーの巻きを完結するアイテム。ボトムルアー、操作系ルアーにも対応する懐の広さも併せ持つ。</v>
       </c>
+      <c r="AH433" t="str">
+        <v/>
+      </c>
+      <c r="AI433" t="str">
+        <v/>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
@@ -46334,6 +48932,12 @@
       <c r="AG434" t="str">
         <v>繊細なティップセクションのファストテーパーを採用し、低伸度ラインを組み合わせることで、即掛けが可能になる攻撃的モデル。中量級ルアーの巻きをメインに操作系ルアーも扱いやすいオールマイティーさも併せ持つ。</v>
       </c>
+      <c r="AH434" t="str">
+        <v/>
+      </c>
+      <c r="AI434" t="str">
+        <v/>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
@@ -46435,6 +49039,12 @@
       <c r="AG435" t="str">
         <v>キャストしやすいソリッドティップショートロッド</v>
       </c>
+      <c r="AH435" t="str">
+        <v/>
+      </c>
+      <c r="AI435" t="str">
+        <v/>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
@@ -46536,6 +49146,12 @@
       <c r="AG436" t="str">
         <v>携帯性抜群4ピースモデル</v>
       </c>
+      <c r="AH436" t="str">
+        <v/>
+      </c>
+      <c r="AI436" t="str">
+        <v/>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
@@ -46637,6 +49253,12 @@
       <c r="AG437" t="str">
         <v>携帯性抜群4ピースモデル</v>
       </c>
+      <c r="AH437" t="str">
+        <v/>
+      </c>
+      <c r="AI437" t="str">
+        <v/>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
@@ -46738,6 +49360,12 @@
       <c r="AG438" t="str">
         <v>しなやかで乗りのよいレギュラーテーパー</v>
       </c>
+      <c r="AH438" t="str">
+        <v/>
+      </c>
+      <c r="AI438" t="str">
+        <v/>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
@@ -46839,6 +49467,12 @@
       <c r="AG439" t="str">
         <v>幅広く使えるベーシックモデル</v>
       </c>
+      <c r="AH439" t="str">
+        <v/>
+      </c>
+      <c r="AI439" t="str">
+        <v/>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
@@ -46940,6 +49574,12 @@
       <c r="AG440" t="str">
         <v>幅広く使えるベーシックモデル</v>
       </c>
+      <c r="AH440" t="str">
+        <v/>
+      </c>
+      <c r="AI440" t="str">
+        <v/>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
@@ -47041,6 +49681,12 @@
       <c r="AG441" t="str">
         <v>大型ルアーも使いやすいマルチモデル</v>
       </c>
+      <c r="AH441" t="str">
+        <v/>
+      </c>
+      <c r="AI441" t="str">
+        <v/>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
@@ -47142,6 +49788,12 @@
       <c r="AG442" t="str">
         <v>ロッド操作しやすいミノーイング対応モデル</v>
       </c>
+      <c r="AH442" t="str">
+        <v/>
+      </c>
+      <c r="AI442" t="str">
+        <v/>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
@@ -47243,6 +49895,12 @@
       <c r="AG443" t="str">
         <v>食い込み抜群ソリッドティップ仕様</v>
       </c>
+      <c r="AH443" t="str">
+        <v/>
+      </c>
+      <c r="AI443" t="str">
+        <v/>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
@@ -47344,6 +50002,12 @@
       <c r="AG444" t="str">
         <v>沖のポイントを狙えるロングキャストモデル</v>
       </c>
+      <c r="AH444" t="str">
+        <v/>
+      </c>
+      <c r="AI444" t="str">
+        <v/>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
@@ -47445,6 +50109,12 @@
       <c r="AG445" t="str">
         <v>源流域から渓流域で、正確なキャストでポイントを攻略するショートレングスモデル。</v>
       </c>
+      <c r="AH445" t="str">
+        <v/>
+      </c>
+      <c r="AI445" t="str">
+        <v/>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
@@ -47546,6 +50216,12 @@
       <c r="AG446" t="str">
         <v>渓流域から里川などの中流域まで使えるオールラウンドモデル。</v>
       </c>
+      <c r="AH446" t="str">
+        <v/>
+      </c>
+      <c r="AI446" t="str">
+        <v/>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
@@ -47647,6 +50323,12 @@
       <c r="AG447" t="str">
         <v>渓流域から中流域まで使用でき、大型魚まで対応するモデル。</v>
       </c>
+      <c r="AH447" t="str">
+        <v/>
+      </c>
+      <c r="AI447" t="str">
+        <v/>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
@@ -47748,6 +50430,12 @@
       <c r="AG448" t="str">
         <v>渓流域から本流域まで幅広く使用でき、ロングキャストも可能なモデル。</v>
       </c>
+      <c r="AH448" t="str">
+        <v/>
+      </c>
+      <c r="AI448" t="str">
+        <v/>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
@@ -47849,6 +50537,12 @@
       <c r="AG449" t="str">
         <v>渓流域から本流域で、不意の大物とのやり取りにも対応したロングキャストモデル。</v>
       </c>
+      <c r="AH449" t="str">
+        <v/>
+      </c>
+      <c r="AI449" t="str">
+        <v/>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
@@ -47950,6 +50644,12 @@
       <c r="AG450" t="str">
         <v>源流域から渓流域で、手返しよく且つ正確なキャストを可能にするベイトモデル。</v>
       </c>
+      <c r="AH450" t="str">
+        <v/>
+      </c>
+      <c r="AI450" t="str">
+        <v/>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
@@ -48051,6 +50751,12 @@
       <c r="AG451" t="str">
         <v>渓流域から中流域にてミノーを軸にあらゆるルアーをこなすオールマイティーモデル。</v>
       </c>
+      <c r="AH451" t="str">
+        <v/>
+      </c>
+      <c r="AI451" t="str">
+        <v/>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
@@ -48152,6 +50858,12 @@
       <c r="AG452" t="str">
         <v>渓流域やリバータイプの管理釣り場に最適なアイテム近距離のラインコントロールがしやすいロッドアクションフックサイズ#12～#18位のドライフライを中心とした釣りに向いている</v>
       </c>
+      <c r="AH452" t="str">
+        <v/>
+      </c>
+      <c r="AI452" t="str">
+        <v/>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
@@ -48253,6 +50965,12 @@
       <c r="AG453" t="str">
         <v>渓流から中流、ポンドタイプの管理釣り場でも使えるオールラウンダー中距離域で安定したループを形成しやすいロッドアクションフックサイズ#8～#16位のドライは勿論、ニンフフィッシングにも最適</v>
       </c>
+      <c r="AH453" t="str">
+        <v/>
+      </c>
+      <c r="AI453" t="str">
+        <v/>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
@@ -48354,6 +51072,12 @@
       <c r="AG454" t="str">
         <v>ポンドタイプの管理釣り場で活躍。キャスティングの基礎を覚えるには最適。近距離から遠投までラインの重さを感じて投げやすいアクションで、ドライフライは勿論、大型のニンフやウェット、マーカーを付けたニンフフィッシングなどに最適。</v>
       </c>
+      <c r="AH454" t="str">
+        <v/>
+      </c>
+      <c r="AI454" t="str">
+        <v/>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
@@ -48455,6 +51179,12 @@
       <c r="AG455" t="str">
         <v>湾岸部や漁港内などの使用を想定したショートレングスモデル。ショートレングス且つ素直に曲がり込むテーパーは誰もが投げやすく、そしてスムーズなやり取り、取り込みを約束する2ピースモデル。</v>
       </c>
+      <c r="AH455" t="str">
+        <v/>
+      </c>
+      <c r="AI455" t="str">
+        <v/>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
@@ -48556,6 +51286,12 @@
       <c r="AG456" t="str">
         <v>あらゆるフィールドで活躍するオールラウンドモデル。軽い力でもウキルアーを遠投が可能なテーパーを採用。また食い渋り時に有効なウキフカセ釣法にも対応するソフトなティップを併せ持つ。</v>
       </c>
+      <c r="AH456" t="str">
+        <v/>
+      </c>
+      <c r="AI456" t="str">
+        <v/>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
@@ -48657,6 +51393,12 @@
       <c r="AG457" t="str">
         <v>磯場の立ち込みやウキルアーの長い仕掛けを遠投し、沖を回遊するフレッシュなサケを狙い、確実なフッキングで掛けるバットと食い込みの良いティップを併せ持つ。一日軽快に扱える軽量性と投げやすいテーパーも特徴の遠投モデル。</v>
       </c>
+      <c r="AH457" t="str">
+        <v/>
+      </c>
+      <c r="AI457" t="str">
+        <v/>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
@@ -48758,6 +51500,12 @@
       <c r="AG458" t="str">
         <v>携帯性を活かして源流域へアプローチし、軽量ルアーを使用しアキュラシーキャストでピンスポットを攻略するモデル。</v>
       </c>
+      <c r="AH458" t="str">
+        <v/>
+      </c>
+      <c r="AI458" t="str">
+        <v/>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
@@ -48859,6 +51607,12 @@
       <c r="AG459" t="str">
         <v>機動性に優れたテレスコモデル。ショートレングスを活かした、小渓流のピンスポット攻略に最適なモデル。源流域への遡行にもオススメ</v>
       </c>
+      <c r="AH459" t="str">
+        <v/>
+      </c>
+      <c r="AI459" t="str">
+        <v/>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
@@ -48960,6 +51714,12 @@
       <c r="AG460" t="str">
         <v>ロッドアクションにこだわった3ピースモデル。源流域から渓流まで楽しめ、アキュラシーキャストが決まるショートレングスバーサタイルモデル。</v>
       </c>
+      <c r="AH460" t="str">
+        <v/>
+      </c>
+      <c r="AI460" t="str">
+        <v/>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
@@ -49061,6 +51821,12 @@
       <c r="AG461" t="str">
         <v>源流域から渓流域に対応し、ミノーを中心としたルアーの操作性を高めたショートレングスモデル。</v>
       </c>
+      <c r="AH461" t="str">
+        <v/>
+      </c>
+      <c r="AI461" t="str">
+        <v/>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
@@ -49162,6 +51928,12 @@
       <c r="AG462" t="str">
         <v>機動性に優れたテレスコモデル。あらゆる場所に携行し、幅広いルアーを軽快に楽しめるスタンダードモデル。</v>
       </c>
+      <c r="AH462" t="str">
+        <v/>
+      </c>
+      <c r="AI462" t="str">
+        <v/>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
@@ -49263,6 +52035,12 @@
       <c r="AG463" t="str">
         <v>ミノーを中心としたルアーを快適に操り、尺越えのトラウトにも余裕をもって対峙可能なテレスコモデル。</v>
       </c>
+      <c r="AH463" t="str">
+        <v/>
+      </c>
+      <c r="AI463" t="str">
+        <v/>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
@@ -49364,6 +52142,12 @@
       <c r="AG464" t="str">
         <v>ロッドアクションにこだわった3ピースモデル。渓流から里川の開けた場所での遠投も可能なバーサタイルモデル。</v>
       </c>
+      <c r="AH464" t="str">
+        <v/>
+      </c>
+      <c r="AI464" t="str">
+        <v/>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
@@ -49465,6 +52249,12 @@
       <c r="AG465" t="str">
         <v>渓流域から中流域まで広く対応し、ミノーを中心としたルアーの操作性を高め、流心で掛けた尺上サイズとも対峙できるモデル。</v>
       </c>
+      <c r="AH465" t="str">
+        <v/>
+      </c>
+      <c r="AI465" t="str">
+        <v/>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
@@ -49566,6 +52356,12 @@
       <c r="AG466" t="str">
         <v>機動性に優れたテレスコモデル。ミノーを中心に、中流域での遠投も可能なロングディスタンスモデル。</v>
       </c>
+      <c r="AH466" t="str">
+        <v/>
+      </c>
+      <c r="AI466" t="str">
+        <v/>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
@@ -49667,6 +52463,12 @@
       <c r="AG467" t="str">
         <v>湖沼や中流域～本流域に対応し、ミノーやスプーンを用い、湖沼では遠投、流れの強い河川ではパワー負けすることなく攻略が可能なモデル。</v>
       </c>
+      <c r="AH467" t="str">
+        <v/>
+      </c>
+      <c r="AI467" t="str">
+        <v/>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
@@ -49768,6 +52570,12 @@
       <c r="AG468" t="str">
         <v>源流域から渓流域にて、正確なキャストでポイントを射貫き、狙った魚を確実に仕留めるショートレングスベイトモデル。</v>
       </c>
+      <c r="AH468" t="str">
+        <v/>
+      </c>
+      <c r="AI468" t="str">
+        <v/>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
@@ -49869,6 +52677,12 @@
       <c r="AG469" t="str">
         <v>ロッドアクションにこだわった3ピースモデル。源流域から渓流域にて、手返しの良いピンスポットキャストを可能にするショートレングスベイトモデル。</v>
       </c>
+      <c r="AH469" t="str">
+        <v/>
+      </c>
+      <c r="AI469" t="str">
+        <v/>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
@@ -49970,6 +52784,12 @@
       <c r="AG470" t="str">
         <v>機動性に優れたテレスコモデル。ピンポイントを手返しよく攻略できるベイトモデル。源流域への遡行にもオススメ。</v>
       </c>
+      <c r="AH470" t="str">
+        <v/>
+      </c>
+      <c r="AI470" t="str">
+        <v/>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
@@ -50071,6 +52891,12 @@
       <c r="AG471" t="str">
         <v>ロッドアクションにこだわった3ピースモデル。渓流から里川でのピンポイントや、開けたシチュエーションでのロングキャストも可能なベイトモデル。</v>
       </c>
+      <c r="AH471" t="str">
+        <v/>
+      </c>
+      <c r="AI471" t="str">
+        <v/>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
@@ -50172,6 +52998,12 @@
       <c r="AG472" t="str">
         <v>釣場でも目を引く赤いリールシート、バットカラーを採用。トラウトフィッシングを楽しく演出。</v>
       </c>
+      <c r="AH472" t="str">
+        <v/>
+      </c>
+      <c r="AI472" t="str">
+        <v/>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
@@ -50273,6 +53105,12 @@
       <c r="AG473" t="str">
         <v>釣場でも目を引く赤いリールシート、バットカラーを採用。トラウトフィッシングを楽しく演出。</v>
       </c>
+      <c r="AH473" t="str">
+        <v/>
+      </c>
+      <c r="AI473" t="str">
+        <v/>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
@@ -50374,6 +53212,12 @@
       <c r="AG474" t="str">
         <v>操作性に優れた形状のグリップに、シャンパンゴールドのメタルパーツを配置。</v>
       </c>
+      <c r="AH474" t="str">
+        <v/>
+      </c>
+      <c r="AI474" t="str">
+        <v/>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
@@ -50475,6 +53319,12 @@
       <c r="AG475" t="str">
         <v>操作性に優れた形状のグリップに、シャンパンゴールドのメタルパーツを配置。</v>
       </c>
+      <c r="AH475" t="str">
+        <v/>
+      </c>
+      <c r="AI475" t="str">
+        <v/>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
@@ -50576,6 +53426,12 @@
       <c r="AG476" t="str">
         <v>操作性に優れた形状のグリップに、シャンパンゴールドのメタルパーツを配置。</v>
       </c>
+      <c r="AH476" t="str">
+        <v/>
+      </c>
+      <c r="AI476" t="str">
+        <v/>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
@@ -50677,6 +53533,12 @@
       <c r="AG477" t="str">
         <v>マイクロスプーンなどの軽量ルアーも投げやすいレギュラーテーパーモデル</v>
       </c>
+      <c r="AH477" t="str">
+        <v/>
+      </c>
+      <c r="AI477" t="str">
+        <v/>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
@@ -50778,6 +53640,12 @@
       <c r="AG478" t="str">
         <v>スプーンからプラグまで使えるオールマイティーモデル</v>
       </c>
+      <c r="AH478" t="str">
+        <v/>
+      </c>
+      <c r="AI478" t="str">
+        <v/>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
@@ -50879,6 +53747,12 @@
       <c r="AG479" t="str">
         <v>ミノーやプラグを操作しやすく、重めのルアーにも対応したモデル</v>
       </c>
+      <c r="AH479" t="str">
+        <v/>
+      </c>
+      <c r="AI479" t="str">
+        <v/>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
@@ -50980,6 +53854,12 @@
       <c r="AG480" t="str">
         <v>小規模ポンドから大規模ポンド、レギュラーサイズから大型のトラウトまで、あらゆるシチュエーションに対応するモデル</v>
       </c>
+      <c r="AH480" t="str">
+        <v/>
+      </c>
+      <c r="AI480" t="str">
+        <v/>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
@@ -51081,6 +53961,12 @@
       <c r="AG481" t="str">
         <v>大規模ポンドや大型トラウトのいるポンドで、ルアーを遠投し沖のスレていないトラウトを狙うのにオススメのモデル</v>
       </c>
+      <c r="AH481" t="str">
+        <v/>
+      </c>
+      <c r="AI481" t="str">
+        <v/>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
@@ -51182,6 +54068,12 @@
       <c r="AG482" t="str">
         <v>410UL-Sはより繊細なゲームを制するためのスーパーショートフィネスモデル。アンダー1gの超軽量ジグヘッドを操り、ナチュラルに漂わせてアジに口を使わせることができる。近距離戦を得意とし、湾内や漁港に居つく豆アジや低活性のアジはもちろん、微かな流れや潮のヨレを感じて攻略する繊細なアジングゲームも展開可能。</v>
       </c>
+      <c r="AH482" t="str">
+        <v/>
+      </c>
+      <c r="AI482" t="str">
+        <v/>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
@@ -51283,6 +54175,12 @@
       <c r="AG483" t="str">
         <v>48L-Sは繊細かつシャープな掛け感にこだわったスーパーショートモデル。1g前後の軽量ジグヘッドやメタルジグを持ち前のショートレングスで軽快に操り、細かいシェイクなどの誘いを正確に演出。近距離戦を得意とし、湾内や漁港に居つく豆アジや低活性のアジはもちろん、微かな流れや潮のヨレを感じて攻略する繊細なアジングゲームも展開可能。</v>
       </c>
+      <c r="AH483" t="str">
+        <v/>
+      </c>
+      <c r="AI483" t="str">
+        <v/>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
@@ -51384,6 +54282,12 @@
       <c r="AG484" t="str">
         <v>54L-Tはチューブラーティップならではの高い操作性と反響感度を高めたショートモデル。中空構造による軽量感はソリッド穂先とは一線を画しながらも、1g前後の軽量ジグヘッドやメタルジグを思いのまま操作できる。光量が多く、飛距離が必要な常夜灯の明暗部につくアジや、シャローのボトム近辺をリフト＆フォールで攻略するテンポの速いアジングゲームにもお勧め。</v>
       </c>
+      <c r="AH484" t="str">
+        <v/>
+      </c>
+      <c r="AI484" t="str">
+        <v/>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
@@ -51485,6 +54389,12 @@
       <c r="AG485" t="str">
         <v>55L-Sは飛距離と操作性のバランスを追求したショートモデル。1g前後の軽量ジグヘッドやメタルジグを広範囲にキャストしサーチできる飛距離と、張りのあるソリッドティップにより細かいシェイクなどの誘いを的確に演出。中近距離戦を得意とし、湾内や常夜灯まわりの明暗部はもちろん、微かな流れや潮のヨレを感じて攻略する繊細なアジングゲームも展開可能。</v>
       </c>
+      <c r="AH485" t="str">
+        <v/>
+      </c>
+      <c r="AI485" t="str">
+        <v/>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
@@ -51586,6 +54496,12 @@
       <c r="AG486" t="str">
         <v>64UL-Sは漁港内を手早く広く探るのに欠かせないスタンダードライトモデル。アンダー1gの超軽量ジグヘッドを遠投し、やる気のあるフレッシュなアジをテンポよく掛けていくことができる。しなやかに、かつ張りのあるブランクで中遠距離戦を得意とし、足場の高い堤防はもちろん、常夜灯の明暗部外で捕食してくるアジのアタリを即掛けしていくハイスピードなアジングゲームも展開可能。</v>
       </c>
+      <c r="AH486" t="str">
+        <v/>
+      </c>
+      <c r="AI486" t="str">
+        <v/>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
@@ -51687,6 +54603,12 @@
       <c r="AG487" t="str">
         <v>66L-Sはジグ単アジングゲームにおいて最もポピュラーなスタンダードモデル。1g前後のジグヘッドを中心に、スプリットショットやメタルジグなどの幅広いルアーに対応する。足場の高い堤防などでも操作が行いやすく、ストロークを活かしたリフト＆フォールで、アジが追尾してくるレンジを広範囲に探りながら誘い、バイトを弾かずオートマチックなフッキングが決まるのも魅力。</v>
       </c>
+      <c r="AH487" t="str">
+        <v/>
+      </c>
+      <c r="AI487" t="str">
+        <v/>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
@@ -51788,6 +54710,12 @@
       <c r="AG488" t="str">
         <v>711ML-Sは沖の流れやブレイクを制するパワーロングモデル。バイトを弾かず食い込ませるしなやかな穂先と、重量のある抵抗の大きいリグにも負けず遠投できる強いバットで、狙いのバージンスポットを射抜く。リグの操作性に優れ、遠投先でのフッキングが決まる張りとパワーのあるベリーにチューニングしており、キャロやフロートを的確に操ることができる。遠投が必要なサーフアジングや、ジグ単では届かないポイントにリグを届けるシチュエーションにも対応。</v>
       </c>
+      <c r="AH488" t="str">
+        <v/>
+      </c>
+      <c r="AI488" t="str">
+        <v/>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
@@ -51889,6 +54817,12 @@
       <c r="AG489" t="str">
         <v/>
       </c>
+      <c r="AH489" t="str">
+        <v/>
+      </c>
+      <c r="AI489" t="str">
+        <v/>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
@@ -51990,6 +54924,12 @@
       <c r="AG490" t="str">
         <v/>
       </c>
+      <c r="AH490" t="str">
+        <v/>
+      </c>
+      <c r="AI490" t="str">
+        <v/>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
@@ -52091,6 +55031,12 @@
       <c r="AG491" t="str">
         <v/>
       </c>
+      <c r="AH491" t="str">
+        <v/>
+      </c>
+      <c r="AI491" t="str">
+        <v/>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
@@ -52192,6 +55138,12 @@
       <c r="AG492" t="str">
         <v/>
       </c>
+      <c r="AH492" t="str">
+        <v/>
+      </c>
+      <c r="AI492" t="str">
+        <v/>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
@@ -52293,6 +55245,12 @@
       <c r="AG493" t="str">
         <v/>
       </c>
+      <c r="AH493" t="str">
+        <v/>
+      </c>
+      <c r="AI493" t="str">
+        <v/>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
@@ -52394,6 +55352,12 @@
       <c r="AG494" t="str">
         <v>的確なルアー操作でメバルを虜にするショートロッド。 プラグからワームまでルアーを選ばないので、幅広い状況に対応できる。</v>
       </c>
+      <c r="AH494" t="str">
+        <v/>
+      </c>
+      <c r="AI494" t="str">
+        <v/>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
@@ -52495,6 +55459,12 @@
       <c r="AG495" t="str">
         <v>シンキングペンシルなどのプラグや、ジグヘッドリグを遠投し、広範囲のメバルを探るロングロッド。感度と操作性が大きく向上し、遠くのマイクロルアーの状況も的確に把握できる。</v>
       </c>
+      <c r="AH495" t="str">
+        <v/>
+      </c>
+      <c r="AI495" t="str">
+        <v/>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
@@ -52596,6 +55566,12 @@
       <c r="AG496" t="str">
         <v>大型のフロートや、メタルジグなどで大型メバルを狙うためのハイパワーロッド。 ルアーの対応力が広いので、メバル以外のターゲットにも多彩に対応する懐の広さを持つ。</v>
       </c>
+      <c r="AH496" t="str">
+        <v/>
+      </c>
+      <c r="AI496" t="str">
+        <v/>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
@@ -52697,6 +55673,12 @@
       <c r="AG497" t="str">
         <v>オカッパリ、ボート問わず自在なキャストでアプローチするショートロッド。壁際の明暗やシモリ際にプラグやジグヘッドリグを撃ち込める。</v>
       </c>
+      <c r="AH497" t="str">
+        <v/>
+      </c>
+      <c r="AI497" t="str">
+        <v/>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
@@ -52798,6 +55780,12 @@
       <c r="AG498" t="str">
         <v>ベイトタックルのメリットはアキュラシー。軽量プラグやジグヘッドリグを正確に沖のシモリや潮目などへ送り届けることができる。</v>
       </c>
+      <c r="AH498" t="str">
+        <v/>
+      </c>
+      <c r="AI498" t="str">
+        <v/>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
@@ -52899,6 +55887,12 @@
       <c r="AG499" t="str">
         <v>シャローエリアのメインアイテムとなるショートモデル。軽量なメガトップR穂先を搭載。自在にラインテンションを操ってワームに生命感を注ぎ込むと同時に、即アワセを実現する。</v>
       </c>
+      <c r="AH499" t="str">
+        <v/>
+      </c>
+      <c r="AI499" t="str">
+        <v/>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
@@ -53000,6 +55994,12 @@
       <c r="AG500" t="str">
         <v>ディープエリアで真価を発揮するパワーモデル。棚を広く、手返し良く探る調子を実現。レングスを長めにしつつも、軽量なメガトップRの穂先と張りのある穂持ちでレスポンスを向上。長さを感じさせずワームを自然に操れる。</v>
       </c>
+      <c r="AH500" t="str">
+        <v/>
+      </c>
+      <c r="AI500" t="str">
+        <v/>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
@@ -53101,6 +56101,12 @@
       <c r="AG501" t="str">
         <v>振動増幅効果を持つＳＭＴ搭載のベイトモデル。深い場所で真価を発揮し、二枚潮などのシチュエーションでもアタリを明確に感じ取ることができる。粘りのあるブランクにより、長時間のファイトでもアジをバラしにくい。</v>
       </c>
+      <c r="AH501" t="str">
+        <v/>
+      </c>
+      <c r="AI501" t="str">
+        <v/>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
@@ -53202,6 +56208,12 @@
       <c r="AG502" t="str">
         <v>チューブラーの反響感度を最大限発揮させるチューニングを施したジグ単専用ロッド。極細チューブラーティップが織りなす軽さと絶妙に穂先にモタれる手感度は、まさに水中をイメージできる高感度ソナー。ULクラスのしなやかさからは想像できないシャープに誘って掛ける使用感のブランクは、燕のような軽快な身のこなしで、俊敏かつ正確にターゲットを仕留めることが出来る。</v>
       </c>
+      <c r="AH502" t="str">
+        <v/>
+      </c>
+      <c r="AI502" t="str">
+        <v/>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
@@ -53303,6 +56315,12 @@
       <c r="AG503" t="str">
         <v>超軽量なジグヘッドリグ専用ロッド。マイクロルアーの状態を正確に把握し、的確に操作する。違和感なく食い込ませ、シャープに掛ける。そんな相反する要素を究極まで追い求めたブランクは、しなやかさと張りを理想的なバランスで兼ね備える。マイクロゲームの理想形を追求した華麗なブランクは、美しいベンドカーブでアジ・メバルを往なす。</v>
       </c>
+      <c r="AH503" t="str">
+        <v/>
+      </c>
+      <c r="AI503" t="str">
+        <v/>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
@@ -53404,6 +56422,12 @@
       <c r="AG504" t="str">
         <v>掛け調子のジグヘッドリグロッドのスタンダードとして、ジグヘッドリグの釣りの醍醐味であるルアーの操作性と、リニアな掛け感を突き詰めた。ジグヘッドリグやスプリットショット、メタルジグなどを駆使し、積極的に誘って掛けるアクティブなゲーム展開を得意とする。凛とした張りのあるブランクが、抜群の操作性と切れのあるアワセでゲームの主導権を握る。</v>
       </c>
+      <c r="AH504" t="str">
+        <v/>
+      </c>
+      <c r="AI504" t="str">
+        <v/>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
@@ -53505,6 +56529,12 @@
       <c r="AG505" t="str">
         <v>鋭敏なチューブラーティップと短めのレングスが冴えわたる感度と操作性実現。シンペンやトップといったプラグから、メタルジグ、ワームまで幅広いルアーを自在に操り、ダイレクトにアジ・メバルと対峙するためのテクニカルモデルあらゆるルアーを駆使して状況にアジャストし、アタリを瞬時に掛ける一方、ファイトでは粘り調子に性格を変えて大物の引きを制御。攻めと柔軟性を合わせ持つ。</v>
       </c>
+      <c r="AH505" t="str">
+        <v/>
+      </c>
+      <c r="AI505" t="str">
+        <v/>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
@@ -53606,6 +56636,12 @@
       <c r="AG506" t="str">
         <v>しなやかながら張りと粘りのあるブランクが、小型プラグやジグヘッドリグを遠投、ルアーの動きに追従し、わずかな流れの変化をも捉える。楽器が絃の張りを変えて旋律を奏でるように、ラインテンションを操ってルアーの動きや軌道を自在に変える。リトリーブ、ドリフト、ステイ……ルアーに生命を宿すかの如く、自然に波間を漂わせてアジ・メバルを誘惑する。</v>
       </c>
+      <c r="AH506" t="str">
+        <v/>
+      </c>
+      <c r="AI506" t="str">
+        <v/>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
@@ -53707,6 +56743,12 @@
       <c r="AG507" t="str">
         <v>メタルジグやプラグに息吹を吹き込むアクションを実現しながら、ストラクチャーから大型メバルを瞬時に引き離す剛胆なベンドカーブを追求した最高峰ロッド。ルアーアクションまでのタイムラグを極限まで減らしたハイレスポンスな使用感に加え、スレた大型メバルのショートバイトも確実にフッキングに持ち込みながら、余裕を持ったやり取りが可能。</v>
       </c>
+      <c r="AH507" t="str">
+        <v/>
+      </c>
+      <c r="AI507" t="str">
+        <v/>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
@@ -53808,6 +56850,12 @@
       <c r="AG508" t="str">
         <v>68L-Tは鋭敏なチューブラーティップを取り回しのよいレングスで操るショートモデル。レスポンスに優れたティップでフィネスよりのジグヘッドリグを操り、ナチュラルに漂わせてメバルに口を使わせることができる。地磯周りや足場の低い堤防などをフィネスリグでテンポよくランガンしていくスタイルにも最適で、短時間でコンディションを把握するのにもおススメ。</v>
       </c>
+      <c r="AH508" t="str">
+        <v/>
+      </c>
+      <c r="AI508" t="str">
+        <v/>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
@@ -53909,6 +56957,12 @@
       <c r="AG509" t="str">
         <v>610L-Sは繊細なソリッドティップを取り回しのよいレングスで操るショートモデル。足場の低い堤防や小磯で活躍する操作性に加え、しなやかで食い込みに優れたティップによりバイトを弾きにくい。ジグヘッドリグやプラグをメインとしたナイトゲームはもちろん、ルアーをロッドで細かく動かして誘うことが多いデイゲームにも最適。</v>
       </c>
+      <c r="AH509" t="str">
+        <v/>
+      </c>
+      <c r="AI509" t="str">
+        <v/>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
@@ -54010,6 +57064,12 @@
       <c r="AG510" t="str">
         <v>72L-Tはチューブラーティップならではの高い操作性と反響感度を高めたライトスタンダードモデル。軽量ジグヘッドリグやプラグを遠投し、ロッドアクションの支点を高くして誘う釣法にも完全対応した設計。レングスをいかし、足元のストラクチャーをかわしたり、飛距離が必要なポイントでフィネスリグをテンポよく通していくスタイルにも対応可能。</v>
       </c>
+      <c r="AH510" t="str">
+        <v/>
+      </c>
+      <c r="AI510" t="str">
+        <v/>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
@@ -54111,6 +57171,12 @@
       <c r="AG511" t="str">
         <v>74UL-Sは繊細なソリッドティップによってメバルの小気味よいアタリをオートマチックに乗せられるオールラウンドモデル。使用頻度の高い1g前後の小型ジグヘッドリグや、3g前後の小型プラグを遠投し、漂わせてヒットさせるメバルゲームの基本操作までしっかりと対応する。</v>
       </c>
+      <c r="AH511" t="str">
+        <v/>
+      </c>
+      <c r="AI511" t="str">
+        <v/>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
@@ -54212,6 +57278,12 @@
       <c r="AG512" t="str">
         <v>710ML-Tはジグヘッドリグやプラグ、フロートリグで沖のブレイクやボトムに潜むメバルを狙うためのパワーモデル。小磯やサーフ、ゴロタ場などの大場所で、遠投に必要なブランクの張り、ルアーを操作するティップのバランスを追求したことで、ショートロッドでは届かないポイントを攻略可能。</v>
       </c>
+      <c r="AH512" t="str">
+        <v/>
+      </c>
+      <c r="AI512" t="str">
+        <v/>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
@@ -54313,6 +57385,12 @@
       <c r="AG513" t="str">
         <v>83M-Tはボトムに潜む大型メバルを狙うためのハイパワーモデル。磯やサーフ、ゴロタ場などの大場所で、重めのジグヘッドリグや大型プラグ、フロートリグで沖のブレイクや激流といったシーンをメインに活躍する。メバルだけにとどまらず、フィールドを共にするシーバスやクロダイなどが混在するシチュエーションでも活躍する。</v>
       </c>
+      <c r="AH513" t="str">
+        <v/>
+      </c>
+      <c r="AI513" t="str">
+        <v/>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
@@ -54414,6 +57492,12 @@
       <c r="AG514" t="str">
         <v>73ULB-Tは軽量プラグやジグヘッドリグを正確にキャストし、パーミングによる手感度まで求めたベイトフィネスモデル。レギュラーテーパーよりに設計したブランクは、しなやかなベンドカーブを描き、投げやすく扱いやすい設計。さらにベイトモデルならではの手全体に響く感度は、カーボンで一体成形したグリップエンドと相性抜群で、ボトムタッチや瞬間的なアタリをアングラーへ確実に伝達する。</v>
       </c>
+      <c r="AH514" t="str">
+        <v/>
+      </c>
+      <c r="AI514" t="str">
+        <v/>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
@@ -54515,6 +57599,12 @@
       <c r="AG515" t="str">
         <v>76LB-Tはフロートやキャロなどの遠投から、プラグやメタルジグを幅広く使えるオールラウンドベイトモデル。レギュラーテーパーのように投げやすく、ファストテーパーのような操作性を追求したブランクは、キレのあるアクションを実現し、パワーのあるバットで大型メバルも根から引きはがす。さらにベイトモデルならではの手全体に響く感度は、カーボンで一体成形したグリップエンドと相性抜群で、ボトムタッチや瞬間的なアタリをアングラーへ確実に伝達する。</v>
       </c>
+      <c r="AH515" t="str">
+        <v/>
+      </c>
+      <c r="AI515" t="str">
+        <v/>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
@@ -54616,6 +57706,12 @@
       <c r="AG516" t="str">
         <v>操作性の高いショートモデル。ジグヘッドリグやプラグを細かくコントロールするのに最適。幅広いルアーウエイトを快適に扱えるように調整した張りと粘りにより、アジやメバルをはじめとするターゲットに最適。ボートからのライトゲームにも対応する。</v>
       </c>
+      <c r="AH516" t="str">
+        <v/>
+      </c>
+      <c r="AI516" t="str">
+        <v/>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
@@ -54717,6 +57813,12 @@
       <c r="AG517" t="str">
         <v>遠投に適したレングスと、食い込みのよいしなやかな穂先を組み合わせた軽量リグの遠投用ロッド。ジグヘッドリグをはじめ、シンキングペンシルやミノー、小型のキャロの釣りを得意とする。メバルやアジをはじめとするあらゆるターゲットに最適。足場の高い堤防や港湾部では欠かせない。</v>
       </c>
+      <c r="AH517" t="str">
+        <v/>
+      </c>
+      <c r="AI517" t="str">
+        <v/>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
@@ -54818,6 +57920,12 @@
       <c r="AG518" t="str">
         <v>感度と操作性に優れるしなやかなチューブラーティップの遠投釣法用ロッド。重めのジグヘッドリグやキャロ、フロートリグに最適。強いバットを持つので、メバルの他にクロダイやシーバスが混じりやすいイカや稚アユパターンのプラッギングや、根魚が混じりやすいアジのメタルジグ釣法などにおいても頼もしい一本。</v>
       </c>
+      <c r="AH518" t="str">
+        <v/>
+      </c>
+      <c r="AI518" t="str">
+        <v/>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
@@ -54919,6 +58027,12 @@
       <c r="AG519" t="str">
         <v>港内を主戦場とするショートモデル。短くしたことで水中の状況を把握しやすく、ルアーを的確に操ることができる。軽量なジグヘッドリグをエサのように漂わせて釣るスタイルに最適。</v>
       </c>
+      <c r="AH519" t="str">
+        <v/>
+      </c>
+      <c r="AI519" t="str">
+        <v/>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
@@ -55020,6 +58134,12 @@
       <c r="AG520" t="str">
         <v>アジ・メバルのオールラウンドモデル。軽量なジグヘッドリグやメタルジグ、プラグなどに対応し、漁港や小磯など、幅広い釣り場に対応できる。初めての1本に最適。</v>
       </c>
+      <c r="AH520" t="str">
+        <v/>
+      </c>
+      <c r="AI520" t="str">
+        <v/>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
@@ -55121,6 +58241,12 @@
       <c r="AG521" t="str">
         <v>レスポンスが高いチューブラー穂先によってルアー操作をしやすいので、細かなシェイクやトゥイッチなどで積極的に誘いを入れる釣りに最適。手に響くようなアタリも魅力。</v>
       </c>
+      <c r="AH521" t="str">
+        <v/>
+      </c>
+      <c r="AI521" t="str">
+        <v/>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
@@ -55222,6 +58348,12 @@
       <c r="AG522" t="str">
         <v>小型のプラグやジグヘッドリグを遠投して広く探り、魚の居場所を探し出す展開を得意とする。繊細な穂先を持つ乗せ調子で、オートマチックなフッキングが心地よい。</v>
       </c>
+      <c r="AH522" t="str">
+        <v/>
+      </c>
+      <c r="AI522" t="str">
+        <v/>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
@@ -55323,6 +58455,12 @@
       <c r="AG523" t="str">
         <v>スプリットやキャロに対応する遠投モデル。全体的に張りのあるブランクスによって、水中の重いリグもメリハリをつけて操作できる。</v>
       </c>
+      <c r="AH523" t="str">
+        <v/>
+      </c>
+      <c r="AI523" t="str">
+        <v/>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
@@ -55424,6 +58562,12 @@
       <c r="AG524" t="str">
         <v>足場の低い堤防や小磯で活躍するソリッドティップのショートモデル。操作性が高く、小技が効きやすいので軽量ジグヘッドリグやプラグをメインとしたナイトゲームはもちろん、ルアーをロッドで細かく動かして誘うことが多いデイゲームにも最適。ボートゲームにも対応する。</v>
       </c>
+      <c r="AH524" t="str">
+        <v/>
+      </c>
+      <c r="AI524" t="str">
+        <v/>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
@@ -55525,6 +58669,12 @@
       <c r="AG525" t="str">
         <v>しなやかなソリッドティップによってメバルの小気味よいアタリをオートマチックに乗せられるオールラウンドモデル。使用頻度の高い1g前後の小型ジグヘッドリグや、3g前後の小型プラグを遠投し、漂わせてヒットさせるメバルゲームの基本操作をしっかりと体現できる。</v>
       </c>
+      <c r="AH525" t="str">
+        <v/>
+      </c>
+      <c r="AI525" t="str">
+        <v/>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
@@ -55626,6 +58776,12 @@
       <c r="AG526" t="str">
         <v>操作性の高いチューブラーティップを搭載するハイレスポンスモデル。プラグはもちろん、一般的な5g前後のフロートリグなどを的確に操作できる。癖のないテーパーなので、メタルジグやジグヘッドリグなども幅広くカバー。掛けを重視しつつも掛かると胴に入るテーパーでバレを防ぎたいアングラーにお勧めの1本。</v>
       </c>
+      <c r="AH526" t="str">
+        <v/>
+      </c>
+      <c r="AI526" t="str">
+        <v/>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
@@ -55727,6 +58883,12 @@
       <c r="AG527" t="str">
         <v>小磯やサーフ、ゴロタ場などの大場所で、重めのジグヘッドリグや大型のフロートリグ、大型プラグで沖のブレイクや激流、ボトムに潜む大型メバルを狙うためのハイパワーモデル。メバルだけにとどまらず、フィールドを共にするシーバスやクロダイなどが混じってしまうシチュエーションでも活躍する。</v>
       </c>
+      <c r="AH527" t="str">
+        <v/>
+      </c>
+      <c r="AI527" t="str">
+        <v/>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
@@ -55828,6 +58990,12 @@
       <c r="AG528" t="str">
         <v>漁港内を手早く探るのに欠かせないショートロッド。軽いジグヘッドリグやメタルジグをきびきびと動かして、アジのアタリを即掛けするハイスピードゲームが楽しめる。</v>
       </c>
+      <c r="AH528" t="str">
+        <v/>
+      </c>
+      <c r="AI528" t="str">
+        <v/>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
@@ -55929,6 +59097,12 @@
       <c r="AG529" t="str">
         <v>繊細なゲームを制するためのショートモデル。ターゲットは港内を泳ぐ豆アジや低活性のアジ。水中の状況を的確に把握し、1g前後の軽量なジグヘッドリグを漂わせて口元へ送り込む。</v>
       </c>
+      <c r="AH529" t="str">
+        <v/>
+      </c>
+      <c r="AI529" t="str">
+        <v/>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
@@ -56030,6 +59204,12 @@
       <c r="AG530" t="str">
         <v>漁港でのアジングにおいて最もスタンダードとなるはじめの1本。ジグヘッドリグを中心にスプリットショットやメタルジグなどの幅広いルアーに対応する。足場の高い堤防などでも操作が行いやすい。</v>
       </c>
+      <c r="AH530" t="str">
+        <v/>
+      </c>
+      <c r="AI530" t="str">
+        <v/>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
@@ -56131,6 +59311,12 @@
       <c r="AG531" t="str">
         <v>沖の流れやブレイクを制する遠投モデル。食い込みのよいしなやかな穂先と、遠投に適した強いバッド、操作性に優れる張りのあるベリーを組み合わせており、キャロやフロートを自在に操ることができる。</v>
       </c>
+      <c r="AH531" t="str">
+        <v/>
+      </c>
+      <c r="AI531" t="str">
+        <v/>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
@@ -56232,6 +59418,12 @@
       <c r="AG532" t="str">
         <v>レスポンスに優れたチューブラーティップの遠投モデル。漁港の外面やゴロタ浜、磯などで、重めのフロートやキャロ、メタルジグなどを遠投し、広範囲にいるアジを手返しよく探るスタイルに最適。</v>
       </c>
+      <c r="AH532" t="str">
+        <v/>
+      </c>
+      <c r="AI532" t="str">
+        <v/>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
@@ -56333,6 +59525,12 @@
       <c r="AG533" t="str">
         <v>食い渋る状況下や、ウネリの大きいシチュエーションで活躍するフィネスモデル。柔軟な調子とやや長めのレングスによって、仕掛けをフリーな状態に保つことに長けており、アジに違和感なく口を使わせる。</v>
       </c>
+      <c r="AH533" t="str">
+        <v/>
+      </c>
+      <c r="AI533" t="str">
+        <v/>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
@@ -56434,6 +59632,12 @@
       <c r="AG534" t="str">
         <v>高感度な穂先でアタリを感知し、即掛けに持っていく攻めのハイレスポンスモデル。短めのレングスを使用して、ワームにアクションをつけて積極的にアジを誘い、アジからの信号を明確に感知できるダイレクト感が魅力。</v>
       </c>
+      <c r="AH534" t="str">
+        <v/>
+      </c>
+      <c r="AI534" t="str">
+        <v/>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
@@ -56535,10 +59739,16 @@
       <c r="AG535" t="str">
         <v>重い錘負荷に対応するディープ攻略モデル。深場に潜む大物のアタリを明確に感知。ハイパワーなバットによって、50cm級のモンスターにも対応する。</v>
       </c>
+      <c r="AH535" t="str">
+        <v/>
+      </c>
+      <c r="AI535" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AG535"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AI535"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/daiwa_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_rod_import.xlsx
@@ -455,7 +455,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v>images/daiwa_rods/モアザン ブランジーノ CGSmorethan BRANZINO CGS_morethan_BRANZINO_CGS_94ML_4550133545030.jpg</v>
@@ -490,7 +490,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v>images/daiwa_rods/モアザンMORETHAN_MORETHAN_93MLM_J_4550133452109.jpg</v>
@@ -525,7 +525,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v>images/daiwa_rods/ラブラックス AGS BS（ボートシーバス）LABRAX AGS BS（BOAT SEABASS）_LabraxAGS_BS_64MSQ.jpg</v>
@@ -560,7 +560,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v>images/daiwa_rods/モアザン ブランジーノ EX AGS ベイトモデルMORETHAN BRANZINO EX AGS_MORETHAN_BRANZINO_EX_AGS_80HB_4550133384608.jpg</v>
@@ -595,7 +595,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v>images/daiwa_rods/ラブラックス AGSLABRAX AGS_LabRaxAGS_86ML_1.jpg</v>
@@ -630,7 +630,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v>images/daiwa_rods/モアザン ワイズメンMORETHAN WISEMEN_morethan-WISEMEN_AGS_130M-4.jpg</v>
@@ -665,7 +665,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H8" t="str">
         <v>images/daiwa_rods/スカイハイSKYHIGH_SKYHIGH_90ML_4550133433894.jpg</v>
@@ -700,7 +700,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H9" t="str">
         <v>images/daiwa_rods/モアザン ブランジーノ EX AGSMORETHAN BRANZINO EX AGS_Morethan_Brabzino_EX_AGS_87LML.jpg</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H10" t="str">
         <v>images/daiwa_rods/シーバスフラットXSEABASS FLAT X_SeabassFlatX_86ML.jpg</v>
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H11" t="str">
         <v>images/daiwa_rods/ラテオLATEO_LATEO_96MLMK_4550133384950.jpg</v>
@@ -805,7 +805,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v>images/daiwa_rods/ラテオ BSLATEO BS_LATEO_BS_68MBW_4550133337994.png</v>
@@ -840,7 +840,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H13" t="str">
         <v>images/daiwa_rods/スカイハイ ボートゲームSKYHIGH BOATGAME_SKYHIGH_BOATGAME_68MB.jpg</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H14" t="str">
         <v>images/daiwa_rods/ハートランド AGS（ベイトキャスティングモデル）HEARTLAND AGS（BAITCASTING MODELS）_HL741MHRB-SVAGS17.jpg</v>
@@ -910,7 +910,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H15" t="str">
         <v>images/daiwa_rods/ハートランド AGS（スピニングモデル）HEARTLAND AGS（SPINNING MODELS）_6102LFS-AGS13.jpg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H16" t="str">
         <v>images/daiwa_rods/スティーズ（ベイトキャスティングモデル）STEEZ（BAITCASTING MODEL）_STEEZ_C64L-SV_ST_BF_4550133551437.jpg</v>
@@ -980,7 +980,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H17" t="str">
         <v>images/daiwa_rods/スティーズ （スピニングモデル）STEEZ（SPINNING MODEL）_STEEZ_S60XUL-SV_ST_4550133551550.jpg</v>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H18" t="str">
         <v>images/daiwa_rods/スティーズ ショアコンペティション（ベイトキャスティングモデル）STEEZ SHORE COMPETITION（BAITCASTING MODEL）_STEEZSCC64MLLM4550133551451.jpg</v>
@@ -1050,7 +1050,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H19" t="str">
         <v>images/daiwa_rods/スティーズ リアルコントロールSTEEZ REAL CONTROL_SteezRC_S510XUL-SV_ST.jpg</v>
@@ -1085,7 +1085,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H20" t="str">
         <v>images/daiwa_rods/ハートランド（スピニングモデル）HEARTLAND（SPINNING MODELS）_HL_6102MLFS-19.jpg</v>
@@ -1120,7 +1120,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H21" t="str">
         <v>images/daiwa_rods/ハートランド（ベイトキャスティングモデル）HEARTLAND（BAITCASTING MODELS）_HEARTLAND_7112MRB-25_4550133434167.jpg</v>
@@ -1155,7 +1155,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H22" t="str">
         <v>images/daiwa_rods/ブラックレーベル トラベルBLACK LABEL TRAVEL_BlackLabelTravel_NC63MH-5-F.jpg</v>
@@ -1190,7 +1190,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v>images/daiwa_rods/スティーズ ショアコンペティション（スピニングモデル）STEEZ SHORE COMPETITION（SPINNING MODEL）_STEEZ_SC_S69UL_4550133551604.jpg</v>
@@ -1225,7 +1225,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H24" t="str">
         <v>images/daiwa_rods/SWAGGERSWAGGER_SWAGGER_C66M-5_4550133500237.jpg</v>
@@ -1260,7 +1260,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H25" t="str">
         <v>images/daiwa_rods/ブラックレーベルBLACK LABEL_BLX_C63MH-FR_4550133444241.jpg</v>
@@ -1295,7 +1295,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H26" t="str">
         <v>images/daiwa_rods/タトゥーラ エリートTATULA ELITE_TATULA_ELITE_691MLRB_05807342.jpg</v>
@@ -1330,7 +1330,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H27" t="str">
         <v>images/daiwa_rods/タトゥーラTATULA_TATULA_6101MRB_4550133341472.jpg</v>
@@ -1365,7 +1365,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H28" t="str">
         <v>images/daiwa_rods/タトゥーラ トラベルTATULA TRAVEL_TATULA_TRAVEL_664MLRB_4550133544897.jpg</v>
@@ -1400,7 +1400,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H29" t="str">
         <v>images/daiwa_rods/B.B.B（トリプルビー）B.B.B_BBB636TMLRB.jpg</v>
@@ -1435,7 +1435,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H30" t="str">
         <v>images/daiwa_rods/ブレイゾンBLAZON_Blazon_C64L-2-BF.jpg</v>
@@ -1470,7 +1470,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H31" t="str">
         <v>images/daiwa_rods/カムイランケタムKAMUY RANKE TAM_KamuyRankeTam_121XH.jpg</v>
@@ -1505,7 +1505,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H32" t="str">
         <v>images/daiwa_rods/モバイルパックMOBILE PACK_MobilePack_766TML.jpg</v>
@@ -1540,7 +1540,7 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H33" t="str">
         <v>images/daiwa_rods/ブレイゾン モバイルBLAZON MOBILE_BlazonMobile_6106TMHB.jpg</v>
@@ -1575,7 +1575,7 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H34" t="str">
         <v>images/daiwa_rods/シルバークリーク AK（アキアジ）SILVER CREEK AK（AKIAJI）_SILVERCREEK_AK_130H.jpg</v>
@@ -1610,7 +1610,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H35" t="str">
         <v>images/daiwa_rods/シルバークリーク グラスプログレッシブSILVER CREEK GLASS PROGRESSIVE_SilverCreek_GP_48UL-G.jpg</v>
@@ -1645,7 +1645,7 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H36" t="str">
         <v>images/daiwa_rods/タトゥーラ XTTATULA XT_TATULA_XT_6102MHRB_4550133169373.jpg</v>
@@ -1680,7 +1680,7 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H37" t="str">
         <v>images/daiwa_rods/プレッソ-LTD AGSPRESSO-LTD AGS_Presso-LTDAGS_55M-SMT.jpg</v>
@@ -1715,7 +1715,7 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H38" t="str">
         <v>images/daiwa_rods/シルバークリーク トラッドSilver Creek Trad_SILVER_CREEK_TRAD_48UL_4550133340833.jpg</v>
@@ -1750,7 +1750,7 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H39" t="str">
         <v>images/daiwa_rods/シルバークリーク AurumSILVER CREEK AURUM_Silver_Creek_Aurum_410L_4550133444968.jpg</v>
@@ -1785,7 +1785,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H40" t="str">
         <v>images/daiwa_rods/プレッソ AIR AGSPRESSO AIR AGS_PressoAirAGS_510UL.jpg</v>
@@ -1820,7 +1820,7 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H41" t="str">
         <v>images/daiwa_rods/シルバークリーク レイクジギングSILVER CREEK LAKE JIGGING_SILVER_CREEK_LAKE_JIGGING_63LB-T_4550133453359.jpg</v>
@@ -1855,7 +1855,7 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H42" t="str">
         <v>images/daiwa_rods/ピュアリストPURELIST_Purelist_53ULW.jpg</v>
@@ -1890,7 +1890,7 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H43" t="str">
         <v>images/daiwa_rods/プレッソ MXPRESSO MX_PRESSO_MX_60UL_4550133544835.jpg</v>
@@ -1925,7 +1925,7 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H44" t="str">
         <v>images/daiwa_rods/イプリミIPRIMI_Iprimi56XXUL-S.jpg</v>
@@ -1960,7 +1960,7 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H45" t="str">
         <v>images/daiwa_rods/トラウト X NTTROUT X NT_Trout_X_NT_53ULN.jpg</v>
@@ -1995,7 +1995,7 @@
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H46" t="str">
         <v>images/daiwa_rods/ロッホモア フライコンボLOCHMOR FLY COMBO_LochomorFlyCombo803.jpg</v>
@@ -2030,7 +2030,7 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H47" t="str">
         <v>images/daiwa_rods/ピュアリスト AKPURELIST AK_PurelistAK_126H-3.jpg</v>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H48" t="str">
         <v>images/daiwa_rods/ワイズストリームWISE STREAM_WiseStream_46TULQ.jpg</v>
@@ -2100,7 +2100,7 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H49" t="str">
         <v>images/daiwa_rods/トラウト X ATTROUT X AT_TroutX_AT60UL.jpg</v>
@@ -2135,7 +2135,7 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H50" t="str">
         <v>images/daiwa_rods/月下美人 MX アジングGEKKABIJIN MX AJING_GEKKABIJIN_MX_AJING_48L-S_4550133338359.jpg</v>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H51" t="str">
         <v>images/daiwa_rods/月下美人 AIRGEKKABIJIN AIR_GEKKABIJIN_AIR_63XULB-T_W_4550133338298.png</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H52" t="str">
         <v>images/daiwa_rods/月下美人 AIR AJINGBOATGEKKABIJIN AIR AJINGBOAT_GEKKABIJIN_AIR_AB_69L-SK_4550133338328.jpg</v>
@@ -2240,7 +2240,7 @@
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H53" t="str">
         <v>images/daiwa_rods/月下美人 EXGEKKABIJIN EX_Gekka_EX_68LTQ.jpg</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H54" t="str">
         <v>images/daiwa_rods/月下美人 MXGEKKABIJIN MX_GEKKABIJIN_MX_68L-T_4550133338397.jpg</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H55" t="str">
         <v>images/daiwa_rods/月下美人 MX モバイルGEKKABIJIN MX MOBILE_GekkaMXMB_72UL-5.jpg</v>
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H56" t="str">
         <v>images/daiwa_rods/アジメバル ＸAJIMEBARU X_AJI_MEBARU_X_510UL-S_4550133164699.png</v>
@@ -2380,7 +2380,7 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H57" t="str">
         <v>images/daiwa_rods/月下美人（メバルモデル）GEKKABIJIN MEBARUMODEL_Gekka_Mebaru_1.jpg</v>
@@ -2415,7 +2415,7 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H58" t="str">
         <v>images/daiwa_rods/月下美人 AJINGGEKKABIJIN AJING_GekkaAJing510UL-S_1.jpg</v>
@@ -2450,7 +2450,7 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H59" t="str">
         <v>images/daiwa_rods/月下美人 MX AJING BOATGEKKABIJIN MX AJING BOAT_Gekka_MxAjingBoat_64L-S.jpg</v>

--- a/GearSage-client/pkgGear/data_raw/daiwa_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_rod_import.xlsx
@@ -458,7 +458,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>images/daiwa_rods/モアザン ブランジーノ CGSmorethan BRANZINO CGS_morethan_BRANZINO_CGS_94ML_4550133545030.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%20%E3%83%96%E3%83%A9%E3%83%B3%E3%82%B8%E3%83%BC%E3%83%8E%20CGSmorethan%20BRANZINO%20CGS_morethan_BRANZINO_CGS_94ML_4550133545030.jpg</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -493,7 +493,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>images/daiwa_rods/モアザンMORETHAN_MORETHAN_93MLM_J_4550133452109.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3MORETHAN_MORETHAN_93MLM_J_4550133452109.jpg</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -528,7 +528,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>images/daiwa_rods/ラブラックス AGS BS（ボートシーバス）LABRAX AGS BS（BOAT SEABASS）_LabraxAGS_BS_64MSQ.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A9%E3%83%96%E3%83%A9%E3%83%83%E3%82%AF%E3%82%B9%20AGS%20BS%EF%BC%88%E3%83%9C%E3%83%BC%E3%83%88%E3%82%B7%E3%83%BC%E3%83%90%E3%82%B9%EF%BC%89LABRAX%20AGS%20BS%EF%BC%88BOAT%20SEABASS%EF%BC%89_LabraxAGS_BS_64MSQ.jpg</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -563,7 +563,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>images/daiwa_rods/モアザン ブランジーノ EX AGS ベイトモデルMORETHAN BRANZINO EX AGS_MORETHAN_BRANZINO_EX_AGS_80HB_4550133384608.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%20%E3%83%96%E3%83%A9%E3%83%B3%E3%82%B8%E3%83%BC%E3%83%8E%20EX%20AGS%20%E3%83%99%E3%82%A4%E3%83%88%E3%83%A2%E3%83%87%E3%83%ABMORETHAN%20BRANZINO%20EX%20AGS_MORETHAN_BRANZINO_EX_AGS_80HB_4550133384608.jpg</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -598,7 +598,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>images/daiwa_rods/ラブラックス AGSLABRAX AGS_LabRaxAGS_86ML_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A9%E3%83%96%E3%83%A9%E3%83%83%E3%82%AF%E3%82%B9%20AGSLABRAX%20AGS_LabRaxAGS_86ML_1.jpg</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -633,7 +633,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>images/daiwa_rods/モアザン ワイズメンMORETHAN WISEMEN_morethan-WISEMEN_AGS_130M-4.jpg</v>
+        <v/>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -668,7 +668,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>images/daiwa_rods/スカイハイSKYHIGH_SKYHIGH_90ML_4550133433894.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%82%AB%E3%82%A4%E3%83%8F%E3%82%A4SKYHIGH_SKYHIGH_90ML_4550133433894.jpg</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>images/daiwa_rods/モアザン ブランジーノ EX AGSMORETHAN BRANZINO EX AGS_Morethan_Brabzino_EX_AGS_87LML.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%20%E3%83%96%E3%83%A9%E3%83%B3%E3%82%B8%E3%83%BC%E3%83%8E%20EX%20AGSMORETHAN%20BRANZINO%20EX%20AGS_Morethan_Brabzino_EX_AGS_87LML.jpg</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -738,7 +738,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>images/daiwa_rods/シーバスフラットXSEABASS FLAT X_SeabassFlatX_86ML.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%BC%E3%83%90%E3%82%B9%E3%83%95%E3%83%A9%E3%83%83%E3%83%88XSEABASS%20FLAT%20X_SeabassFlatX_86ML.jpg</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>images/daiwa_rods/ラテオLATEO_LATEO_96MLMK_4550133384950.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A9%E3%83%86%E3%82%AALATEO_LATEO_96MLMK_4550133384950.jpg</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -808,7 +808,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>images/daiwa_rods/ラテオ BSLATEO BS_LATEO_BS_68MBW_4550133337994.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A9%E3%83%86%E3%82%AA%20BSLATEO%20BS_LATEO_BS_68MBW_4550133337994.png</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -843,7 +843,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>images/daiwa_rods/スカイハイ ボートゲームSKYHIGH BOATGAME_SKYHIGH_BOATGAME_68MB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%82%AB%E3%82%A4%E3%83%8F%E3%82%A4%20%E3%83%9C%E3%83%BC%E3%83%88%E3%82%B2%E3%83%BC%E3%83%A0SKYHIGH%20BOATGAME_SKYHIGH_BOATGAME_68MB.jpg</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -878,7 +878,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>images/daiwa_rods/ハートランド AGS（ベイトキャスティングモデル）HEARTLAND AGS（BAITCASTING MODELS）_HL741MHRB-SVAGS17.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%8F%E3%83%BC%E3%83%88%E3%83%A9%E3%83%B3%E3%83%89%20AGS%EF%BC%88%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89HEARTLAND%20AGS%EF%BC%88BAITCASTING%20MODELS%EF%BC%89_HL741MHRB-SVAGS17.jpg</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>images/daiwa_rods/ハートランド AGS（スピニングモデル）HEARTLAND AGS（SPINNING MODELS）_6102LFS-AGS13.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%8F%E3%83%BC%E3%83%88%E3%83%A9%E3%83%B3%E3%83%89%20AGS%EF%BC%88%E3%82%B9%E3%83%94%E3%83%8B%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89HEARTLAND%20AGS%EF%BC%88SPINNING%20MODELS%EF%BC%89_6102LFS-AGS13.jpg</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -948,7 +948,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>images/daiwa_rods/スティーズ（ベイトキャスティングモデル）STEEZ（BAITCASTING MODEL）_STEEZ_C64L-SV_ST_BF_4550133551437.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%EF%BC%88%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89STEEZ%EF%BC%88BAITCASTING%20MODEL%EF%BC%89_STEEZ_C64L-SV_ST_BF_4550133551437.jpg</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>images/daiwa_rods/スティーズ （スピニングモデル）STEEZ（SPINNING MODEL）_STEEZ_S60XUL-SV_ST_4550133551550.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%EF%BC%88%E3%82%B9%E3%83%94%E3%83%8B%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89STEEZ%EF%BC%88SPINNING%20MODEL%EF%BC%89_STEEZ_S60XUL-SV_ST_4550133551550.jpg</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1018,7 +1018,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>images/daiwa_rods/スティーズ ショアコンペティション（ベイトキャスティングモデル）STEEZ SHORE COMPETITION（BAITCASTING MODEL）_STEEZSCC64MLLM4550133551451.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B7%E3%83%A7%E3%82%A2%E3%82%B3%E3%83%B3%E3%83%9A%E3%83%86%E3%82%A3%E3%82%B7%E3%83%A7%E3%83%B3%EF%BC%88%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89STEEZ%20SHORE%20COMPETITION%EF%BC%88BAITCASTING%20MODEL%EF%BC%89_STEEZSCC64MLLM4550133551451.jpg</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>images/daiwa_rods/スティーズ リアルコントロールSTEEZ REAL CONTROL_SteezRC_S510XUL-SV_ST.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%AA%E3%82%A2%E3%83%AB%E3%82%B3%E3%83%B3%E3%83%88%E3%83%AD%E3%83%BC%E3%83%ABSTEEZ%20REAL%20CONTROL_SteezRC_S510XUL-SV_ST.jpg</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1088,7 +1088,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>images/daiwa_rods/ハートランド（スピニングモデル）HEARTLAND（SPINNING MODELS）_HL_6102MLFS-19.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%8F%E3%83%BC%E3%83%88%E3%83%A9%E3%83%B3%E3%83%89%EF%BC%88%E3%82%B9%E3%83%94%E3%83%8B%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89HEARTLAND%EF%BC%88SPINNING%20MODELS%EF%BC%89_HL_6102MLFS-19.jpg</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>images/daiwa_rods/ハートランド（ベイトキャスティングモデル）HEARTLAND（BAITCASTING MODELS）_HEARTLAND_7112MRB-25_4550133434167.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%8F%E3%83%BC%E3%83%88%E3%83%A9%E3%83%B3%E3%83%89%EF%BC%88%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89HEARTLAND%EF%BC%88BAITCASTING%20MODELS%EF%BC%89_HEARTLAND_7112MRB-25_4550133434167.jpg</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1158,7 +1158,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>images/daiwa_rods/ブラックレーベル トラベルBLACK LABEL TRAVEL_BlackLabelTravel_NC63MH-5-F.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%96%E3%83%A9%E3%83%83%E3%82%AF%E3%83%AC%E3%83%BC%E3%83%99%E3%83%AB%20%E3%83%88%E3%83%A9%E3%83%99%E3%83%ABBLACK%20LABEL%20TRAVEL_BlackLabelTravel_NC63MH-5-F.jpg</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1193,7 +1193,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>images/daiwa_rods/スティーズ ショアコンペティション（スピニングモデル）STEEZ SHORE COMPETITION（SPINNING MODEL）_STEEZ_SC_S69UL_4550133551604.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B7%E3%83%A7%E3%82%A2%E3%82%B3%E3%83%B3%E3%83%9A%E3%83%86%E3%82%A3%E3%82%B7%E3%83%A7%E3%83%B3%EF%BC%88%E3%82%B9%E3%83%94%E3%83%8B%E3%83%B3%E3%82%B0%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89STEEZ%20SHORE%20COMPETITION%EF%BC%88SPINNING%20MODEL%EF%BC%89_STEEZ_SC_S69UL_4550133551604.jpg</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1228,7 +1228,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>images/daiwa_rods/SWAGGERSWAGGER_SWAGGER_C66M-5_4550133500237.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/SWAGGERSWAGGER_SWAGGER_C66M-5_4550133500237.jpg</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>images/daiwa_rods/ブラックレーベルBLACK LABEL_BLX_C63MH-FR_4550133444241.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%96%E3%83%A9%E3%83%83%E3%82%AF%E3%83%AC%E3%83%BC%E3%83%99%E3%83%ABBLACK%20LABEL_BLX_C63MH-FR_4550133444241.jpg</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1298,7 +1298,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>images/daiwa_rods/タトゥーラ エリートTATULA ELITE_TATULA_ELITE_691MLRB_05807342.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20%E3%82%A8%E3%83%AA%E3%83%BC%E3%83%88TATULA%20ELITE_TATULA_ELITE_691MLRB_05807342.jpg</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>images/daiwa_rods/タトゥーラTATULA_TATULA_6101MRB_4550133341472.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9TATULA_TATULA_6101MRB_4550133341472.jpg</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1368,7 +1368,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>images/daiwa_rods/タトゥーラ トラベルTATULA TRAVEL_TATULA_TRAVEL_664MLRB_4550133544897.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20%E3%83%88%E3%83%A9%E3%83%99%E3%83%ABTATULA%20TRAVEL_TATULA_TRAVEL_664MLRB_4550133544897.jpg</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1403,7 +1403,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>images/daiwa_rods/B.B.B（トリプルビー）B.B.B_BBB636TMLRB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/B.B.B%EF%BC%88%E3%83%88%E3%83%AA%E3%83%97%E3%83%AB%E3%83%93%E3%83%BC%EF%BC%89B.B.B_BBB636TMLRB.jpg</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1438,7 +1438,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>images/daiwa_rods/ブレイゾンBLAZON_Blazon_C64L-2-BF.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%96%E3%83%AC%E3%82%A4%E3%82%BE%E3%83%B3BLAZON_Blazon_C64L-2-BF.jpg</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1473,7 +1473,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>images/daiwa_rods/カムイランケタムKAMUY RANKE TAM_KamuyRankeTam_121XH.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%AB%E3%83%A0%E3%82%A4%E3%83%A9%E3%83%B3%E3%82%B1%E3%82%BF%E3%83%A0KAMUY%20RANKE%20TAM_KamuyRankeTam_121XH.jpg</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1508,7 +1508,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>images/daiwa_rods/モバイルパックMOBILE PACK_MobilePack_766TML.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%A2%E3%83%90%E3%82%A4%E3%83%AB%E3%83%91%E3%83%83%E3%82%AFMOBILE%20PACK_MobilePack_766TML.jpg</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>images/daiwa_rods/ブレイゾン モバイルBLAZON MOBILE_BlazonMobile_6106TMHB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%96%E3%83%AC%E3%82%A4%E3%82%BE%E3%83%B3%20%E3%83%A2%E3%83%90%E3%82%A4%E3%83%ABBLAZON%20MOBILE_BlazonMobile_6106TMHB.jpg</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1578,7 +1578,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>images/daiwa_rods/シルバークリーク AK（アキアジ）SILVER CREEK AK（AKIAJI）_SILVERCREEK_AK_130H.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20AK%EF%BC%88%E3%82%A2%E3%82%AD%E3%82%A2%E3%82%B8%EF%BC%89SILVER%20CREEK%20AK%EF%BC%88AKIAJI%EF%BC%89_SILVERCREEK_AK_130H.jpg</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1613,7 +1613,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>images/daiwa_rods/シルバークリーク グラスプログレッシブSILVER CREEK GLASS PROGRESSIVE_SilverCreek_GP_48UL-G.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20%E3%82%B0%E3%83%A9%E3%82%B9%E3%83%97%E3%83%AD%E3%82%B0%E3%83%AC%E3%83%83%E3%82%B7%E3%83%96SILVER%20CREEK%20GLASS%20PROGRESSIVE_SilverCreek_GP_48UL-G.jpg</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1648,7 +1648,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>images/daiwa_rods/タトゥーラ XTTATULA XT_TATULA_XT_6102MHRB_4550133169373.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20XTTATULA%20XT_TATULA_XT_6102MHRB_4550133169373.jpg</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1683,7 +1683,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>images/daiwa_rods/プレッソ-LTD AGSPRESSO-LTD AGS_Presso-LTDAGS_55M-SMT.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD-LTD%20AGSPRESSO-LTD%20AGS_Presso-LTDAGS_55M-SMT.jpg</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1718,7 +1718,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>images/daiwa_rods/シルバークリーク トラッドSilver Creek Trad_SILVER_CREEK_TRAD_48UL_4550133340833.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20%E3%83%88%E3%83%A9%E3%83%83%E3%83%89Silver%20Creek%20Trad_SILVER_CREEK_TRAD_48UL_4550133340833.jpg</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1753,7 +1753,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>images/daiwa_rods/シルバークリーク AurumSILVER CREEK AURUM_Silver_Creek_Aurum_410L_4550133444968.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20AurumSILVER%20CREEK%20AURUM_Silver_Creek_Aurum_410L_4550133444968.jpg</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1788,7 +1788,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>images/daiwa_rods/プレッソ AIR AGSPRESSO AIR AGS_PressoAirAGS_510UL.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20AIR%20AGSPRESSO%20AIR%20AGS_PressoAirAGS_510UL.jpg</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1823,7 +1823,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>images/daiwa_rods/シルバークリーク レイクジギングSILVER CREEK LAKE JIGGING_SILVER_CREEK_LAKE_JIGGING_63LB-T_4550133453359.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20%E3%83%AC%E3%82%A4%E3%82%AF%E3%82%B8%E3%82%AE%E3%83%B3%E3%82%B0SILVER%20CREEK%20LAKE%20JIGGING_SILVER_CREEK_LAKE_JIGGING_63LB-T_4550133453359.jpg</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1858,7 +1858,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>images/daiwa_rods/ピュアリストPURELIST_Purelist_53ULW.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%94%E3%83%A5%E3%82%A2%E3%83%AA%E3%82%B9%E3%83%88PURELIST_Purelist_53ULW.jpg</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1893,7 +1893,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>images/daiwa_rods/プレッソ MXPRESSO MX_PRESSO_MX_60UL_4550133544835.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20MXPRESSO%20MX_PRESSO_MX_60UL_4550133544835.jpg</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1928,7 +1928,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>images/daiwa_rods/イプリミIPRIMI_Iprimi56XXUL-S.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%A4%E3%83%97%E3%83%AA%E3%83%9FIPRIMI_Iprimi56XXUL-S.jpg</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1963,7 +1963,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>images/daiwa_rods/トラウト X NTTROUT X NT_Trout_X_NT_53ULN.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%88%E3%83%A9%E3%82%A6%E3%83%88%20X%20NTTROUT%20X%20NT_Trout_X_NT_53ULN.jpg</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1998,7 +1998,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>images/daiwa_rods/ロッホモア フライコンボLOCHMOR FLY COMBO_LochomorFlyCombo803.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%AD%E3%83%83%E3%83%9B%E3%83%A2%E3%82%A2%20%E3%83%95%E3%83%A9%E3%82%A4%E3%82%B3%E3%83%B3%E3%83%9CLOCHMOR%20FLY%20COMBO_LochomorFlyCombo803.jpg</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2033,7 +2033,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>images/daiwa_rods/ピュアリスト AKPURELIST AK_PurelistAK_126H-3.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%94%E3%83%A5%E3%82%A2%E3%83%AA%E3%82%B9%E3%83%88%20AKPURELIST%20AK_PurelistAK_126H-3.jpg</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2068,7 +2068,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>images/daiwa_rods/ワイズストリームWISE STREAM_WiseStream_46TULQ.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%AF%E3%82%A4%E3%82%BA%E3%82%B9%E3%83%88%E3%83%AA%E3%83%BC%E3%83%A0WISE%20STREAM_WiseStream_46TULQ.jpg</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>images/daiwa_rods/トラウト X ATTROUT X AT_TroutX_AT60UL.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%83%88%E3%83%A9%E3%82%A6%E3%83%88%20X%20ATTROUT%20X%20AT_TroutX_AT60UL.jpg</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2138,7 +2138,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>images/daiwa_rods/月下美人 MX アジングGEKKABIJIN MX AJING_GEKKABIJIN_MX_AJING_48L-S_4550133338359.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20MX%20%E3%82%A2%E3%82%B8%E3%83%B3%E3%82%B0GEKKABIJIN%20MX%20AJING_GEKKABIJIN_MX_AJING_48L-S_4550133338359.jpg</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2173,7 +2173,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>images/daiwa_rods/月下美人 AIRGEKKABIJIN AIR_GEKKABIJIN_AIR_63XULB-T_W_4550133338298.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20AIRGEKKABIJIN%20AIR_GEKKABIJIN_AIR_63XULB-T_W_4550133338298.png</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2208,7 +2208,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>images/daiwa_rods/月下美人 AIR AJINGBOATGEKKABIJIN AIR AJINGBOAT_GEKKABIJIN_AIR_AB_69L-SK_4550133338328.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20AIR%20AJINGBOATGEKKABIJIN%20AIR%20AJINGBOAT_GEKKABIJIN_AIR_AB_69L-SK_4550133338328.jpg</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>images/daiwa_rods/月下美人 EXGEKKABIJIN EX_Gekka_EX_68LTQ.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20EXGEKKABIJIN%20EX_Gekka_EX_68LTQ.jpg</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2278,7 +2278,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>images/daiwa_rods/月下美人 MXGEKKABIJIN MX_GEKKABIJIN_MX_68L-T_4550133338397.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20MXGEKKABIJIN%20MX_GEKKABIJIN_MX_68L-T_4550133338397.jpg</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>images/daiwa_rods/月下美人 MX モバイルGEKKABIJIN MX MOBILE_GekkaMXMB_72UL-5.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20MX%20%E3%83%A2%E3%83%90%E3%82%A4%E3%83%ABGEKKABIJIN%20MX%20MOBILE_GekkaMXMB_72UL-5.jpg</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2348,7 +2348,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>images/daiwa_rods/アジメバル ＸAJIMEBARU X_AJI_MEBARU_X_510UL-S_4550133164699.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E3%82%A2%E3%82%B8%E3%83%A1%E3%83%90%E3%83%AB%20%EF%BC%B8AJIMEBARU%20X_AJI_MEBARU_X_510UL-S_4550133164699.png</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>images/daiwa_rods/月下美人（メバルモデル）GEKKABIJIN MEBARUMODEL_Gekka_Mebaru_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%EF%BC%88%E3%83%A1%E3%83%90%E3%83%AB%E3%83%A2%E3%83%87%E3%83%AB%EF%BC%89GEKKABIJIN%20MEBARUMODEL_Gekka_Mebaru_1.jpg</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2418,7 +2418,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>images/daiwa_rods/月下美人 AJINGGEKKABIJIN AJING_GekkaAJing510UL-S_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20AJINGGEKKABIJIN%20AJING_GekkaAJing510UL-S_1.jpg</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>images/daiwa_rods/月下美人 MX AJING BOATGEKKABIJIN MX AJING BOAT_Gekka_MxAjingBoat_64L-S.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_rods/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20MX%20AJING%20BOATGEKKABIJIN%20MX%20AJING%20BOAT_Gekka_MxAjingBoat_64L-S.jpg</v>
       </c>
       <c r="I59" t="str">
         <v/>
